--- a/mapa_interactivo_NEW.xlsx
+++ b/mapa_interactivo_NEW.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R167"/>
+  <dimension ref="A1:R174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2317,22 +2317,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t xml:space="preserve">8306 </t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5/19/2025</t>
+          <t>5/26/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ALBARELLOS AV. 3180</t>
+          <t>Moldes 2720</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2347,17 +2347,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>806926466</t>
+          <t>806926767</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Columna (metal) inclinada</t>
+          <t xml:space="preserve">Poste - Pasan 5 lingas y la línea de cobre </t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2367,21 +2367,21 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L23" t="n">
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-58.513552</v>
+        <v>-58.464177</v>
       </c>
       <c r="N23" t="n">
-        <v>-34.579829</v>
+        <v>-34.558239</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>PUE-J</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2403,22 +2403,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">8306 </t>
+          <t>6171</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5/26/2025</t>
+          <t>6/18/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Moldes 2720</t>
+          <t>CABELLO 3486</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2433,12 +2433,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>806926767</t>
+          <t>807658640</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poste - Pasan 5 lingas y la línea de cobre </t>
+          <t>Columna inclinada evaluar con inspector un corrimiento</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2453,31 +2453,31 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L24" t="n">
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-58.464177</v>
+        <v>-58.409579</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.558239</v>
+        <v>-34.581134</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>AGU-O</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2489,22 +2489,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6229</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6/18/2025</t>
+          <t>6/24/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CABELLO 3486</t>
+          <t>ALVAREZ THOMAS AV. 309</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2519,17 +2519,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>807658640</t>
+          <t>807762987</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Columna inclinada evaluar con inspector un corrimiento</t>
+          <t xml:space="preserve">Reparar rienda </t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Tensor</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2539,17 +2539,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L25" t="n">
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>-58.409579</v>
+        <v>-58.44848</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.581134</v>
+        <v>-34.581338</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>AGU-O</t>
+          <t>ATH-P</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2575,7 +2575,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6229</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ALVAREZ THOMAS AV. 309</t>
+          <t>Ciudad de la Paz 275</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>807762987</t>
+          <t>807763070</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reparar rienda </t>
+          <t>Aplomar o cambiar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Tensor</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2632,10 +2632,10 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-58.44848</v>
+        <v>-58.441049</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.581338</v>
+        <v>-34.574625</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>ATH-P</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2661,17 +2661,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6/24/2025</t>
+          <t>6/30/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ciudad de la Paz 275</t>
+          <t>SOLER 6017</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2691,12 +2691,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>807763070</t>
+          <t>807851636</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Aplomar o cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L27" t="n">
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-58.441049</v>
+        <v>-58.436808</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.574625</v>
+        <v>-34.577464</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2747,22 +2747,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6295</t>
+          <t>6506</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6/30/2025</t>
+          <t>7/10/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SOLER 6017</t>
+          <t>Ohiggins 1611</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>807851636</t>
+          <t>808148679</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna podrida en la base</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2804,24 +2804,24 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.436808</v>
+        <v>-58.448993</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.577464</v>
+        <v>-34.564383</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2833,22 +2833,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7/10/2025</t>
+          <t>7/17/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ohiggins 1611</t>
+          <t>MILLER 4590</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>808148679</t>
+          <t>808400306</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Columna podrida en la base</t>
+          <t>Columna corroida</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2890,14 +2890,14 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>-58.448993</v>
+        <v>-58.495482</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.564383</v>
+        <v>-34.552614</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2919,7 +2919,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MILLER 4590</t>
+          <t>Pedraza Manuela 4101</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>808400306</t>
+          <t>808400353</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Columna corroida</t>
+          <t xml:space="preserve">Podrida en la base </t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2976,10 +2976,10 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>-58.495482</v>
+        <v>-58.481569</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.552614</v>
+        <v>-34.559853</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>COG-N</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3005,22 +3005,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6538</t>
+          <t>-531</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7/17/2025</t>
+          <t>7/25/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pedraza Manuela 4101</t>
+          <t>Joaquin V Gonzalez 4632</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>808400353</t>
+          <t>808530239</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Podrida en la base </t>
+          <t>Cambiar por prfv y usar esa 114 en Libertad 820</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3062,14 +3062,14 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.481569</v>
+        <v>-58.513643</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.559853</v>
+        <v>-34.594169</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3079,34 +3079,34 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>COG-N</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1PUE</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>-531</t>
+          <t>6512</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7/25/2025</t>
+          <t>7/28/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Joaquin V Gonzalez 4632</t>
+          <t>GASCON 1195</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>808530239</t>
+          <t>808571975</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Cambiar por prfv y usar esa 114 en Libertad 820</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3148,51 +3148,51 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.513643</v>
+        <v>-58.423127</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.594169</v>
+        <v>-34.596476</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1PUE</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6512</t>
+          <t>-538</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7/28/2025</t>
+          <t>7/31/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GASCON 1195</t>
+          <t>Malabia 964</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>808571975</t>
+          <t>808609237</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar poste mal estado por PRFV</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3227,17 +3227,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L33" t="n">
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.423127</v>
+        <v>-58.433634</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.596476</v>
+        <v>-34.595018</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>VCR-I</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3263,22 +3263,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>-538</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7/31/2025</t>
+          <t>8/12/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Malabia 964</t>
+          <t>RIVAS, GRAL. 2345</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>808609237</t>
+          <t>808918698</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Cambiar poste mal estado por PRFV</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3313,31 +3313,31 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L34" t="n">
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.433634</v>
+        <v>-58.482497</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.595018</v>
+        <v>-34.598714</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>VCR-I</t>
+          <t>PUE-A</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3349,7 +3349,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>6917</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>RIVAS, GRAL. 2345</t>
+          <t>BRIN, MINISTRO 1375</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>808918698</t>
+          <t>808918700</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>PIcada</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3406,24 +3406,24 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.482497</v>
+        <v>-58.355342</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.598714</v>
+        <v>-34.63565</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>PUE-A</t>
+          <t>CON-G</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3435,7 +3435,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>-550</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BRIN, MINISTRO 1375</t>
+          <t>Fitz roy 267</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>808918700</t>
+          <t>808918720</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>PIcada</t>
+          <t>Aplomar columna</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3492,24 +3492,24 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.355342</v>
+        <v>-58.451378</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.63565</v>
+        <v>-34.596195</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>CON-G</t>
+          <t>VCR-?</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3521,22 +3521,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>-550</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>8/12/2025</t>
+          <t>8/14/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fitz roy 267</t>
+          <t>SUPERI 1459</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3551,17 +3551,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>808918720</t>
+          <t>808972965</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Aplomar columna</t>
+          <t>Poste con base quebrada ver si es posible desmonte</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3571,21 +3571,21 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L37" t="n">
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.451378</v>
+        <v>-58.460834</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.596195</v>
+        <v>-34.573753</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>VCR-?</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3607,17 +3607,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>-559</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>8/14/2025</t>
+          <t>8/21/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SUPERI 1459</t>
+          <t>Av. Del Libertador 6736</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3637,17 +3637,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>808972965</t>
+          <t>809098713</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Poste con base quebrada ver si es posible desmonte</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3657,21 +3657,21 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L38" t="n">
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.460834</v>
+        <v>-58.453398</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.573753</v>
+        <v>-34.550238</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>BLO-E</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3693,22 +3693,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>-559</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>8/21/2025</t>
+          <t>8/25/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Av. Del Libertador 6736</t>
+          <t>VERA 445</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>809098713</t>
+          <t>809155622</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Correrla para sacarla del cantero</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3750,24 +3750,24 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.453398</v>
+        <v>-58.437181</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.550238</v>
+        <v>-34.5995</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>BLO-E</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3779,22 +3779,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>8/25/2025</t>
+          <t>9/1/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VERA 445</t>
+          <t>VILELA 3699</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3809,12 +3809,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>809155622</t>
+          <t>809371823</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Correrla para sacarla del cantero</t>
+          <t xml:space="preserve">Cambiar </t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3829,31 +3829,31 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L40" t="n">
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.437181</v>
+        <v>-58.482817</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.5995</v>
+        <v>-34.550845</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3865,17 +3865,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7111</t>
+          <t>-587</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>9/1/2025</t>
+          <t>9/8/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>VILELA 3699</t>
+          <t>ARIAS 4048</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>809371823</t>
+          <t>809526164</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cambiar </t>
+          <t>Cambiar 114 picada</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3915,17 +3915,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L41" t="n">
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.482817</v>
+        <v>-58.488936</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.550845</v>
+        <v>-34.549005</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3951,27 +3951,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>-587</t>
+          <t>7229</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>9/8/2025</t>
+          <t>9/16/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ARIAS 4048</t>
+          <t>AZURDUY JUANA 2627</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>809526164</t>
+          <t>ICD30814490</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Cambiar 114 picada</t>
+          <t>Colocar columna para pedir traspaso de nodo propio</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4008,10 +4008,10 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.488936</v>
+        <v>-58.469008</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.549005</v>
+        <v>-34.552083</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4037,27 +4037,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7229</t>
+          <t>S01186963</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AZURDUY JUANA 2627</t>
+          <t>WASHINGTON 4274</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ICD30814490</t>
+          <t>809800217</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Colocar columna para pedir traspaso de nodo propio</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4094,10 +4094,10 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.469008</v>
+        <v>-58.484797</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.552083</v>
+        <v>-34.550364</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4123,17 +4123,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S01186963</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>9/22/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>WASHINGTON 4274</t>
+          <t>RUIZ HUIDOBRO 3620</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4153,17 +4153,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>809800217</t>
+          <t>ICD30934235</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Trapaso de redes y desmonte</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4180,10 +4180,10 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.484797</v>
+        <v>-58.484082</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.550364</v>
+        <v>-34.549702</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>RUIZ HUIDOBRO 3620</t>
+          <t>VERA 1021</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4239,22 +4239,22 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>ICD30934235</t>
+          <t>809910087</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Trapaso de redes y desmonte</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4266,24 +4266,24 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.484082</v>
+        <v>-58.442045</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.549702</v>
+        <v>-34.594303</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4295,22 +4295,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>9/22/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>VERA 1021</t>
+          <t>TRES ARROYOS 2911</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>809910087</t>
+          <t>810056868</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4352,24 +4352,24 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.442045</v>
+        <v>-58.476877</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.594303</v>
+        <v>-34.617525</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>NRA-M</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4381,22 +4381,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>9/29/2025</t>
+          <t>10/2/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TRES ARROYOS 2911</t>
+          <t>MOLDES 2688</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>810056868</t>
+          <t>810132881</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar o desmontar poste ver con inspector</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4438,14 +4438,14 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.476877</v>
+        <v>-58.463815</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.617525</v>
+        <v>-34.558663</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>NRA-M</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4467,22 +4467,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10/2/2025</t>
+          <t>10/6/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MOLDES 2688</t>
+          <t>MERCEDES 3774</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>810132881</t>
+          <t>810244452</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Cambiar o desmontar poste ver con inspector</t>
+          <t>Poste inclinado</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4517,21 +4517,21 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L48" t="n">
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.463815</v>
+        <v>-58.511139</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.558663</v>
+        <v>-34.602167</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4541,34 +4541,34 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>PUE-P</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1PUE</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10/6/2025</t>
+          <t>10/8/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MERCEDES 3774</t>
+          <t>ESTADO PLURINACIONAL DE BOLIVIA 3965</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4583,17 +4583,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>810244452</t>
+          <t>810259142</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Poste inclinado</t>
+          <t>Aplomar poste</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4610,10 +4610,10 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.511139</v>
+        <v>-58.493945</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.602167</v>
+        <v>-34.589471</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -4627,34 +4627,34 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>PUE-P</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1PUE</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10/8/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ESTADO PLURINACIONAL DE BOLIVIA 3965</t>
+          <t>BULGARIA 4387</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4669,17 +4669,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>810259142</t>
+          <t>810333040</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Aplomar poste</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4696,10 +4696,10 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.493945</v>
+        <v>-58.503223</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.589471</v>
+        <v>-34.590763</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -4713,34 +4713,34 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>PUE-N</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PUE</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BULGARIA 4387</t>
+          <t>MAGARIÑOS CERVANTES, A. 1382</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>810333040</t>
+          <t>810421913</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>cambiar esta doblada</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4775,17 +4775,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L51" t="n">
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.503223</v>
+        <v>-58.461</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.590763</v>
+        <v>-34.604483</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -4799,19 +4799,19 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>PUE-N</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PUE</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7582</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4821,12 +4821,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MAGARIÑOS CERVANTES, A. 1382</t>
+          <t>CIUDAD DE LA PAZ 3008</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>810421913</t>
+          <t>810421914</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>cambiar esta doblada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4868,14 +4868,14 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.461</v>
+        <v>-58.464818</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.604483</v>
+        <v>-34.554931</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4897,22 +4897,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/29/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 3008</t>
+          <t>QUITO 4180</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>810421914</t>
+          <t>810471618</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4954,24 +4954,24 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.464818</v>
+        <v>-58.425596</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.554931</v>
+        <v>-34.617038</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -7479,7 +7479,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S00016541</t>
+          <t xml:space="preserve">7969 </t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Aguirre 660</t>
+          <t xml:space="preserve">HELGUERA 4770 </t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>811238749</t>
+          <t>811238727</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -7536,46 +7536,46 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.436893</v>
+        <v>-58.505298</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.596419</v>
+        <v>-34.587467</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>PUE-N</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PUE</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">7969 </t>
+          <t>8098</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">HELGUERA 4770 </t>
+          <t>RIVERA, PEDRO I., DR. 4448</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>811238727</t>
+          <t>811299428</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7622,14 +7622,14 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.505298</v>
+        <v>-58.481135</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.587467</v>
+        <v>-34.568427</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -7639,19 +7639,19 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>PUE-N</t>
+          <t>PUE-E</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PUE</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>RIVERA, PEDRO I., DR. 4448</t>
+          <t>ALBARELLOS AV. 3031</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>811299428</t>
+          <t>811299423</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7708,14 +7708,14 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.481135</v>
+        <v>-58.511732</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.568427</v>
+        <v>-34.578688</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>PUE-E</t>
+          <t>PUE-J</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -7737,7 +7737,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t xml:space="preserve">7215 </t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ALBARELLOS AV. 3031</t>
+          <t xml:space="preserve">MAURE 3996 </t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>811299423</t>
+          <t>811299417</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7794,14 +7794,14 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.511732</v>
+        <v>-58.451687</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.578688</v>
+        <v>-34.586223</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>PUE-J</t>
+          <t>ATH-L</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7823,22 +7823,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">7215 </t>
+          <t>7987</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAURE 3996 </t>
+          <t>Terrada 2309</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7853,7 +7853,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>811299417</t>
+          <t>811299433</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7873,21 +7873,21 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L87" t="n">
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.451687</v>
+        <v>-58.482084</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.586223</v>
+        <v>-34.608289</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>ATH-L</t>
+          <t>NRA-P</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7909,22 +7909,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>S01139199</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Terrada 2309</t>
+          <t>CRAMER 4320</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>811299433</t>
+          <t>811299481</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7959,21 +7959,21 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L88" t="n">
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.482084</v>
+        <v>-58.476445</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.608289</v>
+        <v>-34.544981</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>NRA-P</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7995,17 +7995,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S01139199</t>
+          <t xml:space="preserve">8090 </t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>1/5/2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CRAMER 4320</t>
+          <t>Vedia 3506</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -8025,17 +8025,17 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>811299481</t>
+          <t xml:space="preserve">02125435 </t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>desmonte y traspasar red</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -8052,10 +8052,10 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.476445</v>
+        <v>-58.486704</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.544981</v>
+        <v>-34.544613</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8081,22 +8081,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">8090 </t>
+          <t>-717</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1/5/2026</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Vedia 3506</t>
+          <t>Ibera 2218</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8111,17 +8111,17 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">02125435 </t>
+          <t>811453864</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>desmonte y traspasar red</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -8138,10 +8138,10 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.486704</v>
+        <v>-58.46286</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.544613</v>
+        <v>-34.552702</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>BLO-R</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8167,7 +8167,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>-717</t>
+          <t xml:space="preserve">8173 </t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ibera 2218</t>
+          <t>SUCRE, ANTONIO JOSE DE, MCAL. 1563</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>811453864</t>
+          <t xml:space="preserve">02313712 </t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8224,10 +8224,10 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.46286</v>
+        <v>-58.446858</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.552702</v>
+        <v>-34.559026</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>BLO-R</t>
+          <t>BLO-A</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8253,7 +8253,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">8173 </t>
+          <t>-719</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SUCRE, ANTONIO JOSE DE, MCAL. 1563</t>
+          <t>MENDOZA 2160</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">02313712 </t>
+          <t>811453860</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -8310,10 +8310,10 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.446858</v>
+        <v>-58.455182</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.559026</v>
+        <v>-34.559761</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>BLO-A</t>
+          <t>BLO-O</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8339,22 +8339,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>-719</t>
+          <t>S01180016</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MENDOZA 2160</t>
+          <t>FITZ ROY 1730</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>811453860</t>
+          <t>811454223</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8396,24 +8396,24 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.455182</v>
+        <v>-58.436051</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.559761</v>
+        <v>-34.583855</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>BLO-O</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8425,7 +8425,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S01180016</t>
+          <t>S01180023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FITZ ROY 1730</t>
+          <t>VEGA, NICETO, CNEL. AV. 5420</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>811454223</t>
+          <t>811454198</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -8482,10 +8482,10 @@
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.436051</v>
+        <v>-58.437628</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.583855</v>
+        <v>-34.587953</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>ATH-?</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8511,7 +8511,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S01180023</t>
+          <t>S01180086</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>VEGA, NICETO, CNEL. AV. 5420</t>
+          <t>BONPLAND 1471</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>811454198</t>
+          <t>811454194</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -8568,10 +8568,10 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.437628</v>
+        <v>-58.439513</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.587953</v>
+        <v>-34.585314</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>ATH-?</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8597,7 +8597,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S01180086</t>
+          <t>S01200482</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BONPLAND 1471</t>
+          <t>GONZALEZ, ELPIDIO 2749</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>811454194</t>
+          <t>811454117</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>quebrada</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -8647,31 +8647,31 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L96" t="n">
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.439513</v>
+        <v>-58.481266</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.585314</v>
+        <v>-34.608522</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>NRA-O</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8683,7 +8683,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S01199169</t>
+          <t>S01204059</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BELAUSTEGUI, LUIS, DR. 3306</t>
+          <t>BUFANO, ALFREDO R. 2580</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>811454123</t>
+          <t>811454109</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -8740,14 +8740,14 @@
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.482601</v>
+        <v>-58.478411</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.619205</v>
+        <v>-34.6039</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>DEV-K</t>
+          <t>NRA-P</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8769,7 +8769,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S01200482</t>
+          <t>S01220047</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GONZALEZ, ELPIDIO 2749</t>
+          <t>MAURE 2958</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>811454117</t>
+          <t>811454097</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>quebrada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -8819,31 +8819,31 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L98" t="n">
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.481266</v>
+        <v>-58.446339</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.608522</v>
+        <v>-34.576306</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>NRA-O</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8855,7 +8855,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S01204059</t>
+          <t>S01306211</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8865,12 +8865,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BUFANO, ALFREDO R. 2580</t>
+          <t>WASHINGTON 3943</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>811454109</t>
+          <t>811453965</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -8905,21 +8905,21 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L99" t="n">
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.478411</v>
+        <v>-58.48286</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.6039</v>
+        <v>-34.55278</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>NRA-P</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8941,7 +8941,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S01220047</t>
+          <t>S01313361</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MAURE 2958</t>
+          <t>CABILDO AV. 805</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>811454097</t>
+          <t>811453963</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -8991,31 +8991,31 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L100" t="n">
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.446339</v>
+        <v>-58.444955</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.576306</v>
+        <v>-34.569791</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>COG-C</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9027,7 +9027,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S01306211</t>
+          <t>S01343333</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>WASHINGTON 3943</t>
+          <t xml:space="preserve">GONZALEZ, JOAQUIN V. 3542 </t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>811453965</t>
+          <t>811453949</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -9084,14 +9084,14 @@
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.48286</v>
+        <v>-58.506708</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.55278</v>
+        <v>-34.601841</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9113,7 +9113,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S01313361</t>
+          <t>S01389798</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CABILDO AV. 805</t>
+          <t>GUALEGUAYCHU 4682</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>811453963</t>
+          <t>811453943</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9163,21 +9163,21 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L102" t="n">
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.444955</v>
+        <v>-58.518214</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.569791</v>
+        <v>-34.596516</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -9187,19 +9187,19 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>COG-C</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1PUE</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S01343333</t>
+          <t>S01384321</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9209,12 +9209,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ, JOAQUIN V. 3542 </t>
+          <t>AZURDUY JUANA 2685</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>811453949</t>
+          <t>811453930</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9249,21 +9249,21 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L103" t="n">
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.506708</v>
+        <v>-58.469341</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.601841</v>
+        <v>-34.552269</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9285,7 +9285,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S01389798</t>
+          <t>S01384337</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU 4682</t>
+          <t xml:space="preserve">MOLDES 3502 </t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>811453943</t>
+          <t>811453925</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>base quebrada</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -9335,21 +9335,21 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L104" t="n">
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.518214</v>
+        <v>-58.470282</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.596516</v>
+        <v>-34.551553</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -9359,19 +9359,19 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>COG-M</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1PUE</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S01378200</t>
+          <t>S01392303</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ESTADO PLURINACIONAL DE BOLIVIA 440</t>
+          <t>Moldes 1999</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9401,12 +9401,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>811453938</t>
+          <t>811453918</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -9428,24 +9428,24 @@
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.467248</v>
+        <v>-58.458535</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.625736</v>
+        <v>-34.564674</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>COG-G</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9457,22 +9457,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S01384321</t>
+          <t>8095</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AZURDUY JUANA 2685</t>
+          <t>MANZANARES 3853</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>811453930</t>
+          <t>811454324</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -9514,10 +9514,10 @@
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.469341</v>
+        <v>-58.482488</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.552269</v>
+        <v>-34.554114</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9543,22 +9543,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S01384337</t>
+          <t>8094</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOLDES 3502 </t>
+          <t xml:space="preserve">GARCIA DEL RIO 3789 </t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>811453925</t>
+          <t>811454305</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>base quebrada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -9600,10 +9600,10 @@
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.470282</v>
+        <v>-58.482473</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.551553</v>
+        <v>-34.553018</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>COG-M</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9629,22 +9629,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S01392303</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Moldes 1999</t>
+          <t>Nogoya 3644</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9659,12 +9659,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>811453918</t>
+          <t>811454515</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -9686,14 +9686,14 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.458535</v>
+        <v>-58.497751</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.564674</v>
+        <v>-34.606408</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>COG-G</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9715,22 +9715,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MANZANARES 3853</t>
+          <t>Pje. Manuel Sola 4440</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>811454324</t>
+          <t>811454508</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -9772,14 +9772,14 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.482488</v>
+        <v>-58.507954</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.554114</v>
+        <v>-34.610808</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>DEV-D</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -9801,22 +9801,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t xml:space="preserve">8112 </t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA DEL RIO 3789 </t>
+          <t>MANZANARES 2073</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9831,12 +9831,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>811454305</t>
+          <t>811454483</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -9851,17 +9851,17 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L110" t="n">
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.482473</v>
+        <v>-58.465953</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.553018</v>
+        <v>-34.545637</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9887,7 +9887,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>8186</t>
+          <t xml:space="preserve">8114 </t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9897,12 +9897,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Nogoya 3644</t>
+          <t>ARGERICH 5774</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>811454515</t>
+          <t>811454454</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -9937,21 +9937,21 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L111" t="n">
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.497751</v>
+        <v>-58.511147</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.606408</v>
+        <v>-34.578665</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>PUE-J</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9973,22 +9973,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>8316</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/15/2026</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Pje. Manuel Sola 4440</t>
+          <t>ESTOMBA 212</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10003,12 +10003,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>811454508</t>
+          <t>811454532</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10023,21 +10023,21 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L112" t="n">
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.507954</v>
+        <v>-58.469045</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.610808</v>
+        <v>-34.588525</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>DEV-D</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10059,22 +10059,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">8112 </t>
+          <t>-731</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MANZANARES 2073</t>
+          <t>Ruiz Huidobro 3643</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10089,14 +10089,10 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>811454483</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
+          <t>811498060</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -10109,17 +10105,17 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.465953</v>
+        <v>-58.484505</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.545637</v>
+        <v>-34.549798</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -10133,7 +10129,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10145,22 +10141,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">8114 </t>
+          <t>-732</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ARGERICH 5774</t>
+          <t xml:space="preserve"> Valentin Alsina 1685</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10173,14 +10169,10 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>811454454</t>
-        </is>
-      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -10195,31 +10187,27 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L114" t="n">
         <v>1</v>
       </c>
-      <c r="M114" t="n">
-        <v>-58.511147</v>
-      </c>
-      <c r="N114" t="n">
-        <v>-34.578665</v>
-      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>No ubicado</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>No clasificado, consultar con mantenimiento</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>PUE-J</t>
+          <t>No ubicado</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10231,22 +10219,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>-733</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1/15/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ESTOMBA 212</t>
+          <t xml:space="preserve"> Dorrego 2755</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -10261,12 +10249,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>811454532</t>
+          <t>811498056</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -10281,31 +10269,31 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L115" t="n">
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.469045</v>
+        <v>-58.432319</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.588525</v>
+        <v>-34.574385</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10317,7 +10305,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>-731</t>
+          <t xml:space="preserve">6428 </t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10327,7 +10315,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ruiz Huidobro 3643</t>
+          <t>MONROE 4070</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -10347,10 +10335,14 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>811498060</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
+          <t>811498053</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>corroida</t>
+        </is>
+      </c>
       <c r="I116" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -10363,21 +10355,21 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L116" t="n">
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.484505</v>
+        <v>-58.475842</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.549798</v>
+        <v>-34.568215</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -10387,7 +10379,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>ATH-J</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10399,7 +10391,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>-732</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10409,12 +10401,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Valentin Alsina 1685</t>
+          <t>AZURDUY JUANA 3630</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10427,7 +10419,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>811498050</t>
+        </is>
+      </c>
       <c r="H117" t="inlineStr">
         <is>
           <t>inclinada</t>
@@ -10451,21 +10447,25 @@
       <c r="L117" t="n">
         <v>1</v>
       </c>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
+      <c r="M117" t="n">
+        <v>-58.477583</v>
+      </c>
+      <c r="N117" t="n">
+        <v>-34.5569</v>
+      </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>No ubicado</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>No clasificado, consultar con mantenimiento</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>No ubicado</t>
+          <t>COG-N</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10477,22 +10477,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>-733</t>
+          <t>S01215930</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/20/2026</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dorrego 2755</t>
+          <t>UGARTE, MANUEL 2750</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10507,7 +10507,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>811498056</t>
+          <t>811498072</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -10534,24 +10534,24 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.432319</v>
+        <v>-58.465042</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.574385</v>
+        <v>-34.557947</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10563,17 +10563,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">6428 </t>
+          <t>8181</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/22/2026</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MONROE 4070</t>
+          <t xml:space="preserve">FREIRE, RAMON, CAP. GRAL. 4748 </t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -10593,12 +10593,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>811498053</t>
+          <t>811498074</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada base quebrada</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -10613,21 +10613,21 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L119" t="n">
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.475842</v>
+        <v>-58.482951</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.568215</v>
+        <v>-34.544273</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>ATH-J</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10649,17 +10649,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>S01318042</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>AZURDUY JUANA 3630</t>
+          <t>UGARTE, MANUEL 3815</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>811498050</t>
+          <t>811626754</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -10706,10 +10706,10 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.477583</v>
+        <v>-58.476138</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.5569</v>
+        <v>-34.563825</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -10735,22 +10735,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S01215930</t>
+          <t>S01377458</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1/20/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>UGARTE, MANUEL 2750</t>
+          <t>ANDONAEGUI 2752</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -10765,12 +10765,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>811498072</t>
+          <t>811626748</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -10792,14 +10792,14 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.465042</v>
+        <v>-58.492149</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.557947</v>
+        <v>-34.573534</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>PUE-D</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10821,22 +10821,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>8181</t>
+          <t>S01397288</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1/22/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREIRE, RAMON, CAP. GRAL. 4748 </t>
+          <t xml:space="preserve">MOLDES 1918 </t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -10851,41 +10851,29 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>811498074</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>inclinada base quebrada</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>Poste</t>
-        </is>
-      </c>
+          <t>inclinadaq</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
       <c r="L122" t="n">
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.482951</v>
+        <v>-58.458035</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.544273</v>
+        <v>-34.565387</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -10895,7 +10883,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>COG-G</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10907,7 +10895,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S01318042</t>
+          <t>S01397364</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10917,12 +10905,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>UGARTE, MANUEL 3815</t>
+          <t>AVILES, VIRREY 3008</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -10937,12 +10925,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>811626754</t>
+          <t>811626732</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -10964,14 +10952,14 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.476138</v>
+        <v>-58.457207</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.563825</v>
+        <v>-34.571602</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -10981,7 +10969,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>COG-N</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10993,22 +10981,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S01377458</t>
+          <t>-740</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ANDONAEGUI 2752</t>
+          <t>Gutemberg 350</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11023,12 +11011,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>811626748</t>
+          <t>811626800</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -11043,17 +11031,17 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L124" t="n">
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.492149</v>
+        <v>-58.471803</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.573534</v>
+        <v>-34.592463</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -11067,7 +11055,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>PUE-D</t>
+          <t>PUE-?</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11079,22 +11067,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S01397288</t>
+          <t>-741</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOLDES 1918 </t>
+          <t>Gutemberg 320</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11109,29 +11097,41 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811626794</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>inclinadaq</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
+          <t>mal estado</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
       <c r="L125" t="n">
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.458035</v>
+        <v>-58.470581</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.565387</v>
+        <v>-34.592428</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>COG-G</t>
+          <t>PUE-?</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11153,17 +11153,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S01397364</t>
+          <t>-742</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AVILES, VIRREY 3008</t>
+          <t>BLANCO ENCALADA 899</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11183,17 +11183,17 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>811626732</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>desmonte</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -11203,21 +11203,21 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L126" t="n">
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.457207</v>
+        <v>-58.443393</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.571602</v>
+        <v>-34.549873</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>BLO-B</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11239,7 +11239,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>-740</t>
+          <t>-743</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Gutemberg 350</t>
+          <t>Giribone 1411</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -11269,12 +11269,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>811626800</t>
+          <t>811626791</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -11289,21 +11289,21 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L127" t="n">
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.471803</v>
+        <v>-58.462095</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.592463</v>
+        <v>-34.579585</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -11313,7 +11313,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>PUE-?</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11325,22 +11325,18 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>-741</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>1/27/2026</t>
-        </is>
-      </c>
+          <t>S01243988</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Gutemberg 320</t>
+          <t xml:space="preserve"> LAVOISIER 3556 </t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11355,12 +11351,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>811626794</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>mal estado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -11375,17 +11371,17 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L128" t="n">
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.470581</v>
+        <v>-58.502869</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.592428</v>
+        <v>-34.567437</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -11399,7 +11395,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>PUE-?</t>
+          <t>PUE-H</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11411,22 +11407,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>-742</t>
+          <t>S01396837</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BLANCO ENCALADA 899</t>
+          <t>DEHEZA 3622</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -11441,17 +11437,17 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811626963</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>desmonte</t>
+          <t>inclinado base quebrada</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -11468,10 +11464,10 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.443393</v>
+        <v>-58.485735</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.549873</v>
+        <v>-34.546249</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -11485,7 +11481,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>BLO-B</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11497,22 +11493,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>-743</t>
+          <t>S01406731</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Giribone 1411</t>
+          <t xml:space="preserve"> CORREA 1807</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -11527,12 +11523,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>811626791</t>
+          <t>811626953</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -11554,14 +11550,14 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.462095</v>
+        <v>-58.466595</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.579585</v>
+        <v>-34.54099</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -11571,7 +11567,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11583,18 +11579,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S01243988</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
+          <t>S01406737</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1/29/2026</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LAVOISIER 3556 </t>
+          <t>GRECIA 4281</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11609,12 +11609,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811626921</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inlinada</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -11636,14 +11636,14 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.502869</v>
+        <v>-58.466965</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.567437</v>
+        <v>-34.541488</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>PUE-H</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11665,22 +11665,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S01396837</t>
+          <t>S01406812</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>DEHEZA 3622</t>
+          <t xml:space="preserve">VUELTA DE OBLIGADO 3201 </t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11695,12 +11695,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>811626963</t>
+          <t>811626783</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>inclinado base quebrada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -11715,17 +11715,17 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L132" t="n">
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.485735</v>
+        <v>-58.464784</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.546249</v>
+        <v>-34.551419</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>BLO-R</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11751,7 +11751,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S01406731</t>
+          <t>S01451118</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CORREA 1807</t>
+          <t>ESCOBAR 2911</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>811626953</t>
+          <t>811626883</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -11808,14 +11808,14 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.466595</v>
+        <v>-58.509608</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.54099</v>
+        <v>-34.578546</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -11825,7 +11825,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>PUE-J</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11837,17 +11837,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S01406737</t>
+          <t>S00019326</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>GRECIA 4281</t>
+          <t>OLLEROS 3050</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11867,12 +11867,12 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>811626921</t>
+          <t>811627002</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>inlinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -11894,24 +11894,24 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.466965</v>
+        <v>-58.447708</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.541488</v>
+        <v>-34.577055</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>ATH-P</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11923,17 +11923,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S01406812</t>
+          <t>S00021988</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">VUELTA DE OBLIGADO 3201 </t>
+          <t>ALVAREZ THOMAS AV. 1115</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>811626783</t>
+          <t>811626996</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -11980,14 +11980,14 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.464784</v>
+        <v>-58.457565</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.551419</v>
+        <v>-34.578379</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -11997,7 +11997,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>BLO-R</t>
+          <t>ATH-O</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -12009,22 +12009,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S01451118</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ESCOBAR 2911</t>
+          <t xml:space="preserve">SANABRIA 2386 </t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12039,12 +12039,12 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>811626883</t>
+          <t>811626991</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -12059,21 +12059,21 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L136" t="n">
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.509608</v>
+        <v>-58.503452</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.578546</v>
+        <v>-34.614501</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>PUE-J</t>
+          <t>DEV-D</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12095,7 +12095,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S00019326</t>
+          <t>S01450787</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>OLLEROS 3050</t>
+          <t>HERNANDEZ, JOSE 2110</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -12125,12 +12125,12 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>811627002</t>
+          <t>811626983</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -12145,31 +12145,31 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.447708</v>
+        <v>-58.450727</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.577055</v>
+        <v>-34.56425</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>ATH-P</t>
+          <t>BLO-M</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12181,22 +12181,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S00021988</t>
+          <t>-745</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ALVAREZ THOMAS AV. 1115</t>
+          <t>Gamarra 1546</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12211,12 +12211,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>811626996</t>
+          <t>811627113</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -12238,14 +12238,14 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.457565</v>
+        <v>-58.477231</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.578379</v>
+        <v>-34.58242</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -12255,7 +12255,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>ATH-O</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12267,17 +12267,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>S00036520</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANABRIA 2386 </t>
+          <t>SEGUROLA AV. 856</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>811626991</t>
+          <t>811627070</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroidaq</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -12317,17 +12317,17 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L139" t="n">
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.503452</v>
+        <v>-58.490765</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.614501</v>
+        <v>-34.627337</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -12341,34 +12341,34 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>DEV-D</t>
+          <t>DEV-I</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-26011.PO.1DEV</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S01450787</t>
+          <t xml:space="preserve">900009468810 </t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>HERNANDEZ, JOSE 2110</t>
+          <t xml:space="preserve">CUENCA 3033 </t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12383,12 +12383,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>811626983</t>
+          <t>811627041</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -12403,21 +12403,21 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.450727</v>
+        <v>-58.494814</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.56425</v>
+        <v>-34.601905</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -12427,7 +12427,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>BLO-M</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12439,22 +12439,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>-745</t>
+          <t>S01337226</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/6/2026</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Gamarra 1546</t>
+          <t>MOLDES 3055</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>811627113</t>
+          <t>811627125</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -12496,14 +12496,14 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.477231</v>
+        <v>-58.466692</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.58242</v>
+        <v>-34.555283</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12525,22 +12525,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S00036520</t>
+          <t>S01375612</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/6/2026</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SEGUROLA AV. 856</t>
+          <t>LACROZE, FEDERICO AV. 2834</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12555,7 +12555,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>811627070</t>
+          <t>811627118</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -12582,51 +12582,51 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.490765</v>
+        <v>-58.447177</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.627337</v>
+        <v>-34.574158</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>DEV-I</t>
+          <t>ATH-P</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>ARATO-26011.PO.1DEV</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">900009468810 </t>
+          <t xml:space="preserve">8301 </t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUENCA 3033 </t>
+          <t>ARENGREEN 1584</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12641,12 +12641,12 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>811627041</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -12668,24 +12668,24 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.494814</v>
+        <v>-58.453265</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.601905</v>
+        <v>-34.615073</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>NRA-I</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12697,22 +12697,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S01337226</t>
+          <t>8312</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2/6/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>MOLDES 3055</t>
+          <t>AIZPURUA 3796</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -12727,12 +12727,12 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>811627125</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -12747,21 +12747,21 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L144" t="n">
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.466692</v>
+        <v>-58.505811</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.555283</v>
+        <v>-34.565014</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -12771,7 +12771,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>PUE-H</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12783,22 +12783,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S01375612</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2/6/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>LACROZE, FEDERICO AV. 2834</t>
+          <t>ARENAL, CONCEPCION 3814</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12813,12 +12813,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>811627118</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>corroidaq</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -12840,24 +12840,24 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.447177</v>
+        <v>-58.447805</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.574158</v>
+        <v>-34.587018</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>ATH-P</t>
+          <t>ATH-L</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12869,7 +12869,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">8301 </t>
+          <t>8323</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ARENGREEN 1584</t>
+          <t>WARNES AV. 2239</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -12919,31 +12919,31 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L146" t="n">
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.453265</v>
+        <v>-58.467815</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.615073</v>
+        <v>-34.596225</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>NRA-I</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12955,7 +12955,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12965,12 +12965,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>AIZPURUA 3796</t>
+          <t>PAZ SOLDAN 4991</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base quebrada</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -13005,17 +13005,17 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L147" t="n">
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.505811</v>
+        <v>-58.468466</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.565014</v>
+        <v>-34.594154</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>PUE-H</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -13041,7 +13041,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ARENAL, CONCEPCION 3814</t>
+          <t xml:space="preserve"> GUALEGUAYCHU 4754</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinado, base quebrada</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -13086,26 +13086,26 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L148" t="n">
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.447805</v>
+        <v>-58.518803</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.587018</v>
+        <v>-34.595866</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -13115,19 +13115,19 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>ATH-L</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1PUE</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13137,12 +13137,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>WARNES AV. 2239</t>
+          <t>BLANCO ENCALADA 823</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13162,7 +13162,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinado base quebrada</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -13177,21 +13177,21 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L149" t="n">
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.467815</v>
+        <v>-58.442692</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.596225</v>
+        <v>-34.549454</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -13201,7 +13201,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>BLO-B</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13213,22 +13213,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>PAZ SOLDAN 4991</t>
+          <t>DORREGO AV. 2699</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>base quebrada</t>
+          <t>base corrodia</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -13263,31 +13263,31 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L150" t="n">
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.468466</v>
+        <v>-58.432807</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.594154</v>
+        <v>-34.574343</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -13299,22 +13299,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GUALEGUAYCHU 4754</t>
+          <t>ASUNCION 2373</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13334,7 +13334,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>inclinado, base quebrada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -13349,17 +13349,17 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L151" t="n">
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>-58.518803</v>
+        <v>-58.490913</v>
       </c>
       <c r="N151" t="n">
-        <v>-34.595866</v>
+        <v>-34.588328</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -13373,34 +13373,34 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1PUE</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>BLANCO ENCALADA 823</t>
+          <t xml:space="preserve">ZAMUDIO 3884 </t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>inclinado base quebrada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -13435,21 +13435,21 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L152" t="n">
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.442692</v>
+        <v>-58.491114</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.549454</v>
+        <v>-34.588808</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>BLO-B</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -13471,22 +13471,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2/11/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>RODRIGUEZ PEÑA 110</t>
+          <t>BEIRO, FRANCISCO AV. 2435</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13506,10 +13506,14 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
       <c r="J153" t="inlineStr">
         <is>
           <t>Sin equipos</t>
@@ -13517,31 +13521,31 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L153" t="n">
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>-58.390735</v>
+        <v>-58.488914</v>
       </c>
       <c r="N153" t="n">
-        <v>-34.607742</v>
+        <v>-34.59164</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>CEN-E</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -13553,22 +13557,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>8365</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2699</t>
+          <t xml:space="preserve">PEREZ ROSALES, VICENTE 4086 </t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13588,7 +13592,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>base corrodia</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -13610,24 +13614,24 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>-58.432807</v>
+        <v>-58.491823</v>
       </c>
       <c r="N154" t="n">
-        <v>-34.574343</v>
+        <v>-34.587028</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -13639,17 +13643,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>ASUNCION 2373</t>
+          <t>CARACAS 3559</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -13674,7 +13678,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -13696,10 +13700,10 @@
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>-58.490913</v>
+        <v>-58.487793</v>
       </c>
       <c r="N155" t="n">
-        <v>-34.588328</v>
+        <v>-34.590403</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -13725,7 +13729,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>8362</t>
+          <t>8368</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13735,7 +13739,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAMUDIO 3884 </t>
+          <t>CARACAS 3519</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -13760,7 +13764,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -13782,10 +13786,10 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>-58.491114</v>
+        <v>-58.487627</v>
       </c>
       <c r="N156" t="n">
-        <v>-34.588808</v>
+        <v>-34.590585</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -13811,7 +13815,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13821,12 +13825,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>BEIRO, FRANCISCO AV. 2435</t>
+          <t>VARELA, JOSE PEDRO 3545</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -13846,7 +13850,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -13861,17 +13865,17 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L157" t="n">
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>-58.488914</v>
+        <v>-58.502073</v>
       </c>
       <c r="N157" t="n">
-        <v>-34.59164</v>
+        <v>-34.601294</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -13885,7 +13889,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -13897,7 +13901,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>8365</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13907,12 +13911,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ ROSALES, VICENTE 4086 </t>
+          <t>ANDONAEGUI 2383</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -13932,7 +13936,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -13954,10 +13958,10 @@
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>-58.491823</v>
+        <v>-58.489606</v>
       </c>
       <c r="N158" t="n">
-        <v>-34.587028</v>
+        <v>-34.57655</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -13971,7 +13975,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>ATH-C</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -13983,7 +13987,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13993,12 +13997,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>CARACAS 3559</t>
+          <t>CRAMER 4262</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14018,7 +14022,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -14040,14 +14044,14 @@
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>-58.487793</v>
+        <v>-58.476168</v>
       </c>
       <c r="N159" t="n">
-        <v>-34.590403</v>
+        <v>-34.545546</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -14057,7 +14061,7 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -14069,7 +14073,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14079,12 +14083,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>CARACAS 3519</t>
+          <t xml:space="preserve">CRAMER 4322 </t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14104,7 +14108,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida inclnada</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -14126,14 +14130,14 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>-58.487627</v>
+        <v>-58.476454</v>
       </c>
       <c r="N160" t="n">
-        <v>-34.590585</v>
+        <v>-34.544962</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -14143,7 +14147,7 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -14155,7 +14159,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>8382</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14165,7 +14169,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>VARELA, JOSE PEDRO 3545</t>
+          <t>SANTO TOME 3588</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -14190,7 +14194,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -14212,14 +14216,14 @@
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>-58.502073</v>
+        <v>-58.4947</v>
       </c>
       <c r="N161" t="n">
-        <v>-34.601294</v>
+        <v>-34.60925</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -14229,7 +14233,7 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>DEV-D</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -14241,7 +14245,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>S00117686</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14251,12 +14255,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>ANDONAEGUI 2383</t>
+          <t>DORREGO AV. 2778</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14276,7 +14280,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>inlinada</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -14298,24 +14302,24 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>-58.489606</v>
+        <v>-58.432102</v>
       </c>
       <c r="N162" t="n">
-        <v>-34.57655</v>
+        <v>-34.574248</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>ATH-C</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -14327,7 +14331,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>S00506048</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14337,12 +14341,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>CRAMER 4262</t>
+          <t>TERRADA 1088</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14362,12 +14366,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Tensor</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -14377,21 +14381,21 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L163" t="n">
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>-58.476168</v>
+        <v>-58.472866</v>
       </c>
       <c r="N163" t="n">
-        <v>-34.545546</v>
+        <v>-34.620121</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -14401,7 +14405,7 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>NRA-M</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -14413,22 +14417,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>-748</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRAMER 4322 </t>
+          <t>GUTENBERG 340</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14448,7 +14452,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>base corroida inclnada</t>
+          <t>inclinado base podrida</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -14463,21 +14467,21 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L164" t="n">
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>-58.476454</v>
+        <v>-58.471395</v>
       </c>
       <c r="N164" t="n">
-        <v>-34.544962</v>
+        <v>-34.592451</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -14487,7 +14491,7 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>PUE-?</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -14499,22 +14503,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>-750</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>SANTO TOME 3588</t>
+          <t>JURAMENTO 4979</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14534,7 +14538,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -14549,21 +14553,21 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L165" t="n">
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>-58.4947</v>
+        <v>-58.481188</v>
       </c>
       <c r="N165" t="n">
-        <v>-34.60925</v>
+        <v>-34.577198</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -14573,7 +14577,7 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>DEV-D</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -14585,22 +14589,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S00117686</t>
+          <t>-753</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2778</t>
+          <t>CISNEROS, VIRREY 1610</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14620,7 +14624,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>inlinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -14635,31 +14639,31 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L166" t="n">
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>-58.432102</v>
+        <v>-58.469727</v>
       </c>
       <c r="N166" t="n">
-        <v>-34.574248</v>
+        <v>-34.612013</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -14671,84 +14675,686 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S00506048</t>
+          <t>-754</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>TERRADA 1088</t>
+          <t>PINO, VIRREY DEL 1503</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" t="n">
+        <v>-58.442723</v>
+      </c>
+      <c r="N167" t="n">
+        <v>-34.56085</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>BLO-A</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>-755</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2/23/2026</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>CONDE 4296</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>corroida</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L168" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" t="n">
+        <v>-58.481187</v>
+      </c>
+      <c r="N168" t="n">
+        <v>-34.548301</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>COG-P</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>-757</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2/23/2026</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>FRAGATA PRES. SARMIENTO 1390</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>1</v>
+      </c>
+      <c r="M169" t="n">
+        <v>-58.456778</v>
+      </c>
+      <c r="N169" t="n">
+        <v>-34.609187</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>NRA-I</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>-761</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2/23/2026</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>MOLDES 2901</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="n">
+        <v>-58.465305</v>
+      </c>
+      <c r="N170" t="n">
+        <v>-34.556794</v>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>COG-K</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>-762</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2/23/2026</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>ROSETTI 444</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>corroida inclinada</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L171" t="n">
+        <v>1</v>
+      </c>
+      <c r="M171" t="n">
+        <v>-58.450184</v>
+      </c>
+      <c r="N171" t="n">
+        <v>-34.584646</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>ATH-L</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>S00506118</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2/23/2026</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>TERRERO 588</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
         <is>
           <t>Pendiente ADM</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>tensor roto</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Tensor</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
+        <v>1</v>
+      </c>
+      <c r="M172" t="n">
+        <v>-58.459689</v>
+      </c>
+      <c r="N172" t="n">
+        <v>-34.620032</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>NRA-D</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>-763</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2/24/2026</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Ricardo Gutiérrez 3702</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
         <is>
           <t>Terminal</t>
         </is>
       </c>
-      <c r="L167" t="n">
-        <v>1</v>
-      </c>
-      <c r="M167" t="n">
-        <v>-58.472866</v>
-      </c>
-      <c r="N167" t="n">
-        <v>-34.620121</v>
-      </c>
-      <c r="O167" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="P167" t="inlineStr">
+      <c r="L173" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" t="n">
+        <v>-58.504321</v>
+      </c>
+      <c r="N173" t="n">
+        <v>-34.602304</v>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
         <is>
           <t>Capital Norte</t>
         </is>
       </c>
-      <c r="Q167" t="inlineStr">
-        <is>
-          <t>NRA-M</t>
-        </is>
-      </c>
-      <c r="R167" t="inlineStr">
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>DEV-C</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>S01295589</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2/24/2026</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>CABILDO AV. 1008</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L174" t="n">
+        <v>1</v>
+      </c>
+      <c r="M174" t="n">
+        <v>-58.446714</v>
+      </c>
+      <c r="N174" t="n">
+        <v>-34.569183</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>COG-C</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_NEW.xlsx
+++ b/mapa_interactivo_NEW.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R174"/>
+  <dimension ref="A1:R170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5069,17 +5069,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>-669</t>
+          <t>7806</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>11/5/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Aizpurua  3790</t>
+          <t>ROOSEVELT FRANKLIN D. 4665</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>810573441</t>
+          <t>810651339</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>cambiar columna doblada</t>
+          <t>Poste inclinado</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5119,21 +5119,21 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L55" t="n">
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.505762</v>
+        <v>-58.482196</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.565075</v>
+        <v>-34.570432</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>PUE-H</t>
+          <t>ATH-E</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5155,7 +5155,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ROOSEVELT FRANKLIN D. 4665</t>
+          <t>BURELA 1589</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>810651339</t>
+          <t>810651370</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Poste inclinado</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5205,21 +5205,21 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L56" t="n">
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.482196</v>
+        <v>-58.485747</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.570432</v>
+        <v>-34.58538</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>ATH-E</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5241,22 +5241,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>7811</t>
+          <t>-673</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>11/17/2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BURELA 1589</t>
+          <t>Bauness 2195</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>810651370</t>
+          <t>810787633</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Sacar columna con prioridad  Tensar linga en columna continua</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5298,10 +5298,10 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.485747</v>
+        <v>-58.485702</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.58538</v>
+        <v>-34.576702</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>ATH-C</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5327,7 +5327,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>-673</t>
+          <t>-674</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bauness 2195</t>
+          <t>Miller 3597</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>810787633</t>
+          <t>810787625</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sacar columna con prioridad  Tensar linga en columna continua</t>
+          <t>Aplomar/ enderezar columna y colocar rienda a pique</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5384,14 +5384,14 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.485702</v>
+        <v>-58.489898</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.576702</v>
+        <v>-34.560497</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>ATH-C</t>
+          <t>PUE-F</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5413,22 +5413,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>-674</t>
+          <t>S01089776</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Miller 3597</t>
+          <t>ARGERICH 3717</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>810787625</t>
+          <t>810804318</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Aplomar/ enderezar columna y colocar rienda a pique</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5470,14 +5470,14 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.489898</v>
+        <v>-58.497051</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.560497</v>
+        <v>-34.594109</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>PUE-F</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5499,22 +5499,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S01089776</t>
+          <t>-680</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ARGERICH 3717</t>
+          <t>UGARTE, MANUEL 1796</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>810804318</t>
+          <t>810820827</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5556,14 +5556,14 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.497051</v>
+        <v>-58.455584</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.594109</v>
+        <v>-34.553164</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>BLO-D</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5585,7 +5585,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>-680</t>
+          <t>S01126628</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>UGARTE, MANUEL 1796</t>
+          <t>RIVERA, PEDRO I., DR. 3385</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5615,12 +5615,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>810820827</t>
+          <t>810820813</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5642,14 +5642,14 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.455584</v>
+        <v>-58.47104</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.553164</v>
+        <v>-34.562322</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>BLO-D</t>
+          <t>COG-I</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5671,7 +5671,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S01126628</t>
+          <t>S01144183</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>RIVERA, PEDRO I., DR. 3385</t>
+          <t>DE LOS CONSTITUYENTES AV. 4318</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>810820813</t>
+          <t>810820640</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5728,14 +5728,14 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.47104</v>
+        <v>-58.490526</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.562322</v>
+        <v>-34.583417</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>COG-I</t>
+          <t>PUE-K</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5757,7 +5757,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S01144183</t>
+          <t>S01171313</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DE LOS CONSTITUYENTES AV. 4318</t>
+          <t xml:space="preserve"> LOPE DE VEGA AV. 3128 </t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>810820640</t>
+          <t>810820624</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5814,14 +5814,14 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.490526</v>
+        <v>-58.525417</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.583417</v>
+        <v>-34.613865</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>PUE-K</t>
+          <t>DEV-G</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5843,7 +5843,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S01171313</t>
+          <t xml:space="preserve">7870 </t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LOPE DE VEGA AV. 3128 </t>
+          <t>MAGARIÑOS CERVANTES, A. 4803</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>810820624</t>
+          <t>810820571</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada, tensor roto</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5893,17 +5893,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L64" t="n">
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.525417</v>
+        <v>-58.500609</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.613865</v>
+        <v>-34.626542</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -5917,19 +5917,19 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>DEV-G</t>
+          <t>DEV-I</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-26011.PO.1DEV</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870 </t>
+          <t xml:space="preserve">7867 </t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MAGARIÑOS CERVANTES, A. 4803</t>
+          <t>DIAZ, CESAR, GRAL. 1450</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5959,12 +5959,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>810820571</t>
+          <t>810820533</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>inclinada, tensor roto</t>
+          <t>muy inclinada</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5979,21 +5979,21 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.500609</v>
+        <v>-58.461219</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.626542</v>
+        <v>-34.605928</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -6003,34 +6003,34 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>DEV-I</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>ARATO-26011.PO.1DEV</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">7867 </t>
+          <t>-684</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/26/2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>DIAZ, CESAR, GRAL. 1450</t>
+          <t>LONDRES 4280</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6045,12 +6045,13 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>810820533</t>
+          <t xml:space="preserve">01639693 </t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>muy inclinada</t>
+          <t xml:space="preserve">Columna 114 picada en base con receptor óptico propio, ver de colocar otra columna a la derecha asi poder traspasar el mismo receptor y Cdo propio.
+</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6060,22 +6061,22 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L66" t="n">
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.461219</v>
+        <v>-58.48081</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.605928</v>
+        <v>-34.582354</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -6089,7 +6090,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6101,7 +6102,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>-684</t>
+          <t>7882</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6111,12 +6112,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>LONDRES 4280</t>
+          <t xml:space="preserve">BELAUSTEGUI, LUIS, DR. 3490 </t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6131,13 +6132,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">01639693 </t>
+          <t>810862856</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Columna 114 picada en base con receptor óptico propio, ver de colocar otra columna a la derecha asi poder traspasar el mismo receptor y Cdo propio.
-</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6147,26 +6147,26 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L67" t="n">
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.48081</v>
+        <v>-58.484549</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.582354</v>
+        <v>-34.620529</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>DEV-K</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6188,7 +6188,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>7882</t>
+          <t xml:space="preserve">6436 </t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">BELAUSTEGUI, LUIS, DR. 3490 </t>
+          <t xml:space="preserve">ARIAS 4306 </t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6218,12 +6218,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>810862856</t>
+          <t>810862832</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6238,21 +6238,21 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.484549</v>
+        <v>-58.49108</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.620529</v>
+        <v>-34.550102</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>DEV-K</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6274,17 +6274,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">6436 </t>
+          <t>-695</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>11/26/2025</t>
+          <t>12/3/2025</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARIAS 4306 </t>
+          <t>Estomba 2626</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6304,17 +6304,17 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>810862832</t>
+          <t>810984651</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>desmontar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6331,14 +6331,14 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.49108</v>
+        <v>-58.47538</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.550102</v>
+        <v>-34.566015</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>PUE-E</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6360,17 +6360,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S00964409</t>
+          <t>-698</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>11/28/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CERETTI 3556</t>
+          <t>Franklin D. Roosevelt 5469</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6390,12 +6390,13 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>810877550</t>
+          <t xml:space="preserve">02019355 </t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t xml:space="preserve">corroida colocar columna pedir traspaso
+</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6405,7 +6406,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6417,10 +6418,10 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.502145</v>
+        <v>-58.491346</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.566981</v>
+        <v>-34.575773</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -6434,7 +6435,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>PUE-H</t>
+          <t>PUE-C</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6446,22 +6447,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>-695</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>12/3/2025</t>
+          <t>12/16/2025</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Estomba 2626</t>
+          <t>GUTIERREZ, RICARDO 3351</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6476,12 +6477,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>810984651</t>
+          <t>811198642</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>desmontar</t>
+          <t>poste inclinado</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6496,21 +6497,21 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L71" t="n">
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.47538</v>
+        <v>-58.498056</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.566015</v>
+        <v>-34.601454</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -6520,7 +6521,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>PUE-E</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6532,22 +6533,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>-698</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/16/2025</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Franklin D. Roosevelt 5469</t>
+          <t>DIAZ, CESAR, GRAL. 2053</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6562,13 +6563,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">02019355 </t>
+          <t>811198627</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">corroida colocar columna pedir traspaso
-</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6578,22 +6578,22 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L72" t="n">
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.491346</v>
+        <v>-58.468739</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.575773</v>
+        <v>-34.608957</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>PUE-C</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6619,22 +6619,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t xml:space="preserve">7921 </t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>12/16/2025</t>
+          <t>12/17/2025</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GUTIERREZ, RICARDO 3351</t>
+          <t>O'HIGGINS 4298</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>811198642</t>
+          <t>811198660</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6676,14 +6676,14 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.498056</v>
+        <v>-58.468046</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.601454</v>
+        <v>-34.541893</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6705,22 +6705,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-706</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>12/16/2025</t>
+          <t>12/17/2025</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>DIAZ, CESAR, GRAL. 2053</t>
+          <t>PAZ, MARCOS 1505</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>811198627</t>
+          <t>811181316</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6762,14 +6762,14 @@
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.468739</v>
+        <v>-58.500094</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.608957</v>
+        <v>-34.626115</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -6779,29 +6779,29 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>DEV-I</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-26011.PO.1DEV</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">7921 </t>
+          <t>7938</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>12/17/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>O'HIGGINS 4298</t>
+          <t xml:space="preserve"> O'HIGGINS 4321</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>811198660</t>
+          <t>811198748</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6848,10 +6848,10 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.468046</v>
+        <v>-58.468227</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.541893</v>
+        <v>-34.541506</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -6877,22 +6877,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>-706</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>12/17/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PAZ, MARCOS 1505</t>
+          <t xml:space="preserve">PLAZA, VICTORINO DE LA, DR. 1754 </t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>811181316</t>
+          <t>811198702</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6927,21 +6927,21 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L76" t="n">
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.500094</v>
+        <v>-58.451448</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.626115</v>
+        <v>-34.547978</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -6951,34 +6951,34 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>DEV-I</t>
+          <t>BLO-D</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>ARATO-26011.PO.1DEV</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>S01028030</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve"> O'HIGGINS 4321</t>
+          <t xml:space="preserve">MARTIN PESCADOR 2296 </t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6993,12 +6993,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>811198748</t>
+          <t>811198686</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>poste inclinado</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7013,21 +7013,21 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.468227</v>
+        <v>-58.493624</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.541506</v>
+        <v>-34.610119</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7049,22 +7049,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>S01215915</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ALBARELLOS AV. 3153</t>
+          <t xml:space="preserve"> MOLDES 2906</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>811198739</t>
+          <t>811198663</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>base crroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7099,21 +7099,21 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L78" t="n">
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.512482</v>
+        <v>-58.465461</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.579056</v>
+        <v>-34.556738</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>PUE-J</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7135,22 +7135,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>-707</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/22/2025</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLAZA, VICTORINO DE LA, DR. 1754 </t>
+          <t>Camargo 257</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7165,12 +7165,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>811198702</t>
+          <t>811238662</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7192,14 +7192,14 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.451448</v>
+        <v>-58.438123</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.547978</v>
+        <v>-34.602541</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -7209,7 +7209,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>BLO-D</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7221,22 +7221,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S01028030</t>
+          <t xml:space="preserve">7969 </t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTIN PESCADOR 2296 </t>
+          <t xml:space="preserve">HELGUERA 4770 </t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>811198686</t>
+          <t>811238727</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7278,14 +7278,14 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.493624</v>
+        <v>-58.505298</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.610119</v>
+        <v>-34.587467</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -7295,34 +7295,34 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>PUE-N</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PUE</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S01215915</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MOLDES 2906</t>
+          <t>RIVERA, PEDRO I., DR. 4448</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7337,12 +7337,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>811198663</t>
+          <t>811299428</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7357,21 +7357,21 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L81" t="n">
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.465461</v>
+        <v>-58.481135</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.556738</v>
+        <v>-34.568427</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>PUE-E</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7393,17 +7393,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>-707</t>
+          <t xml:space="preserve">7215 </t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>12/22/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Camargo 257</t>
+          <t xml:space="preserve">MAURE 3996 </t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>811238662</t>
+          <t>811299417</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7450,14 +7450,14 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.438123</v>
+        <v>-58.451687</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.602541</v>
+        <v>-34.586223</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>ATH-L</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7479,22 +7479,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">7969 </t>
+          <t>7987</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">HELGUERA 4770 </t>
+          <t>Terrada 2309</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7509,12 +7509,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>811238727</t>
+          <t>811299433</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7529,17 +7529,17 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L83" t="n">
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.505298</v>
+        <v>-58.482084</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.587467</v>
+        <v>-34.608289</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -7553,29 +7553,29 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>PUE-N</t>
+          <t>NRA-P</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PUE</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>S01139199</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>RIVERA, PEDRO I., DR. 4448</t>
+          <t>CRAMER 4320</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>811299428</t>
+          <t>811299481</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7622,14 +7622,14 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.481135</v>
+        <v>-58.476445</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.568427</v>
+        <v>-34.544981</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>PUE-E</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -7651,17 +7651,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t xml:space="preserve">8090 </t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>1/5/2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ALBARELLOS AV. 3031</t>
+          <t>Vedia 3506</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7681,17 +7681,17 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>811299423</t>
+          <t xml:space="preserve">02125435 </t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>desmonte y traspasar red</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -7708,14 +7708,14 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.511732</v>
+        <v>-58.486704</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.578688</v>
+        <v>-34.544613</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>PUE-J</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -7737,22 +7737,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">7215 </t>
+          <t>-717</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAURE 3996 </t>
+          <t>Ibera 2218</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>811299417</t>
+          <t>811453864</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7794,14 +7794,14 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.451687</v>
+        <v>-58.46286</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.586223</v>
+        <v>-34.552702</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>ATH-L</t>
+          <t>BLO-R</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7823,22 +7823,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t xml:space="preserve">8173 </t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Terrada 2309</t>
+          <t>SUCRE, ANTONIO JOSE DE, MCAL. 1563</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7853,12 +7853,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>811299433</t>
+          <t xml:space="preserve">02313712 </t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7868,26 +7868,26 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L87" t="n">
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.482084</v>
+        <v>-58.446858</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.608289</v>
+        <v>-34.559026</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>NRA-P</t>
+          <t>BLO-A</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7909,22 +7909,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S01139199</t>
+          <t>-719</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CRAMER 4320</t>
+          <t>MENDOZA 2160</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>811299481</t>
+          <t>811453860</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7966,10 +7966,10 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.476445</v>
+        <v>-58.455182</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.544981</v>
+        <v>-34.559761</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>BLO-O</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7995,22 +7995,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">8090 </t>
+          <t>S01180016</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1/5/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Vedia 3506</t>
+          <t>FITZ ROY 1730</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8025,17 +8025,17 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">02125435 </t>
+          <t>811454223</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>desmonte y traspasar red</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -8052,24 +8052,24 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.486704</v>
+        <v>-58.436051</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.544613</v>
+        <v>-34.583855</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8081,22 +8081,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>-717</t>
+          <t>S01180023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ibera 2218</t>
+          <t>VEGA, NICETO, CNEL. AV. 5420</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>811453864</t>
+          <t>811454198</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8138,24 +8138,24 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.46286</v>
+        <v>-58.437628</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.552702</v>
+        <v>-34.587953</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>BLO-R</t>
+          <t>ATH-?</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8167,22 +8167,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">8173 </t>
+          <t>S01180086</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SUCRE, ANTONIO JOSE DE, MCAL. 1563</t>
+          <t>BONPLAND 1471</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">02313712 </t>
+          <t>811454194</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8224,24 +8224,24 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.446858</v>
+        <v>-58.439513</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.559026</v>
+        <v>-34.585314</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>BLO-A</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8253,22 +8253,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>-719</t>
+          <t>S01200482</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MENDOZA 2160</t>
+          <t>GONZALEZ, ELPIDIO 2749</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>811453860</t>
+          <t>811454117</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>quebrada</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8303,21 +8303,21 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L92" t="n">
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.455182</v>
+        <v>-58.481266</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.559761</v>
+        <v>-34.608522</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>BLO-O</t>
+          <t>NRA-O</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8339,7 +8339,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S01180016</t>
+          <t>S01204059</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FITZ ROY 1730</t>
+          <t>BUFANO, ALFREDO R. 2580</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>811454223</t>
+          <t>811454109</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8396,24 +8396,24 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.436051</v>
+        <v>-58.478411</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.583855</v>
+        <v>-34.6039</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>NRA-P</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8425,7 +8425,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S01180023</t>
+          <t>S01220047</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>VEGA, NICETO, CNEL. AV. 5420</t>
+          <t>MAURE 2958</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>811454198</t>
+          <t>811454097</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -8482,10 +8482,10 @@
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.437628</v>
+        <v>-58.446339</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.587953</v>
+        <v>-34.576306</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>ATH-?</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8511,7 +8511,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S01180086</t>
+          <t>S01306211</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BONPLAND 1471</t>
+          <t>WASHINGTON 3943</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>811454194</t>
+          <t>811453965</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -8561,31 +8561,31 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L95" t="n">
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.439513</v>
+        <v>-58.48286</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.585314</v>
+        <v>-34.55278</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8597,7 +8597,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S01200482</t>
+          <t>S01313361</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GONZALEZ, ELPIDIO 2749</t>
+          <t>CABILDO AV. 805</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>811454117</t>
+          <t>811453963</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>quebrada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -8654,14 +8654,14 @@
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.481266</v>
+        <v>-58.444955</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.608522</v>
+        <v>-34.569791</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>NRA-O</t>
+          <t>COG-C</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8683,7 +8683,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S01204059</t>
+          <t>S01389798</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BUFANO, ALFREDO R. 2580</t>
+          <t>GUALEGUAYCHU 4682</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>811454109</t>
+          <t>811453943</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -8740,10 +8740,10 @@
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.478411</v>
+        <v>-58.518214</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.6039</v>
+        <v>-34.596516</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -8757,19 +8757,19 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>NRA-P</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1PUE</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S01220047</t>
+          <t>S01384321</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MAURE 2958</t>
+          <t>AZURDUY JUANA 2685</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>811454097</t>
+          <t>811453930</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -8826,24 +8826,24 @@
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.446339</v>
+        <v>-58.469341</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.576306</v>
+        <v>-34.552269</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8855,7 +8855,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S01306211</t>
+          <t>S01384337</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8865,12 +8865,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>WASHINGTON 3943</t>
+          <t xml:space="preserve">MOLDES 3502 </t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>811453965</t>
+          <t>811453925</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>base quebrada</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -8912,10 +8912,10 @@
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.48286</v>
+        <v>-58.470282</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.55278</v>
+        <v>-34.551553</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>COG-M</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8941,7 +8941,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S01313361</t>
+          <t>S01392303</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CABILDO AV. 805</t>
+          <t>Moldes 1999</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>811453963</t>
+          <t>811453918</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -8991,17 +8991,17 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L100" t="n">
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.444955</v>
+        <v>-58.458535</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.569791</v>
+        <v>-34.564674</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>COG-C</t>
+          <t>COG-G</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9027,22 +9027,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S01343333</t>
+          <t>8095</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ, JOAQUIN V. 3542 </t>
+          <t>MANZANARES 3853</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -9057,12 +9057,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>811453949</t>
+          <t>811454324</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9077,21 +9077,21 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L101" t="n">
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.506708</v>
+        <v>-58.482488</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.601841</v>
+        <v>-34.554114</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9113,22 +9113,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S01389798</t>
+          <t>8094</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU 4682</t>
+          <t xml:space="preserve">GARCIA DEL RIO 3789 </t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>811453943</t>
+          <t>811454305</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -9163,21 +9163,21 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L102" t="n">
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.518214</v>
+        <v>-58.482473</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.596516</v>
+        <v>-34.553018</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -9187,34 +9187,34 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1PUE</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S01384321</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AZURDUY JUANA 2685</t>
+          <t>Nogoya 3644</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>811453930</t>
+          <t>811454515</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9256,14 +9256,14 @@
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.469341</v>
+        <v>-58.497751</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.552269</v>
+        <v>-34.606408</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9285,22 +9285,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S01384337</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOLDES 3502 </t>
+          <t>Pje. Manuel Sola 4440</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>811453925</t>
+          <t>811454508</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>base quebrada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -9335,21 +9335,21 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L104" t="n">
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.470282</v>
+        <v>-58.507954</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.551553</v>
+        <v>-34.610808</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>COG-M</t>
+          <t>DEV-D</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9371,17 +9371,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S01392303</t>
+          <t xml:space="preserve">8112 </t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Moldes 1999</t>
+          <t>MANZANARES 2073</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -9401,12 +9401,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>811453918</t>
+          <t>811454483</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -9428,14 +9428,14 @@
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.458535</v>
+        <v>-58.465953</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.564674</v>
+        <v>-34.545637</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>COG-G</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9457,17 +9457,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t xml:space="preserve">8114 </t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MANZANARES 3853</t>
+          <t>ARGERICH 5774</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>811454324</t>
+          <t>811454454</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -9507,21 +9507,21 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L106" t="n">
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.482488</v>
+        <v>-58.511147</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.554114</v>
+        <v>-34.578665</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>PUE-J</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9543,22 +9543,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>1/15/2026</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA DEL RIO 3789 </t>
+          <t>ESTOMBA 212</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>811454305</t>
+          <t>811454532</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -9593,21 +9593,21 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L107" t="n">
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.482473</v>
+        <v>-58.469045</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.553018</v>
+        <v>-34.588525</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9629,22 +9629,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>8186</t>
+          <t>-731</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Nogoya 3644</t>
+          <t>Ruiz Huidobro 3643</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9659,14 +9659,10 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>811454515</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>corroida</t>
-        </is>
-      </c>
+          <t>811498060</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -9679,21 +9675,21 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L108" t="n">
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.497751</v>
+        <v>-58.484505</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.606408</v>
+        <v>-34.549798</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -9703,7 +9699,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9715,22 +9711,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>8316</t>
+          <t>-732</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Pje. Manuel Sola 4440</t>
+          <t xml:space="preserve"> Valentin Alsina 1685</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9743,14 +9739,10 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>811454508</t>
-        </is>
-      </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -9771,25 +9763,21 @@
       <c r="L109" t="n">
         <v>1</v>
       </c>
-      <c r="M109" t="n">
-        <v>-58.507954</v>
-      </c>
-      <c r="N109" t="n">
-        <v>-34.610808</v>
-      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>No ubicado</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>No clasificado, consultar con mantenimiento</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>DEV-D</t>
+          <t>No ubicado</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -9801,22 +9789,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">8112 </t>
+          <t>-733</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MANZANARES 2073</t>
+          <t xml:space="preserve"> Dorrego 2755</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9831,12 +9819,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>811454483</t>
+          <t>811498056</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -9858,24 +9846,24 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.465953</v>
+        <v>-58.432319</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.545637</v>
+        <v>-34.574385</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9887,17 +9875,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8114 </t>
+          <t xml:space="preserve">6428 </t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ARGERICH 5774</t>
+          <t>MONROE 4070</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9917,12 +9905,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>811454454</t>
+          <t>811498053</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -9937,21 +9925,21 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L111" t="n">
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.511147</v>
+        <v>-58.475842</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.578665</v>
+        <v>-34.568215</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -9961,7 +9949,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>PUE-J</t>
+          <t>ATH-J</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9973,22 +9961,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1/15/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ESTOMBA 212</t>
+          <t>AZURDUY JUANA 3630</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10003,7 +9991,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>811454532</t>
+          <t>811498050</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -10023,21 +10011,21 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L112" t="n">
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.469045</v>
+        <v>-58.477583</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.588525</v>
+        <v>-34.5569</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -10047,7 +10035,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>COG-N</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10059,22 +10047,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>-731</t>
+          <t>S01215930</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/20/2026</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ruiz Huidobro 3643</t>
+          <t>UGARTE, MANUEL 2750</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10089,10 +10077,14 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>811498060</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
+          <t>811498072</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>corroida</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -10105,17 +10097,17 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.484505</v>
+        <v>-58.465042</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.549798</v>
+        <v>-34.557947</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -10129,7 +10121,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10141,22 +10133,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>-732</t>
+          <t>8181</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/22/2026</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Valentin Alsina 1685</t>
+          <t xml:space="preserve">FREIRE, RAMON, CAP. GRAL. 4748 </t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10169,10 +10161,14 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>811498074</t>
+        </is>
+      </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada base quebrada</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -10187,27 +10183,31 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L114" t="n">
         <v>1</v>
       </c>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
+      <c r="M114" t="n">
+        <v>-58.482951</v>
+      </c>
+      <c r="N114" t="n">
+        <v>-34.544273</v>
+      </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>No ubicado</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>No clasificado, consultar con mantenimiento</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>No ubicado</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10219,22 +10219,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>-733</t>
+          <t>S01318042</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dorrego 2755</t>
+          <t>UGARTE, MANUEL 3815</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -10249,12 +10249,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>811498056</t>
+          <t>811626754</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -10276,24 +10276,24 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.432319</v>
+        <v>-58.476138</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.574385</v>
+        <v>-34.563825</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>COG-N</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10305,22 +10305,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">6428 </t>
+          <t>S01397288</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>MONROE 4070</t>
+          <t xml:space="preserve">MOLDES 1918 </t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10335,37 +10335,25 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>811498053</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>corroida</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
+          <t>inclinadaq</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
       <c r="L116" t="n">
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.475842</v>
+        <v>-58.458035</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.568215</v>
+        <v>-34.565387</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -10379,7 +10367,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>ATH-J</t>
+          <t>COG-G</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10391,22 +10379,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>S01397364</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>AZURDUY JUANA 3630</t>
+          <t>AVILES, VIRREY 3008</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10421,12 +10409,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>811498050</t>
+          <t>811626732</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -10448,14 +10436,14 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.477583</v>
+        <v>-58.457207</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.5569</v>
+        <v>-34.571602</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -10465,7 +10453,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>COG-N</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10477,22 +10465,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S01215930</t>
+          <t>-740</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1/20/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>UGARTE, MANUEL 2750</t>
+          <t>Gutemberg 350</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10507,12 +10495,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>811498072</t>
+          <t>811626800</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -10527,21 +10515,21 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L118" t="n">
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.465042</v>
+        <v>-58.471803</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.557947</v>
+        <v>-34.592463</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -10551,7 +10539,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>PUE-?</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10563,22 +10551,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>8181</t>
+          <t>-741</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1/22/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREIRE, RAMON, CAP. GRAL. 4748 </t>
+          <t>Gutemberg 320</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -10593,12 +10581,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>811498074</t>
+          <t>811626794</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>inclinada base quebrada</t>
+          <t>mal estado</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -10620,14 +10608,14 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.482951</v>
+        <v>-58.470581</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.544273</v>
+        <v>-34.592428</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -10637,7 +10625,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>PUE-?</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10649,22 +10637,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S01318042</t>
+          <t>-742</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>UGARTE, MANUEL 3815</t>
+          <t>BLANCO ENCALADA 899</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -10679,17 +10667,17 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>811626754</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>desmonte</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -10699,17 +10687,17 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L120" t="n">
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.476138</v>
+        <v>-58.443393</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.563825</v>
+        <v>-34.549873</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -10723,7 +10711,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>COG-N</t>
+          <t>BLO-B</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10735,22 +10723,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S01377458</t>
+          <t>-743</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ANDONAEGUI 2752</t>
+          <t>Giribone 1411</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -10765,12 +10753,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>811626748</t>
+          <t>811626791</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -10792,14 +10780,14 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.492149</v>
+        <v>-58.462095</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.573534</v>
+        <v>-34.579585</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -10809,7 +10797,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>PUE-D</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10821,22 +10809,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S01397288</t>
+          <t>S01396837</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOLDES 1918 </t>
+          <t>DEHEZA 3622</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -10851,29 +10839,41 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811626963</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>inclinadaq</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
+          <t>inclinado base quebrada</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
       <c r="L122" t="n">
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.458035</v>
+        <v>-58.485735</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.565387</v>
+        <v>-34.546249</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>COG-G</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10895,17 +10895,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S01397364</t>
+          <t>S01406731</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>AVILES, VIRREY 3008</t>
+          <t xml:space="preserve"> CORREA 1807</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10925,12 +10925,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>811626732</t>
+          <t>811626953</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -10952,14 +10952,14 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.457207</v>
+        <v>-58.466595</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.571602</v>
+        <v>-34.54099</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10981,22 +10981,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>-740</t>
+          <t>S01406737</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Gutemberg 350</t>
+          <t>GRECIA 4281</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11011,12 +11011,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>811626800</t>
+          <t>811626921</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inlinada</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -11031,21 +11031,21 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L124" t="n">
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.471803</v>
+        <v>-58.466965</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.592463</v>
+        <v>-34.541488</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>PUE-?</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11067,7 +11067,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>-741</t>
+          <t>S01406812</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Gutemberg 320</t>
+          <t xml:space="preserve">VUELTA DE OBLIGADO 3201 </t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>811626794</t>
+          <t>811626783</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>mal estado</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -11117,21 +11117,21 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L125" t="n">
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.470581</v>
+        <v>-58.464784</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.592428</v>
+        <v>-34.551419</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>PUE-?</t>
+          <t>BLO-R</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11153,17 +11153,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>-742</t>
+          <t>S00019326</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>BLANCO ENCALADA 899</t>
+          <t>OLLEROS 3050</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11183,17 +11183,17 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811627002</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>desmonte</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -11203,31 +11203,31 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L126" t="n">
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.443393</v>
+        <v>-58.447708</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.549873</v>
+        <v>-34.577055</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>BLO-B</t>
+          <t>ATH-P</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11239,22 +11239,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>-743</t>
+          <t>S00021988</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Giribone 1411</t>
+          <t>ALVAREZ THOMAS AV. 1115</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11269,12 +11269,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>811626791</t>
+          <t>811626996</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -11296,10 +11296,10 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.462095</v>
+        <v>-58.457565</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.579585</v>
+        <v>-34.578379</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>ATH-O</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11325,18 +11325,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S01243988</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr"/>
+          <t>8249</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2/2/2026</t>
+        </is>
+      </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LAVOISIER 3556 </t>
+          <t xml:space="preserve">SANABRIA 2386 </t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11351,12 +11355,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811626991</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -11371,21 +11375,21 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L128" t="n">
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.502869</v>
+        <v>-58.503452</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.567437</v>
+        <v>-34.614501</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -11395,7 +11399,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>PUE-H</t>
+          <t>DEV-D</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11407,22 +11411,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S01396837</t>
+          <t>S01450787</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>DEHEZA 3622</t>
+          <t>HERNANDEZ, JOSE 2110</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -11437,12 +11441,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>811626963</t>
+          <t>811626983</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>inclinado base quebrada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -11464,14 +11468,14 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.485735</v>
+        <v>-58.450727</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.546249</v>
+        <v>-34.56425</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -11481,7 +11485,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>BLO-M</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11493,22 +11497,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S01406731</t>
+          <t>-745</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CORREA 1807</t>
+          <t>Gamarra 1546</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -11523,12 +11527,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>811626953</t>
+          <t>811627113</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -11550,14 +11554,14 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.466595</v>
+        <v>-58.477231</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.54099</v>
+        <v>-34.58242</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -11567,7 +11571,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11579,22 +11583,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S01406737</t>
+          <t>S00036520</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>GRECIA 4281</t>
+          <t>SEGUROLA AV. 856</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11609,12 +11613,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>811626921</t>
+          <t>811627070</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>inlinada</t>
+          <t>corroidaq</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -11636,14 +11640,14 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.466965</v>
+        <v>-58.490765</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.541488</v>
+        <v>-34.627337</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -11653,34 +11657,34 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>DEV-I</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-26011.PO.1DEV</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S01406812</t>
+          <t xml:space="preserve">900009468810 </t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">VUELTA DE OBLIGADO 3201 </t>
+          <t xml:space="preserve">CUENCA 3033 </t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11695,12 +11699,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>811626783</t>
+          <t>811627041</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -11715,21 +11719,21 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L132" t="n">
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.464784</v>
+        <v>-58.494814</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.551419</v>
+        <v>-34.601905</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -11739,7 +11743,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>BLO-R</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11751,22 +11755,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S01451118</t>
+          <t>S01337226</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/6/2026</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ESCOBAR 2911</t>
+          <t>MOLDES 3055</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11781,7 +11785,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>811626883</t>
+          <t>811627125</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -11808,14 +11812,14 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.509608</v>
+        <v>-58.466692</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.578546</v>
+        <v>-34.555283</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -11825,7 +11829,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>PUE-J</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11837,17 +11841,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S00019326</t>
+          <t>S01375612</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/6/2026</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>OLLEROS 3050</t>
+          <t>LACROZE, FEDERICO AV. 2834</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11867,12 +11871,12 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>811627002</t>
+          <t>811627118</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>corroidaq</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -11894,10 +11898,10 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.447708</v>
+        <v>-58.447177</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.577055</v>
+        <v>-34.574158</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -11923,22 +11927,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S00021988</t>
+          <t xml:space="preserve">8301 </t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ALVAREZ THOMAS AV. 1115</t>
+          <t>ARENGREEN 1584</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -11953,12 +11957,12 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>811626996</t>
+          <t>812440072</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -11973,31 +11977,31 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L135" t="n">
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.457565</v>
+        <v>-58.453265</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.578379</v>
+        <v>-34.615073</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>ATH-O</t>
+          <t>NRA-I</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -12009,22 +12013,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANABRIA 2386 </t>
+          <t>ARENAL, CONCEPCION 3814</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12039,12 +12043,12 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>811626991</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -12054,26 +12058,26 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L136" t="n">
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.503452</v>
+        <v>-58.447805</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.614501</v>
+        <v>-34.587018</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -12083,7 +12087,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>DEV-D</t>
+          <t>ATH-L</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12095,22 +12099,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S01450787</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>HERNANDEZ, JOSE 2110</t>
+          <t>WARNES AV. 2239</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12125,7 +12129,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>811626983</t>
+          <t>812440018</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -12145,21 +12149,21 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.450727</v>
+        <v>-58.467815</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.56425</v>
+        <v>-34.596225</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -12169,7 +12173,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>BLO-M</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12181,17 +12185,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>-745</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Gamarra 1546</t>
+          <t>PAZ SOLDAN 4991</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -12211,12 +12215,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>811627113</t>
+          <t>812439995</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>base quebrada</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -12231,17 +12235,17 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L138" t="n">
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.477231</v>
+        <v>-58.468466</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.58242</v>
+        <v>-34.594154</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -12255,7 +12259,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12267,22 +12271,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S00036520</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SEGUROLA AV. 856</t>
+          <t xml:space="preserve"> GUALEGUAYCHU 4754</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12297,12 +12301,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>811627070</t>
+          <t>812439956</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>corroidaq</t>
+          <t>inclinado, base quebrada</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -12317,21 +12321,21 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L139" t="n">
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.490765</v>
+        <v>-58.518803</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.627337</v>
+        <v>-34.595866</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -12341,34 +12345,34 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>DEV-I</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>ARATO-26011.PO.1DEV</t>
+          <t>ARATO-25058.PO.1PUE</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">900009468810 </t>
+          <t>8341</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUENCA 3033 </t>
+          <t>BLANCO ENCALADA 823</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12383,12 +12387,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>811627041</t>
+          <t>812439941</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>inclinado base quebrada</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -12403,21 +12407,21 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.494814</v>
+        <v>-58.442692</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.601905</v>
+        <v>-34.549454</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -12427,7 +12431,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>BLO-B</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12439,22 +12443,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S01337226</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2/6/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MOLDES 3055</t>
+          <t>DORREGO AV. 2699</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12469,12 +12473,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>811627125</t>
+          <t>812440089</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>base corrodia</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -12496,24 +12500,24 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.466692</v>
+        <v>-58.432807</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.555283</v>
+        <v>-34.574343</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12525,22 +12529,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S01375612</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2/6/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>LACROZE, FEDERICO AV. 2834</t>
+          <t>ASUNCION 2373</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12555,12 +12559,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>811627118</t>
+          <t>812440083</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>corroidaq</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -12582,24 +12586,24 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.447177</v>
+        <v>-58.490913</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.574158</v>
+        <v>-34.588328</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>ATH-P</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12611,22 +12615,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">8301 </t>
+          <t>8362</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ARENGREEN 1584</t>
+          <t xml:space="preserve">ZAMUDIO 3884 </t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12641,7 +12645,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440257</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -12661,31 +12665,31 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L143" t="n">
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.453265</v>
+        <v>-58.491114</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.615073</v>
+        <v>-34.588808</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>NRA-I</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12697,22 +12701,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>AIZPURUA 3796</t>
+          <t>BEIRO, FRANCISCO AV. 2435</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -12727,12 +12731,12 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440250</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -12747,17 +12751,17 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L144" t="n">
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.505811</v>
+        <v>-58.488914</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.565014</v>
+        <v>-34.59164</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -12771,7 +12775,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>PUE-H</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12783,17 +12787,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>8365</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ARENAL, CONCEPCION 3814</t>
+          <t xml:space="preserve">PEREZ ROSALES, VICENTE 4086 </t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -12813,12 +12817,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440239</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -12828,7 +12832,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -12840,14 +12844,14 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.447805</v>
+        <v>-58.491823</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.587018</v>
+        <v>-34.587028</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -12857,7 +12861,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>ATH-L</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12869,17 +12873,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>WARNES AV. 2239</t>
+          <t>CARACAS 3559</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12899,12 +12903,12 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440223</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -12926,10 +12930,10 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.467815</v>
+        <v>-58.487793</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.596225</v>
+        <v>-34.590403</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -12943,7 +12947,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12955,17 +12959,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>8368</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>PAZ SOLDAN 4991</t>
+          <t>CARACAS 3519</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -12990,7 +12994,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>base quebrada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -13005,17 +13009,17 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L147" t="n">
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.468466</v>
+        <v>-58.487627</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.594154</v>
+        <v>-34.590585</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -13029,7 +13033,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -13041,17 +13045,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GUALEGUAYCHU 4754</t>
+          <t>VARELA, JOSE PEDRO 3545</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -13071,12 +13075,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440219</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>inclinado, base quebrada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -13098,10 +13102,10 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.518803</v>
+        <v>-58.502073</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.595866</v>
+        <v>-34.601294</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -13115,34 +13119,34 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1PUE</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>BLANCO ENCALADA 823</t>
+          <t>ANDONAEGUI 2383</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13157,12 +13161,12 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440211</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>inclinado base quebrada</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -13177,21 +13181,21 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L149" t="n">
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.442692</v>
+        <v>-58.489606</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.549454</v>
+        <v>-34.57655</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -13201,7 +13205,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>BLO-B</t>
+          <t>ATH-C</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13213,22 +13217,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2699</t>
+          <t>CRAMER 4262</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13243,12 +13247,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440206</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>base corrodia</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -13270,24 +13274,24 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.432807</v>
+        <v>-58.476168</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.574343</v>
+        <v>-34.545546</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -13299,22 +13303,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ASUNCION 2373</t>
+          <t xml:space="preserve">CRAMER 4322 </t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13329,12 +13333,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440204</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida inclnada</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -13356,14 +13360,14 @@
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>-58.490913</v>
+        <v>-58.476454</v>
       </c>
       <c r="N151" t="n">
-        <v>-34.588328</v>
+        <v>-34.544962</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -13373,7 +13377,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -13385,7 +13389,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>8362</t>
+          <t>8382</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13395,12 +13399,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAMUDIO 3884 </t>
+          <t>SANTO TOME 3588</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13415,12 +13419,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440197</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -13435,21 +13439,21 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L152" t="n">
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.491114</v>
+        <v>-58.4947</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.588808</v>
+        <v>-34.60925</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -13459,7 +13463,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>DEV-D</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -13471,7 +13475,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>S00117686</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13481,12 +13485,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>BEIRO, FRANCISCO AV. 2435</t>
+          <t>DORREGO AV. 2778</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13501,12 +13505,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440183</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inlinada</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -13528,24 +13532,24 @@
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>-58.488914</v>
+        <v>-58.432102</v>
       </c>
       <c r="N153" t="n">
-        <v>-34.59164</v>
+        <v>-34.574248</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -13557,7 +13561,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>8365</t>
+          <t>S00506048</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13567,12 +13571,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ ROSALES, VICENTE 4086 </t>
+          <t>TERRADA 1088</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13592,12 +13596,12 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Tensor</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -13607,17 +13611,17 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L154" t="n">
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>-58.491823</v>
+        <v>-58.472866</v>
       </c>
       <c r="N154" t="n">
-        <v>-34.587028</v>
+        <v>-34.620121</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -13631,7 +13635,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>NRA-M</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -13643,17 +13647,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>-748</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>CARACAS 3559</t>
+          <t>GUTENBERG 340</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -13673,12 +13677,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440623</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>inclinado base podrida</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -13693,17 +13697,17 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L155" t="n">
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>-58.487793</v>
+        <v>-58.471395</v>
       </c>
       <c r="N155" t="n">
-        <v>-34.590403</v>
+        <v>-34.592451</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -13717,7 +13721,7 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>PUE-?</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -13729,22 +13733,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>-750</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>CARACAS 3519</t>
+          <t>JURAMENTO 4979</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13759,12 +13763,12 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440599</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -13786,10 +13790,10 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>-58.487627</v>
+        <v>-58.481188</v>
       </c>
       <c r="N156" t="n">
-        <v>-34.590585</v>
+        <v>-34.577198</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -13803,7 +13807,7 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -13815,17 +13819,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>-753</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>VARELA, JOSE PEDRO 3545</t>
+          <t>CISNEROS, VIRREY 1610</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -13845,12 +13849,12 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440520</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -13865,17 +13869,17 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L157" t="n">
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>-58.502073</v>
+        <v>-58.469727</v>
       </c>
       <c r="N157" t="n">
-        <v>-34.601294</v>
+        <v>-34.612013</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -13889,7 +13893,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -13901,22 +13905,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>-754</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ANDONAEGUI 2383</t>
+          <t>PINO, VIRREY DEL 1503</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -13931,12 +13935,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440515</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -13958,14 +13962,14 @@
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>-58.489606</v>
+        <v>-58.442723</v>
       </c>
       <c r="N158" t="n">
-        <v>-34.57655</v>
+        <v>-34.56085</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -13975,7 +13979,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>ATH-C</t>
+          <t>BLO-A</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -13987,17 +13991,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>-755</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>CRAMER 4262</t>
+          <t>CONDE 4296</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -14017,12 +14021,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440509</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -14044,10 +14048,10 @@
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>-58.476168</v>
+        <v>-58.481187</v>
       </c>
       <c r="N159" t="n">
-        <v>-34.545546</v>
+        <v>-34.548301</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
@@ -14073,22 +14077,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>-757</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRAMER 4322 </t>
+          <t>FRAGATA PRES. SARMIENTO 1390</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14103,12 +14107,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440373</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>base corroida inclnada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -14130,14 +14134,14 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>-58.476454</v>
+        <v>-58.456778</v>
       </c>
       <c r="N160" t="n">
-        <v>-34.544962</v>
+        <v>-34.609187</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -14147,7 +14151,7 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>NRA-I</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -14159,22 +14163,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>-761</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SANTO TOME 3588</t>
+          <t>MOLDES 2901</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14189,12 +14193,12 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440341</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -14209,21 +14213,21 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L161" t="n">
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>-58.4947</v>
+        <v>-58.465305</v>
       </c>
       <c r="N161" t="n">
-        <v>-34.60925</v>
+        <v>-34.556794</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -14233,7 +14237,7 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>DEV-D</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -14245,22 +14249,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S00117686</t>
+          <t>S00506118</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2778</t>
+          <t>TERRERO 588</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14275,12 +14279,12 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440289</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>inlinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -14302,14 +14306,14 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>-58.432102</v>
+        <v>-58.459689</v>
       </c>
       <c r="N162" t="n">
-        <v>-34.574248</v>
+        <v>-34.620032</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -14319,7 +14323,7 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>NRA-D</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -14331,22 +14335,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S00506048</t>
+          <t>S01295589</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/24/2026</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>TERRADA 1088</t>
+          <t>CABILDO AV. 1008</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14361,17 +14365,17 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440653</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Tensor</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -14381,21 +14385,21 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L163" t="n">
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>-58.472866</v>
+        <v>-58.446714</v>
       </c>
       <c r="N163" t="n">
-        <v>-34.620121</v>
+        <v>-34.569183</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -14405,7 +14409,7 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>NRA-M</t>
+          <t>COG-C</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -14417,22 +14421,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>-748</t>
+          <t>S01406719</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/24/2026</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>GUTENBERG 340</t>
+          <t>3 DE FEBRERO 4481</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14447,12 +14451,12 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440639</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>inclinado base podrida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -14474,14 +14478,14 @@
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>-58.471395</v>
+        <v>-58.467166</v>
       </c>
       <c r="N164" t="n">
-        <v>-34.592451</v>
+        <v>-34.539469</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -14491,7 +14495,7 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>PUE-?</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -14503,17 +14507,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>-750</t>
+          <t>S00867165</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/26/2026</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>JURAMENTO 4979</t>
+          <t xml:space="preserve"> VALLEJOS 2250</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -14560,10 +14564,10 @@
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>-58.481188</v>
+        <v>-58.493418</v>
       </c>
       <c r="N165" t="n">
-        <v>-34.577198</v>
+        <v>-34.583307</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
@@ -14577,7 +14581,7 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>PUE-K</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -14589,22 +14593,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>-753</t>
+          <t xml:space="preserve">8392 </t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/26/2026</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>CISNEROS, VIRREY 1610</t>
+          <t xml:space="preserve">ESTADO PLURINACIONAL DE BOLIVIA 3526 </t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14639,17 +14643,17 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L166" t="n">
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>-58.469727</v>
+        <v>-58.491306</v>
       </c>
       <c r="N166" t="n">
-        <v>-34.612013</v>
+        <v>-34.592511</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
@@ -14663,7 +14667,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -14675,22 +14679,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>-754</t>
+          <t>8397</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/26/2026</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>PINO, VIRREY DEL 1503</t>
+          <t>TERRADA 3739</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14710,7 +14714,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -14732,14 +14736,14 @@
         <v>1</v>
       </c>
       <c r="M167" t="n">
-        <v>-58.442723</v>
+        <v>-58.494807</v>
       </c>
       <c r="N167" t="n">
-        <v>-34.56085</v>
+        <v>-34.592416</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -14749,7 +14753,7 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>BLO-A</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -14761,22 +14765,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>-755</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/26/2026</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>CONDE 4296</t>
+          <t xml:space="preserve"> TERRADA 3695 </t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14796,7 +14800,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -14818,14 +14822,14 @@
         <v>1</v>
       </c>
       <c r="M168" t="n">
-        <v>-58.481187</v>
+        <v>-58.494371</v>
       </c>
       <c r="N168" t="n">
-        <v>-34.548301</v>
+        <v>-34.592899</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -14835,7 +14839,7 @@
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
@@ -14847,22 +14851,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>-757</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/26/2026</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>FRAGATA PRES. SARMIENTO 1390</t>
+          <t>ARGERICH 3865</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14882,7 +14886,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -14904,10 +14908,10 @@
         <v>1</v>
       </c>
       <c r="M169" t="n">
-        <v>-58.456778</v>
+        <v>-58.497904</v>
       </c>
       <c r="N169" t="n">
-        <v>-34.609187</v>
+        <v>-34.593143</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
@@ -14921,7 +14925,7 @@
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>NRA-I</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -14933,22 +14937,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>-761</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/27/2026</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>MOLDES 2901</t>
+          <t>SIMBRON 5855</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -14968,7 +14972,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -14983,21 +14987,21 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L170" t="n">
         <v>1</v>
       </c>
       <c r="M170" t="n">
-        <v>-58.465305</v>
+        <v>-58.527129</v>
       </c>
       <c r="N170" t="n">
-        <v>-34.556794</v>
+        <v>-34.620962</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -15007,354 +15011,10 @@
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>DEV-G</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>-762</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>2/23/2026</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>ROSETTI 444</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>corroida inclinada</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L171" t="n">
-        <v>1</v>
-      </c>
-      <c r="M171" t="n">
-        <v>-58.450184</v>
-      </c>
-      <c r="N171" t="n">
-        <v>-34.584646</v>
-      </c>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>Colegiales</t>
-        </is>
-      </c>
-      <c r="P171" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>ATH-L</t>
-        </is>
-      </c>
-      <c r="R171" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>S00506118</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>2/23/2026</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>TERRERO 588</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L172" t="n">
-        <v>1</v>
-      </c>
-      <c r="M172" t="n">
-        <v>-58.459689</v>
-      </c>
-      <c r="N172" t="n">
-        <v>-34.620032</v>
-      </c>
-      <c r="O172" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P172" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>NRA-D</t>
-        </is>
-      </c>
-      <c r="R172" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>-763</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>2/24/2026</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Ricardo Gutiérrez 3702</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>Terminal</t>
-        </is>
-      </c>
-      <c r="L173" t="n">
-        <v>0</v>
-      </c>
-      <c r="M173" t="n">
-        <v>-58.504321</v>
-      </c>
-      <c r="N173" t="n">
-        <v>-34.602304</v>
-      </c>
-      <c r="O173" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="P173" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q173" t="inlineStr">
-        <is>
-          <t>DEV-C</t>
-        </is>
-      </c>
-      <c r="R173" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>S01295589</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>2/24/2026</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>CABILDO AV. 1008</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L174" t="n">
-        <v>1</v>
-      </c>
-      <c r="M174" t="n">
-        <v>-58.446714</v>
-      </c>
-      <c r="N174" t="n">
-        <v>-34.569183</v>
-      </c>
-      <c r="O174" t="inlineStr">
-        <is>
-          <t>Colegiales</t>
-        </is>
-      </c>
-      <c r="P174" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>COG-C</t>
-        </is>
-      </c>
-      <c r="R174" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_NEW.xlsx
+++ b/mapa_interactivo_NEW.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R170"/>
+  <dimension ref="A1:R175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1PUE</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
@@ -4209,22 +4209,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>9/22/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>VERA 1021</t>
+          <t>TRES ARROYOS 2911</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>809910087</t>
+          <t>810056868</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4266,24 +4266,24 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.442045</v>
+        <v>-58.476877</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.594303</v>
+        <v>-34.617525</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>NRA-M</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4295,22 +4295,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>9/29/2025</t>
+          <t>10/2/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TRES ARROYOS 2911</t>
+          <t>MOLDES 2688</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>810056868</t>
+          <t>810132881</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar o desmontar poste ver con inspector</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4352,14 +4352,14 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.476877</v>
+        <v>-58.463815</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.617525</v>
+        <v>-34.558663</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>NRA-M</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4381,22 +4381,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10/2/2025</t>
+          <t>10/6/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MOLDES 2688</t>
+          <t>MERCEDES 3774</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>810132881</t>
+          <t>810244452</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Cambiar o desmontar poste ver con inspector</t>
+          <t>Poste inclinado</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4431,21 +4431,21 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L47" t="n">
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.463815</v>
+        <v>-58.511139</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.558663</v>
+        <v>-34.602167</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>PUE-P</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4467,22 +4467,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10/6/2025</t>
+          <t>10/8/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MERCEDES 3774</t>
+          <t>ESTADO PLURINACIONAL DE BOLIVIA 3965</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4497,17 +4497,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>810244452</t>
+          <t>810259142</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Poste inclinado</t>
+          <t>Aplomar poste</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4524,10 +4524,10 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.511139</v>
+        <v>-58.493945</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.602167</v>
+        <v>-34.589471</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -4541,34 +4541,34 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>PUE-P</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1PUE</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10/8/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ESTADO PLURINACIONAL DE BOLIVIA 3965</t>
+          <t>BULGARIA 4387</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4583,17 +4583,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>810259142</t>
+          <t>810333040</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Aplomar poste</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4610,10 +4610,10 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.493945</v>
+        <v>-58.503223</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.589471</v>
+        <v>-34.590763</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>PUE-N</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4639,22 +4639,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BULGARIA 4387</t>
+          <t>MAGARIÑOS CERVANTES, A. 1382</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>810333040</t>
+          <t>810421913</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>cambiar esta doblada</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4689,17 +4689,17 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L50" t="n">
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.503223</v>
+        <v>-58.461</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.590763</v>
+        <v>-34.604483</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -4713,19 +4713,19 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>PUE-N</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PUE</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7582</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MAGARIÑOS CERVANTES, A. 1382</t>
+          <t>CIUDAD DE LA PAZ 3008</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>810421913</t>
+          <t>810421914</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>cambiar esta doblada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4782,14 +4782,14 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.461</v>
+        <v>-58.464818</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.604483</v>
+        <v>-34.554931</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4811,22 +4811,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/29/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 3008</t>
+          <t>QUITO 4180</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>810421914</t>
+          <t>810471618</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4868,24 +4868,24 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.464818</v>
+        <v>-58.425596</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.554931</v>
+        <v>-34.617038</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4897,22 +4897,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>7697</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>10/29/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>QUITO 4180</t>
+          <t>CONDE 4334</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>810471618</t>
+          <t>810487016</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Poste para cambiar o desmontar ver con inspector</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4947,31 +4947,31 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L53" t="n">
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.425596</v>
+        <v>-58.481509</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.617038</v>
+        <v>-34.547874</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4983,17 +4983,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7697</t>
+          <t>7806</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CONDE 4334</t>
+          <t>ROOSEVELT FRANKLIN D. 4665</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5013,12 +5013,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>810487016</t>
+          <t>810651339</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Poste para cambiar o desmontar ver con inspector</t>
+          <t>Poste inclinado</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5040,14 +5040,14 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.481509</v>
+        <v>-58.482196</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.547874</v>
+        <v>-34.570432</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>ATH-E</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5069,7 +5069,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5079,12 +5079,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ROOSEVELT FRANKLIN D. 4665</t>
+          <t>BURELA 1589</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>810651339</t>
+          <t>810651370</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Poste inclinado</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5119,21 +5119,21 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L55" t="n">
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.482196</v>
+        <v>-58.485747</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.570432</v>
+        <v>-34.58538</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>ATH-E</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5155,22 +5155,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7811</t>
+          <t>-673</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>11/17/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BURELA 1589</t>
+          <t>Bauness 2195</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>810651370</t>
+          <t>810787633</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Sacar columna con prioridad  Tensar linga en columna continua</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5212,10 +5212,10 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.485747</v>
+        <v>-58.485702</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.58538</v>
+        <v>-34.576702</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>ATH-C</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5241,7 +5241,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>-673</t>
+          <t>-674</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bauness 2195</t>
+          <t>Miller 3597</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>810787633</t>
+          <t>810787625</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sacar columna con prioridad  Tensar linga en columna continua</t>
+          <t>Aplomar/ enderezar columna y colocar rienda a pique</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5298,14 +5298,14 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.485702</v>
+        <v>-58.489898</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.576702</v>
+        <v>-34.560497</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>ATH-C</t>
+          <t>PUE-F</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5327,22 +5327,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>-674</t>
+          <t>S01089776</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Miller 3597</t>
+          <t>ARGERICH 3717</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>810787625</t>
+          <t>810804318</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Aplomar/ enderezar columna y colocar rienda a pique</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5384,14 +5384,14 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.489898</v>
+        <v>-58.497051</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.560497</v>
+        <v>-34.594109</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>PUE-F</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5413,22 +5413,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S01089776</t>
+          <t>-680</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ARGERICH 3717</t>
+          <t>UGARTE, MANUEL 1796</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>810804318</t>
+          <t>810820827</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5470,14 +5470,14 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.497051</v>
+        <v>-58.455584</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.594109</v>
+        <v>-34.553164</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>BLO-D</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5499,7 +5499,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>-680</t>
+          <t>S01126628</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>UGARTE, MANUEL 1796</t>
+          <t>RIVERA, PEDRO I., DR. 3385</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>810820827</t>
+          <t>810820813</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5556,14 +5556,14 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.455584</v>
+        <v>-58.47104</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.553164</v>
+        <v>-34.562322</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>BLO-D</t>
+          <t>COG-I</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5585,7 +5585,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S01126628</t>
+          <t>S01144183</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>RIVERA, PEDRO I., DR. 3385</t>
+          <t>DE LOS CONSTITUYENTES AV. 4318</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>810820813</t>
+          <t>810820640</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5642,14 +5642,14 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.47104</v>
+        <v>-58.490526</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.562322</v>
+        <v>-34.583417</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>COG-I</t>
+          <t>PUE-K</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5671,7 +5671,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S01144183</t>
+          <t>S01171313</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DE LOS CONSTITUYENTES AV. 4318</t>
+          <t xml:space="preserve"> LOPE DE VEGA AV. 3128 </t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>810820640</t>
+          <t>810820624</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5728,14 +5728,14 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.490526</v>
+        <v>-58.525417</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.583417</v>
+        <v>-34.613865</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>PUE-K</t>
+          <t>DEV-G</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5757,7 +5757,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S01171313</t>
+          <t xml:space="preserve">7870 </t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LOPE DE VEGA AV. 3128 </t>
+          <t>MAGARIÑOS CERVANTES, A. 4803</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>810820624</t>
+          <t>810820571</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada, tensor roto</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5807,17 +5807,17 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L63" t="n">
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.525417</v>
+        <v>-58.500609</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.613865</v>
+        <v>-34.626542</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>DEV-G</t>
+          <t>DEV-I</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5843,7 +5843,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870 </t>
+          <t xml:space="preserve">7867 </t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MAGARIÑOS CERVANTES, A. 4803</t>
+          <t>DIAZ, CESAR, GRAL. 1450</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>810820571</t>
+          <t>810820533</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>inclinada, tensor roto</t>
+          <t>muy inclinada</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5893,21 +5893,21 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L64" t="n">
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.500609</v>
+        <v>-58.461219</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.626542</v>
+        <v>-34.605928</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -5917,34 +5917,34 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>DEV-I</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>ARATO-26011.PO.1DEV</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">7867 </t>
+          <t>-684</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/26/2025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DIAZ, CESAR, GRAL. 1450</t>
+          <t>LONDRES 4280</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5959,12 +5959,13 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>810820533</t>
+          <t xml:space="preserve">01639693 </t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>muy inclinada</t>
+          <t xml:space="preserve">Columna 114 picada en base con receptor óptico propio, ver de colocar otra columna a la derecha asi poder traspasar el mismo receptor y Cdo propio.
+</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5974,22 +5975,22 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.461219</v>
+        <v>-58.48081</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.605928</v>
+        <v>-34.582354</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -6003,7 +6004,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6015,7 +6016,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>-684</t>
+          <t>7882</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6025,12 +6026,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LONDRES 4280</t>
+          <t xml:space="preserve">BELAUSTEGUI, LUIS, DR. 3490 </t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6045,13 +6046,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">01639693 </t>
+          <t>810862856</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Columna 114 picada en base con receptor óptico propio, ver de colocar otra columna a la derecha asi poder traspasar el mismo receptor y Cdo propio.
-</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6061,26 +6061,26 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L66" t="n">
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.48081</v>
+        <v>-58.484549</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.582354</v>
+        <v>-34.620529</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>DEV-K</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6102,7 +6102,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>7882</t>
+          <t xml:space="preserve">6436 </t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">BELAUSTEGUI, LUIS, DR. 3490 </t>
+          <t xml:space="preserve">ARIAS 4306 </t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>810862856</t>
+          <t>810862832</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6152,21 +6152,21 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L67" t="n">
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.484549</v>
+        <v>-58.49108</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.620529</v>
+        <v>-34.550102</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>DEV-K</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6188,17 +6188,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">6436 </t>
+          <t>-695</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>11/26/2025</t>
+          <t>12/3/2025</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARIAS 4306 </t>
+          <t>Estomba 2626</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6218,17 +6218,17 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>810862832</t>
+          <t>810984651</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>desmontar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6245,14 +6245,14 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.49108</v>
+        <v>-58.47538</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.550102</v>
+        <v>-34.566015</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>PUE-E</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6274,17 +6274,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>-695</t>
+          <t>-698</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12/3/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Estomba 2626</t>
+          <t>Franklin D. Roosevelt 5469</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6304,22 +6304,23 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>810984651</t>
+          <t xml:space="preserve">02019355 </t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>desmontar</t>
+          <t xml:space="preserve">corroida colocar columna pedir traspaso
+</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6331,14 +6332,14 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.47538</v>
+        <v>-58.491346</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.566015</v>
+        <v>-34.575773</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -6348,7 +6349,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>PUE-E</t>
+          <t>PUE-C</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6360,22 +6361,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>-698</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/16/2025</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Franklin D. Roosevelt 5469</t>
+          <t>GUTIERREZ, RICARDO 3351</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6390,38 +6391,37 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">02019355 </t>
+          <t>811198642</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">corroida colocar columna pedir traspaso
-</t>
+          <t>poste inclinado</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L70" t="n">
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.491346</v>
+        <v>-58.498056</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.575773</v>
+        <v>-34.601454</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>PUE-C</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6447,7 +6447,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GUTIERREZ, RICARDO 3351</t>
+          <t>DIAZ, CESAR, GRAL. 2053</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6477,17 +6477,17 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>811198642</t>
+          <t>811198627</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>poste inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6497,17 +6497,17 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L71" t="n">
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.498056</v>
+        <v>-58.468739</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.601454</v>
+        <v>-34.608957</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6533,22 +6533,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">7921 </t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>12/16/2025</t>
+          <t>12/17/2025</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>DIAZ, CESAR, GRAL. 2053</t>
+          <t>O'HIGGINS 4298</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>811198627</t>
+          <t>811198660</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>poste inclinado</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6583,21 +6583,21 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L72" t="n">
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.468739</v>
+        <v>-58.468046</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.608957</v>
+        <v>-34.541893</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6619,7 +6619,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">7921 </t>
+          <t>-706</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6629,12 +6629,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>O'HIGGINS 4298</t>
+          <t>PAZ, MARCOS 1505</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>811198660</t>
+          <t>811181316</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>poste inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6669,21 +6669,21 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L73" t="n">
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.468046</v>
+        <v>-58.500094</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.541893</v>
+        <v>-34.626115</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>DEV-I</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6705,22 +6705,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>-706</t>
+          <t>7938</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>12/17/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PAZ, MARCOS 1505</t>
+          <t xml:space="preserve"> O'HIGGINS 4321</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>811181316</t>
+          <t>811198748</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>poste inclinado</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6755,21 +6755,21 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L74" t="n">
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.500094</v>
+        <v>-58.468227</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.626115</v>
+        <v>-34.541506</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -6779,19 +6779,19 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>DEV-I</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>ARATO-26011.PO.1DEV</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve"> O'HIGGINS 4321</t>
+          <t xml:space="preserve">PLAZA, VICTORINO DE LA, DR. 1754 </t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>811198748</t>
+          <t>811198702</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>poste inclinado</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6841,17 +6841,17 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L75" t="n">
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.468227</v>
+        <v>-58.451448</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.541506</v>
+        <v>-34.547978</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>BLO-D</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -6877,22 +6877,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>S01028030</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLAZA, VICTORINO DE LA, DR. 1754 </t>
+          <t xml:space="preserve">MARTIN PESCADOR 2296 </t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>811198702</t>
+          <t>811198686</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6934,14 +6934,14 @@
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.451448</v>
+        <v>-58.493624</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.547978</v>
+        <v>-34.610119</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>BLO-D</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6963,7 +6963,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S01028030</t>
+          <t>S01215915</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6973,12 +6973,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTIN PESCADOR 2296 </t>
+          <t xml:space="preserve"> MOLDES 2906</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6993,12 +6993,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>811198686</t>
+          <t>811198663</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7013,21 +7013,21 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.493624</v>
+        <v>-58.465461</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.610119</v>
+        <v>-34.556738</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7049,22 +7049,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S01215915</t>
+          <t>-707</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/22/2025</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MOLDES 2906</t>
+          <t>Camargo 257</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>811198663</t>
+          <t>811238662</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7099,21 +7099,21 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L78" t="n">
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.465461</v>
+        <v>-58.438123</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.556738</v>
+        <v>-34.602541</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7135,22 +7135,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>-707</t>
+          <t xml:space="preserve">7969 </t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>12/22/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Camargo 257</t>
+          <t xml:space="preserve">HELGUERA 4770 </t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>811238662</t>
+          <t>811238727</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7192,10 +7192,10 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.438123</v>
+        <v>-58.505298</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.602541</v>
+        <v>-34.587467</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>PUE-N</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7221,17 +7221,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">7969 </t>
+          <t>8098</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">HELGUERA 4770 </t>
+          <t>RIVERA, PEDRO I., DR. 4448</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>811238727</t>
+          <t>811299428</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -7278,14 +7278,14 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.505298</v>
+        <v>-58.481135</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.587467</v>
+        <v>-34.568427</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -7295,19 +7295,19 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>PUE-N</t>
+          <t>PUE-E</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PUE</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t xml:space="preserve">7215 </t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7317,12 +7317,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>RIVERA, PEDRO I., DR. 4448</t>
+          <t xml:space="preserve">MAURE 3996 </t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7337,12 +7337,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>811299428</t>
+          <t>811299417</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7364,10 +7364,10 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.481135</v>
+        <v>-58.451687</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.568427</v>
+        <v>-34.586223</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>PUE-E</t>
+          <t>ATH-L</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7393,22 +7393,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">7215 </t>
+          <t>7987</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAURE 3996 </t>
+          <t>Terrada 2309</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>811299417</t>
+          <t>811299433</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -7443,21 +7443,21 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L82" t="n">
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.451687</v>
+        <v>-58.482084</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.586223</v>
+        <v>-34.608289</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>ATH-L</t>
+          <t>NRA-P</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7479,22 +7479,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>S01139199</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Terrada 2309</t>
+          <t>CRAMER 4320</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7509,12 +7509,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>811299433</t>
+          <t>811299481</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7529,21 +7529,21 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L83" t="n">
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.482084</v>
+        <v>-58.476445</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.608289</v>
+        <v>-34.544981</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>NRA-P</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -7565,17 +7565,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S01139199</t>
+          <t xml:space="preserve">8090 </t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>1/5/2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CRAMER 4320</t>
+          <t>Vedia 3506</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7595,17 +7595,17 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>811299481</t>
+          <t xml:space="preserve">02125435 </t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>desmonte y traspasar red</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -7622,10 +7622,10 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.476445</v>
+        <v>-58.486704</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.544981</v>
+        <v>-34.544613</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -7651,22 +7651,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8090 </t>
+          <t>-717</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1/5/2026</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Vedia 3506</t>
+          <t>Ibera 2218</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7681,17 +7681,17 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">02125435 </t>
+          <t>811453864</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>desmonte y traspasar red</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -7708,10 +7708,10 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.486704</v>
+        <v>-58.46286</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.544613</v>
+        <v>-34.552702</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>BLO-R</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -7737,7 +7737,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>-717</t>
+          <t xml:space="preserve">8173 </t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ibera 2218</t>
+          <t>SUCRE, ANTONIO JOSE DE, MCAL. 1563</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>811453864</t>
+          <t xml:space="preserve">02313712 </t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -7794,10 +7794,10 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.46286</v>
+        <v>-58.446858</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.552702</v>
+        <v>-34.559026</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>BLO-R</t>
+          <t>BLO-A</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7823,7 +7823,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">8173 </t>
+          <t>-719</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7833,7 +7833,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SUCRE, ANTONIO JOSE DE, MCAL. 1563</t>
+          <t>MENDOZA 2160</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7853,12 +7853,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">02313712 </t>
+          <t>811453860</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -7880,10 +7880,10 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.446858</v>
+        <v>-58.455182</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.559026</v>
+        <v>-34.559761</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>BLO-A</t>
+          <t>BLO-O</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7909,22 +7909,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>-719</t>
+          <t>S01180016</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MENDOZA 2160</t>
+          <t>FITZ ROY 1730</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>811453860</t>
+          <t>811454223</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7966,24 +7966,24 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.455182</v>
+        <v>-58.436051</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.559761</v>
+        <v>-34.583855</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>BLO-O</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7995,7 +7995,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S01180016</t>
+          <t>S01180023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FITZ ROY 1730</t>
+          <t>VEGA, NICETO, CNEL. AV. 5420</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>811454223</t>
+          <t>811454198</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8052,10 +8052,10 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.436051</v>
+        <v>-58.437628</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.583855</v>
+        <v>-34.587953</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>ATH-?</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8081,7 +8081,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S01180023</t>
+          <t>S01180086</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>VEGA, NICETO, CNEL. AV. 5420</t>
+          <t>BONPLAND 1471</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>811454198</t>
+          <t>811454194</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8138,10 +8138,10 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.437628</v>
+        <v>-58.439513</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.587953</v>
+        <v>-34.585314</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>ATH-?</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8167,7 +8167,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S01180086</t>
+          <t>S01200482</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BONPLAND 1471</t>
+          <t>GONZALEZ, ELPIDIO 2749</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>811454194</t>
+          <t>811454117</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>quebrada</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8217,31 +8217,31 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L91" t="n">
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.439513</v>
+        <v>-58.481266</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.585314</v>
+        <v>-34.608522</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>NRA-O</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8253,7 +8253,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S01200482</t>
+          <t>S01204059</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GONZALEZ, ELPIDIO 2749</t>
+          <t>BUFANO, ALFREDO R. 2580</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>811454117</t>
+          <t>811454109</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>quebrada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L92" t="n">
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.481266</v>
+        <v>-58.478411</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.608522</v>
+        <v>-34.6039</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>NRA-O</t>
+          <t>NRA-P</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8339,7 +8339,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S01204059</t>
+          <t>S01220047</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BUFANO, ALFREDO R. 2580</t>
+          <t>MAURE 2958</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>811454109</t>
+          <t>811454097</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -8396,24 +8396,24 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.478411</v>
+        <v>-58.446339</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.6039</v>
+        <v>-34.576306</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>NRA-P</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8425,7 +8425,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S01220047</t>
+          <t>S01306211</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MAURE 2958</t>
+          <t>WASHINGTON 3943</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>811454097</t>
+          <t>811453965</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -8475,31 +8475,31 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L94" t="n">
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.446339</v>
+        <v>-58.48286</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.576306</v>
+        <v>-34.55278</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8511,7 +8511,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S01306211</t>
+          <t>S01313361</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>WASHINGTON 3943</t>
+          <t>CABILDO AV. 805</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>811453965</t>
+          <t>811453963</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -8568,14 +8568,14 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.48286</v>
+        <v>-58.444955</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.55278</v>
+        <v>-34.569791</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>COG-C</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8597,7 +8597,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S01313361</t>
+          <t>S01389798</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CABILDO AV. 805</t>
+          <t>GUALEGUAYCHU 4682</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>811453963</t>
+          <t>811453943</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -8647,21 +8647,21 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L96" t="n">
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.444955</v>
+        <v>-58.518214</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.569791</v>
+        <v>-34.596516</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>COG-C</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8683,7 +8683,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S01389798</t>
+          <t>S01384321</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8693,12 +8693,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU 4682</t>
+          <t>AZURDUY JUANA 2685</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>811453943</t>
+          <t>811453930</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -8740,14 +8740,14 @@
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.518214</v>
+        <v>-58.469341</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.596516</v>
+        <v>-34.552269</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -8757,19 +8757,19 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1PUE</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S01384321</t>
+          <t>S01384337</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AZURDUY JUANA 2685</t>
+          <t xml:space="preserve">MOLDES 3502 </t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>811453930</t>
+          <t>811453925</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base quebrada</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -8819,17 +8819,17 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L98" t="n">
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.469341</v>
+        <v>-58.470282</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.552269</v>
+        <v>-34.551553</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>COG-M</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8855,7 +8855,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S01384337</t>
+          <t>S01392303</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOLDES 3502 </t>
+          <t>Moldes 1999</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>811453925</t>
+          <t>811453918</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>base quebrada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -8905,21 +8905,21 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L99" t="n">
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.470282</v>
+        <v>-58.458535</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.551553</v>
+        <v>-34.564674</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>COG-M</t>
+          <t>COG-G</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8941,22 +8941,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S01392303</t>
+          <t>8095</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Moldes 1999</t>
+          <t>MANZANARES 3853</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>811453918</t>
+          <t>811454324</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -8998,14 +8998,14 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.458535</v>
+        <v>-58.482488</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.564674</v>
+        <v>-34.554114</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>COG-G</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9027,7 +9027,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>8094</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MANZANARES 3853</t>
+          <t xml:space="preserve">GARCIA DEL RIO 3789 </t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -9057,12 +9057,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>811454324</t>
+          <t>811454305</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9077,17 +9077,17 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L101" t="n">
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.482488</v>
+        <v>-58.482473</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.554114</v>
+        <v>-34.553018</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -9113,22 +9113,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA DEL RIO 3789 </t>
+          <t>Nogoya 3644</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>811454305</t>
+          <t>811454515</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9163,21 +9163,21 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L102" t="n">
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.482473</v>
+        <v>-58.497751</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.553018</v>
+        <v>-34.606408</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9199,7 +9199,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>8186</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9209,7 +9209,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Nogoya 3644</t>
+          <t>Pje. Manuel Sola 4440</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>811454515</t>
+          <t>811454508</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9256,10 +9256,10 @@
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.497751</v>
+        <v>-58.507954</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.606408</v>
+        <v>-34.610808</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>DEV-D</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9285,7 +9285,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>8316</t>
+          <t xml:space="preserve">8112 </t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Pje. Manuel Sola 4440</t>
+          <t>MANZANARES 2073</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>811454508</t>
+          <t>811454483</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -9342,14 +9342,14 @@
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.507954</v>
+        <v>-58.465953</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.610808</v>
+        <v>-34.545637</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>DEV-D</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9371,7 +9371,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">8112 </t>
+          <t xml:space="preserve">8114 </t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MANZANARES 2073</t>
+          <t>ARGERICH 5774</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9401,12 +9401,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>811454483</t>
+          <t>811454454</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -9421,21 +9421,21 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L105" t="n">
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.465953</v>
+        <v>-58.511147</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.545637</v>
+        <v>-34.578665</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>PUE-J</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9457,22 +9457,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">8114 </t>
+          <t>8129</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/15/2026</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ARGERICH 5774</t>
+          <t>ESTOMBA 212</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>811454454</t>
+          <t>811454532</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -9507,21 +9507,21 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L106" t="n">
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.511147</v>
+        <v>-58.469045</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.578665</v>
+        <v>-34.588525</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>PUE-J</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9543,22 +9543,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>-731</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1/15/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ESTOMBA 212</t>
+          <t>Ruiz Huidobro 3643</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9573,14 +9573,10 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>811454532</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
+          <t>811498060</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -9593,21 +9589,21 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L107" t="n">
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.469045</v>
+        <v>-58.484505</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.588525</v>
+        <v>-34.549798</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -9617,7 +9613,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9629,7 +9625,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>-731</t>
+          <t>-732</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9639,12 +9635,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ruiz Huidobro 3643</t>
+          <t xml:space="preserve"> Valentin Alsina 1685</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9657,12 +9653,12 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>811498060</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>inclinada</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -9675,31 +9671,27 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L108" t="n">
         <v>1</v>
       </c>
-      <c r="M108" t="n">
-        <v>-58.484505</v>
-      </c>
-      <c r="N108" t="n">
-        <v>-34.549798</v>
-      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>No ubicado</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>No clasificado, consultar con mantenimiento</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>No ubicado</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9711,7 +9703,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>-732</t>
+          <t>-733</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9721,12 +9713,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Valentin Alsina 1685</t>
+          <t xml:space="preserve"> Dorrego 2755</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9739,10 +9731,14 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>811498056</t>
+        </is>
+      </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -9763,21 +9759,25 @@
       <c r="L109" t="n">
         <v>1</v>
       </c>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
+      <c r="M109" t="n">
+        <v>-58.432319</v>
+      </c>
+      <c r="N109" t="n">
+        <v>-34.574385</v>
+      </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>No ubicado</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>No clasificado, consultar con mantenimiento</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>No ubicado</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -9789,7 +9789,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>-733</t>
+          <t xml:space="preserve">6428 </t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9799,12 +9799,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dorrego 2755</t>
+          <t>MONROE 4070</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>811498056</t>
+          <t>811498053</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -9846,24 +9846,24 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.432319</v>
+        <v>-58.475842</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.574385</v>
+        <v>-34.568215</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>ATH-J</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9875,7 +9875,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">6428 </t>
+          <t>7270</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9885,7 +9885,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MONROE 4070</t>
+          <t>AZURDUY JUANA 3630</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9905,12 +9905,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>811498053</t>
+          <t>811498050</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -9932,14 +9932,14 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.475842</v>
+        <v>-58.477583</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.568215</v>
+        <v>-34.5569</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>ATH-J</t>
+          <t>COG-N</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9961,22 +9961,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>S01215930</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/20/2026</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AZURDUY JUANA 3630</t>
+          <t>UGARTE, MANUEL 2750</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9991,12 +9991,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>811498050</t>
+          <t>811498072</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10018,10 +10018,10 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.477583</v>
+        <v>-58.465042</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.5569</v>
+        <v>-34.557947</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>COG-N</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10047,22 +10047,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S01215930</t>
+          <t>8181</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1/20/2026</t>
+          <t>1/22/2026</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>UGARTE, MANUEL 2750</t>
+          <t xml:space="preserve">FREIRE, RAMON, CAP. GRAL. 4748 </t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>811498072</t>
+          <t>811498074</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada base quebrada</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10097,17 +10097,17 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.465042</v>
+        <v>-58.482951</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.557947</v>
+        <v>-34.544273</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10133,17 +10133,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>8181</t>
+          <t>S01318042</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1/22/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREIRE, RAMON, CAP. GRAL. 4748 </t>
+          <t>UGARTE, MANUEL 3815</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>811498074</t>
+          <t>811626754</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>inclinada base quebrada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -10183,17 +10183,17 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L114" t="n">
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.482951</v>
+        <v>-58.476138</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.544273</v>
+        <v>-34.563825</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>COG-N</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10219,7 +10219,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S01318042</t>
+          <t>S01397288</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10229,12 +10229,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>UGARTE, MANUEL 3815</t>
+          <t xml:space="preserve">MOLDES 1918 </t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -10249,41 +10249,29 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>811626754</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>base corroida</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
+          <t>inclinadaq</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="n">
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.476138</v>
+        <v>-58.458035</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.563825</v>
+        <v>-34.565387</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -10293,7 +10281,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>COG-N</t>
+          <t>COG-G</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10305,7 +10293,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S01397288</t>
+          <t>S01397364</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10315,7 +10303,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOLDES 1918 </t>
+          <t>AVILES, VIRREY 3008</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -10335,25 +10323,37 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811626732</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>inclinadaq</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
+          <t>corroida</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
       <c r="L116" t="n">
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.458035</v>
+        <v>-58.457207</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.565387</v>
+        <v>-34.571602</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>COG-G</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10379,22 +10379,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S01397364</t>
+          <t>-740</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>AVILES, VIRREY 3008</t>
+          <t>Gutemberg 350</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>811626732</t>
+          <t>811626800</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -10429,21 +10429,21 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L117" t="n">
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.457207</v>
+        <v>-58.471803</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.571602</v>
+        <v>-34.592463</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -10453,7 +10453,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>PUE-?</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10465,7 +10465,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>-740</t>
+          <t>-741</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10475,7 +10475,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Gutemberg 350</t>
+          <t>Gutemberg 320</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -10495,12 +10495,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>811626800</t>
+          <t>811626794</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>mal estado</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -10522,10 +10522,10 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.471803</v>
+        <v>-58.470581</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.592463</v>
+        <v>-34.592428</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>-741</t>
+          <t>-742</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Gutemberg 320</t>
+          <t>BLANCO ENCALADA 899</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -10581,17 +10581,17 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>811626794</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>mal estado</t>
+          <t>desmonte</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -10608,14 +10608,14 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.470581</v>
+        <v>-58.443393</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.592428</v>
+        <v>-34.549873</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -10625,7 +10625,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>PUE-?</t>
+          <t>BLO-B</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10637,7 +10637,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>-742</t>
+          <t>-743</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10647,12 +10647,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>BLANCO ENCALADA 899</t>
+          <t>Giribone 1411</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -10667,17 +10667,17 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811626791</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>desmonte</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -10687,21 +10687,21 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L120" t="n">
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.443393</v>
+        <v>-58.462095</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.549873</v>
+        <v>-34.579585</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>BLO-B</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10723,22 +10723,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>-743</t>
+          <t>S01396837</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Giribone 1411</t>
+          <t>DEHEZA 3622</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -10753,12 +10753,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>811626791</t>
+          <t>811626963</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado base quebrada</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -10773,21 +10773,21 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L121" t="n">
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.462095</v>
+        <v>-58.485735</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.579585</v>
+        <v>-34.546249</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10809,7 +10809,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S01396837</t>
+          <t>S01406731</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10819,12 +10819,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>DEHEZA 3622</t>
+          <t xml:space="preserve"> CORREA 1807</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -10839,12 +10839,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>811626963</t>
+          <t>811626953</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>inclinado base quebrada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -10859,17 +10859,17 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L122" t="n">
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.485735</v>
+        <v>-58.466595</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.546249</v>
+        <v>-34.54099</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10895,7 +10895,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S01406731</t>
+          <t>S01406737</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CORREA 1807</t>
+          <t>GRECIA 4281</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10925,12 +10925,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>811626953</t>
+          <t>811626921</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inlinada</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -10952,10 +10952,10 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.466595</v>
+        <v>-58.466965</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.54099</v>
+        <v>-34.541488</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
@@ -10981,17 +10981,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S01406737</t>
+          <t>S01406812</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>GRECIA 4281</t>
+          <t xml:space="preserve">VUELTA DE OBLIGADO 3201 </t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -11011,12 +11011,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>811626921</t>
+          <t>811626783</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>inlinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -11038,10 +11038,10 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.466965</v>
+        <v>-58.464784</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.541488</v>
+        <v>-34.551419</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>BLO-R</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11067,17 +11067,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S01406812</t>
+          <t>S00019326</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">VUELTA DE OBLIGADO 3201 </t>
+          <t>OLLEROS 3050</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>811626783</t>
+          <t>811627002</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -11124,24 +11124,24 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.464784</v>
+        <v>-58.447708</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.551419</v>
+        <v>-34.577055</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>BLO-R</t>
+          <t>ATH-P</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11153,7 +11153,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S00019326</t>
+          <t>S00021988</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>OLLEROS 3050</t>
+          <t>ALVAREZ THOMAS AV. 1115</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11183,12 +11183,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>811627002</t>
+          <t>811626996</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -11210,24 +11210,24 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.447708</v>
+        <v>-58.457565</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.577055</v>
+        <v>-34.578379</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>ATH-P</t>
+          <t>ATH-O</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11239,7 +11239,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S00021988</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11249,12 +11249,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ALVAREZ THOMAS AV. 1115</t>
+          <t xml:space="preserve">SANABRIA 2386 </t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11269,12 +11269,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>811626996</t>
+          <t>811626991</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -11289,21 +11289,21 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L127" t="n">
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.457565</v>
+        <v>-58.503452</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.578379</v>
+        <v>-34.614501</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -11313,7 +11313,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>ATH-O</t>
+          <t>DEV-D</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11325,7 +11325,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>S01450787</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11335,12 +11335,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANABRIA 2386 </t>
+          <t>HERNANDEZ, JOSE 2110</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11355,12 +11355,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>811626991</t>
+          <t>811626983</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -11382,14 +11382,14 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.503452</v>
+        <v>-58.450727</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.614501</v>
+        <v>-34.56425</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>DEV-D</t>
+          <t>BLO-M</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11411,22 +11411,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S01450787</t>
+          <t>-745</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>HERNANDEZ, JOSE 2110</t>
+          <t>Gamarra 1546</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>811626983</t>
+          <t>811627113</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -11461,21 +11461,21 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L129" t="n">
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.450727</v>
+        <v>-58.477231</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.56425</v>
+        <v>-34.58242</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>BLO-M</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11497,7 +11497,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>-745</t>
+          <t>S00036520</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Gamarra 1546</t>
+          <t>SEGUROLA AV. 856</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -11527,12 +11527,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>811627113</t>
+          <t>811627070</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>corroidaq</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -11554,14 +11554,14 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.477231</v>
+        <v>-58.490765</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.58242</v>
+        <v>-34.627337</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>DEV-I</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11583,7 +11583,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S00036520</t>
+          <t xml:space="preserve">900009468810 </t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SEGUROLA AV. 856</t>
+          <t xml:space="preserve">CUENCA 3033 </t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>811627070</t>
+          <t>811627041</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>corroidaq</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -11633,17 +11633,17 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L131" t="n">
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.490765</v>
+        <v>-58.494814</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.627337</v>
+        <v>-34.601905</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -11657,34 +11657,34 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>DEV-I</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>ARATO-26011.PO.1DEV</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">900009468810 </t>
+          <t>S01337226</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/6/2026</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUENCA 3033 </t>
+          <t>MOLDES 3055</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>811627041</t>
+          <t>811627125</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -11719,21 +11719,21 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L132" t="n">
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.494814</v>
+        <v>-58.466692</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.601905</v>
+        <v>-34.555283</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11755,7 +11755,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S01337226</t>
+          <t>S01375612</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11765,7 +11765,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MOLDES 3055</t>
+          <t>LACROZE, FEDERICO AV. 2834</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -11785,12 +11785,12 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>811627125</t>
+          <t>811627118</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroidaq</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -11812,24 +11812,24 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.466692</v>
+        <v>-58.447177</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.555283</v>
+        <v>-34.574158</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>ATH-P</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11841,22 +11841,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S01375612</t>
+          <t xml:space="preserve">8301 </t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2/6/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>LACROZE, FEDERICO AV. 2834</t>
+          <t>ARENGREEN 1584</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -11871,12 +11871,12 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>811627118</t>
+          <t>812440072</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>corroidaq</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -11891,21 +11891,21 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L134" t="n">
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.447177</v>
+        <v>-58.453265</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.574158</v>
+        <v>-34.615073</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>ATH-P</t>
+          <t>NRA-I</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11927,7 +11927,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">8301 </t>
+          <t>8322</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11937,12 +11937,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ARENGREEN 1584</t>
+          <t>ARENAL, CONCEPCION 3814</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -11957,12 +11957,12 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>812440072</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -11972,36 +11972,36 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L135" t="n">
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.453265</v>
+        <v>-58.447805</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.615073</v>
+        <v>-34.587018</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>NRA-I</t>
+          <t>ATH-L</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -12013,7 +12013,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12023,7 +12023,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ARENAL, CONCEPCION 3814</t>
+          <t>WARNES AV. 2239</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440018</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -12070,14 +12070,14 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.447805</v>
+        <v>-58.467815</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.587018</v>
+        <v>-34.596225</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -12087,7 +12087,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>ATH-L</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12099,7 +12099,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>WARNES AV. 2239</t>
+          <t>PAZ SOLDAN 4991</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -12129,12 +12129,12 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>812440018</t>
+          <t>812439995</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base quebrada</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -12149,17 +12149,17 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.467815</v>
+        <v>-58.468466</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.596225</v>
+        <v>-34.594154</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12195,12 +12195,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>PAZ SOLDAN 4991</t>
+          <t xml:space="preserve"> GUALEGUAYCHU 4754</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12215,12 +12215,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>812439995</t>
+          <t>812439956</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>base quebrada</t>
+          <t>inclinado, base quebrada</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -12242,10 +12242,10 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.468466</v>
+        <v>-58.518803</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.594154</v>
+        <v>-34.595866</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12271,7 +12271,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12281,12 +12281,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GUALEGUAYCHU 4754</t>
+          <t>BLANCO ENCALADA 823</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12301,12 +12301,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>812439956</t>
+          <t>812439941</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>inclinado, base quebrada</t>
+          <t>inclinado base quebrada</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -12328,14 +12328,14 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.518803</v>
+        <v>-58.442692</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.595866</v>
+        <v>-34.549454</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -12345,34 +12345,34 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>BLO-B</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1PUE</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>BLANCO ENCALADA 823</t>
+          <t>DORREGO AV. 2699</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12387,12 +12387,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>812439941</t>
+          <t>812440089</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>inclinado base quebrada</t>
+          <t>base corrodia</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -12407,31 +12407,31 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.442692</v>
+        <v>-58.432807</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.549454</v>
+        <v>-34.574343</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>BLO-B</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12443,7 +12443,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12453,12 +12453,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2699</t>
+          <t>ASUNCION 2373</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12473,12 +12473,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>812440089</t>
+          <t>812440083</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>base corrodia</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -12500,24 +12500,24 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.432807</v>
+        <v>-58.490913</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.574343</v>
+        <v>-34.588328</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12529,17 +12529,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ASUNCION 2373</t>
+          <t xml:space="preserve">ZAMUDIO 3884 </t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -12559,12 +12559,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>812440083</t>
+          <t>812440257</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -12586,10 +12586,10 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.490913</v>
+        <v>-58.491114</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.588328</v>
+        <v>-34.588808</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>8362</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAMUDIO 3884 </t>
+          <t>BEIRO, FRANCISCO AV. 2435</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -12645,7 +12645,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>812440257</t>
+          <t>812440250</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -12672,10 +12672,10 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.491114</v>
+        <v>-58.488914</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.588808</v>
+        <v>-34.59164</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>8365</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>BEIRO, FRANCISCO AV. 2435</t>
+          <t xml:space="preserve">PEREZ ROSALES, VICENTE 4086 </t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>812440250</t>
+          <t>812440239</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -12758,10 +12758,10 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.488914</v>
+        <v>-58.491823</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.59164</v>
+        <v>-34.587028</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>8365</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ ROSALES, VICENTE 4086 </t>
+          <t>CARACAS 3559</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -12817,12 +12817,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>812440239</t>
+          <t>812440223</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -12844,10 +12844,10 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.491823</v>
+        <v>-58.487793</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.587028</v>
+        <v>-34.590403</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8368</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CARACAS 3559</t>
+          <t>CARACAS 3519</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12903,12 +12903,12 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>812440223</t>
+          <t>812503552</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -12930,10 +12930,10 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.487793</v>
+        <v>-58.487627</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.590403</v>
+        <v>-34.590585</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12969,12 +12969,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>CARACAS 3519</t>
+          <t>VARELA, JOSE PEDRO 3545</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -12989,12 +12989,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440219</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -13009,17 +13009,17 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L147" t="n">
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.487627</v>
+        <v>-58.502073</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.590585</v>
+        <v>-34.601294</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -13045,7 +13045,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>VARELA, JOSE PEDRO 3545</t>
+          <t>ANDONAEGUI 2383</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>812440219</t>
+          <t>812440211</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -13095,17 +13095,17 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L148" t="n">
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.502073</v>
+        <v>-58.489606</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.601294</v>
+        <v>-34.57655</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>ATH-C</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13131,7 +13131,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ANDONAEGUI 2383</t>
+          <t>CRAMER 4262</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>812440211</t>
+          <t>812440206</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -13188,14 +13188,14 @@
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.489606</v>
+        <v>-58.476168</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.57655</v>
+        <v>-34.545546</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -13205,7 +13205,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>ATH-C</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13217,7 +13217,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13227,7 +13227,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>CRAMER 4262</t>
+          <t xml:space="preserve">CRAMER 4322 </t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>812440206</t>
+          <t>812440204</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>base corroida inclnada</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -13274,10 +13274,10 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.476168</v>
+        <v>-58.476454</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.545546</v>
+        <v>-34.544962</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8382</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13313,12 +13313,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRAMER 4322 </t>
+          <t>SANTO TOME 3588</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13333,12 +13333,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>812440204</t>
+          <t>812440197</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>base corroida inclnada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -13353,21 +13353,21 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L151" t="n">
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>-58.476454</v>
+        <v>-58.4947</v>
       </c>
       <c r="N151" t="n">
-        <v>-34.544962</v>
+        <v>-34.60925</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -13377,7 +13377,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>DEV-D</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -13389,7 +13389,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>S00117686</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13399,12 +13399,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SANTO TOME 3588</t>
+          <t>DORREGO AV. 2778</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>812440197</t>
+          <t>812440183</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inlinada</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -13439,31 +13439,31 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L152" t="n">
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.4947</v>
+        <v>-58.432102</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.60925</v>
+        <v>-34.574248</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>DEV-D</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -13475,7 +13475,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S00117686</t>
+          <t>S00506048</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2778</t>
+          <t>TERRADA 1088</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13505,17 +13505,17 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>812440183</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>inlinada</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Tensor</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -13525,31 +13525,31 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L153" t="n">
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>-58.432102</v>
+        <v>-58.472866</v>
       </c>
       <c r="N153" t="n">
-        <v>-34.574248</v>
+        <v>-34.620121</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>NRA-M</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -13561,22 +13561,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S00506048</t>
+          <t>-748</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>TERRADA 1088</t>
+          <t>GUTENBERG 340</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13591,17 +13591,17 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440623</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>inclinado base podrida</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Tensor</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -13611,17 +13611,17 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L154" t="n">
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>-58.472866</v>
+        <v>-58.471395</v>
       </c>
       <c r="N154" t="n">
-        <v>-34.620121</v>
+        <v>-34.592451</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>NRA-M</t>
+          <t>PUE-?</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -13647,7 +13647,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>-748</t>
+          <t>-750</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13657,12 +13657,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>GUTENBERG 340</t>
+          <t>JURAMENTO 4979</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13677,12 +13677,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>812440623</t>
+          <t>812440599</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>inclinado base podrida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -13697,17 +13697,17 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L155" t="n">
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>-58.471395</v>
+        <v>-58.481188</v>
       </c>
       <c r="N155" t="n">
-        <v>-34.592451</v>
+        <v>-34.577198</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>PUE-?</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -13733,7 +13733,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>-750</t>
+          <t>-753</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13743,12 +13743,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>JURAMENTO 4979</t>
+          <t>CISNEROS, VIRREY 1610</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>812440599</t>
+          <t>812440520</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -13783,17 +13783,17 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L156" t="n">
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>-58.481188</v>
+        <v>-58.469727</v>
       </c>
       <c r="N156" t="n">
-        <v>-34.577198</v>
+        <v>-34.612013</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -13819,7 +13819,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>-753</t>
+          <t>-754</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13829,12 +13829,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>CISNEROS, VIRREY 1610</t>
+          <t>PINO, VIRREY DEL 1503</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>812440520</t>
+          <t>812440515</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -13869,21 +13869,21 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L157" t="n">
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>-58.469727</v>
+        <v>-58.442723</v>
       </c>
       <c r="N157" t="n">
-        <v>-34.612013</v>
+        <v>-34.56085</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>BLO-A</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -13905,7 +13905,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>-754</t>
+          <t>-755</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13915,12 +13915,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PINO, VIRREY DEL 1503</t>
+          <t>CONDE 4296</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -13935,12 +13935,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>812440515</t>
+          <t>812440509</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -13962,10 +13962,10 @@
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>-58.442723</v>
+        <v>-58.481187</v>
       </c>
       <c r="N158" t="n">
-        <v>-34.56085</v>
+        <v>-34.548301</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>BLO-A</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -13991,7 +13991,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>-755</t>
+          <t>-757</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>CONDE 4296</t>
+          <t>FRAGATA PRES. SARMIENTO 1390</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14021,12 +14021,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>812440509</t>
+          <t>812440373</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -14048,14 +14048,14 @@
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>-58.481187</v>
+        <v>-58.456778</v>
       </c>
       <c r="N159" t="n">
-        <v>-34.548301</v>
+        <v>-34.609187</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>NRA-I</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -14077,7 +14077,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>-757</t>
+          <t>-761</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14087,12 +14087,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>FRAGATA PRES. SARMIENTO 1390</t>
+          <t>MOLDES 2901</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14107,7 +14107,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>812440373</t>
+          <t>812440341</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -14134,14 +14134,14 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>-58.456778</v>
+        <v>-58.465305</v>
       </c>
       <c r="N160" t="n">
-        <v>-34.609187</v>
+        <v>-34.556794</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>NRA-I</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -14163,7 +14163,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>-761</t>
+          <t>S00506118</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>MOLDES 2901</t>
+          <t>TERRERO 588</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>812440341</t>
+          <t>812440289</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -14220,24 +14220,24 @@
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>-58.465305</v>
+        <v>-58.459689</v>
       </c>
       <c r="N161" t="n">
-        <v>-34.556794</v>
+        <v>-34.620032</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>NRA-D</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -14249,22 +14249,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S00506118</t>
+          <t>S01295589</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/24/2026</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>TERRERO 588</t>
+          <t>CABILDO AV. 1008</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14279,7 +14279,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>812440289</t>
+          <t>812440653</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -14306,24 +14306,24 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>-58.459689</v>
+        <v>-58.446714</v>
       </c>
       <c r="N162" t="n">
-        <v>-34.620032</v>
+        <v>-34.569183</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>NRA-D</t>
+          <t>COG-C</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -14335,7 +14335,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S01295589</t>
+          <t>-764</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>CABILDO AV. 1008</t>
+          <t>CASEROS AV. 3547</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14365,12 +14365,12 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>812440653</t>
+          <t>812440642</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>colocar en 3543</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -14392,24 +14392,24 @@
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>-58.446714</v>
+        <v>-58.41515</v>
       </c>
       <c r="N163" t="n">
-        <v>-34.569183</v>
+        <v>-34.638705</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>COG-C</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812503628</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -14623,7 +14623,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812503597</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -14709,7 +14709,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812503610</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -14795,7 +14795,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812503605</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812503589</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -14967,7 +14967,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812503637</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -15015,6 +15015,436 @@
         </is>
       </c>
       <c r="R170" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>-765</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>3/2/2026</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>AVALOS 180</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>812503657</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L171" t="n">
+        <v>1</v>
+      </c>
+      <c r="M171" t="n">
+        <v>-58.465874</v>
+      </c>
+      <c r="N171" t="n">
+        <v>-34.594613</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>ATH-F</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>-766</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>3/2/2026</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>CONDE 3080</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>812503654</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
+        <v>1</v>
+      </c>
+      <c r="M172" t="n">
+        <v>-58.47322</v>
+      </c>
+      <c r="N172" t="n">
+        <v>-34.558645</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>COG-L</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>-768</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>3/2/2026</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>CONCORDIA 3581</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>812503649</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" t="n">
+        <v>-58.502724</v>
+      </c>
+      <c r="N173" t="n">
+        <v>-34.599311</v>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>PUE-B</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>-767</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>3/2/2026</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>CONCORDIA 3525</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>812503647</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
+      <c r="L174" t="n">
+        <v>1</v>
+      </c>
+      <c r="M174" t="n">
+        <v>-58.502389</v>
+      </c>
+      <c r="N174" t="n">
+        <v>-34.599679</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>PUE-B</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>-769</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>3/2/2026</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>RIVERA, PEDRO I., DR. 2734</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>corroida</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Nodo/Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L175" t="n">
+        <v>1</v>
+      </c>
+      <c r="M175" t="n">
+        <v>-58.464354</v>
+      </c>
+      <c r="N175" t="n">
+        <v>-34.5587</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>COG-K</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_NEW.xlsx
+++ b/mapa_interactivo_NEW.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R160"/>
+  <dimension ref="A1:R158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3951,22 +3951,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>7582</t>
+          <t>7508</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/14/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MAGARIÑOS CERVANTES, A. 1382</t>
+          <t>11 DE SEPTIEMBRE DE 1888 3988</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>810421913</t>
+          <t>00995927</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>cambiar esta doblada</t>
+          <t>Picada colocar columna para pedir traspasos tiene nodo teco y tlc</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4008,14 +4008,14 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.461</v>
+        <v>-58.4635</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.604483</v>
+        <v>-34.542844</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>BLO-F</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -5328,7 +5328,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7882</t>
+          <t xml:space="preserve">6436 </t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">BELAUSTEGUI, LUIS, DR. 3490 </t>
+          <t xml:space="preserve">ARIAS 4306 </t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>810862856</t>
+          <t>810862832</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5378,21 +5378,21 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L58" t="n">
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.484549</v>
+        <v>-58.49108</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.620529</v>
+        <v>-34.550102</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>DEV-K</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5414,17 +5414,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">6436 </t>
+          <t>-695</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>11/26/2025</t>
+          <t>12/3/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARIAS 4306 </t>
+          <t>Estomba 2626</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5444,17 +5444,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>810862832</t>
+          <t>810984651</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>desmontar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5471,14 +5471,14 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.49108</v>
+        <v>-58.47538</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.550102</v>
+        <v>-34.566015</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>PUE-E</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5500,17 +5500,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>-695</t>
+          <t>-698</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>12/3/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Estomba 2626</t>
+          <t>Franklin D. Roosevelt 5469</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5530,22 +5530,23 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>810984651</t>
+          <t xml:space="preserve">02019355 </t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>desmontar</t>
+          <t xml:space="preserve">corroida colocar columna pedir traspaso
+</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5557,14 +5558,14 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.47538</v>
+        <v>-58.491346</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.566015</v>
+        <v>-34.575773</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5574,7 +5575,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>PUE-E</t>
+          <t>PUE-C</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5586,22 +5587,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>-698</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/16/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Franklin D. Roosevelt 5469</t>
+          <t>DIAZ, CESAR, GRAL. 2053</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5616,13 +5617,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">02019355 </t>
+          <t>811198627</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">corroida colocar columna pedir traspaso
-</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L61" t="n">
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.491346</v>
+        <v>-58.468739</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.575773</v>
+        <v>-34.608957</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>PUE-C</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5673,22 +5673,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t xml:space="preserve">7921 </t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12/16/2025</t>
+          <t>12/17/2025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GUTIERREZ, RICARDO 3351</t>
+          <t>O'HIGGINS 4298</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>811198642</t>
+          <t>811198660</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5730,14 +5730,14 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.498056</v>
+        <v>-58.468046</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.601454</v>
+        <v>-34.541893</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5759,22 +5759,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-706</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>12/16/2025</t>
+          <t>12/17/2025</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DIAZ, CESAR, GRAL. 2053</t>
+          <t>PAZ, MARCOS 1505</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>811198627</t>
+          <t>811181316</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5816,14 +5816,14 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.468739</v>
+        <v>-58.500094</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.608957</v>
+        <v>-34.626115</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>DEV-I</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5845,17 +5845,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">7921 </t>
+          <t>7938</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12/17/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>O'HIGGINS 4298</t>
+          <t xml:space="preserve"> O'HIGGINS 4321</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>811198660</t>
+          <t>811198748</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5902,10 +5902,10 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.468046</v>
+        <v>-58.468227</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.541893</v>
+        <v>-34.541506</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -5931,22 +5931,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>-706</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>12/17/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PAZ, MARCOS 1505</t>
+          <t xml:space="preserve">PLAZA, VICTORINO DE LA, DR. 1754 </t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5961,12 +5961,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>811181316</t>
+          <t>811198702</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5981,21 +5981,21 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.500094</v>
+        <v>-58.451448</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.626115</v>
+        <v>-34.547978</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>DEV-I</t>
+          <t>BLO-D</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6017,22 +6017,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>S01028030</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve"> O'HIGGINS 4321</t>
+          <t xml:space="preserve">MARTIN PESCADOR 2296 </t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>811198748</t>
+          <t>811198686</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>poste inclinado</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6067,21 +6067,21 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L66" t="n">
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.468227</v>
+        <v>-58.493624</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.541506</v>
+        <v>-34.610119</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6103,22 +6103,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>-707</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/22/2025</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLAZA, VICTORINO DE LA, DR. 1754 </t>
+          <t>Camargo 257</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>811198702</t>
+          <t>811238662</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6160,14 +6160,14 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.451448</v>
+        <v>-58.438123</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.547978</v>
+        <v>-34.602541</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>BLO-D</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6189,22 +6189,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S01028030</t>
+          <t xml:space="preserve">7969 </t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTIN PESCADOR 2296 </t>
+          <t xml:space="preserve">HELGUERA 4770 </t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6219,12 +6219,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>811198686</t>
+          <t>811238727</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6246,14 +6246,14 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.493624</v>
+        <v>-58.505298</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.610119</v>
+        <v>-34.587467</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>PUE-N</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6275,22 +6275,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>-707</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12/22/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Camargo 257</t>
+          <t>RIVERA, PEDRO I., DR. 4448</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>811238662</t>
+          <t>811299428</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6332,14 +6332,14 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.438123</v>
+        <v>-58.481135</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.602541</v>
+        <v>-34.568427</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>PUE-E</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6361,22 +6361,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">7969 </t>
+          <t xml:space="preserve">7215 </t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">HELGUERA 4770 </t>
+          <t xml:space="preserve">MAURE 3996 </t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>811238727</t>
+          <t>811299417</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6418,14 +6418,14 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.505298</v>
+        <v>-58.451687</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.587467</v>
+        <v>-34.586223</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>PUE-N</t>
+          <t>ATH-L</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6447,22 +6447,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>7987</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>RIVERA, PEDRO I., DR. 4448</t>
+          <t>Terrada 2309</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>811299428</t>
+          <t>811299433</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6497,21 +6497,21 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L71" t="n">
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.481135</v>
+        <v>-58.482084</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.568427</v>
+        <v>-34.608289</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>PUE-E</t>
+          <t>NRA-P</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6533,22 +6533,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">7215 </t>
+          <t>S01139199</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAURE 3996 </t>
+          <t>CRAMER 4320</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>811299417</t>
+          <t>811299481</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6590,14 +6590,14 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.451687</v>
+        <v>-58.476445</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.586223</v>
+        <v>-34.544981</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>ATH-L</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6619,22 +6619,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t xml:space="preserve">8090 </t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>1/5/2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Terrada 2309</t>
+          <t>Vedia 3506</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6649,17 +6649,17 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>811299433</t>
+          <t xml:space="preserve">02125435 </t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>desmonte y traspasar red</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6669,21 +6669,21 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L73" t="n">
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.482084</v>
+        <v>-58.486704</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.608289</v>
+        <v>-34.544613</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>NRA-P</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6705,22 +6705,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S01139199</t>
+          <t xml:space="preserve">8173 </t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CRAMER 4320</t>
+          <t>SUCRE, ANTONIO JOSE DE, MCAL. 1563</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>811299481</t>
+          <t xml:space="preserve">02313712 </t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -6762,10 +6762,10 @@
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.476445</v>
+        <v>-58.446858</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.544981</v>
+        <v>-34.559026</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>BLO-A</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6791,22 +6791,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">8090 </t>
+          <t>-719</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1/5/2026</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Vedia 3506</t>
+          <t>MENDOZA 2160</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6821,17 +6821,17 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">02125435 </t>
+          <t>811453860</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>desmonte y traspasar red</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -6848,10 +6848,10 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.486704</v>
+        <v>-58.455182</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.544613</v>
+        <v>-34.559761</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>BLO-O</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -6877,22 +6877,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">8173 </t>
+          <t>S01180016</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SUCRE, ANTONIO JOSE DE, MCAL. 1563</t>
+          <t>FITZ ROY 1730</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">02313712 </t>
+          <t>811454223</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -6934,24 +6934,24 @@
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.446858</v>
+        <v>-58.436051</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.559026</v>
+        <v>-34.583855</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>BLO-A</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6963,22 +6963,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>-719</t>
+          <t>S01180023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MENDOZA 2160</t>
+          <t>VEGA, NICETO, CNEL. AV. 5420</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6993,12 +6993,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>811453860</t>
+          <t>811454198</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7020,24 +7020,24 @@
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.455182</v>
+        <v>-58.437628</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.559761</v>
+        <v>-34.587953</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>BLO-O</t>
+          <t>ATH-?</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7049,7 +7049,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S01180016</t>
+          <t>S01180086</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FITZ ROY 1730</t>
+          <t>BONPLAND 1471</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>811454223</t>
+          <t>811454194</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7106,10 +7106,10 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.436051</v>
+        <v>-58.439513</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.583855</v>
+        <v>-34.585314</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S01180023</t>
+          <t>S01200482</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>VEGA, NICETO, CNEL. AV. 5420</t>
+          <t>GONZALEZ, ELPIDIO 2749</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7165,12 +7165,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>811454198</t>
+          <t>811454117</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>quebrada</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7185,31 +7185,31 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L79" t="n">
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.437628</v>
+        <v>-58.481266</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.587953</v>
+        <v>-34.608522</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>ATH-?</t>
+          <t>NRA-O</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7221,7 +7221,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S01180086</t>
+          <t>S01204059</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BONPLAND 1471</t>
+          <t>BUFANO, ALFREDO R. 2580</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>811454194</t>
+          <t>811454109</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -7278,24 +7278,24 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.439513</v>
+        <v>-58.478411</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.585314</v>
+        <v>-34.6039</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>NRA-P</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7307,7 +7307,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S01200482</t>
+          <t>S01220047</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7317,12 +7317,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GONZALEZ, ELPIDIO 2749</t>
+          <t>MAURE 2958</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7337,12 +7337,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>811454117</t>
+          <t>811454097</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>quebrada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7357,31 +7357,31 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L81" t="n">
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.481266</v>
+        <v>-58.446339</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.608522</v>
+        <v>-34.576306</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>NRA-O</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7393,7 +7393,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S01204059</t>
+          <t>S01306211</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BUFANO, ALFREDO R. 2580</t>
+          <t>WASHINGTON 3943</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>811454109</t>
+          <t>811453965</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7443,21 +7443,21 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L82" t="n">
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.478411</v>
+        <v>-58.48286</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.6039</v>
+        <v>-34.55278</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>NRA-P</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7479,7 +7479,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S01220047</t>
+          <t>S01313361</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MAURE 2958</t>
+          <t>CABILDO AV. 805</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7509,12 +7509,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>811454097</t>
+          <t>811453963</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7529,31 +7529,31 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L83" t="n">
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.446339</v>
+        <v>-58.444955</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.576306</v>
+        <v>-34.569791</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>COG-C</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -7565,7 +7565,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S01306211</t>
+          <t>S01389798</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>WASHINGTON 3943</t>
+          <t>GUALEGUAYCHU 4682</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>811453965</t>
+          <t>811453943</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7615,21 +7615,21 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L84" t="n">
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.48286</v>
+        <v>-58.518214</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.55278</v>
+        <v>-34.596516</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -7651,7 +7651,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S01313361</t>
+          <t>S01384321</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CABILDO AV. 805</t>
+          <t>AZURDUY JUANA 2685</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7681,12 +7681,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>811453963</t>
+          <t>811453930</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7701,21 +7701,21 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L85" t="n">
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.444955</v>
+        <v>-58.469341</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.569791</v>
+        <v>-34.552269</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>COG-C</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -7737,7 +7737,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S01389798</t>
+          <t>S01392303</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU 4682</t>
+          <t>Moldes 1999</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>811453943</t>
+          <t>811453918</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7794,14 +7794,14 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.518214</v>
+        <v>-58.458535</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.596516</v>
+        <v>-34.564674</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>COG-G</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7823,22 +7823,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S01384321</t>
+          <t>8095</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AZURDUY JUANA 2685</t>
+          <t>MANZANARES 3853</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7853,7 +7853,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>811453930</t>
+          <t>811454324</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7880,10 +7880,10 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.469341</v>
+        <v>-58.482488</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.552269</v>
+        <v>-34.554114</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7909,22 +7909,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S01392303</t>
+          <t>8094</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Moldes 1999</t>
+          <t xml:space="preserve">GARCIA DEL RIO 3789 </t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>811453918</t>
+          <t>811454305</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7959,21 +7959,21 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L88" t="n">
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.458535</v>
+        <v>-58.482473</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.564674</v>
+        <v>-34.553018</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>COG-G</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7995,22 +7995,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MANZANARES 3853</t>
+          <t>Nogoya 3644</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>811454324</t>
+          <t>811454515</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8052,14 +8052,14 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.482488</v>
+        <v>-58.497751</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.554114</v>
+        <v>-34.606408</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8081,22 +8081,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA DEL RIO 3789 </t>
+          <t>Pje. Manuel Sola 4440</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>811454305</t>
+          <t>811454508</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8131,21 +8131,21 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L90" t="n">
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.482473</v>
+        <v>-58.507954</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.553018</v>
+        <v>-34.610808</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>DEV-D</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8167,7 +8167,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8186</t>
+          <t xml:space="preserve">8112 </t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Nogoya 3644</t>
+          <t>MANZANARES 2073</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>811454515</t>
+          <t>811454483</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8224,14 +8224,14 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.497751</v>
+        <v>-58.465953</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.606408</v>
+        <v>-34.545637</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8253,7 +8253,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>8316</t>
+          <t xml:space="preserve">8114 </t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pje. Manuel Sola 4440</t>
+          <t>ARGERICH 5774</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>811454508</t>
+          <t>811454454</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8303,21 +8303,21 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L92" t="n">
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.507954</v>
+        <v>-58.511147</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.610808</v>
+        <v>-34.578665</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>DEV-D</t>
+          <t>PUE-J</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8339,22 +8339,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8112 </t>
+          <t>8129</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/15/2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MANZANARES 2073</t>
+          <t>ESTOMBA 212</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>811454483</t>
+          <t>811454532</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -8389,21 +8389,21 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L93" t="n">
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.465953</v>
+        <v>-58.469045</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.545637</v>
+        <v>-34.588525</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8425,17 +8425,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">8114 </t>
+          <t>-731</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ARGERICH 5774</t>
+          <t>Ruiz Huidobro 3643</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -8455,14 +8455,10 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>811454454</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>inclinado</t>
-        </is>
-      </c>
+          <t>811498060</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -8482,14 +8478,14 @@
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.511147</v>
+        <v>-58.484505</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.578665</v>
+        <v>-34.549798</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -8499,7 +8495,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>PUE-J</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8511,22 +8507,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>-732</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1/15/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ESTOMBA 212</t>
+          <t xml:space="preserve"> Valentin Alsina 1685</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8539,11 +8535,7 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>811454532</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>inclinada</t>
@@ -8561,31 +8553,27 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L95" t="n">
         <v>1</v>
       </c>
-      <c r="M95" t="n">
-        <v>-58.469045</v>
-      </c>
-      <c r="N95" t="n">
-        <v>-34.588525</v>
-      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>No ubicado</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>No clasificado, consultar con mantenimiento</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>No ubicado</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8597,7 +8585,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>-731</t>
+          <t>-733</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8607,12 +8595,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ruiz Huidobro 3643</t>
+          <t xml:space="preserve"> Dorrego 2755</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8627,10 +8615,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>811498060</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>811498056</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>corroida</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -8643,31 +8635,31 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L96" t="n">
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.484505</v>
+        <v>-58.432319</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.549798</v>
+        <v>-34.574385</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8679,7 +8671,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>-732</t>
+          <t xml:space="preserve">6428 </t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8689,12 +8681,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Valentin Alsina 1685</t>
+          <t>MONROE 4070</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8707,10 +8699,14 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>811498053</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -8731,21 +8727,25 @@
       <c r="L97" t="n">
         <v>1</v>
       </c>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+      <c r="M97" t="n">
+        <v>-58.475842</v>
+      </c>
+      <c r="N97" t="n">
+        <v>-34.568215</v>
+      </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>No ubicado</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>No clasificado, consultar con mantenimiento</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>No ubicado</t>
+          <t>ATH-J</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8757,7 +8757,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>-733</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dorrego 2755</t>
+          <t>AZURDUY JUANA 3630</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8787,12 +8787,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>811498056</t>
+          <t>811498050</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -8814,24 +8814,24 @@
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.432319</v>
+        <v>-58.477583</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.574385</v>
+        <v>-34.5569</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>COG-N</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8843,22 +8843,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">6428 </t>
+          <t>S01215930</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/20/2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MONROE 4070</t>
+          <t>UGARTE, MANUEL 2750</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>811498053</t>
+          <t>811498072</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -8900,14 +8900,14 @@
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.475842</v>
+        <v>-58.465042</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.568215</v>
+        <v>-34.557947</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>ATH-J</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8929,17 +8929,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>8181</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/22/2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AZURDUY JUANA 3630</t>
+          <t xml:space="preserve">FREIRE, RAMON, CAP. GRAL. 4748 </t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>811498050</t>
+          <t>811498074</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada base quebrada</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -8979,17 +8979,17 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L100" t="n">
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.477583</v>
+        <v>-58.482951</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.5569</v>
+        <v>-34.544273</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>COG-N</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9015,22 +9015,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S01215930</t>
+          <t>S01318042</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1/20/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>UGARTE, MANUEL 2750</t>
+          <t>UGARTE, MANUEL 3815</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -9045,12 +9045,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>811498072</t>
+          <t>811626754</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9072,10 +9072,10 @@
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.465042</v>
+        <v>-58.476138</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.557947</v>
+        <v>-34.563825</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>COG-N</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9101,22 +9101,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>8181</t>
+          <t>S01397288</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1/22/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREIRE, RAMON, CAP. GRAL. 4748 </t>
+          <t xml:space="preserve">MOLDES 1918 </t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9131,41 +9131,29 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>811498074</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>inclinada base quebrada</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>Poste</t>
-        </is>
-      </c>
+          <t>inclinadaq</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
       <c r="L102" t="n">
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.482951</v>
+        <v>-58.458035</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.544273</v>
+        <v>-34.565387</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -9175,7 +9163,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>COG-G</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9187,7 +9175,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S01318042</t>
+          <t>S01397364</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9197,12 +9185,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>UGARTE, MANUEL 3815</t>
+          <t>AVILES, VIRREY 3008</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9217,12 +9205,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>811626754</t>
+          <t>811626732</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9244,14 +9232,14 @@
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.476138</v>
+        <v>-58.457207</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.563825</v>
+        <v>-34.571602</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -9261,7 +9249,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>COG-N</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9273,22 +9261,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S01397288</t>
+          <t>-740</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOLDES 1918 </t>
+          <t>Gutemberg 350</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -9303,29 +9291,41 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811626800</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>inclinadaq</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
+          <t>inclinado</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
       <c r="L104" t="n">
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.458035</v>
+        <v>-58.471803</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.565387</v>
+        <v>-34.592463</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>COG-G</t>
+          <t>PUE-?</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9347,22 +9347,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S01397364</t>
+          <t>-741</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>AVILES, VIRREY 3008</t>
+          <t>Gutemberg 320</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9377,12 +9377,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>811626732</t>
+          <t>811626794</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>mal estado</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -9397,21 +9397,21 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L105" t="n">
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.457207</v>
+        <v>-58.470581</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.571602</v>
+        <v>-34.592428</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>PUE-?</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9433,7 +9433,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>-740</t>
+          <t>-742</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Gutemberg 350</t>
+          <t>BLANCO ENCALADA 899</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9463,17 +9463,17 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>811626800</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>desmonte</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -9490,14 +9490,14 @@
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.471803</v>
+        <v>-58.443393</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.592463</v>
+        <v>-34.549873</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>PUE-?</t>
+          <t>BLO-B</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9519,7 +9519,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>-741</t>
+          <t>-743</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Gutemberg 320</t>
+          <t>Giribone 1411</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -9549,12 +9549,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>811626794</t>
+          <t>811626791</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>mal estado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -9569,21 +9569,21 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L107" t="n">
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.470581</v>
+        <v>-58.462095</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.592428</v>
+        <v>-34.579585</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -9593,7 +9593,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>PUE-?</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9605,22 +9605,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>-742</t>
+          <t>S01396837</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>BLANCO ENCALADA 899</t>
+          <t>DEHEZA 3622</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9635,17 +9635,17 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811626963</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>desmonte</t>
+          <t>inclinado base quebrada</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -9662,10 +9662,10 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.443393</v>
+        <v>-58.485735</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.549873</v>
+        <v>-34.546249</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>BLO-B</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9691,22 +9691,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>-743</t>
+          <t>S01406731</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Giribone 1411</t>
+          <t xml:space="preserve"> CORREA 1807</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>811626791</t>
+          <t>811626953</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -9748,14 +9748,14 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.462095</v>
+        <v>-58.466595</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.579585</v>
+        <v>-34.54099</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -9777,7 +9777,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S01396837</t>
+          <t>S01406737</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>DEHEZA 3622</t>
+          <t>GRECIA 4281</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9807,12 +9807,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>811626963</t>
+          <t>811626921</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>inclinado base quebrada</t>
+          <t>inlinada</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -9827,17 +9827,17 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L110" t="n">
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.485735</v>
+        <v>-58.466965</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.546249</v>
+        <v>-34.541488</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9863,17 +9863,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S01406731</t>
+          <t>S01406812</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CORREA 1807</t>
+          <t xml:space="preserve">VUELTA DE OBLIGADO 3201 </t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>811626953</t>
+          <t>811626783</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -9920,10 +9920,10 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.466595</v>
+        <v>-58.464784</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.54099</v>
+        <v>-34.551419</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>BLO-R</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9949,17 +9949,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S01406737</t>
+          <t>S00019326</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>GRECIA 4281</t>
+          <t>OLLEROS 3050</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>811626921</t>
+          <t>811627002</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>inlinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10006,24 +10006,24 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.466965</v>
+        <v>-58.447708</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.541488</v>
+        <v>-34.577055</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>ATH-P</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10035,17 +10035,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S01406812</t>
+          <t>S00021988</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">VUELTA DE OBLIGADO 3201 </t>
+          <t>ALVAREZ THOMAS AV. 1115</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>811626783</t>
+          <t>811626996</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10092,14 +10092,14 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.464784</v>
+        <v>-58.457565</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.551419</v>
+        <v>-34.578379</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>BLO-R</t>
+          <t>ATH-O</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10121,7 +10121,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S00019326</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>OLLEROS 3050</t>
+          <t xml:space="preserve">SANABRIA 2386 </t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10151,12 +10151,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>811627002</t>
+          <t>811626991</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -10171,31 +10171,31 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L114" t="n">
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.447708</v>
+        <v>-58.503452</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.577055</v>
+        <v>-34.614501</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>ATH-P</t>
+          <t>DEV-D</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10207,7 +10207,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S00021988</t>
+          <t>S01450787</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10217,7 +10217,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ALVAREZ THOMAS AV. 1115</t>
+          <t>HERNANDEZ, JOSE 2110</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -10237,7 +10237,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>811626996</t>
+          <t>811626983</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -10257,17 +10257,17 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L115" t="n">
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.457565</v>
+        <v>-58.450727</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.578379</v>
+        <v>-34.56425</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>ATH-O</t>
+          <t>BLO-M</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10293,22 +10293,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>-745</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANABRIA 2386 </t>
+          <t>Gamarra 1546</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>811626991</t>
+          <t>811627113</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -10343,21 +10343,21 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L116" t="n">
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.503452</v>
+        <v>-58.477231</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.614501</v>
+        <v>-34.58242</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -10367,7 +10367,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>DEV-D</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10379,22 +10379,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S01450787</t>
+          <t>S00036520</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>HERNANDEZ, JOSE 2110</t>
+          <t>SEGUROLA AV. 856</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>811626983</t>
+          <t>811627070</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroidaq</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -10429,21 +10429,21 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L117" t="n">
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.450727</v>
+        <v>-58.490765</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.56425</v>
+        <v>-34.627337</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -10453,7 +10453,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>BLO-M</t>
+          <t>DEV-I</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10465,7 +10465,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>-745</t>
+          <t xml:space="preserve">900009468810 </t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Gamarra 1546</t>
+          <t xml:space="preserve">CUENCA 3033 </t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10495,12 +10495,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>811627113</t>
+          <t>811627041</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -10515,21 +10515,21 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L118" t="n">
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.477231</v>
+        <v>-58.494814</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.58242</v>
+        <v>-34.601905</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10551,22 +10551,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S00036520</t>
+          <t>S01337226</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/6/2026</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SEGUROLA AV. 856</t>
+          <t>MOLDES 3055</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>811627070</t>
+          <t>811627125</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>corroidaq</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -10608,14 +10608,14 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.490765</v>
+        <v>-58.466692</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.627337</v>
+        <v>-34.555283</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -10625,7 +10625,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>DEV-I</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10637,22 +10637,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">900009468810 </t>
+          <t>S01375612</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/6/2026</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUENCA 3033 </t>
+          <t>LACROZE, FEDERICO AV. 2834</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -10667,12 +10667,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>811627041</t>
+          <t>811627118</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>corroidaq</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -10687,31 +10687,31 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L120" t="n">
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.494814</v>
+        <v>-58.447177</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.601905</v>
+        <v>-34.574158</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>ATH-P</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10723,22 +10723,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S01337226</t>
+          <t xml:space="preserve">8301 </t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2/6/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MOLDES 3055</t>
+          <t>ARENGREEN 1584</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>811627125</t>
+          <t>812440072</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -10773,31 +10773,31 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L121" t="n">
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.466692</v>
+        <v>-58.453265</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.555283</v>
+        <v>-34.615073</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>NRA-I</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10809,22 +10809,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S01375612</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2/6/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>LACROZE, FEDERICO AV. 2834</t>
+          <t>ARENAL, CONCEPCION 3814</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -10839,12 +10839,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>811627118</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>corroidaq</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -10866,24 +10866,24 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.447177</v>
+        <v>-58.447805</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.574158</v>
+        <v>-34.587018</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>ATH-P</t>
+          <t>ATH-L</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10895,7 +10895,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">8301 </t>
+          <t>8323</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10905,12 +10905,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ARENGREEN 1584</t>
+          <t>WARNES AV. 2239</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -10925,12 +10925,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>812440072</t>
+          <t>812440018</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -10945,31 +10945,31 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L123" t="n">
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.453265</v>
+        <v>-58.467815</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.615073</v>
+        <v>-34.596225</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>NRA-I</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10981,7 +10981,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ARENAL, CONCEPCION 3814</t>
+          <t>PAZ SOLDAN 4991</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -11011,12 +11011,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812439995</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>base quebrada</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -11026,26 +11026,26 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L124" t="n">
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.447805</v>
+        <v>-58.468466</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.587018</v>
+        <v>-34.594154</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>ATH-L</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11067,7 +11067,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>WARNES AV. 2239</t>
+          <t xml:space="preserve"> GUALEGUAYCHU 4754</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>812440018</t>
+          <t>812439956</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinado, base quebrada</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -11117,17 +11117,17 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L125" t="n">
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.467815</v>
+        <v>-58.518803</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.596225</v>
+        <v>-34.595866</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11153,7 +11153,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11163,12 +11163,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PAZ SOLDAN 4991</t>
+          <t>BLANCO ENCALADA 823</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11183,12 +11183,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>812439995</t>
+          <t>812439941</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>base quebrada</t>
+          <t>inclinado base quebrada</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -11210,14 +11210,14 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.468466</v>
+        <v>-58.442692</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.594154</v>
+        <v>-34.549454</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>BLO-B</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11239,22 +11239,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GUALEGUAYCHU 4754</t>
+          <t>DORREGO AV. 2699</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11269,12 +11269,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>812439956</t>
+          <t>812440089</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>inclinado, base quebrada</t>
+          <t>base corrodia</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -11289,31 +11289,31 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L127" t="n">
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.518803</v>
+        <v>-58.432807</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.595866</v>
+        <v>-34.574343</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11325,22 +11325,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BLANCO ENCALADA 823</t>
+          <t>BEIRO, FRANCISCO AV. 2435</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11355,12 +11355,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>812439941</t>
+          <t>812440250</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>inclinado base quebrada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -11375,21 +11375,21 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L128" t="n">
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.442692</v>
+        <v>-58.488914</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.549454</v>
+        <v>-34.59164</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>BLO-B</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11411,22 +11411,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2699</t>
+          <t>CARACAS 3559</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>812440089</t>
+          <t>812440223</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>base corrodia</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -11468,24 +11468,24 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.432807</v>
+        <v>-58.487793</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.574343</v>
+        <v>-34.590403</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11497,7 +11497,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>8368</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>BEIRO, FRANCISCO AV. 2435</t>
+          <t>CARACAS 3519</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11527,12 +11527,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>812440250</t>
+          <t>812503552</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -11554,10 +11554,10 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.488914</v>
+        <v>-58.487627</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.59164</v>
+        <v>-34.590585</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CARACAS 3559</t>
+          <t>VARELA, JOSE PEDRO 3545</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>812440223</t>
+          <t>812440219</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -11633,17 +11633,17 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L131" t="n">
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.487793</v>
+        <v>-58.502073</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.590403</v>
+        <v>-34.601294</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11669,7 +11669,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11679,12 +11679,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CARACAS 3519</t>
+          <t>ANDONAEGUI 2383</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>812503552</t>
+          <t>812440211</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -11726,10 +11726,10 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.487627</v>
+        <v>-58.489606</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.590585</v>
+        <v>-34.57655</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>ATH-C</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11755,7 +11755,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11765,12 +11765,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>VARELA, JOSE PEDRO 3545</t>
+          <t>CRAMER 4262</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11785,12 +11785,12 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>812440219</t>
+          <t>812440206</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -11805,21 +11805,21 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L133" t="n">
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.502073</v>
+        <v>-58.476168</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.601294</v>
+        <v>-34.545546</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11841,7 +11841,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ANDONAEGUI 2383</t>
+          <t xml:space="preserve">CRAMER 4322 </t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11871,12 +11871,12 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>812440211</t>
+          <t>812440204</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>base corroida inclnada</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -11898,14 +11898,14 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.489606</v>
+        <v>-58.476454</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.57655</v>
+        <v>-34.544962</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>ATH-C</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11927,7 +11927,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>8382</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11937,12 +11937,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>CRAMER 4262</t>
+          <t>SANTO TOME 3588</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -11957,12 +11957,12 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>812440206</t>
+          <t>812440197</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -11977,21 +11977,21 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L135" t="n">
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.476168</v>
+        <v>-58.4947</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.545546</v>
+        <v>-34.60925</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>DEV-D</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -12013,7 +12013,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>S00117686</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12023,12 +12023,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRAMER 4322 </t>
+          <t>DORREGO AV. 2778</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>812440204</t>
+          <t>812440183</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>base corroida inclnada</t>
+          <t>inlinada</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -12070,24 +12070,24 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.476454</v>
+        <v>-58.432102</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.544962</v>
+        <v>-34.574248</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12099,7 +12099,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>S00506048</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SANTO TOME 3588</t>
+          <t>TERRADA 1088</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12129,17 +12129,17 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>812440197</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Tensor</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -12149,21 +12149,21 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.4947</v>
+        <v>-58.472866</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.60925</v>
+        <v>-34.620121</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>DEV-D</t>
+          <t>NRA-M</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12185,22 +12185,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S00117686</t>
+          <t>-748</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2778</t>
+          <t>GUTENBERG 340</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12215,12 +12215,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>812440183</t>
+          <t>812440623</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>inlinada</t>
+          <t>inclinado base podrida</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -12235,31 +12235,31 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L138" t="n">
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.432102</v>
+        <v>-58.471395</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.574248</v>
+        <v>-34.592451</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>PUE-?</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12271,22 +12271,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S00506048</t>
+          <t>-750</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>TERRADA 1088</t>
+          <t>JURAMENTO 4979</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12301,17 +12301,17 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440599</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Tensor</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -12321,17 +12321,17 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L139" t="n">
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.472866</v>
+        <v>-58.481188</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.620121</v>
+        <v>-34.577198</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -12345,7 +12345,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>NRA-M</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12357,7 +12357,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>-748</t>
+          <t>-753</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>GUTENBERG 340</t>
+          <t>CISNEROS, VIRREY 1610</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12387,12 +12387,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>812440623</t>
+          <t>812440520</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>inclinado base podrida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -12407,17 +12407,17 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.471395</v>
+        <v>-58.469727</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.592451</v>
+        <v>-34.612013</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>PUE-?</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12443,7 +12443,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>-750</t>
+          <t>-754</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12453,12 +12453,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>JURAMENTO 4979</t>
+          <t>PINO, VIRREY DEL 1503</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12473,7 +12473,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>812440599</t>
+          <t>812440515</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -12500,14 +12500,14 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.481188</v>
+        <v>-58.442723</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.577198</v>
+        <v>-34.56085</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>BLO-A</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12529,7 +12529,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>-753</t>
+          <t>-755</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CISNEROS, VIRREY 1610</t>
+          <t>CONDE 4296</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12559,12 +12559,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>812440520</t>
+          <t>812440509</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -12579,21 +12579,21 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L142" t="n">
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.469727</v>
+        <v>-58.481187</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.612013</v>
+        <v>-34.548301</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12615,7 +12615,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>-754</t>
+          <t>-757</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12625,12 +12625,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>PINO, VIRREY DEL 1503</t>
+          <t>FRAGATA PRES. SARMIENTO 1390</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12645,7 +12645,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>812440515</t>
+          <t>812440373</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -12672,14 +12672,14 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.442723</v>
+        <v>-58.456778</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.56085</v>
+        <v>-34.609187</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -12689,7 +12689,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>BLO-A</t>
+          <t>NRA-I</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12701,7 +12701,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>-755</t>
+          <t>-761</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12711,12 +12711,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CONDE 4296</t>
+          <t>MOLDES 2901</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -12731,12 +12731,12 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>812440509</t>
+          <t>812440341</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -12758,10 +12758,10 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.481187</v>
+        <v>-58.465305</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.548301</v>
+        <v>-34.556794</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12787,7 +12787,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>-757</t>
+          <t>S00506118</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12797,12 +12797,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>FRAGATA PRES. SARMIENTO 1390</t>
+          <t>TERRERO 588</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12817,12 +12817,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>812440373</t>
+          <t>812440289</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -12844,24 +12844,24 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.456778</v>
+        <v>-58.459689</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.609187</v>
+        <v>-34.620032</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>NRA-I</t>
+          <t>NRA-D</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12873,17 +12873,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>-761</t>
+          <t>S01295589</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/24/2026</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MOLDES 2901</t>
+          <t>CABILDO AV. 1008</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12903,12 +12903,12 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>812440341</t>
+          <t>812440653</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -12930,14 +12930,14 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.465305</v>
+        <v>-58.446714</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.556794</v>
+        <v>-34.569183</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>COG-C</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12959,22 +12959,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S00506118</t>
+          <t>S01406719</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/24/2026</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>TERRERO 588</t>
+          <t>3 DE FEBRERO 4481</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>812440289</t>
+          <t>812440639</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -13009,31 +13009,31 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L147" t="n">
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.459689</v>
+        <v>-58.467166</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.620032</v>
+        <v>-34.539469</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>NRA-D</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -13045,22 +13045,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S01295589</t>
+          <t>S00867165</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2/24/2026</t>
+          <t>2/26/2026</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>CABILDO AV. 1008</t>
+          <t xml:space="preserve"> VALLEJOS 2250</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>812440653</t>
+          <t>812503628</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -13102,14 +13102,14 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.446714</v>
+        <v>-58.493418</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.569183</v>
+        <v>-34.583307</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>COG-C</t>
+          <t>PUE-K</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13131,22 +13131,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S01406719</t>
+          <t xml:space="preserve">8392 </t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2/24/2026</t>
+          <t>2/26/2026</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>3 DE FEBRERO 4481</t>
+          <t xml:space="preserve">ESTADO PLURINACIONAL DE BOLIVIA 3526 </t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13161,12 +13161,12 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>812440639</t>
+          <t>812503597</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -13181,21 +13181,21 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L149" t="n">
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.467166</v>
+        <v>-58.491306</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.539469</v>
+        <v>-34.592511</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -13205,7 +13205,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13217,7 +13217,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S00867165</t>
+          <t>8397</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13227,12 +13227,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VALLEJOS 2250</t>
+          <t>TERRADA 3739</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>812503628</t>
+          <t>812503610</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -13274,10 +13274,10 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.493418</v>
+        <v>-58.494807</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.583307</v>
+        <v>-34.592416</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>PUE-K</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -13303,7 +13303,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">8392 </t>
+          <t>8398</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESTADO PLURINACIONAL DE BOLIVIA 3526 </t>
+          <t xml:space="preserve"> TERRADA 3695 </t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -13333,12 +13333,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>812503597</t>
+          <t>812503605</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -13360,10 +13360,10 @@
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>-58.491306</v>
+        <v>-58.494371</v>
       </c>
       <c r="N151" t="n">
-        <v>-34.592511</v>
+        <v>-34.592899</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -13389,22 +13389,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>8397</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2/26/2026</t>
+          <t>2/27/2026</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>TERRADA 3739</t>
+          <t>SIMBRON 5855</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>812503610</t>
+          <t>812503637</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -13439,21 +13439,21 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L152" t="n">
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.494807</v>
+        <v>-58.527129</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.592416</v>
+        <v>-34.620962</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -13463,7 +13463,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>DEV-G</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -13475,17 +13475,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>8398</t>
+          <t>-765</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2/26/2026</t>
+          <t>3/2/2026</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TERRADA 3695 </t>
+          <t>AVALOS 180</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -13505,12 +13505,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>812503605</t>
+          <t>812503657</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -13532,10 +13532,10 @@
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>-58.494371</v>
+        <v>-58.465874</v>
       </c>
       <c r="N153" t="n">
-        <v>-34.592899</v>
+        <v>-34.594613</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -13561,22 +13561,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>S00208304</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2/27/2026</t>
+          <t>3/2/2026</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>SIMBRON 5855</t>
+          <t>CONDE 3080</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13591,12 +13591,12 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>812503637</t>
+          <t>812503654</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -13611,21 +13611,21 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L154" t="n">
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>-58.527129</v>
+        <v>-58.47322</v>
       </c>
       <c r="N154" t="n">
-        <v>-34.620962</v>
+        <v>-34.558645</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>DEV-G</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -13647,7 +13647,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>-765</t>
+          <t>-768</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13657,12 +13657,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>AVALOS 180</t>
+          <t>CONCORDIA 3581</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13677,12 +13677,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>812503657</t>
+          <t>812503649</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -13697,17 +13697,17 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L155" t="n">
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>-58.465874</v>
+        <v>-58.502724</v>
       </c>
       <c r="N155" t="n">
-        <v>-34.594613</v>
+        <v>-34.599311</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -13733,7 +13733,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>-766</t>
+          <t>-767</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13743,12 +13743,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>CONDE 3080</t>
+          <t>CONCORDIA 3525</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>812503654</t>
+          <t>812503647</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -13783,21 +13783,21 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L156" t="n">
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>-58.47322</v>
+        <v>-58.502389</v>
       </c>
       <c r="N156" t="n">
-        <v>-34.558645</v>
+        <v>-34.599679</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -13807,7 +13807,7 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -13819,7 +13819,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>-768</t>
+          <t>-769</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13829,12 +13829,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>CONCORDIA 3581</t>
+          <t>RIVERA, PEDRO I., DR. 2734</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -13849,12 +13849,12 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>812503649</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -13864,26 +13864,26 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L157" t="n">
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>-58.502724</v>
+        <v>-58.464354</v>
       </c>
       <c r="N157" t="n">
-        <v>-34.599311</v>
+        <v>-34.5587</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -13905,22 +13905,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>-767</t>
+          <t>S00106358</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>3/2/2026</t>
+          <t>3/4/2026</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>CONCORDIA 3525</t>
+          <t>TRONADOR 1194</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -13935,7 +13935,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>812503647</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -13955,21 +13955,21 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L158" t="n">
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>-58.502389</v>
+        <v>-58.466138</v>
       </c>
       <c r="N158" t="n">
-        <v>-34.599679</v>
+        <v>-34.579638</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -13979,182 +13979,10 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>-769</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>3/2/2026</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>RIVERA, PEDRO I., DR. 2734</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>corroida</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>Nodo/Fuente Teco</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L159" t="n">
-        <v>1</v>
-      </c>
-      <c r="M159" t="n">
-        <v>-58.464354</v>
-      </c>
-      <c r="N159" t="n">
-        <v>-34.5587</v>
-      </c>
-      <c r="O159" t="inlineStr">
-        <is>
-          <t>Saavedra</t>
-        </is>
-      </c>
-      <c r="P159" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q159" t="inlineStr">
-        <is>
-          <t>COG-K</t>
-        </is>
-      </c>
-      <c r="R159" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>S00106358</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>3/4/2026</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>TRONADOR 1194</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L160" t="n">
-        <v>1</v>
-      </c>
-      <c r="M160" t="n">
-        <v>-58.466138</v>
-      </c>
-      <c r="N160" t="n">
-        <v>-34.579638</v>
-      </c>
-      <c r="O160" t="inlineStr">
-        <is>
-          <t>Colegiales</t>
-        </is>
-      </c>
-      <c r="P160" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q160" t="inlineStr">
-        <is>
-          <t>ATH-H</t>
-        </is>
-      </c>
-      <c r="R160" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_NEW.xlsx
+++ b/mapa_interactivo_NEW.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,96 +413,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R158"/>
+  <dimension ref="A1:R182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Caso</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>F. De Reclamo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Direccion</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Comuna</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Proveedor Asignado</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>OT</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Tipo de tarea</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Equipo</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Tipo de Elemento</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Attachments</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Coordenada_X</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Coordenada_Y</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Operacion</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>PD</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>N2</t>
         </is>
@@ -1715,7 +1703,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">7966 </t>
+          <t>7966</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3445,7 +3433,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>WASHINGTON 4274</t>
+          <t>WASHINGTON 4273</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3492,10 +3480,10 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.484797</v>
+        <v>-58.484798</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.550364</v>
+        <v>-34.550226</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -4037,22 +4025,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>8482</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 3008</t>
+          <t>San Blas 2591</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4067,12 +4055,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>810421914</t>
+          <t>810416660</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4094,14 +4082,14 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.464818</v>
+        <v>-58.477427</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.554931</v>
+        <v>-34.609261</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4111,7 +4099,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>NRA-Q</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4123,22 +4111,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10/29/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>QUITO 4180</t>
+          <t>CIUDAD DE LA PAZ 3008</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4153,12 +4141,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>810471618</t>
+          <t>810421914</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4180,24 +4168,24 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.425596</v>
+        <v>-58.464818</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.617038</v>
+        <v>-34.554931</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4209,22 +4197,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7697</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>10/29/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CONDE 4334</t>
+          <t>QUITO 4180</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4239,12 +4227,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>810487016</t>
+          <t>810471618</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Poste para cambiar o desmontar ver con inspector</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4259,31 +4247,31 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L45" t="n">
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.481509</v>
+        <v>-58.425596</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.547874</v>
+        <v>-34.617038</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4295,17 +4283,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>7697</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ROOSEVELT FRANKLIN D. 4665</t>
+          <t>CONDE 4334</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4325,12 +4313,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>810651339</t>
+          <t>810487016</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Poste inclinado</t>
+          <t>Poste para cambiar o desmontar ver con inspector</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4352,14 +4340,14 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.482196</v>
+        <v>-58.481509</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.570432</v>
+        <v>-34.547874</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4369,7 +4357,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>ATH-E</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4381,7 +4369,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7811</t>
+          <t>7806</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4391,12 +4379,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BURELA 1589</t>
+          <t>ROOSEVELT FRANKLIN D. 4665</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4411,12 +4399,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>810651370</t>
+          <t>810651339</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Poste inclinado</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4431,21 +4419,21 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L47" t="n">
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.485747</v>
+        <v>-58.482196</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.58538</v>
+        <v>-34.570432</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4455,7 +4443,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>ATH-E</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4467,22 +4455,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>-673</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bauness 2195</t>
+          <t>BURELA 1589</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4497,12 +4485,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>810787633</t>
+          <t>810651370</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sacar columna con prioridad  Tensar linga en columna continua</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4524,10 +4512,10 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.485702</v>
+        <v>-58.485747</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.576702</v>
+        <v>-34.58538</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -4541,7 +4529,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>ATH-C</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4553,22 +4541,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S00921590</t>
+          <t>-673</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/17/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CASEROS AV. 3621</t>
+          <t>Bauness 2195</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4583,12 +4571,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>810804462</t>
+          <t>810787633</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>columna inclinada corroida</t>
+          <t>Sacar columna con prioridad  Tensar linga en columna continua</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4610,24 +4598,24 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.416134</v>
+        <v>-58.485702</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.638879</v>
+        <v>-34.576702</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>ATH-C</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4639,7 +4627,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S00921597</t>
+          <t>S00921590</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4649,7 +4637,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CASEROS AV. 3507</t>
+          <t>CASEROS AV. 3621</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4669,7 +4657,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>810804451</t>
+          <t>810804462</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4696,10 +4684,10 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.414769</v>
+        <v>-58.416134</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.638638</v>
+        <v>-34.638879</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -4725,7 +4713,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S01089776</t>
+          <t>S00921597</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4735,12 +4723,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ARGERICH 3717</t>
+          <t>CASEROS AV. 3507</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4755,12 +4743,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>810804318</t>
+          <t>810804451</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>columna inclinada corroida</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4782,24 +4770,24 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.497051</v>
+        <v>-58.414769</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.594109</v>
+        <v>-34.638638</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4811,22 +4799,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S01126628</t>
+          <t>S01089776</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>RIVERA, PEDRO I., DR. 3385</t>
+          <t>ARGERICH 3717</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4841,12 +4829,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>810820813</t>
+          <t>810804318</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4868,14 +4856,14 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.47104</v>
+        <v>-58.497051</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.562322</v>
+        <v>-34.594109</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -4885,7 +4873,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>COG-I</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4897,7 +4885,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S01144183</t>
+          <t>S01126628</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4907,7 +4895,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DE LOS CONSTITUYENTES AV. 4318</t>
+          <t>RIVERA, PEDRO I., DR. 3385</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4927,7 +4915,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>810820640</t>
+          <t>810820813</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4954,14 +4942,14 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.490526</v>
+        <v>-58.47104</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.583417</v>
+        <v>-34.562322</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4971,7 +4959,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>PUE-K</t>
+          <t>COG-I</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4983,7 +4971,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S01171313</t>
+          <t>S01144183</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4993,12 +4981,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LOPE DE VEGA AV. 3128 </t>
+          <t>DE LOS CONSTITUYENTES AV. 4318</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5013,12 +5001,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>810820624</t>
+          <t>810820640</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5040,14 +5028,14 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.525417</v>
+        <v>-58.490526</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.613865</v>
+        <v>-34.583417</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5057,7 +5045,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>DEV-G</t>
+          <t>PUE-K</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5069,7 +5057,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870 </t>
+          <t>S01171313</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5079,7 +5067,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MAGARIÑOS CERVANTES, A. 4803</t>
+          <t xml:space="preserve"> LOPE DE VEGA AV. 3128 </t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5099,12 +5087,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>810820571</t>
+          <t>810820624</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>inclinada, tensor roto</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5119,17 +5107,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L55" t="n">
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.500609</v>
+        <v>-58.525417</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.626542</v>
+        <v>-34.613865</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -5143,7 +5131,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>DEV-I</t>
+          <t>DEV-G</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5155,7 +5143,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">7867 </t>
+          <t>7870</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5165,12 +5153,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DIAZ, CESAR, GRAL. 1450</t>
+          <t>MAGARIÑOS CERVANTES, A. 4803</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5185,12 +5173,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>810820533</t>
+          <t>810820571</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>muy inclinada</t>
+          <t>inclinada, tensor roto</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5205,21 +5193,21 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L56" t="n">
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.461219</v>
+        <v>-58.500609</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.605928</v>
+        <v>-34.626542</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5229,7 +5217,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>DEV-I</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5241,22 +5229,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>-684</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>11/26/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LONDRES 4280</t>
+          <t>DIAZ, CESAR, GRAL. 1450</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5271,13 +5259,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">01639693 </t>
+          <t>810820533</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Columna 114 picada en base con receptor óptico propio, ver de colocar otra columna a la derecha asi poder traspasar el mismo receptor y Cdo propio.
-</t>
+          <t>muy inclinada</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5287,22 +5274,22 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L57" t="n">
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.48081</v>
+        <v>-58.461219</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.582354</v>
+        <v>-34.605928</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -5316,7 +5303,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5328,7 +5315,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">6436 </t>
+          <t>-684</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5338,12 +5325,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARIAS 4306 </t>
+          <t>LONDRES 4280</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5358,12 +5345,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>810862832</t>
+          <t xml:space="preserve">01639693 </t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>Columna 114 picada en base con receptor óptico propio ver de colocar otra columna a la derecha asi poder traspasar el mismo receptor y Cdo propio</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5373,7 +5360,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5385,14 +5372,14 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.49108</v>
+        <v>-58.48081</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.550102</v>
+        <v>-34.582354</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5402,7 +5389,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5414,17 +5401,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>-695</t>
+          <t>6436</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>12/3/2025</t>
+          <t>11/26/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Estomba 2626</t>
+          <t xml:space="preserve">ARIAS 4306 </t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5444,17 +5431,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>810984651</t>
+          <t>810862832</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>desmontar</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5471,14 +5458,14 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.47538</v>
+        <v>-58.49108</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.566015</v>
+        <v>-34.550102</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5488,7 +5475,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>PUE-E</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5500,17 +5487,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>-698</t>
+          <t>-695</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/3/2025</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Franklin D. Roosevelt 5469</t>
+          <t>Estomba 2626</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5530,23 +5517,22 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">02019355 </t>
+          <t>810984651</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">corroida colocar columna pedir traspaso
-</t>
+          <t>desmontar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5558,14 +5544,14 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.491346</v>
+        <v>-58.47538</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.575773</v>
+        <v>-34.566015</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5575,7 +5561,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>PUE-C</t>
+          <t>PUE-E</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5587,22 +5573,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-698</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12/16/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DIAZ, CESAR, GRAL. 2053</t>
+          <t>Franklin D. Roosevelt 5469</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5617,12 +5603,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>811198627</t>
+          <t xml:space="preserve">02019355 </t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida colocar columna pedir traspaso</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5632,22 +5618,22 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L61" t="n">
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.468739</v>
+        <v>-58.491346</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.608957</v>
+        <v>-34.575773</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -5661,7 +5647,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>PUE-C</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5673,22 +5659,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">7921 </t>
+          <t>43</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12/17/2025</t>
+          <t>12/16/2025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>O'HIGGINS 4298</t>
+          <t>DIAZ, CESAR, GRAL. 2053</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5703,12 +5689,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>811198660</t>
+          <t>811198627</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>poste inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5723,21 +5709,21 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L62" t="n">
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.468046</v>
+        <v>-58.468739</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.541893</v>
+        <v>-34.608957</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -5747,7 +5733,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5759,7 +5745,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>-706</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5769,12 +5755,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PAZ, MARCOS 1505</t>
+          <t>O'HIGGINS 4298</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5789,12 +5775,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>811181316</t>
+          <t>811198660</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>poste inclinado</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5809,21 +5795,21 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L63" t="n">
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.500094</v>
+        <v>-58.468046</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.626115</v>
+        <v>-34.541893</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5833,7 +5819,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>DEV-I</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5845,22 +5831,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>-706</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/17/2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve"> O'HIGGINS 4321</t>
+          <t>PAZ, MARCOS 1505</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5875,12 +5861,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>811198748</t>
+          <t>811181316</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>poste inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5895,21 +5881,21 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L64" t="n">
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.468227</v>
+        <v>-58.500094</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.541506</v>
+        <v>-34.626115</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -5919,7 +5905,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>DEV-I</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -6189,7 +6175,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">7969 </t>
+          <t>7969</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6361,7 +6347,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">7215 </t>
+          <t>7215</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6619,7 +6605,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">8090 </t>
+          <t>8090</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6705,7 +6691,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">8173 </t>
+          <t>8173</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8167,7 +8153,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">8112 </t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8253,7 +8239,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">8114 </t>
+          <t>8114</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8671,7 +8657,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">6428 </t>
+          <t>6428</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9777,17 +9763,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S01406737</t>
+          <t>S01406812</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>GRECIA 4281</t>
+          <t xml:space="preserve">VUELTA DE OBLIGADO 3201 </t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9807,12 +9793,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>811626921</t>
+          <t>811626783</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>inlinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -9834,10 +9820,10 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.466965</v>
+        <v>-58.464784</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.541488</v>
+        <v>-34.551419</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -9851,7 +9837,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>BLO-R</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9863,17 +9849,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S01406812</t>
+          <t>S00019326</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">VUELTA DE OBLIGADO 3201 </t>
+          <t>OLLEROS 3050</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9893,12 +9879,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>811626783</t>
+          <t>811627002</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -9920,24 +9906,24 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.464784</v>
+        <v>-58.447708</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.551419</v>
+        <v>-34.577055</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>BLO-R</t>
+          <t>ATH-P</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9949,7 +9935,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S00019326</t>
+          <t>S00021988</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9959,7 +9945,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>OLLEROS 3050</t>
+          <t>ALVAREZ THOMAS AV. 1115</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -9979,12 +9965,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>811627002</t>
+          <t>811626996</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10006,24 +9992,24 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.447708</v>
+        <v>-58.457565</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.577055</v>
+        <v>-34.578379</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>ATH-P</t>
+          <t>ATH-O</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10035,7 +10021,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S00021988</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10045,12 +10031,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ALVAREZ THOMAS AV. 1115</t>
+          <t xml:space="preserve">SANABRIA 2386 </t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10065,12 +10051,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>811626996</t>
+          <t>811626991</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10085,21 +10071,21 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.457565</v>
+        <v>-58.503452</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.578379</v>
+        <v>-34.614501</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -10109,7 +10095,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>ATH-O</t>
+          <t>DEV-D</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10121,7 +10107,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>S01450787</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10131,12 +10117,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANABRIA 2386 </t>
+          <t>HERNANDEZ, JOSE 2110</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10151,12 +10137,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>811626991</t>
+          <t>811626983</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -10178,14 +10164,14 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.503452</v>
+        <v>-58.450727</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.614501</v>
+        <v>-34.56425</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -10195,7 +10181,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>DEV-D</t>
+          <t>BLO-M</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10207,22 +10193,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S01450787</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>HERNANDEZ, JOSE 2110</t>
+          <t>Gamarra 1546</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -10237,12 +10223,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>811626983</t>
+          <t>811627113</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -10257,21 +10243,21 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L115" t="n">
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.450727</v>
+        <v>-58.477231</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.56425</v>
+        <v>-34.58242</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -10281,7 +10267,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>BLO-M</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10293,7 +10279,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>-745</t>
+          <t>S00036520</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10303,12 +10289,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Gamarra 1546</t>
+          <t>SEGUROLA AV. 856</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10323,12 +10309,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>811627113</t>
+          <t>811627070</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>corroidaq</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -10350,14 +10336,14 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.477231</v>
+        <v>-58.490765</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.58242</v>
+        <v>-34.627337</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -10367,7 +10353,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>DEV-I</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10379,7 +10365,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S00036520</t>
+          <t>900009468810</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10389,12 +10375,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SEGUROLA AV. 856</t>
+          <t xml:space="preserve">CUENCA 3033 </t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10409,12 +10395,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>811627070</t>
+          <t>811627041</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>corroidaq</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -10429,17 +10415,17 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L117" t="n">
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.490765</v>
+        <v>-58.494814</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.627337</v>
+        <v>-34.601905</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -10453,7 +10439,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>DEV-I</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10465,22 +10451,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">900009468810 </t>
+          <t>S01337226</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/6/2026</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUENCA 3033 </t>
+          <t>MOLDES 3055</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10495,12 +10481,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>811627041</t>
+          <t>811627125</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -10515,21 +10501,21 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L118" t="n">
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.494814</v>
+        <v>-58.466692</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.601905</v>
+        <v>-34.555283</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -10539,7 +10525,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10551,7 +10537,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S01337226</t>
+          <t>S01375612</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10561,7 +10547,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MOLDES 3055</t>
+          <t>LACROZE, FEDERICO AV. 2834</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -10581,12 +10567,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>811627125</t>
+          <t>811627118</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroidaq</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -10608,24 +10594,24 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.466692</v>
+        <v>-58.447177</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.555283</v>
+        <v>-34.574158</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>ATH-P</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10637,22 +10623,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S01375612</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2/6/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>LACROZE, FEDERICO AV. 2834</t>
+          <t>ARENGREEN 1584</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -10667,12 +10653,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>811627118</t>
+          <t>812440072</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>corroidaq</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -10687,21 +10673,21 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L120" t="n">
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.447177</v>
+        <v>-58.453265</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.574158</v>
+        <v>-34.615073</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -10711,7 +10697,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>ATH-P</t>
+          <t>NRA-I</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10723,7 +10709,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">8301 </t>
+          <t>8322</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10733,12 +10719,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ARENGREEN 1584</t>
+          <t>ARENAL, CONCEPCION 3814</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -10753,12 +10739,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>812440072</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -10768,36 +10754,36 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L121" t="n">
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.453265</v>
+        <v>-58.447805</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.615073</v>
+        <v>-34.587018</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>NRA-I</t>
+          <t>ATH-L</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10809,7 +10795,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10819,7 +10805,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ARENAL, CONCEPCION 3814</t>
+          <t>WARNES AV. 2239</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10839,12 +10825,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440018</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -10854,7 +10840,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -10866,14 +10852,14 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.447805</v>
+        <v>-58.467815</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.587018</v>
+        <v>-34.596225</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -10883,7 +10869,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>ATH-L</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10895,7 +10881,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10905,7 +10891,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>WARNES AV. 2239</t>
+          <t>PAZ SOLDAN 4991</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10925,12 +10911,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>812440018</t>
+          <t>812439995</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base quebrada</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -10945,17 +10931,17 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L123" t="n">
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.467815</v>
+        <v>-58.468466</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.596225</v>
+        <v>-34.594154</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
@@ -10981,7 +10967,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10991,12 +10977,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>PAZ SOLDAN 4991</t>
+          <t xml:space="preserve"> GUALEGUAYCHU 4754</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11011,12 +10997,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>812439995</t>
+          <t>812439956</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>base quebrada</t>
+          <t>inclinado, base quebrada</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -11038,10 +11024,10 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.468466</v>
+        <v>-58.518803</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.594154</v>
+        <v>-34.595866</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -11055,7 +11041,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11067,7 +11053,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11077,12 +11063,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GUALEGUAYCHU 4754</t>
+          <t>BLANCO ENCALADA 823</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11097,12 +11083,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>812439956</t>
+          <t>812439941</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>inclinado, base quebrada</t>
+          <t>inclinado base quebrada</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -11124,14 +11110,14 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.518803</v>
+        <v>-58.442692</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.595866</v>
+        <v>-34.549454</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -11141,7 +11127,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>BLO-B</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11153,22 +11139,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>BLANCO ENCALADA 823</t>
+          <t>DORREGO AV. 2699</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11183,12 +11169,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>812439941</t>
+          <t>812440089</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>inclinado base quebrada</t>
+          <t>base corrodia</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -11203,31 +11189,31 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L126" t="n">
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.442692</v>
+        <v>-58.432807</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.549454</v>
+        <v>-34.574343</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>BLO-B</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11239,22 +11225,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2699</t>
+          <t>BEIRO, FRANCISCO AV. 2435</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11269,12 +11255,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>812440089</t>
+          <t>812440250</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>base corrodia</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -11296,24 +11282,24 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.432807</v>
+        <v>-58.488914</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.574343</v>
+        <v>-34.59164</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11325,7 +11311,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11335,7 +11321,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BEIRO, FRANCISCO AV. 2435</t>
+          <t>CARACAS 3559</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -11355,12 +11341,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>812440250</t>
+          <t>812440223</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -11382,10 +11368,10 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.488914</v>
+        <v>-58.487793</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.59164</v>
+        <v>-34.590403</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -11411,7 +11397,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8368</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11421,7 +11407,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CARACAS 3559</t>
+          <t>CARACAS 3519</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -11441,12 +11427,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>812440223</t>
+          <t>812503552</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -11468,10 +11454,10 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.487793</v>
+        <v>-58.487627</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.590403</v>
+        <v>-34.590585</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -11497,7 +11483,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11507,12 +11493,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CARACAS 3519</t>
+          <t>VARELA, JOSE PEDRO 3545</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -11527,12 +11513,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>812503552</t>
+          <t>812440219</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -11547,17 +11533,17 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L130" t="n">
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.487627</v>
+        <v>-58.502073</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.590585</v>
+        <v>-34.601294</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -11571,7 +11557,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11583,7 +11569,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11593,12 +11579,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>VARELA, JOSE PEDRO 3545</t>
+          <t>ANDONAEGUI 2383</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11613,12 +11599,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>812440219</t>
+          <t>812440211</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -11633,17 +11619,17 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L131" t="n">
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.502073</v>
+        <v>-58.489606</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.601294</v>
+        <v>-34.57655</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -11657,7 +11643,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>ATH-C</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11669,7 +11655,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11679,7 +11665,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ANDONAEGUI 2383</t>
+          <t>CRAMER 4262</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -11699,7 +11685,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>812440211</t>
+          <t>812440206</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -11726,14 +11712,14 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.489606</v>
+        <v>-58.476168</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.57655</v>
+        <v>-34.545546</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -11743,7 +11729,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>ATH-C</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11755,7 +11741,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11765,7 +11751,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>CRAMER 4262</t>
+          <t xml:space="preserve">CRAMER 4322 </t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -11785,12 +11771,12 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>812440206</t>
+          <t>812440204</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>base corroida inclnada</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -11812,10 +11798,10 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.476168</v>
+        <v>-58.476454</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.545546</v>
+        <v>-34.544962</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -11841,7 +11827,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8382</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11851,12 +11837,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRAMER 4322 </t>
+          <t>SANTO TOME 3588</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -11871,12 +11857,12 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>812440204</t>
+          <t>812440197</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>base corroida inclnada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -11891,21 +11877,21 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L134" t="n">
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.476454</v>
+        <v>-58.4947</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.544962</v>
+        <v>-34.60925</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -11915,7 +11901,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>DEV-D</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11927,7 +11913,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>S00117686</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11937,12 +11923,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SANTO TOME 3588</t>
+          <t>DORREGO AV. 2778</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -11957,12 +11943,12 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>812440197</t>
+          <t>812440183</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inlinada</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -11977,31 +11963,31 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L135" t="n">
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.4947</v>
+        <v>-58.432102</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.60925</v>
+        <v>-34.574248</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>DEV-D</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -12013,7 +11999,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S00117686</t>
+          <t>S00506048</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12023,12 +12009,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2778</t>
+          <t>TERRADA 1088</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12043,17 +12029,17 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>812440183</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>inlinada</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Tensor</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -12063,31 +12049,31 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L136" t="n">
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.432102</v>
+        <v>-58.472866</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.574248</v>
+        <v>-34.620121</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>NRA-M</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12099,22 +12085,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S00506048</t>
+          <t>-748</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>TERRADA 1088</t>
+          <t>GUTENBERG 340</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12129,17 +12115,17 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440623</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>inclinado base podrida</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Tensor</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -12149,17 +12135,17 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.472866</v>
+        <v>-58.471395</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.620121</v>
+        <v>-34.592451</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -12173,7 +12159,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>NRA-M</t>
+          <t>PUE-?</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12185,7 +12171,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>-748</t>
+          <t>-750</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12195,12 +12181,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>GUTENBERG 340</t>
+          <t>JURAMENTO 4979</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12215,12 +12201,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>812440623</t>
+          <t>812440599</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>inclinado base podrida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -12235,17 +12221,17 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L138" t="n">
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.471395</v>
+        <v>-58.481188</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.592451</v>
+        <v>-34.577198</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -12259,7 +12245,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>PUE-?</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12271,7 +12257,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>-750</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12281,12 +12267,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>JURAMENTO 4979</t>
+          <t>CISNEROS, VIRREY 1610</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12301,7 +12287,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>812440599</t>
+          <t>812440520</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -12321,17 +12307,17 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L139" t="n">
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.481188</v>
+        <v>-58.469727</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.577198</v>
+        <v>-34.612013</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -12345,7 +12331,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12357,7 +12343,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>-753</t>
+          <t>-754</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12367,12 +12353,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>CISNEROS, VIRREY 1610</t>
+          <t>PINO, VIRREY DEL 1503</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12387,7 +12373,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>812440520</t>
+          <t>812440515</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -12407,21 +12393,21 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.469727</v>
+        <v>-58.442723</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.612013</v>
+        <v>-34.56085</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -12431,7 +12417,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>BLO-A</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12443,7 +12429,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>-754</t>
+          <t>-755</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12453,12 +12439,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PINO, VIRREY DEL 1503</t>
+          <t>CONDE 4296</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12473,12 +12459,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>812440515</t>
+          <t>812440509</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -12500,10 +12486,10 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.442723</v>
+        <v>-58.481187</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.56085</v>
+        <v>-34.548301</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -12517,7 +12503,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>BLO-A</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12529,7 +12515,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>-755</t>
+          <t>8550</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12539,12 +12525,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CONDE 4296</t>
+          <t>FRAGATA PRES. SARMIENTO 1390</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12559,12 +12545,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>812440509</t>
+          <t>812440373</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -12586,14 +12572,14 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.481187</v>
+        <v>-58.456778</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.548301</v>
+        <v>-34.609187</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -12603,7 +12589,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>NRA-I</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12615,7 +12601,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>-757</t>
+          <t>-761</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12625,12 +12611,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>FRAGATA PRES. SARMIENTO 1390</t>
+          <t>MOLDES 2901</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12645,7 +12631,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>812440373</t>
+          <t>812440341</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -12672,14 +12658,14 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.456778</v>
+        <v>-58.465305</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.609187</v>
+        <v>-34.556794</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -12689,7 +12675,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>NRA-I</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12701,7 +12687,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>-761</t>
+          <t>S00506118</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12711,12 +12697,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>MOLDES 2901</t>
+          <t>TERRERO 588</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -12731,12 +12717,12 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>812440341</t>
+          <t>812440289</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -12758,24 +12744,24 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.465305</v>
+        <v>-58.459689</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.556794</v>
+        <v>-34.620032</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>NRA-D</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12787,22 +12773,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S00506118</t>
+          <t>S01295589</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/24/2026</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>TERRERO 588</t>
+          <t>CABILDO AV. 1008</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12817,7 +12803,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>812440289</t>
+          <t>812440653</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -12844,24 +12830,24 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.459689</v>
+        <v>-58.446714</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.620032</v>
+        <v>-34.569183</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>NRA-D</t>
+          <t>COG-C</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12873,7 +12859,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S01295589</t>
+          <t>S01406719</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12883,7 +12869,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CABILDO AV. 1008</t>
+          <t>3 DE FEBRERO 4481</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12903,7 +12889,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>812440653</t>
+          <t>812440639</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -12923,21 +12909,21 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L146" t="n">
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.446714</v>
+        <v>-58.467166</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.569183</v>
+        <v>-34.539469</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -12947,7 +12933,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>COG-C</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12959,22 +12945,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S01406719</t>
+          <t>S00867165</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2/24/2026</t>
+          <t>2/26/2026</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>3 DE FEBRERO 4481</t>
+          <t xml:space="preserve"> VALLEJOS 2250</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -12989,12 +12975,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>812440639</t>
+          <t>812503628</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -13009,21 +12995,21 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L147" t="n">
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.467166</v>
+        <v>-58.493418</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.539469</v>
+        <v>-34.583307</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -13033,7 +13019,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>PUE-K</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -13045,7 +13031,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S00867165</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13055,12 +13041,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VALLEJOS 2250</t>
+          <t xml:space="preserve">ESTADO PLURINACIONAL DE BOLIVIA 3526 </t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13075,7 +13061,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>812503628</t>
+          <t>812503597</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -13102,10 +13088,10 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.493418</v>
+        <v>-58.491306</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.583307</v>
+        <v>-34.592511</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -13119,7 +13105,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>PUE-K</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13131,7 +13117,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">8392 </t>
+          <t>8397</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13141,7 +13127,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESTADO PLURINACIONAL DE BOLIVIA 3526 </t>
+          <t>TERRADA 3739</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -13161,12 +13147,12 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>812503597</t>
+          <t>812503610</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -13188,10 +13174,10 @@
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.491306</v>
+        <v>-58.494807</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.592511</v>
+        <v>-34.592416</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -13217,7 +13203,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>8397</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13227,7 +13213,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>TERRADA 3739</t>
+          <t xml:space="preserve"> TERRADA 3695 </t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -13247,7 +13233,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>812503610</t>
+          <t>812503605</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -13274,10 +13260,10 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.494807</v>
+        <v>-58.494371</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.592416</v>
+        <v>-34.592899</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -13303,22 +13289,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>8398</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2/26/2026</t>
+          <t>2/27/2026</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TERRADA 3695 </t>
+          <t>SIMBRON 5855</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13333,12 +13319,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>812503605</t>
+          <t>812503637</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -13353,21 +13339,21 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L151" t="n">
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>-58.494371</v>
+        <v>-58.527129</v>
       </c>
       <c r="N151" t="n">
-        <v>-34.592899</v>
+        <v>-34.620962</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -13377,7 +13363,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>DEV-G</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -13389,22 +13375,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>-765</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2/27/2026</t>
+          <t>3/2/2026</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SIMBRON 5855</t>
+          <t>AVALOS 180</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13419,12 +13405,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>812503637</t>
+          <t>812503657</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -13439,21 +13425,21 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L152" t="n">
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.527129</v>
+        <v>-58.465874</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.620962</v>
+        <v>-34.594613</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -13463,7 +13449,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>DEV-G</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -13475,7 +13461,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>-765</t>
+          <t>S00208304</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13485,12 +13471,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>AVALOS 180</t>
+          <t>CONDE 3080</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13505,12 +13491,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>812503657</t>
+          <t>812503654</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -13532,14 +13518,14 @@
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>-58.465874</v>
+        <v>-58.47322</v>
       </c>
       <c r="N153" t="n">
-        <v>-34.594613</v>
+        <v>-34.558645</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -13549,7 +13535,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -13561,7 +13547,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S00208304</t>
+          <t>-768</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13571,12 +13557,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>CONDE 3080</t>
+          <t>CONCORDIA 3581</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13591,7 +13577,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>812503654</t>
+          <t>812503649</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -13611,21 +13597,21 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L154" t="n">
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>-58.47322</v>
+        <v>-58.502724</v>
       </c>
       <c r="N154" t="n">
-        <v>-34.558645</v>
+        <v>-34.599311</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -13635,7 +13621,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -13647,7 +13633,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>-768</t>
+          <t>-767</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13657,7 +13643,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>CONCORDIA 3581</t>
+          <t>CONCORDIA 3525</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -13677,7 +13663,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>812503649</t>
+          <t>812503647</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -13704,10 +13690,10 @@
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>-58.502724</v>
+        <v>-58.502389</v>
       </c>
       <c r="N155" t="n">
-        <v>-34.599311</v>
+        <v>-34.599679</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -13733,7 +13719,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>-767</t>
+          <t>-769</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13743,12 +13729,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>CONCORDIA 3525</t>
+          <t>RIVERA, PEDRO I., DR. 2734</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13763,12 +13749,12 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>812503647</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -13778,26 +13764,26 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L156" t="n">
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>-58.502389</v>
+        <v>-58.464354</v>
       </c>
       <c r="N156" t="n">
-        <v>-34.599679</v>
+        <v>-34.5587</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -13807,7 +13793,7 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -13819,22 +13805,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>-769</t>
+          <t>S00106358</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>3/2/2026</t>
+          <t>3/4/2026</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>RIVERA, PEDRO I., DR. 2734</t>
+          <t>TRONADOR 1194</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -13854,7 +13840,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -13864,7 +13850,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -13876,14 +13862,14 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>-58.464354</v>
+        <v>-58.466138</v>
       </c>
       <c r="N157" t="n">
-        <v>-34.5587</v>
+        <v>-34.579638</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -13893,7 +13879,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -13905,84 +13891,2144 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>S00106358</t>
+          <t>S00169078</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>3/4/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>TRONADOR 1194</t>
+          <t>LOPEZ, CARLOS ANTONIO 3911</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>inclinado</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" t="n">
+        <v>-58.516319</v>
+      </c>
+      <c r="N158" t="n">
+        <v>-34.593592</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>PUE-O</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>S00190060</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>3/5/2026</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OBISPO SAN ALBERTO 3176 </t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
+        <v>1</v>
+      </c>
+      <c r="M159" t="n">
+        <v>-58.509545</v>
+      </c>
+      <c r="N159" t="n">
+        <v>-34.584532</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>PUE-M</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>S00195815</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>3/5/2026</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>PEDRAZA, MANUELA 3345</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>1</v>
+      </c>
+      <c r="M160" t="n">
+        <v>-58.474542</v>
+      </c>
+      <c r="N160" t="n">
+        <v>-34.556088</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>COG-N</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>8491</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>3/6/2026</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>OROÑO, NICASIO 2540</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
         <is>
           <t>Pendiente ADM</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" t="n">
+        <v>-58.459566</v>
+      </c>
+      <c r="N161" t="n">
+        <v>-34.597579</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>NRA-N</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>ARATO-25058.PO.1NRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>8496</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>3/6/2026</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>COSTA RICA 5733</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>base corroida inclinada</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>1</v>
+      </c>
+      <c r="M162" t="n">
+        <v>-58.436004</v>
+      </c>
+      <c r="N162" t="n">
+        <v>-34.58156</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>ATH-M</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>8500</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>3/6/2026</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>LAVOISIER 3556</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
         <is>
           <t>inclinada</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
         <is>
           <t>Pasante</t>
         </is>
       </c>
-      <c r="L158" t="n">
-        <v>1</v>
-      </c>
-      <c r="M158" t="n">
-        <v>-58.466138</v>
-      </c>
-      <c r="N158" t="n">
-        <v>-34.579638</v>
-      </c>
-      <c r="O158" t="inlineStr">
-        <is>
-          <t>Colegiales</t>
-        </is>
-      </c>
-      <c r="P158" t="inlineStr">
+      <c r="L163" t="n">
+        <v>1</v>
+      </c>
+      <c r="M163" t="n">
+        <v>-58.502869</v>
+      </c>
+      <c r="N163" t="n">
+        <v>-34.567437</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
         <is>
           <t>Capital Norte</t>
         </is>
       </c>
-      <c r="Q158" t="inlineStr">
-        <is>
-          <t>ATH-H</t>
-        </is>
-      </c>
-      <c r="R158" t="inlineStr">
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>PUE-H</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>8508</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>3/6/2026</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>NEWBERY, JORGE 3117</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" t="n">
+        <v>-58.446446</v>
+      </c>
+      <c r="N164" t="n">
+        <v>-34.578293</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>ATH-B</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>8511</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>3/6/2026</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>SOLDADO DE LA INDEPENDENCIA 851</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
+        <v>1</v>
+      </c>
+      <c r="M165" t="n">
+        <v>-58.435443</v>
+      </c>
+      <c r="N165" t="n">
+        <v>-34.56693</v>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>BLO-I</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>900009605910</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>3/6/2026</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BORDABEHERE, ENZO 2801 </t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>columna inclinada</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
+      <c r="L166" t="n">
+        <v>1</v>
+      </c>
+      <c r="M166" t="n">
+        <v>-58.480297</v>
+      </c>
+      <c r="N166" t="n">
+        <v>-34.600118</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>PUE-A</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>8480</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>3/5/2026</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>NAZCA AV. 3312</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>columna inclinada</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" t="n">
+        <v>-58.492236</v>
+      </c>
+      <c r="N167" t="n">
+        <v>-34.598228</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>PUE-B</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>8519</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>3/9/2026</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>OROÑO, NICASIO 2170</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Columna Picada</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L168" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" t="n">
+        <v>-58.460865</v>
+      </c>
+      <c r="N168" t="n">
+        <v>-34.601594</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>NRA-N</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>ARATO-25058.PO.1NRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>8528</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>3/9/2026</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>MOLDES 3006</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Columna Picada</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>1</v>
+      </c>
+      <c r="M169" t="n">
+        <v>-58.466299</v>
+      </c>
+      <c r="N169" t="n">
+        <v>-34.555783</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>COG-L</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>8534</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>3/9/2026</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARGERICH 3561 </t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Columna Picada</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="n">
+        <v>-58.495986</v>
+      </c>
+      <c r="N170" t="n">
+        <v>-34.595286</v>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>PUE-G</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>8435</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>3/9/2026</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>DE LOS INCAS AV. 4857</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>corroida</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L171" t="n">
+        <v>1</v>
+      </c>
+      <c r="M171" t="n">
+        <v>-58.478518</v>
+      </c>
+      <c r="N171" t="n">
+        <v>-34.58436</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>ATH-S</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>8437</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>3/9/2026</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>AVALOS 1654</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
+        <v>1</v>
+      </c>
+      <c r="M172" t="n">
+        <v>-58.480338</v>
+      </c>
+      <c r="N172" t="n">
+        <v>-34.581544</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>ATH-D</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>8438</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>3/9/2026</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAMARRA 1751 </t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" t="n">
+        <v>-58.479932</v>
+      </c>
+      <c r="N173" t="n">
+        <v>-34.580069</v>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>ATH-D</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>8439</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>3/9/2026</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CADIZ 4091 </t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L174" t="n">
+        <v>1</v>
+      </c>
+      <c r="M174" t="n">
+        <v>-58.478929</v>
+      </c>
+      <c r="N174" t="n">
+        <v>-34.580774</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>ATH-D</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>8441</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>3/9/2026</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> VICTORICA, BENJAMIN, GENERAL, AV. 2330</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L175" t="n">
+        <v>1</v>
+      </c>
+      <c r="M175" t="n">
+        <v>-58.478983</v>
+      </c>
+      <c r="N175" t="n">
+        <v>-34.579669</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>ATH-D</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>8442</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>3/9/2026</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>BERNA 2425</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L176" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" t="n">
+        <v>-58.47814</v>
+      </c>
+      <c r="N176" t="n">
+        <v>-34.581156</v>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>ATH-D</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>8443</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>3/9/2026</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>BERNA 2449</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M177" t="n">
+        <v>-58.478248</v>
+      </c>
+      <c r="N177" t="n">
+        <v>-34.581288</v>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>ATH-D</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>8447</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>3/9/2026</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AVALOS 1301 </t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L178" t="n">
+        <v>1</v>
+      </c>
+      <c r="M178" t="n">
+        <v>-58.477244</v>
+      </c>
+      <c r="N178" t="n">
+        <v>-34.584896</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>ATH-G</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>8448</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>3/9/2026</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>GAMARRA 1504</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>inclinada corroida</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L179" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" t="n">
+        <v>-58.476783</v>
+      </c>
+      <c r="N179" t="n">
+        <v>-34.582937</v>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>ATH-S</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>8450</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>3/9/2026</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>GANDARA 3308</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L180" t="n">
+        <v>1</v>
+      </c>
+      <c r="M180" t="n">
+        <v>-58.485416</v>
+      </c>
+      <c r="N180" t="n">
+        <v>-34.586085</v>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>ATH-S</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>8449</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>3/9/2026</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>GIRIBONE 3355</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L181" t="n">
+        <v>1</v>
+      </c>
+      <c r="M181" t="n">
+        <v>-58.486528</v>
+      </c>
+      <c r="N181" t="n">
+        <v>-34.585612</v>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>ATH-S</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>-771</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2/18/2026</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>SAN BLAS 4112</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
+      <c r="L182" t="n">
+        <v>1</v>
+      </c>
+      <c r="M182" t="n">
+        <v>-58.494458</v>
+      </c>
+      <c r="N182" t="n">
+        <v>-34.620078</v>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>DEV-J</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_NEW.xlsx
+++ b/mapa_interactivo_NEW.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R148"/>
+  <dimension ref="A1:R147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Gamarra 1546</t>
+          <t>GAMARRA 1550</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8202,10 +8202,10 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.477231</v>
+        <v>-58.477255</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.58242</v>
+        <v>-34.582395</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -8317,22 +8317,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>900009468810</t>
+          <t>S01337226</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/6/2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUENCA 3033 </t>
+          <t>MOLDES 3055</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>811627041</t>
+          <t>811627125</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8367,21 +8367,21 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L93" t="n">
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.494814</v>
+        <v>-58.466692</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.601905</v>
+        <v>-34.555283</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8403,7 +8403,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S01337226</t>
+          <t>S01375612</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MOLDES 3055</t>
+          <t>LACROZE, FEDERICO AV. 2834</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>811627125</t>
+          <t>811627118</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroidaq</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -8460,24 +8460,24 @@
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.466692</v>
+        <v>-58.447177</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.555283</v>
+        <v>-34.574158</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>ATH-P</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8489,22 +8489,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S01375612</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2/6/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>LACROZE, FEDERICO AV. 2834</t>
+          <t>ARENGREEN 1584</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>811627118</t>
+          <t>812440072</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>corroidaq</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -8539,21 +8539,21 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L95" t="n">
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.447177</v>
+        <v>-58.453265</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.574158</v>
+        <v>-34.615073</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>ATH-P</t>
+          <t>NRA-I</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8575,7 +8575,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8585,12 +8585,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ARENGREEN 1584</t>
+          <t>ARENAL, CONCEPCION 3814</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>812440072</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -8620,36 +8620,36 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L96" t="n">
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.453265</v>
+        <v>-58.447805</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.615073</v>
+        <v>-34.587018</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>NRA-I</t>
+          <t>ATH-L</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8661,7 +8661,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ARENAL, CONCEPCION 3814</t>
+          <t>WARNES AV. 2239</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8691,12 +8691,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440018</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -8706,7 +8706,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -8718,14 +8718,14 @@
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.447805</v>
+        <v>-58.467815</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.587018</v>
+        <v>-34.596225</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>ATH-L</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8747,7 +8747,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>WARNES AV. 2239</t>
+          <t>PAZ SOLDAN 4991</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>812440018</t>
+          <t>812439995</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base quebrada</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -8797,17 +8797,17 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L98" t="n">
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.467815</v>
+        <v>-58.468466</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.596225</v>
+        <v>-34.594154</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PAZ SOLDAN 4991</t>
+          <t xml:space="preserve"> GUALEGUAYCHU 4754</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8863,12 +8863,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>812439995</t>
+          <t>812439956</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>base quebrada</t>
+          <t>inclinado, base quebrada</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -8890,10 +8890,10 @@
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.468466</v>
+        <v>-58.518803</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.594154</v>
+        <v>-34.595866</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8919,7 +8919,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8929,12 +8929,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GUALEGUAYCHU 4754</t>
+          <t>BLANCO ENCALADA 823</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>812439956</t>
+          <t>812439941</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>inclinado, base quebrada</t>
+          <t>inclinado base quebrada</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -8976,14 +8976,14 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.518803</v>
+        <v>-58.442692</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.595866</v>
+        <v>-34.549454</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>BLO-B</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9005,22 +9005,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BLANCO ENCALADA 823</t>
+          <t>DORREGO AV. 2699</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -9035,12 +9035,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>812439941</t>
+          <t>812440089</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>inclinado base quebrada</t>
+          <t>base corrodia</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9055,31 +9055,31 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L101" t="n">
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.442692</v>
+        <v>-58.432807</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.549454</v>
+        <v>-34.574343</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>BLO-B</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9091,22 +9091,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2699</t>
+          <t>BEIRO, FRANCISCO AV. 2435</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>812440089</t>
+          <t>812440250</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>base corrodia</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9148,24 +9148,24 @@
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.432807</v>
+        <v>-58.488914</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.574343</v>
+        <v>-34.59164</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9177,7 +9177,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BEIRO, FRANCISCO AV. 2435</t>
+          <t>CARACAS 3559</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -9207,12 +9207,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>812440250</t>
+          <t>812440223</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9234,10 +9234,10 @@
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.488914</v>
+        <v>-58.487793</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.59164</v>
+        <v>-34.590403</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8368</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CARACAS 3559</t>
+          <t>CARACAS 3519</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>812440223</t>
+          <t>812503552</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -9320,10 +9320,10 @@
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.487793</v>
+        <v>-58.487627</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.590403</v>
+        <v>-34.590585</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CARACAS 3519</t>
+          <t>VARELA, JOSE PEDRO 3545</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>812503552</t>
+          <t>812440219</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -9399,17 +9399,17 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L105" t="n">
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.487627</v>
+        <v>-58.502073</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.590585</v>
+        <v>-34.601294</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9435,7 +9435,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>VARELA, JOSE PEDRO 3545</t>
+          <t>ANDONAEGUI 2383</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>812440219</t>
+          <t>812440211</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -9485,17 +9485,17 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L106" t="n">
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.502073</v>
+        <v>-58.489606</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.601294</v>
+        <v>-34.57655</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>ATH-C</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9521,7 +9521,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ANDONAEGUI 2383</t>
+          <t>CRAMER 4262</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>812440211</t>
+          <t>812440206</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -9578,14 +9578,14 @@
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.489606</v>
+        <v>-58.476168</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.57655</v>
+        <v>-34.545546</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -9595,7 +9595,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>ATH-C</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9607,7 +9607,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CRAMER 4262</t>
+          <t xml:space="preserve">CRAMER 4322 </t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>812440206</t>
+          <t>812440204</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>base corroida inclnada</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -9664,10 +9664,10 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.476168</v>
+        <v>-58.476454</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.545546</v>
+        <v>-34.544962</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8382</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRAMER 4322 </t>
+          <t>SANTO TOME 3588</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>812440204</t>
+          <t>812440197</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>base corroida inclnada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -9743,21 +9743,21 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L109" t="n">
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.476454</v>
+        <v>-58.4947</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.544962</v>
+        <v>-34.60925</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>DEV-D</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -9779,7 +9779,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>S00117686</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SANTO TOME 3588</t>
+          <t>DORREGO AV. 2778</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9809,12 +9809,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>812440197</t>
+          <t>812440183</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inlinada</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -9829,31 +9829,31 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L110" t="n">
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.4947</v>
+        <v>-58.432102</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.60925</v>
+        <v>-34.574248</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>DEV-D</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9865,7 +9865,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S00117686</t>
+          <t>S00506048</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9875,12 +9875,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2778</t>
+          <t>TERRADA 1088</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9895,17 +9895,17 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>812440183</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>inlinada</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Tensor</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -9915,31 +9915,31 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L111" t="n">
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.432102</v>
+        <v>-58.472866</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.574248</v>
+        <v>-34.620121</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>NRA-M</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9951,22 +9951,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S00506048</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TERRADA 1088</t>
+          <t>CISNEROS, VIRREY 1610</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9981,17 +9981,17 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440520</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Tensor</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -10008,10 +10008,10 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.472866</v>
+        <v>-58.469727</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.620121</v>
+        <v>-34.612013</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>NRA-M</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10037,7 +10037,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8550</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CISNEROS, VIRREY 1610</t>
+          <t>FRAGATA PRES. SARMIENTO 1390</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>812440520</t>
+          <t>812440373</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -10087,17 +10087,17 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.469727</v>
+        <v>-58.456778</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.612013</v>
+        <v>-34.609187</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>NRA-I</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10123,7 +10123,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>8550</t>
+          <t>S00506118</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>FRAGATA PRES. SARMIENTO 1390</t>
+          <t>TERRERO 588</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>812440373</t>
+          <t>812440289</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -10180,24 +10180,24 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.456778</v>
+        <v>-58.459689</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.609187</v>
+        <v>-34.620032</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>NRA-I</t>
+          <t>NRA-D</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10209,22 +10209,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S00506118</t>
+          <t>S01295589</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/24/2026</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TERRERO 588</t>
+          <t>CABILDO AV. 1008</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>812440289</t>
+          <t>812440653</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -10266,24 +10266,24 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.459689</v>
+        <v>-58.446714</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.620032</v>
+        <v>-34.569183</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>NRA-D</t>
+          <t>COG-C</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10295,7 +10295,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S01295589</t>
+          <t>S01406719</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CABILDO AV. 1008</t>
+          <t>3 DE FEBRERO 4481</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>812440653</t>
+          <t>812440639</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -10345,21 +10345,21 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L116" t="n">
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.446714</v>
+        <v>-58.467166</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.569183</v>
+        <v>-34.539469</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>COG-C</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10381,22 +10381,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S01406719</t>
+          <t>S00867165</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2/24/2026</t>
+          <t>2/26/2026</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>3 DE FEBRERO 4481</t>
+          <t xml:space="preserve"> VALLEJOS 2250</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10411,12 +10411,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>812440639</t>
+          <t>812503628</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -10431,21 +10431,21 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L117" t="n">
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.467166</v>
+        <v>-58.493418</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.539469</v>
+        <v>-34.583307</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>PUE-K</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10467,7 +10467,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S00867165</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VALLEJOS 2250</t>
+          <t xml:space="preserve">ESTADO PLURINACIONAL DE BOLIVIA 3526 </t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10497,7 +10497,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>812503628</t>
+          <t>812503597</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -10524,10 +10524,10 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.493418</v>
+        <v>-58.491306</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.583307</v>
+        <v>-34.592511</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>PUE-K</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10553,7 +10553,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>8392</t>
+          <t>8397</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESTADO PLURINACIONAL DE BOLIVIA 3526 </t>
+          <t>TERRADA 3739</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>812503597</t>
+          <t>812503610</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -10610,10 +10610,10 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.491306</v>
+        <v>-58.494807</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.592511</v>
+        <v>-34.592416</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -10639,7 +10639,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>8397</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>TERRADA 3739</t>
+          <t xml:space="preserve"> TERRADA 3695 </t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>812503610</t>
+          <t>812503605</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -10696,10 +10696,10 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.494807</v>
+        <v>-58.494371</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.592416</v>
+        <v>-34.592899</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -10725,22 +10725,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>8398</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2/26/2026</t>
+          <t>2/27/2026</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TERRADA 3695 </t>
+          <t>SIMBRON 5855</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -10755,12 +10755,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>812503605</t>
+          <t>812503637</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -10775,21 +10775,21 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L121" t="n">
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.494371</v>
+        <v>-58.527129</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.592899</v>
+        <v>-34.620962</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>DEV-G</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10811,22 +10811,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>S00208304</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2/27/2026</t>
+          <t>3/2/2026</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SIMBRON 5855</t>
+          <t>CONDE 3080</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -10841,12 +10841,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>812503637</t>
+          <t>812503654</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -10861,21 +10861,21 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L122" t="n">
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.527129</v>
+        <v>-58.47322</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.620962</v>
+        <v>-34.558645</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>DEV-G</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10897,22 +10897,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S00208304</t>
+          <t>S00106358</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>3/2/2026</t>
+          <t>3/4/2026</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CONDE 3080</t>
+          <t>TRONADOR 1194</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>812503654</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -10954,14 +10954,14 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.47322</v>
+        <v>-58.466138</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.558645</v>
+        <v>-34.579638</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10983,22 +10983,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S00106358</t>
+          <t>S00169078</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3/4/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>TRONADOR 1194</t>
+          <t>LOPEZ, CARLOS ANTONIO 3911</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -11033,21 +11033,21 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L124" t="n">
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.466138</v>
+        <v>-58.516319</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.579638</v>
+        <v>-34.593592</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11069,7 +11069,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S00169078</t>
+          <t>S00190060</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11079,12 +11079,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>LOPEZ, CARLOS ANTONIO 3911</t>
+          <t xml:space="preserve">OBISPO SAN ALBERTO 3176 </t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -11119,17 +11119,17 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L125" t="n">
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.516319</v>
+        <v>-58.509545</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.593592</v>
+        <v>-34.584532</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>PUE-M</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11155,7 +11155,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S00190060</t>
+          <t>S00195815</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11165,7 +11165,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBISPO SAN ALBERTO 3176 </t>
+          <t>PEDRAZA, MANUELA 3345</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -11212,14 +11212,14 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.509545</v>
+        <v>-58.474542</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.584532</v>
+        <v>-34.556088</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>PUE-M</t>
+          <t>COG-N</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11241,22 +11241,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S00195815</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PEDRAZA, MANUELA 3345</t>
+          <t>OROÑO, NICASIO 2540</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11298,14 +11298,14 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.474542</v>
+        <v>-58.459566</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.556088</v>
+        <v>-34.597579</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -11315,19 +11315,19 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>COG-N</t>
+          <t>NRA-N</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1NRA</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11337,12 +11337,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>OROÑO, NICASIO 2540</t>
+          <t>COSTA RICA 5733</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11362,7 +11362,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -11384,36 +11384,36 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.459566</v>
+        <v>-58.436004</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.597579</v>
+        <v>-34.58156</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>NRA-N</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>COSTA RICA 5733</t>
+          <t>LAVOISIER 3556</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -11470,24 +11470,24 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.436004</v>
+        <v>-58.502869</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.58156</v>
+        <v>-34.567437</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>PUE-H</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11499,7 +11499,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>8508</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>LAVOISIER 3556</t>
+          <t>NEWBERY, JORGE 3117</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -11556,24 +11556,24 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.502869</v>
+        <v>-58.446446</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.567437</v>
+        <v>-34.578293</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>PUE-H</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11585,7 +11585,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 3117</t>
+          <t>SOLDADO DE LA INDEPENDENCIA 851</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11642,10 +11642,10 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.446446</v>
+        <v>-58.435443</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.578293</v>
+        <v>-34.56693</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11671,7 +11671,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>900009605910</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11681,12 +11681,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SOLDADO DE LA INDEPENDENCIA 851</t>
+          <t xml:space="preserve">BORDABEHERE, ENZO 2801 </t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -11721,31 +11721,31 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L132" t="n">
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.435443</v>
+        <v>-58.480297</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.56693</v>
+        <v>-34.600118</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>PUE-A</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11757,17 +11757,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>900009605910</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">BORDABEHERE, ENZO 2801 </t>
+          <t>NAZCA AV. 3312</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -11807,17 +11807,17 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L133" t="n">
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.480297</v>
+        <v>-58.492236</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.600118</v>
+        <v>-34.598228</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>PUE-A</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11843,22 +11843,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>8480</t>
+          <t>8519</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>NAZCA AV. 3312</t>
+          <t>OROÑO, NICASIO 2170</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>Columna Picada</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -11900,10 +11900,10 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.492236</v>
+        <v>-58.460865</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.598228</v>
+        <v>-34.601594</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -11917,19 +11917,19 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>NRA-N</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1NRA</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>8519</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11939,12 +11939,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>OROÑO, NICASIO 2170</t>
+          <t>MOLDES 3006</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -11979,21 +11979,21 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L135" t="n">
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.460865</v>
+        <v>-58.466299</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.601594</v>
+        <v>-34.555783</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -12003,19 +12003,19 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>NRA-N</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MOLDES 3006</t>
+          <t xml:space="preserve">ARGERICH 3561 </t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12065,21 +12065,21 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L136" t="n">
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.466299</v>
+        <v>-58.495986</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.555783</v>
+        <v>-34.595286</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12101,7 +12101,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARGERICH 3561 </t>
+          <t>DE LOS INCAS AV. 4857</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Columna Picada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -12158,10 +12158,10 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.495986</v>
+        <v>-58.478518</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.595286</v>
+        <v>-34.58436</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12187,7 +12187,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>8435</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12197,7 +12197,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>DE LOS INCAS AV. 4857</t>
+          <t>AVALOS 1654</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -12244,10 +12244,10 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.478518</v>
+        <v>-58.480338</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.58436</v>
+        <v>-34.581544</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12273,7 +12273,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>AVALOS 1654</t>
+          <t xml:space="preserve">GAMARRA 1751 </t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -12308,7 +12308,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -12330,10 +12330,10 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.480338</v>
+        <v>-58.479932</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.581544</v>
+        <v>-34.580069</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8439</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12369,7 +12369,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAMARRA 1751 </t>
+          <t xml:space="preserve">CADIZ 4091 </t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -12394,7 +12394,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -12416,10 +12416,10 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.479932</v>
+        <v>-58.478929</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.580069</v>
+        <v>-34.580774</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>8441</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12455,7 +12455,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">CADIZ 4091 </t>
+          <t xml:space="preserve"> VICTORICA, BENJAMIN, GENERAL, AV. 2330</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -12502,10 +12502,10 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.478929</v>
+        <v>-58.478983</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.580774</v>
+        <v>-34.579669</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>8442</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VICTORICA, BENJAMIN, GENERAL, AV. 2330</t>
+          <t>BERNA 2425</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -12588,10 +12588,10 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.478983</v>
+        <v>-58.47814</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.579669</v>
+        <v>-34.581156</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>BERNA 2425</t>
+          <t>BERNA 2449</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -12674,10 +12674,10 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.47814</v>
+        <v>-58.478248</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.581156</v>
+        <v>-34.581288</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>8443</t>
+          <t>8447</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12713,7 +12713,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>BERNA 2449</t>
+          <t xml:space="preserve">AVALOS 1301 </t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -12760,10 +12760,10 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.478248</v>
+        <v>-58.477244</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.581288</v>
+        <v>-34.584896</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>ATH-G</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12789,7 +12789,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>8447</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">AVALOS 1301 </t>
+          <t>GAMARRA 1504</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -12846,10 +12846,10 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.477244</v>
+        <v>-58.476783</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.584896</v>
+        <v>-34.582937</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>ATH-G</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12875,7 +12875,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>8448</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12885,7 +12885,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>GAMARRA 1504</t>
+          <t>GANDARA 3308</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -12932,10 +12932,10 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.476783</v>
+        <v>-58.485416</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.582937</v>
+        <v>-34.586085</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>8449</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>GANDARA 3308</t>
+          <t>GIRIBONE 3355</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -13018,10 +13018,10 @@
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.485416</v>
+        <v>-58.486528</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.586085</v>
+        <v>-34.585612</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -13039,92 +13039,6 @@
         </is>
       </c>
       <c r="R147" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>8449</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>3/9/2026</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>GIRIBONE 3355</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L148" t="n">
-        <v>1</v>
-      </c>
-      <c r="M148" t="n">
-        <v>-58.486528</v>
-      </c>
-      <c r="N148" t="n">
-        <v>-34.585612</v>
-      </c>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q148" t="inlineStr">
-        <is>
-          <t>ATH-S</t>
-        </is>
-      </c>
-      <c r="R148" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_NEW.xlsx
+++ b/mapa_interactivo_NEW.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R148"/>
+  <dimension ref="A1:R150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1707,17 +1707,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6/24/2025</t>
+          <t>6/30/2025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ciudad de la Paz 275</t>
+          <t>SOLER 6017</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>807763070</t>
+          <t>807851636</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Aplomar o cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1757,17 +1757,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L16" t="n">
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>-58.441049</v>
+        <v>-58.436808</v>
       </c>
       <c r="N16" t="n">
-        <v>-34.574625</v>
+        <v>-34.577464</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1793,22 +1793,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6295</t>
+          <t>6506</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6/30/2025</t>
+          <t>7/10/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SOLER 6017</t>
+          <t>Ohiggins 1611</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>807851636</t>
+          <t>808148679</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna podrida en la base</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1850,24 +1850,24 @@
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>-58.436808</v>
+        <v>-58.448993</v>
       </c>
       <c r="N17" t="n">
-        <v>-34.577464</v>
+        <v>-34.564383</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1879,22 +1879,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7/10/2025</t>
+          <t>7/17/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ohiggins 1611</t>
+          <t>Pedraza Manuela 4101</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>808148679</t>
+          <t>808400353</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Columna podrida en la base</t>
+          <t xml:space="preserve">Podrida en la base </t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1936,14 +1936,14 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>-58.448993</v>
+        <v>-58.481569</v>
       </c>
       <c r="N18" t="n">
-        <v>-34.564383</v>
+        <v>-34.559853</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>COG-N</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1965,22 +1965,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6538</t>
+          <t>6512</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7/17/2025</t>
+          <t>7/28/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pedraza Manuela 4101</t>
+          <t>GASCON 1195</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>808400353</t>
+          <t>808571975</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Podrida en la base </t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2022,24 +2022,24 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>-58.481569</v>
+        <v>-58.423127</v>
       </c>
       <c r="N19" t="n">
-        <v>-34.559853</v>
+        <v>-34.596476</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>COG-N</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2051,22 +2051,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6512</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7/28/2025</t>
+          <t>8/12/2025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GASCON 1195</t>
+          <t>RIVAS, GRAL. 2345</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2081,12 +2081,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>808571975</t>
+          <t>808918698</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2108,24 +2108,24 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>-58.423127</v>
+        <v>-58.482497</v>
       </c>
       <c r="N20" t="n">
-        <v>-34.596476</v>
+        <v>-34.598714</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>PUE-A</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2137,7 +2137,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>6917</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>RIVAS, GRAL. 2345</t>
+          <t>BRIN, MINISTRO 1375</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>808918698</t>
+          <t>808918700</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>PIcada</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2194,24 +2194,24 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>-58.482497</v>
+        <v>-58.355342</v>
       </c>
       <c r="N21" t="n">
-        <v>-34.598714</v>
+        <v>-34.63565</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>PUE-A</t>
+          <t>CON-G</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2223,22 +2223,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8/12/2025</t>
+          <t>8/14/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BRIN, MINISTRO 1375</t>
+          <t>SUPERI 1459</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2253,17 +2253,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>808918700</t>
+          <t>808972965</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>PIcada</t>
+          <t>Poste con base quebrada ver si es posible desmonte</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2273,31 +2273,31 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L22" t="n">
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>-58.355342</v>
+        <v>-58.460834</v>
       </c>
       <c r="N22" t="n">
-        <v>-34.63565</v>
+        <v>-34.573753</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>CON-G</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2309,22 +2309,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8/14/2025</t>
+          <t>8/25/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SUPERI 1459</t>
+          <t>VERA 445</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2339,17 +2339,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>808972965</t>
+          <t>809155622</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Poste con base quebrada ver si es posible desmonte</t>
+          <t>Correrla para sacarla del cantero</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2359,31 +2359,31 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L23" t="n">
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-58.460834</v>
+        <v>-58.437181</v>
       </c>
       <c r="N23" t="n">
-        <v>-34.573753</v>
+        <v>-34.5995</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2395,22 +2395,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>8/25/2025</t>
+          <t>9/1/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VERA 445</t>
+          <t>VILELA 3699</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2425,12 +2425,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>809155622</t>
+          <t>809371823</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Correrla para sacarla del cantero</t>
+          <t xml:space="preserve">Cambiar </t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2445,31 +2445,31 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L24" t="n">
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-58.437181</v>
+        <v>-58.482817</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.5995</v>
+        <v>-34.550845</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2481,17 +2481,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7111</t>
+          <t>S01186963</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9/1/2025</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>VILELA 3699</t>
+          <t>WASHINGTON 4273</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2511,12 +2511,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>809371823</t>
+          <t>809800217</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cambiar </t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L25" t="n">
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>-58.482817</v>
+        <v>-58.484798</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.550845</v>
+        <v>-34.550226</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2567,17 +2567,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S01186963</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>9/22/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>WASHINGTON 4273</t>
+          <t>RUIZ HUIDOBRO 3620</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2597,17 +2597,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>809800217</t>
+          <t>ICD30934235</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Trapaso de redes y desmonte</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2624,10 +2624,10 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-58.484798</v>
+        <v>-58.484082</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.550226</v>
+        <v>-34.549702</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2653,22 +2653,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>9/22/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RUIZ HUIDOBRO 3620</t>
+          <t>TRES ARROYOS 2911</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2683,17 +2683,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ICD30934235</t>
+          <t>810056868</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Trapaso de redes y desmonte</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2710,14 +2710,14 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-58.484082</v>
+        <v>-58.476877</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.549702</v>
+        <v>-34.617525</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>NRA-M</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2739,17 +2739,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>9/29/2025</t>
+          <t>10/6/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TRES ARROYOS 2911</t>
+          <t>MERCEDES 3774</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>810056868</t>
+          <t>810244452</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Poste inclinado</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2789,21 +2789,21 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L28" t="n">
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.476877</v>
+        <v>-58.511139</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.617525</v>
+        <v>-34.602167</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>NRA-M</t>
+          <t>PUE-P</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2825,22 +2825,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10/6/2025</t>
+          <t>10/8/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MERCEDES 3774</t>
+          <t>ESTADO PLURINACIONAL DE BOLIVIA 3965</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>810244452</t>
+          <t>810259142</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Poste inclinado</t>
+          <t>Aplomar poste</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2882,10 +2882,10 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>-58.511139</v>
+        <v>-58.493945</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.602167</v>
+        <v>-34.589471</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>PUE-P</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2911,22 +2911,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10/8/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ESTADO PLURINACIONAL DE BOLIVIA 3965</t>
+          <t>BULGARIA 4387</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2941,17 +2941,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>810259142</t>
+          <t>810333040</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Aplomar poste</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2968,10 +2968,10 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>-58.493945</v>
+        <v>-58.503223</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.589471</v>
+        <v>-34.590763</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>PUE-N</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2997,22 +2997,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7508</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>10/14/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BULGARIA 4387</t>
+          <t>11 DE SEPTIEMBRE DE 1888 3988</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>810333040</t>
+          <t>00995927</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Picada colocar columna para pedir traspasos tiene nodo teco y tlc</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3042,26 +3042,26 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L31" t="n">
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.503223</v>
+        <v>-58.4635</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.590763</v>
+        <v>-34.542844</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>PUE-N</t>
+          <t>BLO-F</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3083,22 +3083,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7508</t>
+          <t>8482</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10/14/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>11 DE SEPTIEMBRE DE 1888 3988</t>
+          <t>San Blas 2591</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>00995927</t>
+          <t>810416660</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Picada colocar columna para pedir traspasos tiene nodo teco y tlc</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3140,14 +3140,14 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.4635</v>
+        <v>-58.477427</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.542844</v>
+        <v>-34.609261</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>BLO-F</t>
+          <t>NRA-Q</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3169,22 +3169,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Blas 2591</t>
+          <t>CIUDAD DE LA PAZ 3008</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3199,12 +3199,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>810416660</t>
+          <t>810421914</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3226,14 +3226,14 @@
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.477427</v>
+        <v>-58.464818</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.609261</v>
+        <v>-34.554931</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>NRA-Q</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3255,22 +3255,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/29/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 3008</t>
+          <t>QUITO 4180</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>810421914</t>
+          <t>810471618</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3312,24 +3312,24 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.464818</v>
+        <v>-58.425596</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.554931</v>
+        <v>-34.617038</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3341,22 +3341,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>7697</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10/29/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>QUITO 4180</t>
+          <t>CONDE 4334</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>810471618</t>
+          <t>810487016</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Poste para cambiar o desmontar ver con inspector</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3391,31 +3391,31 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L35" t="n">
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.425596</v>
+        <v>-58.481509</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.617038</v>
+        <v>-34.547874</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3427,17 +3427,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7697</t>
+          <t>7806</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CONDE 4334</t>
+          <t>ROOSEVELT FRANKLIN D. 4665</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3457,12 +3457,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>810487016</t>
+          <t>810651339</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Poste para cambiar o desmontar ver con inspector</t>
+          <t>Poste inclinado</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3484,14 +3484,14 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.481509</v>
+        <v>-58.482196</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.547874</v>
+        <v>-34.570432</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>ATH-E</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3513,7 +3513,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3523,12 +3523,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ROOSEVELT FRANKLIN D. 4665</t>
+          <t>BURELA 1589</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>810651339</t>
+          <t>810651370</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Poste inclinado</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3563,21 +3563,21 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L37" t="n">
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.482196</v>
+        <v>-58.485747</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.570432</v>
+        <v>-34.58538</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>ATH-E</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3599,22 +3599,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7811</t>
+          <t>S00921590</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BURELA 1589</t>
+          <t>CASEROS AV. 3621</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>810651370</t>
+          <t>810804462</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>columna inclinada corroida</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3656,24 +3656,24 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.485747</v>
+        <v>-58.416134</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.58538</v>
+        <v>-34.638879</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S00921590</t>
+          <t>S00921597</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CASEROS AV. 3621</t>
+          <t>CASEROS AV. 3507</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>810804462</t>
+          <t>810804451</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3742,10 +3742,10 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.416134</v>
+        <v>-58.414769</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.638879</v>
+        <v>-34.638638</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S00921597</t>
+          <t>S01089776</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CASEROS AV. 3507</t>
+          <t>ARGERICH 3717</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>810804451</t>
+          <t>810804318</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>columna inclinada corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3828,24 +3828,24 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.414769</v>
+        <v>-58.497051</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.638638</v>
+        <v>-34.594109</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3857,22 +3857,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S01089776</t>
+          <t>S01126628</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ARGERICH 3717</t>
+          <t>RIVERA, PEDRO I., DR. 3385</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3887,12 +3887,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>810804318</t>
+          <t>810820813</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3914,14 +3914,14 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.497051</v>
+        <v>-58.47104</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.594109</v>
+        <v>-34.562322</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>COG-I</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3943,7 +3943,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S01126628</t>
+          <t>S01144183</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>RIVERA, PEDRO I., DR. 3385</t>
+          <t>DE LOS CONSTITUYENTES AV. 4318</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>810820813</t>
+          <t>810820640</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4000,14 +4000,14 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.47104</v>
+        <v>-58.490526</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.562322</v>
+        <v>-34.583417</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>COG-I</t>
+          <t>PUE-K</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4029,7 +4029,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S01144183</t>
+          <t>S01171313</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4039,12 +4039,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DE LOS CONSTITUYENTES AV. 4318</t>
+          <t xml:space="preserve"> LOPE DE VEGA AV. 3128 </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4059,12 +4059,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>810820640</t>
+          <t>810820624</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4086,14 +4086,14 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.490526</v>
+        <v>-58.525417</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.583417</v>
+        <v>-34.613865</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>PUE-K</t>
+          <t>DEV-G</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4115,7 +4115,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S01171313</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LOPE DE VEGA AV. 3128 </t>
+          <t>MAGARIÑOS CERVANTES, A. 4803</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>810820624</t>
+          <t>810820571</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada, tensor roto</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4165,17 +4165,17 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L44" t="n">
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.525417</v>
+        <v>-58.500609</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.613865</v>
+        <v>-34.626542</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>DEV-G</t>
+          <t>DEV-I</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4201,7 +4201,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MAGARIÑOS CERVANTES, A. 4803</t>
+          <t>DIAZ, CESAR, GRAL. 1450</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>810820571</t>
+          <t>810820533</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>inclinada, tensor roto</t>
+          <t>muy inclinada</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4251,21 +4251,21 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L45" t="n">
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.500609</v>
+        <v>-58.461219</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.626542</v>
+        <v>-34.605928</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>DEV-I</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4287,22 +4287,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7867</t>
+          <t>6436</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/26/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DIAZ, CESAR, GRAL. 1450</t>
+          <t xml:space="preserve">ARIAS 4306 </t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>810820533</t>
+          <t>810862832</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>muy inclinada</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4337,21 +4337,21 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L46" t="n">
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.461219</v>
+        <v>-58.49108</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.605928</v>
+        <v>-34.550102</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4373,22 +4373,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6436</t>
+          <t>900008939210</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>11/26/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARIAS 4306 </t>
+          <t xml:space="preserve"> LOPEZ, VICENTE 2099</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>810862832</t>
+          <t>811131662</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4430,24 +4430,24 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.49108</v>
+        <v>-58.394159</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.550102</v>
+        <v>-34.588587</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>RET-A</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -5405,22 +5405,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S01180016</t>
+          <t>01018482</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FITZ ROY 1730</t>
+          <t>AGUERO 2364</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5435,12 +5435,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>811454223</t>
+          <t xml:space="preserve">02511365 </t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5462,14 +5462,14 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.436051</v>
+        <v>-58.399462</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.583855</v>
+        <v>-34.585952</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>AGU-H</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5491,7 +5491,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S01180023</t>
+          <t>S01180016</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>VEGA, NICETO, CNEL. AV. 5420</t>
+          <t>FITZ ROY 1730</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>811454198</t>
+          <t>811454223</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5548,10 +5548,10 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.437628</v>
+        <v>-58.436051</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.587953</v>
+        <v>-34.583855</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>ATH-?</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5577,7 +5577,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S01180086</t>
+          <t>S01180023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BONPLAND 1471</t>
+          <t>VEGA, NICETO, CNEL. AV. 5420</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>811454194</t>
+          <t>811454198</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5634,10 +5634,10 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.439513</v>
+        <v>-58.437628</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.585314</v>
+        <v>-34.587953</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>ATH-?</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5663,7 +5663,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S01200482</t>
+          <t>S01180086</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GONZALEZ, ELPIDIO 2749</t>
+          <t>BONPLAND 1471</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>811454117</t>
+          <t>811454194</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>quebrada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5713,31 +5713,31 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L62" t="n">
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.481266</v>
+        <v>-58.439513</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.608522</v>
+        <v>-34.585314</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>NRA-O</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5749,7 +5749,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S01204059</t>
+          <t>S01200482</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BUFANO, ALFREDO R. 2580</t>
+          <t>GONZALEZ, ELPIDIO 2749</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>811454109</t>
+          <t>811454117</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>quebrada</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L63" t="n">
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.478411</v>
+        <v>-58.481266</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.6039</v>
+        <v>-34.608522</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>NRA-P</t>
+          <t>NRA-O</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5835,7 +5835,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S01220047</t>
+          <t>S01204059</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5845,12 +5845,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MAURE 2958</t>
+          <t>BUFANO, ALFREDO R. 2580</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>811454097</t>
+          <t>811454109</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5892,24 +5892,24 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.446339</v>
+        <v>-58.478411</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.576306</v>
+        <v>-34.6039</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>NRA-P</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5921,7 +5921,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S01306211</t>
+          <t>01211534</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>WASHINGTON 3943</t>
+          <t xml:space="preserve"> JUNCAL 2490</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>811453965</t>
+          <t>811454103</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5971,31 +5971,31 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.48286</v>
+        <v>-58.401685</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.55278</v>
+        <v>-34.591336</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6007,7 +6007,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S01313361</t>
+          <t>S01220047</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CABILDO AV. 805</t>
+          <t>MAURE 2958</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>811453963</t>
+          <t>811454097</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6057,31 +6057,31 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L66" t="n">
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.444955</v>
+        <v>-58.446339</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.569791</v>
+        <v>-34.576306</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>COG-C</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6093,7 +6093,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S01389798</t>
+          <t>S01306211</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU 4682</t>
+          <t>WASHINGTON 3943</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>811453943</t>
+          <t>811453965</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6143,21 +6143,21 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L67" t="n">
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.518214</v>
+        <v>-58.48286</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.596516</v>
+        <v>-34.55278</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6179,7 +6179,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S01384321</t>
+          <t>S01313361</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AZURDUY JUANA 2685</t>
+          <t>CABILDO AV. 805</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6209,12 +6209,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>811453930</t>
+          <t>811453963</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6229,21 +6229,21 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.469341</v>
+        <v>-58.444955</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.552269</v>
+        <v>-34.569791</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>COG-C</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6265,7 +6265,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S01392303</t>
+          <t>S01389798</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Moldes 1999</t>
+          <t>GUALEGUAYCHU 4682</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>811453918</t>
+          <t>811453943</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6322,14 +6322,14 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.458535</v>
+        <v>-58.518214</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.564674</v>
+        <v>-34.596516</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>COG-G</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6351,22 +6351,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>S01384321</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MANZANARES 3853</t>
+          <t>AZURDUY JUANA 2685</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>811454324</t>
+          <t>811453930</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6408,10 +6408,10 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.482488</v>
+        <v>-58.469341</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.554114</v>
+        <v>-34.552269</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6437,22 +6437,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>S01392303</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA DEL RIO 3789 </t>
+          <t>Moldes 1999</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6467,12 +6467,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>811454305</t>
+          <t>811453918</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6487,21 +6487,21 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L71" t="n">
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.482473</v>
+        <v>-58.458535</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.553018</v>
+        <v>-34.564674</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>COG-G</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6523,22 +6523,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8186</t>
+          <t>8095</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Nogoya 3644</t>
+          <t>MANZANARES 3853</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>811454515</t>
+          <t>811454324</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6580,14 +6580,14 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.497751</v>
+        <v>-58.482488</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.606408</v>
+        <v>-34.554114</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6609,22 +6609,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>8316</t>
+          <t>8094</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pje. Manuel Sola 4440</t>
+          <t xml:space="preserve">GARCIA DEL RIO 3789 </t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>811454508</t>
+          <t>811454305</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6659,21 +6659,21 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L73" t="n">
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.507954</v>
+        <v>-58.482473</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.610808</v>
+        <v>-34.553018</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>DEV-D</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6695,7 +6695,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MANZANARES 2073</t>
+          <t>Nogoya 3644</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>811454483</t>
+          <t>811454515</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6752,14 +6752,14 @@
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.465953</v>
+        <v>-58.497751</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.545637</v>
+        <v>-34.606408</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6781,7 +6781,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ARGERICH 5774</t>
+          <t>Pje. Manuel Sola 4440</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>811454454</t>
+          <t>811454508</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6831,21 +6831,21 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L75" t="n">
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.511147</v>
+        <v>-58.507954</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.578665</v>
+        <v>-34.610808</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>PUE-J</t>
+          <t>DEV-D</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -6867,22 +6867,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1/15/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ESTOMBA 212</t>
+          <t>MANZANARES 2073</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>811454532</t>
+          <t>811454483</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6917,21 +6917,21 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L76" t="n">
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.469045</v>
+        <v>-58.465953</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.588525</v>
+        <v>-34.545637</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6953,17 +6953,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MONROE 4070</t>
+          <t>ARGERICH 5774</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>811498053</t>
+          <t>811454454</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7003,21 +7003,21 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.475842</v>
+        <v>-58.511147</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.568215</v>
+        <v>-34.578665</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>ATH-J</t>
+          <t>PUE-J</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7039,22 +7039,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/15/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AZURDUY JUANA 3630</t>
+          <t>ESTOMBA 212</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>811498050</t>
+          <t>811454532</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7089,21 +7089,21 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L78" t="n">
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.477583</v>
+        <v>-58.469045</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.5569</v>
+        <v>-34.588525</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>COG-N</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7125,22 +7125,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S01215930</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1/20/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>UGARTE, MANUEL 2750</t>
+          <t>MONROE 4070</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>811498072</t>
+          <t>811498053</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7182,14 +7182,14 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.465042</v>
+        <v>-58.475842</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.557947</v>
+        <v>-34.568215</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>ATH-J</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7211,17 +7211,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>8181</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1/22/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREIRE, RAMON, CAP. GRAL. 4748 </t>
+          <t>AZURDUY JUANA 3630</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>811498074</t>
+          <t>811498050</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>inclinada base quebrada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7261,17 +7261,17 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L80" t="n">
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.482951</v>
+        <v>-58.477583</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.544273</v>
+        <v>-34.5569</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>COG-N</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7297,22 +7297,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S01318042</t>
+          <t>S01215930</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/20/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>UGARTE, MANUEL 3815</t>
+          <t>UGARTE, MANUEL 2750</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7327,12 +7327,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>811626754</t>
+          <t>811498072</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7354,10 +7354,10 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.476138</v>
+        <v>-58.465042</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.563825</v>
+        <v>-34.557947</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>COG-N</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7383,22 +7383,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S01397288</t>
+          <t>8181</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/22/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOLDES 1918 </t>
+          <t xml:space="preserve">FREIRE, RAMON, CAP. GRAL. 4748 </t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7413,29 +7413,41 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811498074</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>inclinadaq</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
+          <t>inclinada base quebrada</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
       <c r="L82" t="n">
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.458035</v>
+        <v>-58.482951</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.565387</v>
+        <v>-34.544273</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -7445,7 +7457,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>COG-G</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7457,7 +7469,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S01397364</t>
+          <t>S01318042</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7467,12 +7479,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AVILES, VIRREY 3008</t>
+          <t>UGARTE, MANUEL 3815</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7487,12 +7499,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>811626732</t>
+          <t>811626754</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7514,14 +7526,14 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.457207</v>
+        <v>-58.476138</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.571602</v>
+        <v>-34.563825</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -7531,7 +7543,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>COG-N</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -7543,22 +7555,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S01396837</t>
+          <t>S01397288</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>DEHEZA 3622</t>
+          <t xml:space="preserve">MOLDES 1918 </t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7573,41 +7585,29 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>811626963</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>inclinado base quebrada</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Poste</t>
-        </is>
-      </c>
+          <t>inclinadaq</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
       <c r="L84" t="n">
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.485735</v>
+        <v>-58.458035</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.546249</v>
+        <v>-34.565387</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>COG-G</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -7629,17 +7629,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S01406731</t>
+          <t>S01397364</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CORREA 1807</t>
+          <t>AVILES, VIRREY 3008</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7659,12 +7659,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>811626953</t>
+          <t>811626732</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7686,14 +7686,14 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.466595</v>
+        <v>-58.457207</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.54099</v>
+        <v>-34.571602</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -7715,22 +7715,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S01406812</t>
+          <t>S01396837</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">VUELTA DE OBLIGADO 3201 </t>
+          <t>DEHEZA 3622</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7745,12 +7745,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>811626783</t>
+          <t>811626963</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinado base quebrada</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7765,17 +7765,17 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L86" t="n">
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.464784</v>
+        <v>-58.485735</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.551419</v>
+        <v>-34.546249</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>BLO-R</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7801,17 +7801,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S00019326</t>
+          <t>S01406731</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>OLLEROS 3050</t>
+          <t xml:space="preserve"> CORREA 1807</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>811627002</t>
+          <t>811626953</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7858,24 +7858,24 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.447708</v>
+        <v>-58.466595</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.577055</v>
+        <v>-34.54099</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>ATH-P</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7887,17 +7887,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S00021988</t>
+          <t>S01406812</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ALVAREZ THOMAS AV. 1115</t>
+          <t xml:space="preserve">VUELTA DE OBLIGADO 3201 </t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>811626996</t>
+          <t>811626783</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7944,14 +7944,14 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.457565</v>
+        <v>-58.464784</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.578379</v>
+        <v>-34.551419</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>ATH-O</t>
+          <t>BLO-R</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7973,7 +7973,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>S00019326</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7983,12 +7983,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANABRIA 2386 </t>
+          <t>OLLEROS 3050</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>811626991</t>
+          <t>811627002</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8023,31 +8023,31 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L89" t="n">
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.503452</v>
+        <v>-58.447708</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.614501</v>
+        <v>-34.577055</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>DEV-D</t>
+          <t>ATH-P</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8059,7 +8059,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S01450787</t>
+          <t>S00021988</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>HERNANDEZ, JOSE 2110</t>
+          <t>ALVAREZ THOMAS AV. 1115</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>811626983</t>
+          <t>811626996</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8109,17 +8109,17 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L90" t="n">
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.450727</v>
+        <v>-58.457565</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.56425</v>
+        <v>-34.578379</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>BLO-M</t>
+          <t>ATH-O</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8145,22 +8145,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8533</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GAMARRA 1550</t>
+          <t xml:space="preserve">SANABRIA 2386 </t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>811627113</t>
+          <t>811626991</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8195,21 +8195,21 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L91" t="n">
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.477255</v>
+        <v>-58.503452</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.582395</v>
+        <v>-34.614501</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>DEV-D</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8231,22 +8231,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S00036520</t>
+          <t>S01450787</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SEGUROLA AV. 856</t>
+          <t>HERNANDEZ, JOSE 2110</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>811627070</t>
+          <t>811626983</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>corroidaq</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8281,21 +8281,21 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L92" t="n">
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.490765</v>
+        <v>-58.450727</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.627337</v>
+        <v>-34.56425</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>DEV-I</t>
+          <t>BLO-M</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8317,22 +8317,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S01337226</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2/6/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MOLDES 3055</t>
+          <t>GAMARRA 1550</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>811627125</t>
+          <t>811627113</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8374,14 +8374,14 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.466692</v>
+        <v>-58.477255</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.555283</v>
+        <v>-34.582395</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8403,22 +8403,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S01375612</t>
+          <t>S00036520</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2/6/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>LACROZE, FEDERICO AV. 2834</t>
+          <t>SEGUROLA AV. 856</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>811627118</t>
+          <t>811627070</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -8460,24 +8460,24 @@
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.447177</v>
+        <v>-58.490765</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.574158</v>
+        <v>-34.627337</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>ATH-P</t>
+          <t>DEV-I</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8489,22 +8489,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>S01337226</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/6/2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ARENGREEN 1584</t>
+          <t>MOLDES 3055</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>812440072</t>
+          <t>811627125</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -8539,31 +8539,31 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L95" t="n">
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.453265</v>
+        <v>-58.466692</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.615073</v>
+        <v>-34.555283</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>NRA-I</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8575,22 +8575,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>S01375612</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/6/2026</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ARENAL, CONCEPCION 3814</t>
+          <t>LACROZE, FEDERICO AV. 2834</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811627118</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>corroidaq</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -8632,24 +8632,24 @@
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.447805</v>
+        <v>-58.447177</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.587018</v>
+        <v>-34.574158</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>ATH-L</t>
+          <t>ATH-P</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8661,7 +8661,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8671,12 +8671,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>WARNES AV. 2239</t>
+          <t>ARENGREEN 1584</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8691,12 +8691,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>812440018</t>
+          <t>812440072</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -8711,31 +8711,31 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L97" t="n">
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.467815</v>
+        <v>-58.453265</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.596225</v>
+        <v>-34.615073</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>NRA-I</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8747,7 +8747,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PAZ SOLDAN 4991</t>
+          <t>ARENAL, CONCEPCION 3814</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>812439995</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>base quebrada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -8792,26 +8792,26 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L98" t="n">
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.468466</v>
+        <v>-58.447805</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.594154</v>
+        <v>-34.587018</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>ATH-L</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8833,7 +8833,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GUALEGUAYCHU 4754</t>
+          <t>WARNES AV. 2239</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8863,12 +8863,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>812439956</t>
+          <t>812440018</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>inclinado, base quebrada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -8883,17 +8883,17 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L99" t="n">
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.518803</v>
+        <v>-58.467815</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.595866</v>
+        <v>-34.596225</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8919,7 +8919,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8929,12 +8929,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BLANCO ENCALADA 823</t>
+          <t>PAZ SOLDAN 4991</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>812439941</t>
+          <t>812439995</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>inclinado base quebrada</t>
+          <t>base quebrada</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -8976,14 +8976,14 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.442692</v>
+        <v>-58.468466</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.549454</v>
+        <v>-34.594154</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>BLO-B</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9005,22 +9005,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2699</t>
+          <t xml:space="preserve"> GUALEGUAYCHU 4754</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -9035,12 +9035,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>812440089</t>
+          <t>812439956</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>base corrodia</t>
+          <t>inclinado, base quebrada</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9055,31 +9055,31 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L101" t="n">
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.432807</v>
+        <v>-58.518803</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.574343</v>
+        <v>-34.595866</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9091,22 +9091,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BEIRO, FRANCISCO AV. 2435</t>
+          <t>BLANCO ENCALADA 823</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>812440250</t>
+          <t>812439941</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinado base quebrada</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9141,21 +9141,21 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L102" t="n">
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.488914</v>
+        <v>-58.442692</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.59164</v>
+        <v>-34.549454</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>BLO-B</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9177,22 +9177,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CARACAS 3559</t>
+          <t>DORREGO AV. 2699</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9207,12 +9207,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>812440223</t>
+          <t>812440089</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>base corrodia</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9234,24 +9234,24 @@
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.487793</v>
+        <v>-58.432807</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.590403</v>
+        <v>-34.574343</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9263,7 +9263,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CARACAS 3519</t>
+          <t>BEIRO, FRANCISCO AV. 2435</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>812503552</t>
+          <t>812440250</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -9320,10 +9320,10 @@
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.487627</v>
+        <v>-58.488914</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.590585</v>
+        <v>-34.59164</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>VARELA, JOSE PEDRO 3545</t>
+          <t>CARACAS 3559</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>812440219</t>
+          <t>812440223</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -9399,17 +9399,17 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L105" t="n">
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.502073</v>
+        <v>-58.487793</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.601294</v>
+        <v>-34.590403</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9435,7 +9435,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>8368</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ANDONAEGUI 2383</t>
+          <t>CARACAS 3519</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>812440211</t>
+          <t>812503552</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -9492,10 +9492,10 @@
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.489606</v>
+        <v>-58.487627</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.57655</v>
+        <v>-34.590585</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>ATH-C</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9521,7 +9521,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CRAMER 4262</t>
+          <t>VARELA, JOSE PEDRO 3545</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>812440206</t>
+          <t>812440219</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -9571,21 +9571,21 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L107" t="n">
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.476168</v>
+        <v>-58.502073</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.545546</v>
+        <v>-34.601294</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -9595,7 +9595,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9607,7 +9607,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRAMER 4322 </t>
+          <t>ANDONAEGUI 2383</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>812440204</t>
+          <t>812440211</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>base corroida inclnada</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -9664,14 +9664,14 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.476454</v>
+        <v>-58.489606</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.544962</v>
+        <v>-34.57655</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>ATH-C</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9693,7 +9693,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SANTO TOME 3588</t>
+          <t>CRAMER 4262</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>812440197</t>
+          <t>812440206</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -9743,21 +9743,21 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L109" t="n">
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.4947</v>
+        <v>-58.476168</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.60925</v>
+        <v>-34.545546</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>DEV-D</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -9779,7 +9779,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S00117686</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2778</t>
+          <t xml:space="preserve">CRAMER 4322 </t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9809,12 +9809,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>812440183</t>
+          <t>812440204</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>inlinada</t>
+          <t>base corroida inclnada</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -9836,24 +9836,24 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.432102</v>
+        <v>-58.476454</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.574248</v>
+        <v>-34.544962</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9865,7 +9865,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S00506048</t>
+          <t>8382</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9875,12 +9875,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TERRADA 1088</t>
+          <t>SANTO TOME 3588</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9895,17 +9895,17 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440197</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Tensor</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -9915,21 +9915,21 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L111" t="n">
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.472866</v>
+        <v>-58.4947</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.620121</v>
+        <v>-34.60925</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>NRA-M</t>
+          <t>DEV-D</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9951,22 +9951,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>S00117686</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CISNEROS, VIRREY 1610</t>
+          <t>DORREGO AV. 2778</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>812440520</t>
+          <t>812440183</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inlinada</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10001,31 +10001,31 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L112" t="n">
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.469727</v>
+        <v>-58.432102</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.612013</v>
+        <v>-34.574248</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10037,22 +10037,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>8550</t>
+          <t>S00506048</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>FRAGATA PRES. SARMIENTO 1390</t>
+          <t>TERRADA 1088</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10067,17 +10067,17 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>812440373</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Tensor</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -10087,17 +10087,17 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.456778</v>
+        <v>-58.472866</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.609187</v>
+        <v>-34.620121</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>NRA-I</t>
+          <t>NRA-M</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10123,7 +10123,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S00506118</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TERRERO 588</t>
+          <t>CISNEROS, VIRREY 1610</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>812440289</t>
+          <t>812440520</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -10173,31 +10173,31 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L114" t="n">
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.459689</v>
+        <v>-58.469727</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.620032</v>
+        <v>-34.612013</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>NRA-D</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10209,22 +10209,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S01295589</t>
+          <t>8550</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2/24/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CABILDO AV. 1008</t>
+          <t>FRAGATA PRES. SARMIENTO 1390</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -10239,12 +10239,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>812440653</t>
+          <t>812440373</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -10266,14 +10266,14 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.446714</v>
+        <v>-58.456778</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.569183</v>
+        <v>-34.609187</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -10283,7 +10283,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>COG-C</t>
+          <t>NRA-I</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10295,22 +10295,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S01406719</t>
+          <t>S00506118</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2/24/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>3 DE FEBRERO 4481</t>
+          <t>TERRERO 588</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>812440639</t>
+          <t>812440289</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -10345,31 +10345,31 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L116" t="n">
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.467166</v>
+        <v>-58.459689</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.539469</v>
+        <v>-34.620032</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>NRA-D</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10381,22 +10381,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S00867165</t>
+          <t>S01295589</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2/26/2026</t>
+          <t>2/24/2026</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VALLEJOS 2250</t>
+          <t>CABILDO AV. 1008</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10411,12 +10411,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>812503628</t>
+          <t>812440653</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -10438,14 +10438,14 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.493418</v>
+        <v>-58.446714</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.583307</v>
+        <v>-34.569183</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>PUE-K</t>
+          <t>COG-C</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10467,22 +10467,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>8392</t>
+          <t>S01406719</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2/26/2026</t>
+          <t>2/24/2026</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESTADO PLURINACIONAL DE BOLIVIA 3526 </t>
+          <t>3 DE FEBRERO 4481</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>812503597</t>
+          <t>812440639</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -10517,21 +10517,21 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L118" t="n">
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.491306</v>
+        <v>-58.467166</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.592511</v>
+        <v>-34.539469</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10553,7 +10553,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>8397</t>
+          <t>S00867165</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TERRADA 3739</t>
+          <t xml:space="preserve"> VALLEJOS 2250</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>812503610</t>
+          <t>812503628</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -10610,10 +10610,10 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.494807</v>
+        <v>-58.493418</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.592416</v>
+        <v>-34.583307</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>PUE-K</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10639,7 +10639,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>8398</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TERRADA 3695 </t>
+          <t xml:space="preserve">ESTADO PLURINACIONAL DE BOLIVIA 3526 </t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -10669,12 +10669,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>812503605</t>
+          <t>812503597</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -10696,10 +10696,10 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.494371</v>
+        <v>-58.491306</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.592899</v>
+        <v>-34.592511</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -10725,22 +10725,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>8397</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2/27/2026</t>
+          <t>2/26/2026</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SIMBRON 5855</t>
+          <t>TERRADA 3739</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -10755,12 +10755,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>812503637</t>
+          <t>812503610</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -10775,21 +10775,21 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L121" t="n">
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.527129</v>
+        <v>-58.494807</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.620962</v>
+        <v>-34.592416</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>DEV-G</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10811,22 +10811,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S00208304</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>3/2/2026</t>
+          <t>2/26/2026</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CONDE 3080</t>
+          <t xml:space="preserve"> TERRADA 3695 </t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>812503654</t>
+          <t>812503605</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -10868,14 +10868,14 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.47322</v>
+        <v>-58.494371</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.558645</v>
+        <v>-34.592899</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10897,22 +10897,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S00106358</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>3/4/2026</t>
+          <t>2/27/2026</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TRONADOR 1194</t>
+          <t>SIMBRON 5855</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812503637</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -10947,21 +10947,21 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L123" t="n">
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.466138</v>
+        <v>-58.527129</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.579638</v>
+        <v>-34.620962</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>DEV-G</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10983,22 +10983,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S00169078</t>
+          <t>S00208304</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/2/2026</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>LOPEZ, CARLOS ANTONIO 3911</t>
+          <t>CONDE 3080</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11013,12 +11013,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812503654</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -11033,21 +11033,21 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L124" t="n">
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.516319</v>
+        <v>-58.47322</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.593592</v>
+        <v>-34.558645</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11069,22 +11069,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S00190060</t>
+          <t>S00106358</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/4/2026</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBISPO SAN ALBERTO 3176 </t>
+          <t>TRONADOR 1194</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11126,14 +11126,14 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.509545</v>
+        <v>-58.466138</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.584532</v>
+        <v>-34.579638</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>PUE-M</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11155,7 +11155,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S00195815</t>
+          <t>S00169078</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11165,12 +11165,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PEDRAZA, MANUELA 3345</t>
+          <t>LOPEZ, CARLOS ANTONIO 3911</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -11205,21 +11205,21 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L126" t="n">
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.474542</v>
+        <v>-58.516319</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.556088</v>
+        <v>-34.593592</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>COG-N</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11241,22 +11241,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>S00190060</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>OROÑO, NICASIO 2540</t>
+          <t xml:space="preserve">OBISPO SAN ALBERTO 3176 </t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -11298,10 +11298,10 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.459566</v>
+        <v>-58.509545</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.597579</v>
+        <v>-34.584532</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -11315,34 +11315,34 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>NRA-N</t>
+          <t>PUE-M</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>S00195815</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>COSTA RICA 5733</t>
+          <t>PEDRAZA, MANUELA 3345</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11362,7 +11362,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -11384,24 +11384,24 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.436004</v>
+        <v>-58.474542</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.58156</v>
+        <v>-34.556088</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>COG-N</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11413,7 +11413,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>LAVOISIER 3556</t>
+          <t>OROÑO, NICASIO 2540</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -11470,10 +11470,10 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.502869</v>
+        <v>-58.459566</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.567437</v>
+        <v>-34.597579</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -11487,19 +11487,19 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>PUE-H</t>
+          <t>NRA-N</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1NRA</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 3117</t>
+          <t>COSTA RICA 5733</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -11556,10 +11556,10 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.446446</v>
+        <v>-58.436004</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.578293</v>
+        <v>-34.58156</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11585,7 +11585,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SOLDADO DE LA INDEPENDENCIA 851</t>
+          <t>LAVOISIER 3556</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -11642,24 +11642,24 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.435443</v>
+        <v>-58.502869</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.56693</v>
+        <v>-34.567437</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>PUE-H</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11671,7 +11671,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>900009605910</t>
+          <t>8508</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11681,12 +11681,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">BORDABEHERE, ENZO 2801 </t>
+          <t>NEWBERY, JORGE 3117</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -11721,31 +11721,31 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L132" t="n">
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.480297</v>
+        <v>-58.446446</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.600118</v>
+        <v>-34.578293</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>PUE-A</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11757,22 +11757,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>8480</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>NAZCA AV. 3312</t>
+          <t>SOLDADO DE LA INDEPENDENCIA 851</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -11814,24 +11814,24 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.492236</v>
+        <v>-58.435443</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.598228</v>
+        <v>-34.56693</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11843,22 +11843,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>8519</t>
+          <t>900009605910</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>OROÑO, NICASIO 2170</t>
+          <t xml:space="preserve">BORDABEHERE ENZO 2801 </t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Columna Picada</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -11893,17 +11893,17 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L134" t="n">
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.460865</v>
+        <v>-58.480297</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.601594</v>
+        <v>-34.600118</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -11917,34 +11917,34 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>NRA-N</t>
+          <t>PUE-A</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MOLDES 3006</t>
+          <t>NAZCA AV. 3312</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Columna Picada</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -11979,21 +11979,21 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L135" t="n">
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.466299</v>
+        <v>-58.492236</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.555783</v>
+        <v>-34.598228</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -12015,7 +12015,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>8519</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12025,7 +12025,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARGERICH 3561 </t>
+          <t>OROÑO, NICASIO 2170</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -12072,10 +12072,10 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.495986</v>
+        <v>-58.460865</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.595286</v>
+        <v>-34.601594</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -12089,19 +12089,19 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>NRA-N</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1NRA</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>8435</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12111,12 +12111,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>DE LOS INCAS AV. 4857</t>
+          <t>MOLDES 3006</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>Columna Picada</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -12151,21 +12151,21 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.478518</v>
+        <v>-58.466299</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.58436</v>
+        <v>-34.555783</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12187,7 +12187,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12197,7 +12197,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>AVALOS 1654</t>
+          <t xml:space="preserve">ARGERICH 3561 </t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>Columna Picada</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -12244,10 +12244,10 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.480338</v>
+        <v>-58.495986</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.581544</v>
+        <v>-34.595286</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12273,7 +12273,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAMARRA 1751 </t>
+          <t>DE LOS INCAS AV. 4857</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -12308,7 +12308,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -12330,10 +12330,10 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.479932</v>
+        <v>-58.478518</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.580069</v>
+        <v>-34.58436</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12359,7 +12359,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12369,7 +12369,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">CADIZ 4091 </t>
+          <t>AVALOS 1654</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -12416,10 +12416,10 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.478929</v>
+        <v>-58.480338</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.580774</v>
+        <v>-34.581544</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12455,7 +12455,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VICTORICA, BENJAMIN, GENERAL, AV. 2330</t>
+          <t xml:space="preserve">GAMARRA 1751 </t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -12502,10 +12502,10 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.478983</v>
+        <v>-58.479932</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.579669</v>
+        <v>-34.580069</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>8439</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>BERNA 2425</t>
+          <t xml:space="preserve">CADIZ 4091 </t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -12588,10 +12588,10 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.47814</v>
+        <v>-58.478929</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.581156</v>
+        <v>-34.580774</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>8443</t>
+          <t>8441</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>BERNA 2449</t>
+          <t xml:space="preserve"> VICTORICA, BENJAMIN, GENERAL, AV. 2330</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -12674,10 +12674,10 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.478248</v>
+        <v>-58.478983</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.581288</v>
+        <v>-34.579669</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>8447</t>
+          <t>8442</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12713,7 +12713,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">AVALOS 1301 </t>
+          <t>BERNA 2425</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -12760,10 +12760,10 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.477244</v>
+        <v>-58.47814</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.584896</v>
+        <v>-34.581156</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>ATH-G</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12789,7 +12789,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>8448</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>GAMARRA 1504</t>
+          <t>BERNA 2449</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -12846,10 +12846,10 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.476783</v>
+        <v>-58.478248</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.582937</v>
+        <v>-34.581288</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12875,7 +12875,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>8447</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12885,7 +12885,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>GANDARA 3308</t>
+          <t xml:space="preserve">AVALOS 1301 </t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -12932,10 +12932,10 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.485416</v>
+        <v>-58.477244</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.586085</v>
+        <v>-34.584896</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>ATH-G</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12961,7 +12961,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>GIRIBONE 3355</t>
+          <t>GAMARRA 1504</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -13018,10 +13018,10 @@
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.486528</v>
+        <v>-58.476783</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.585612</v>
+        <v>-34.582937</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -13047,80 +13047,252 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
+          <t>8450</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>3/9/2026</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>GANDARA 3308</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L148" t="n">
+        <v>1</v>
+      </c>
+      <c r="M148" t="n">
+        <v>-58.485416</v>
+      </c>
+      <c r="N148" t="n">
+        <v>-34.586085</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>ATH-S</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>8449</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>3/9/2026</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>GIRIBONE 3355</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="n">
+        <v>-58.486528</v>
+      </c>
+      <c r="N149" t="n">
+        <v>-34.585612</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>ATH-S</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
           <t>-771</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>2/18/2026</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
+      <c r="C150" t="inlineStr">
         <is>
           <t>SAN BLAS 4112</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="D150" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
         <is>
           <t>Pendiente ADM</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
         <is>
           <t>Poste</t>
         </is>
       </c>
-      <c r="L148" t="n">
-        <v>1</v>
-      </c>
-      <c r="M148" t="n">
+      <c r="L150" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" t="n">
         <v>-58.494458</v>
       </c>
-      <c r="N148" t="n">
+      <c r="N150" t="n">
         <v>-34.620078</v>
       </c>
-      <c r="O148" t="inlineStr">
+      <c r="O150" t="inlineStr">
         <is>
           <t>Devoto</t>
         </is>
       </c>
-      <c r="P148" t="inlineStr">
+      <c r="P150" t="inlineStr">
         <is>
           <t>Capital Norte</t>
         </is>
       </c>
-      <c r="Q148" t="inlineStr">
+      <c r="Q150" t="inlineStr">
         <is>
           <t>DEV-J</t>
         </is>
       </c>
-      <c r="R148" t="inlineStr">
+      <c r="R150" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_NEW.xlsx
+++ b/mapa_interactivo_NEW.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R150"/>
+  <dimension ref="A1:R141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1707,22 +1707,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6295</t>
+          <t>6506</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6/30/2025</t>
+          <t>7/10/2025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SOLER 6017</t>
+          <t>Ohiggins 1611</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>807851636</t>
+          <t>808148679</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna podrida en la base</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1764,24 +1764,24 @@
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>-58.436808</v>
+        <v>-58.448993</v>
       </c>
       <c r="N16" t="n">
-        <v>-34.577464</v>
+        <v>-34.564383</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1793,22 +1793,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7/10/2025</t>
+          <t>7/17/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ohiggins 1611</t>
+          <t>Pedraza Manuela 4101</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>808148679</t>
+          <t>808400353</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Columna podrida en la base</t>
+          <t xml:space="preserve">Podrida en la base </t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1850,14 +1850,14 @@
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>-58.448993</v>
+        <v>-58.481569</v>
       </c>
       <c r="N17" t="n">
-        <v>-34.564383</v>
+        <v>-34.559853</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>COG-N</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1879,22 +1879,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6538</t>
+          <t>6512</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7/17/2025</t>
+          <t>7/28/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pedraza Manuela 4101</t>
+          <t>GASCON 1195</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>808400353</t>
+          <t>808571975</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Podrida en la base </t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1936,24 +1936,24 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>-58.481569</v>
+        <v>-58.423127</v>
       </c>
       <c r="N18" t="n">
-        <v>-34.559853</v>
+        <v>-34.596476</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>COG-N</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1965,22 +1965,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6512</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7/28/2025</t>
+          <t>8/12/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GASCON 1195</t>
+          <t>RIVAS, GRAL. 2345</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>808571975</t>
+          <t>808918698</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2022,24 +2022,24 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>-58.423127</v>
+        <v>-58.482497</v>
       </c>
       <c r="N19" t="n">
-        <v>-34.596476</v>
+        <v>-34.598714</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>PUE-A</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2051,7 +2051,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>6917</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RIVAS, GRAL. 2345</t>
+          <t>BRIN, MINISTRO 1375</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2081,12 +2081,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>808918698</t>
+          <t>808918700</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>PIcada</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2108,24 +2108,24 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>-58.482497</v>
+        <v>-58.355342</v>
       </c>
       <c r="N20" t="n">
-        <v>-34.598714</v>
+        <v>-34.63565</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>PUE-A</t>
+          <t>CON-G</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2137,22 +2137,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8/12/2025</t>
+          <t>8/14/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BRIN, MINISTRO 1375</t>
+          <t>SUPERI 1459</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2167,17 +2167,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>808918700</t>
+          <t>808972965</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>PIcada</t>
+          <t>Poste con base quebrada ver si es posible desmonte</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2187,31 +2187,31 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L21" t="n">
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>-58.355342</v>
+        <v>-58.460834</v>
       </c>
       <c r="N21" t="n">
-        <v>-34.63565</v>
+        <v>-34.573753</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>CON-G</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2223,22 +2223,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8/14/2025</t>
+          <t>8/25/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SUPERI 1459</t>
+          <t>VERA 445</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2253,17 +2253,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>808972965</t>
+          <t>809155622</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Poste con base quebrada ver si es posible desmonte</t>
+          <t>Correrla para sacarla del cantero</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2273,31 +2273,31 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L22" t="n">
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>-58.460834</v>
+        <v>-58.437181</v>
       </c>
       <c r="N22" t="n">
-        <v>-34.573753</v>
+        <v>-34.5995</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2309,22 +2309,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8/25/2025</t>
+          <t>9/1/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>VERA 445</t>
+          <t>VILELA 3699</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>809155622</t>
+          <t>809371823</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Correrla para sacarla del cantero</t>
+          <t xml:space="preserve">Cambiar </t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2359,31 +2359,31 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L23" t="n">
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-58.437181</v>
+        <v>-58.482817</v>
       </c>
       <c r="N23" t="n">
-        <v>-34.5995</v>
+        <v>-34.550845</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2395,17 +2395,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7111</t>
+          <t>S01186963</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9/1/2025</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VILELA 3699</t>
+          <t>WASHINGTON 4273</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2425,12 +2425,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>809371823</t>
+          <t>809800217</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cambiar </t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2445,17 +2445,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L24" t="n">
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-58.482817</v>
+        <v>-58.484798</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.550845</v>
+        <v>-34.550226</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2481,17 +2481,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S01186963</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>9/22/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>WASHINGTON 4273</t>
+          <t>RUIZ HUIDOBRO 3620</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2511,17 +2511,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>809800217</t>
+          <t>ICD30934235</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Trapaso de redes y desmonte</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2538,10 +2538,10 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>-58.484798</v>
+        <v>-58.484082</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.550226</v>
+        <v>-34.549702</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2567,22 +2567,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>9/22/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>RUIZ HUIDOBRO 3620</t>
+          <t>TRES ARROYOS 2911</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2597,17 +2597,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ICD30934235</t>
+          <t>810056868</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Trapaso de redes y desmonte</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2624,14 +2624,14 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-58.484082</v>
+        <v>-58.476877</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.549702</v>
+        <v>-34.617525</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>NRA-M</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2653,17 +2653,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>9/29/2025</t>
+          <t>10/6/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TRES ARROYOS 2911</t>
+          <t>MERCEDES 3774</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2683,12 +2683,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>810056868</t>
+          <t>810244452</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Poste inclinado</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2703,21 +2703,21 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L27" t="n">
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-58.476877</v>
+        <v>-58.511139</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.617525</v>
+        <v>-34.602167</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>NRA-M</t>
+          <t>PUE-P</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2739,22 +2739,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10/6/2025</t>
+          <t>10/8/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MERCEDES 3774</t>
+          <t>ESTADO PLURINACIONAL DE BOLIVIA 3965</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2769,17 +2769,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>810244452</t>
+          <t>810259142</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Poste inclinado</t>
+          <t>Aplomar poste</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2796,10 +2796,10 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.511139</v>
+        <v>-58.493945</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.602167</v>
+        <v>-34.589471</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>PUE-P</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2825,22 +2825,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10/8/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ESTADO PLURINACIONAL DE BOLIVIA 3965</t>
+          <t>BULGARIA 4387</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>810259142</t>
+          <t>810333040</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Aplomar poste</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2882,10 +2882,10 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>-58.493945</v>
+        <v>-58.503223</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.589471</v>
+        <v>-34.590763</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>PUE-N</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2911,22 +2911,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7508</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>10/14/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BULGARIA 4387</t>
+          <t>11 DE SEPTIEMBRE DE 1888 3988</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>810333040</t>
+          <t>00995927</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Picada colocar columna para pedir traspasos tiene nodo teco y tlc</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2956,26 +2956,26 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L30" t="n">
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>-58.503223</v>
+        <v>-58.4635</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.590763</v>
+        <v>-34.542844</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>PUE-N</t>
+          <t>BLO-F</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2997,22 +2997,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7508</t>
+          <t>8482</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10/14/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>11 DE SEPTIEMBRE DE 1888 3988</t>
+          <t>San Blas 2591</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>00995927</t>
+          <t>810416660</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Picada colocar columna para pedir traspasos tiene nodo teco y tlc</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3054,14 +3054,14 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.4635</v>
+        <v>-58.477427</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.542844</v>
+        <v>-34.609261</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>BLO-F</t>
+          <t>NRA-Q</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3083,22 +3083,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Blas 2591</t>
+          <t>CIUDAD DE LA PAZ 3008</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>810416660</t>
+          <t>810421914</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3140,14 +3140,14 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.477427</v>
+        <v>-58.464818</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.609261</v>
+        <v>-34.554931</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>NRA-Q</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3169,22 +3169,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>7697</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 3008</t>
+          <t>CONDE 4334</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3199,12 +3199,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>810421914</t>
+          <t>810487016</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Poste para cambiar o desmontar ver con inspector</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3219,17 +3219,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L33" t="n">
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.464818</v>
+        <v>-58.481509</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.554931</v>
+        <v>-34.547874</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3255,22 +3255,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>7806</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10/29/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>QUITO 4180</t>
+          <t>ROOSEVELT FRANKLIN D. 4665</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>810471618</t>
+          <t>810651339</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Poste inclinado</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3305,31 +3305,31 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L34" t="n">
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.425596</v>
+        <v>-58.482196</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.617038</v>
+        <v>-34.570432</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>ATH-E</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3341,22 +3341,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7697</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CONDE 4334</t>
+          <t>BURELA 1589</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>810487016</t>
+          <t>810651370</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Poste para cambiar o desmontar ver con inspector</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3391,21 +3391,21 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L35" t="n">
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.481509</v>
+        <v>-58.485747</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.547874</v>
+        <v>-34.58538</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3427,22 +3427,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>S00921590</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ROOSEVELT FRANKLIN D. 4665</t>
+          <t>CASEROS AV. 3621</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3457,12 +3457,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>810651339</t>
+          <t>810804462</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Poste inclinado</t>
+          <t>columna inclinada corroida</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3477,31 +3477,31 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L36" t="n">
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.482196</v>
+        <v>-58.416134</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.570432</v>
+        <v>-34.638879</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>ATH-E</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3513,22 +3513,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7811</t>
+          <t>S00921597</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BURELA 1589</t>
+          <t>CASEROS AV. 3507</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>810651370</t>
+          <t>810804451</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>columna inclinada corroida</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3570,24 +3570,24 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.485747</v>
+        <v>-58.414769</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.58538</v>
+        <v>-34.638638</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3599,7 +3599,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S00921590</t>
+          <t>S01089776</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CASEROS AV. 3621</t>
+          <t>ARGERICH 3717</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>810804462</t>
+          <t>810804318</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>columna inclinada corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3656,24 +3656,24 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.416134</v>
+        <v>-58.497051</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.638879</v>
+        <v>-34.594109</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3685,22 +3685,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S00921597</t>
+          <t>S01126628</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CASEROS AV. 3507</t>
+          <t>RIVERA, PEDRO I., DR. 3385</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>810804451</t>
+          <t>810820813</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>columna inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3742,24 +3742,24 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.414769</v>
+        <v>-58.47104</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.638638</v>
+        <v>-34.562322</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>COG-I</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3771,22 +3771,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S01089776</t>
+          <t>S01144183</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ARGERICH 3717</t>
+          <t>DE LOS CONSTITUYENTES AV. 4318</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>810804318</t>
+          <t>810820640</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3828,10 +3828,10 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.497051</v>
+        <v>-58.490526</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.594109</v>
+        <v>-34.583417</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>PUE-K</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3857,7 +3857,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S01126628</t>
+          <t>S01171313</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>RIVERA, PEDRO I., DR. 3385</t>
+          <t xml:space="preserve"> LOPE DE VEGA AV. 3128 </t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3887,12 +3887,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>810820813</t>
+          <t>810820624</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3914,14 +3914,14 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.47104</v>
+        <v>-58.525417</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.562322</v>
+        <v>-34.613865</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>COG-I</t>
+          <t>DEV-G</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3943,7 +3943,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S01144183</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DE LOS CONSTITUYENTES AV. 4318</t>
+          <t>MAGARIÑOS CERVANTES, A. 4803</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>810820640</t>
+          <t>810820571</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada, tensor roto</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3993,21 +3993,21 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L42" t="n">
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.490526</v>
+        <v>-58.500609</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.583417</v>
+        <v>-34.626542</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>PUE-K</t>
+          <t>DEV-I</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4029,7 +4029,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S01171313</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4039,12 +4039,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LOPE DE VEGA AV. 3128 </t>
+          <t>DIAZ, CESAR, GRAL. 1450</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4059,12 +4059,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>810820624</t>
+          <t>810820533</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>muy inclinada</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4079,21 +4079,21 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L43" t="n">
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.525417</v>
+        <v>-58.461219</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.613865</v>
+        <v>-34.605928</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>DEV-G</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4115,22 +4115,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>6436</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/26/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MAGARIÑOS CERVANTES, A. 4803</t>
+          <t xml:space="preserve">ARIAS 4306 </t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>810820571</t>
+          <t>810862832</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>inclinada, tensor roto</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4165,21 +4165,21 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L44" t="n">
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.500609</v>
+        <v>-58.49108</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.626542</v>
+        <v>-34.550102</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>DEV-I</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4201,22 +4201,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7867</t>
+          <t>900008939210</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DIAZ, CESAR, GRAL. 1450</t>
+          <t xml:space="preserve"> LOPEZ, VICENTE 2099</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>810820533</t>
+          <t>811131662</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>muy inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4251,31 +4251,31 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L45" t="n">
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.461219</v>
+        <v>-58.394159</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.605928</v>
+        <v>-34.588587</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>RET-A</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4287,22 +4287,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6436</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11/26/2025</t>
+          <t>12/16/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARIAS 4306 </t>
+          <t>DIAZ, CESAR, GRAL. 2053</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>810862832</t>
+          <t>811198627</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4337,21 +4337,21 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L46" t="n">
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.49108</v>
+        <v>-58.468739</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.550102</v>
+        <v>-34.608957</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4373,22 +4373,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>900008939210</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>12/17/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LOPEZ, VICENTE 2099</t>
+          <t>O'HIGGINS 4298</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>811131662</t>
+          <t>811198660</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>poste inclinado</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4423,31 +4423,31 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L47" t="n">
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.394159</v>
+        <v>-58.468046</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.588587</v>
+        <v>-34.541893</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>RET-A</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4459,22 +4459,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12/16/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DIAZ, CESAR, GRAL. 2053</t>
+          <t xml:space="preserve">PLAZA, VICTORINO DE LA, DR. 1754 </t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>811198627</t>
+          <t>811198702</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4509,21 +4509,21 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L48" t="n">
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.468739</v>
+        <v>-58.451448</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.608957</v>
+        <v>-34.547978</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>BLO-D</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4545,22 +4545,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7921</t>
+          <t>S01028030</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12/17/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>O'HIGGINS 4298</t>
+          <t xml:space="preserve">MARTIN PESCADOR 2296 </t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4575,12 +4575,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>811198660</t>
+          <t>811198686</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>poste inclinado</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4595,21 +4595,21 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L49" t="n">
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.468046</v>
+        <v>-58.493624</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.541893</v>
+        <v>-34.610119</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4631,22 +4631,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>7969</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLAZA, VICTORINO DE LA, DR. 1754 </t>
+          <t xml:space="preserve">HELGUERA 4770 </t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>811198702</t>
+          <t>811238727</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4688,14 +4688,14 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.451448</v>
+        <v>-58.505298</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.547978</v>
+        <v>-34.587467</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>BLO-D</t>
+          <t>PUE-N</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4717,22 +4717,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S01028030</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTIN PESCADOR 2296 </t>
+          <t>RIVERA, PEDRO I., DR. 4448</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>811198686</t>
+          <t>811299428</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4774,14 +4774,14 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.493624</v>
+        <v>-58.481135</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.610119</v>
+        <v>-34.568427</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>PUE-E</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4803,22 +4803,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">HELGUERA 4770 </t>
+          <t xml:space="preserve">MAURE 3996 </t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4833,12 +4833,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>811238727</t>
+          <t>811299417</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4860,14 +4860,14 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.505298</v>
+        <v>-58.451687</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.587467</v>
+        <v>-34.586223</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>PUE-N</t>
+          <t>ATH-L</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4889,22 +4889,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>7987</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>RIVERA, PEDRO I., DR. 4448</t>
+          <t>Terrada 2309</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4919,12 +4919,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>811299428</t>
+          <t>811299433</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4939,21 +4939,21 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L53" t="n">
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.481135</v>
+        <v>-58.482084</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.568427</v>
+        <v>-34.608289</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>PUE-E</t>
+          <t>NRA-P</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4975,22 +4975,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>S01139199</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAURE 3996 </t>
+          <t>CRAMER 4320</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>811299417</t>
+          <t>811299481</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5032,14 +5032,14 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.451687</v>
+        <v>-58.476445</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.586223</v>
+        <v>-34.544981</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>ATH-L</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5061,22 +5061,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>8090</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>1/5/2026</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Terrada 2309</t>
+          <t>Vedia 3506</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5091,17 +5091,17 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>811299433</t>
+          <t xml:space="preserve">02125435 </t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>desmonte y traspasar red</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5111,21 +5111,21 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L55" t="n">
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.482084</v>
+        <v>-58.486704</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.608289</v>
+        <v>-34.544613</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>NRA-P</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5147,22 +5147,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S01139199</t>
+          <t>8173</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CRAMER 4320</t>
+          <t>SUCRE, ANTONIO JOSE DE, MCAL. 1563</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>811299481</t>
+          <t xml:space="preserve">02313712 </t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5204,10 +5204,10 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.476445</v>
+        <v>-58.446858</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.544981</v>
+        <v>-34.559026</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>BLO-A</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5233,22 +5233,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>01018482</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1/5/2026</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Vedia 3506</t>
+          <t>AGUERO 2364</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5263,22 +5263,22 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">02125435 </t>
+          <t xml:space="preserve">02511365 </t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>desmonte y traspasar red</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5290,24 +5290,24 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.486704</v>
+        <v>-58.399462</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.544613</v>
+        <v>-34.585952</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>AGU-H</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5319,22 +5319,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>8173</t>
+          <t>S01180016</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SUCRE, ANTONIO JOSE DE, MCAL. 1563</t>
+          <t>FITZ ROY 1730</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">02313712 </t>
+          <t>811454223</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5376,24 +5376,24 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.446858</v>
+        <v>-58.436051</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.559026</v>
+        <v>-34.583855</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>BLO-A</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5405,22 +5405,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>01018482</t>
+          <t>S01180023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AGUERO 2364</t>
+          <t>VEGA, NICETO, CNEL. AV. 5420</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5435,12 +5435,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">02511365 </t>
+          <t>811454198</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5462,14 +5462,14 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.399462</v>
+        <v>-58.437628</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.585952</v>
+        <v>-34.587953</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>AGU-H</t>
+          <t>ATH-?</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5491,7 +5491,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S01180016</t>
+          <t>S01180086</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FITZ ROY 1730</t>
+          <t>BONPLAND 1471</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>811454223</t>
+          <t>811454194</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5548,10 +5548,10 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.436051</v>
+        <v>-58.439513</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.583855</v>
+        <v>-34.585314</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S01180023</t>
+          <t>S01200482</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>VEGA, NICETO, CNEL. AV. 5420</t>
+          <t>GONZALEZ, ELPIDIO 2749</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>811454198</t>
+          <t>811454117</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>quebrada</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5627,31 +5627,31 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L61" t="n">
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.437628</v>
+        <v>-58.481266</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.587953</v>
+        <v>-34.608522</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>ATH-?</t>
+          <t>NRA-O</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5663,7 +5663,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S01180086</t>
+          <t>S01204059</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BONPLAND 1471</t>
+          <t>BUFANO, ALFREDO R. 2580</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>811454194</t>
+          <t>811454109</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5720,24 +5720,24 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.439513</v>
+        <v>-58.478411</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.585314</v>
+        <v>-34.6039</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>NRA-P</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5749,7 +5749,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S01200482</t>
+          <t>01211534</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GONZALEZ, ELPIDIO 2749</t>
+          <t xml:space="preserve"> JUNCAL 2490</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>811454117</t>
+          <t>811454103</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>quebrada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5799,31 +5799,31 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L63" t="n">
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.481266</v>
+        <v>-58.401685</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.608522</v>
+        <v>-34.591336</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>NRA-O</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5835,7 +5835,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S01204059</t>
+          <t>S01220047</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5845,12 +5845,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BUFANO, ALFREDO R. 2580</t>
+          <t>MAURE 2958</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>811454109</t>
+          <t>811454097</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5892,24 +5892,24 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.478411</v>
+        <v>-58.446339</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.6039</v>
+        <v>-34.576306</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>NRA-P</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5921,7 +5921,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>01211534</t>
+          <t>S01306211</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JUNCAL 2490</t>
+          <t>WASHINGTON 3943</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>811454103</t>
+          <t>811453965</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5971,31 +5971,31 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.401685</v>
+        <v>-58.48286</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.591336</v>
+        <v>-34.55278</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6007,7 +6007,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S01220047</t>
+          <t>S01313361</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MAURE 2958</t>
+          <t>CABILDO AV. 805</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>811454097</t>
+          <t>811453963</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6057,31 +6057,31 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L66" t="n">
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.446339</v>
+        <v>-58.444955</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.576306</v>
+        <v>-34.569791</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>COG-C</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6093,7 +6093,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S01306211</t>
+          <t>S01389798</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>WASHINGTON 3943</t>
+          <t>GUALEGUAYCHU 4682</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>811453965</t>
+          <t>811453943</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6143,21 +6143,21 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L67" t="n">
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.48286</v>
+        <v>-58.518214</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.55278</v>
+        <v>-34.596516</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6179,7 +6179,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S01313361</t>
+          <t>S01384321</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CABILDO AV. 805</t>
+          <t>AZURDUY JUANA 2685</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6209,12 +6209,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>811453963</t>
+          <t>811453930</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6229,21 +6229,21 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.444955</v>
+        <v>-58.469341</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.569791</v>
+        <v>-34.552269</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>COG-C</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6265,7 +6265,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S01389798</t>
+          <t>S01392303</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU 4682</t>
+          <t>Moldes 1999</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>811453943</t>
+          <t>811453918</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6322,14 +6322,14 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.518214</v>
+        <v>-58.458535</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.596516</v>
+        <v>-34.564674</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>COG-G</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6351,22 +6351,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S01384321</t>
+          <t>8095</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AZURDUY JUANA 2685</t>
+          <t>MANZANARES 3853</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>811453930</t>
+          <t>811454324</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6408,10 +6408,10 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.469341</v>
+        <v>-58.482488</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.552269</v>
+        <v>-34.554114</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6437,22 +6437,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S01392303</t>
+          <t>8094</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Moldes 1999</t>
+          <t xml:space="preserve">GARCIA DEL RIO 3789 </t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6467,12 +6467,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>811453918</t>
+          <t>811454305</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6487,21 +6487,21 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L71" t="n">
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.458535</v>
+        <v>-58.482473</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.564674</v>
+        <v>-34.553018</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>COG-G</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6523,22 +6523,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MANZANARES 3853</t>
+          <t>MANZANARES 2073</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6553,12 +6553,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>811454324</t>
+          <t>811454483</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6580,10 +6580,10 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.482488</v>
+        <v>-58.465953</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.554114</v>
+        <v>-34.545637</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6609,17 +6609,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA DEL RIO 3789 </t>
+          <t>ARGERICH 5774</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>811454305</t>
+          <t>811454454</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6666,14 +6666,14 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.482473</v>
+        <v>-58.511147</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.553018</v>
+        <v>-34.578665</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>PUE-J</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6695,22 +6695,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>8186</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/15/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Nogoya 3644</t>
+          <t>ESTOMBA 212</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>811454515</t>
+          <t>811454532</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6745,21 +6745,21 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L74" t="n">
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.497751</v>
+        <v>-58.469045</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.606408</v>
+        <v>-34.588525</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6781,22 +6781,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>8316</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pje. Manuel Sola 4440</t>
+          <t>MONROE 4070</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>811454508</t>
+          <t>811498053</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6838,14 +6838,14 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.507954</v>
+        <v>-58.475842</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.610808</v>
+        <v>-34.568215</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>DEV-D</t>
+          <t>ATH-J</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -6867,22 +6867,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MANZANARES 2073</t>
+          <t>AZURDUY JUANA 3630</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>811454483</t>
+          <t>811498050</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6924,10 +6924,10 @@
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.465953</v>
+        <v>-58.477583</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.545637</v>
+        <v>-34.5569</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>COG-N</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6953,22 +6953,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>S01215930</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/20/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ARGERICH 5774</t>
+          <t>UGARTE, MANUEL 2750</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>811454454</t>
+          <t>811498072</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7003,21 +7003,21 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.511147</v>
+        <v>-58.465042</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.578665</v>
+        <v>-34.557947</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>PUE-J</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7039,22 +7039,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>8181</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1/15/2026</t>
+          <t>1/22/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ESTOMBA 212</t>
+          <t xml:space="preserve">FREIRE, RAMON, CAP. GRAL. 4748 </t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>811454532</t>
+          <t>811498074</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada base quebrada</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7089,21 +7089,21 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L78" t="n">
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.469045</v>
+        <v>-58.482951</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.588525</v>
+        <v>-34.544273</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7125,17 +7125,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>S01318042</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MONROE 4070</t>
+          <t>UGARTE, MANUEL 3815</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>811498053</t>
+          <t>811626754</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7182,14 +7182,14 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.475842</v>
+        <v>-58.476138</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.568215</v>
+        <v>-34.563825</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>ATH-J</t>
+          <t>COG-N</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7211,22 +7211,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>S01397288</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AZURDUY JUANA 3630</t>
+          <t xml:space="preserve">MOLDES 1918 </t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7241,41 +7241,29 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>811498050</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
+          <t>inclinadaq</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="n">
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.477583</v>
+        <v>-58.458035</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.5569</v>
+        <v>-34.565387</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -7285,7 +7273,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>COG-N</t>
+          <t>COG-G</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7297,17 +7285,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S01215930</t>
+          <t>S01397364</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1/20/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>UGARTE, MANUEL 2750</t>
+          <t>AVILES, VIRREY 3008</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7327,7 +7315,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>811498072</t>
+          <t>811626732</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7354,14 +7342,14 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.465042</v>
+        <v>-58.457207</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.557947</v>
+        <v>-34.571602</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -7371,7 +7359,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7383,17 +7371,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>8181</t>
+          <t>S01396837</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1/22/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREIRE, RAMON, CAP. GRAL. 4748 </t>
+          <t>DEHEZA 3622</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -7413,12 +7401,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>811498074</t>
+          <t>811626963</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>inclinada base quebrada</t>
+          <t>inclinado base quebrada</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7440,10 +7428,10 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.482951</v>
+        <v>-58.485735</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.544273</v>
+        <v>-34.546249</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -7469,22 +7457,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S01318042</t>
+          <t>S01406731</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>UGARTE, MANUEL 3815</t>
+          <t xml:space="preserve"> CORREA 1807</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7499,7 +7487,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>811626754</t>
+          <t>811626953</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -7526,10 +7514,10 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.476138</v>
+        <v>-58.466595</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.563825</v>
+        <v>-34.54099</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -7543,7 +7531,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>COG-N</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -7555,17 +7543,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S01397288</t>
+          <t>S01406812</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOLDES 1918 </t>
+          <t xml:space="preserve">VUELTA DE OBLIGADO 3201 </t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7585,29 +7573,41 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811626783</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>inclinadaq</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
       <c r="L84" t="n">
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.458035</v>
+        <v>-58.464784</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.565387</v>
+        <v>-34.551419</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>COG-G</t>
+          <t>BLO-R</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -7629,17 +7629,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S01397364</t>
+          <t>S00019326</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AVILES, VIRREY 3008</t>
+          <t>OLLEROS 3050</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>811626732</t>
+          <t>811627002</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7686,24 +7686,24 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.457207</v>
+        <v>-58.447708</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.571602</v>
+        <v>-34.577055</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>ATH-P</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -7715,22 +7715,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S01396837</t>
+          <t>S00021988</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>DEHEZA 3622</t>
+          <t>ALVAREZ THOMAS AV. 1115</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7745,12 +7745,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>811626963</t>
+          <t>811626996</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>inclinado base quebrada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7765,21 +7765,21 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L86" t="n">
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.485735</v>
+        <v>-58.457565</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.546249</v>
+        <v>-34.578379</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>ATH-O</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7801,17 +7801,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S01406731</t>
+          <t>S01450787</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CORREA 1807</t>
+          <t>HERNANDEZ, JOSE 2110</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>811626953</t>
+          <t>811626983</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7851,21 +7851,21 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L87" t="n">
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.466595</v>
+        <v>-58.450727</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.54099</v>
+        <v>-34.56425</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>BLO-M</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7887,22 +7887,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S01406812</t>
+          <t>S00036520</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">VUELTA DE OBLIGADO 3201 </t>
+          <t>SEGUROLA AV. 856</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>811626783</t>
+          <t>811627070</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroidaq</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7944,14 +7944,14 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.464784</v>
+        <v>-58.490765</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.551419</v>
+        <v>-34.627337</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>BLO-R</t>
+          <t>DEV-I</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7973,17 +7973,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S00019326</t>
+          <t>S01337226</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/6/2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>OLLEROS 3050</t>
+          <t>MOLDES 3055</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>811627002</t>
+          <t>811627125</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8030,24 +8030,24 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.447708</v>
+        <v>-58.466692</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.577055</v>
+        <v>-34.555283</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>ATH-P</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8059,17 +8059,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S00021988</t>
+          <t>S01375612</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/6/2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ALVAREZ THOMAS AV. 1115</t>
+          <t>LACROZE, FEDERICO AV. 2834</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8089,12 +8089,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>811626996</t>
+          <t>811627118</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroidaq</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8116,24 +8116,24 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.457565</v>
+        <v>-58.447177</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.578379</v>
+        <v>-34.574158</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>ATH-O</t>
+          <t>ATH-P</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8145,22 +8145,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANABRIA 2386 </t>
+          <t>ARENGREEN 1584</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>811626991</t>
+          <t>812440072</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8195,31 +8195,31 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L91" t="n">
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.503452</v>
+        <v>-58.453265</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.614501</v>
+        <v>-34.615073</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>DEV-D</t>
+          <t>NRA-I</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8231,22 +8231,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S01450787</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HERNANDEZ, JOSE 2110</t>
+          <t>ARENAL, CONCEPCION 3814</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>811626983</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8276,22 +8276,22 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L92" t="n">
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.450727</v>
+        <v>-58.447805</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.56425</v>
+        <v>-34.587018</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>BLO-M</t>
+          <t>ATH-L</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8317,17 +8317,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>8533</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GAMARRA 1550</t>
+          <t>WARNES AV. 2239</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>811627113</t>
+          <t>812440018</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8374,10 +8374,10 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.477255</v>
+        <v>-58.467815</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.582395</v>
+        <v>-34.596225</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8403,22 +8403,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S00036520</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SEGUROLA AV. 856</t>
+          <t>PAZ SOLDAN 4991</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>811627070</t>
+          <t>812439995</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>corroidaq</t>
+          <t>base quebrada</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -8453,21 +8453,21 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L94" t="n">
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.490765</v>
+        <v>-58.468466</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.627337</v>
+        <v>-34.594154</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>DEV-I</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8489,22 +8489,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S01337226</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2/6/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MOLDES 3055</t>
+          <t xml:space="preserve"> GUALEGUAYCHU 4754</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>811627125</t>
+          <t>812439956</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinado, base quebrada</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -8539,21 +8539,21 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L95" t="n">
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.466692</v>
+        <v>-58.518803</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.555283</v>
+        <v>-34.595866</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8575,17 +8575,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S01375612</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2/6/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>LACROZE, FEDERICO AV. 2834</t>
+          <t>BLANCO ENCALADA 823</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>811627118</t>
+          <t>812439941</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>corroidaq</t>
+          <t>inclinado base quebrada</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -8625,31 +8625,31 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L96" t="n">
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.447177</v>
+        <v>-58.442692</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.574158</v>
+        <v>-34.549454</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>ATH-P</t>
+          <t>BLO-B</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8661,22 +8661,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ARENGREEN 1584</t>
+          <t>DORREGO AV. 2699</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8691,12 +8691,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>812440072</t>
+          <t>812440089</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>base corrodia</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -8711,21 +8711,21 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L97" t="n">
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.453265</v>
+        <v>-58.432807</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.615073</v>
+        <v>-34.574343</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>NRA-I</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8747,17 +8747,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ARENAL, CONCEPCION 3814</t>
+          <t>BEIRO, FRANCISCO AV. 2435</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440250</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -8804,14 +8804,14 @@
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.447805</v>
+        <v>-58.488914</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.587018</v>
+        <v>-34.59164</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>ATH-L</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8833,17 +8833,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>WARNES AV. 2239</t>
+          <t>CARACAS 3559</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8863,12 +8863,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>812440018</t>
+          <t>812440223</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -8890,10 +8890,10 @@
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.467815</v>
+        <v>-58.487793</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.596225</v>
+        <v>-34.590403</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8919,17 +8919,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>8368</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PAZ SOLDAN 4991</t>
+          <t>CARACAS 3519</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>812439995</t>
+          <t>812503552</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>base quebrada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -8969,17 +8969,17 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L100" t="n">
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.468466</v>
+        <v>-58.487627</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.594154</v>
+        <v>-34.590585</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9005,22 +9005,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GUALEGUAYCHU 4754</t>
+          <t>ANDONAEGUI 2383</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -9035,12 +9035,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>812439956</t>
+          <t>812440211</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>inclinado, base quebrada</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9055,17 +9055,17 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L101" t="n">
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.518803</v>
+        <v>-58.489606</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.595866</v>
+        <v>-34.57655</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>ATH-C</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9091,22 +9091,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BLANCO ENCALADA 823</t>
+          <t>CRAMER 4262</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>812439941</t>
+          <t>812440206</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>inclinado base quebrada</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9141,17 +9141,17 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L102" t="n">
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.442692</v>
+        <v>-58.476168</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.549454</v>
+        <v>-34.545546</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>BLO-B</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9177,22 +9177,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2699</t>
+          <t xml:space="preserve">CRAMER 4322 </t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9207,12 +9207,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>812440089</t>
+          <t>812440204</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>base corrodia</t>
+          <t>base corroida inclnada</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9234,24 +9234,24 @@
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.432807</v>
+        <v>-58.476454</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.574343</v>
+        <v>-34.544962</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9263,7 +9263,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>8382</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BEIRO, FRANCISCO AV. 2435</t>
+          <t>SANTO TOME 3588</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>812440250</t>
+          <t>812440197</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -9313,21 +9313,21 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L104" t="n">
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.488914</v>
+        <v>-58.4947</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.59164</v>
+        <v>-34.60925</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>DEV-D</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9349,7 +9349,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>S00117686</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CARACAS 3559</t>
+          <t>DORREGO AV. 2778</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>812440223</t>
+          <t>812440183</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>inlinada</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -9406,24 +9406,24 @@
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.487793</v>
+        <v>-58.432102</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.590403</v>
+        <v>-34.574248</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9435,7 +9435,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>S00506048</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CARACAS 3519</t>
+          <t>TERRADA 1088</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9465,17 +9465,17 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>812503552</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Tensor</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -9485,17 +9485,17 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L106" t="n">
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.487627</v>
+        <v>-58.472866</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.590585</v>
+        <v>-34.620121</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>NRA-M</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9521,17 +9521,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>VARELA, JOSE PEDRO 3545</t>
+          <t>CISNEROS, VIRREY 1610</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>812440219</t>
+          <t>812440520</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -9571,17 +9571,17 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L107" t="n">
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.502073</v>
+        <v>-58.469727</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.601294</v>
+        <v>-34.612013</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9607,22 +9607,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>8550</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ANDONAEGUI 2383</t>
+          <t>FRAGATA PRES. SARMIENTO 1390</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>812440211</t>
+          <t>812440373</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -9664,10 +9664,10 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.489606</v>
+        <v>-58.456778</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.57655</v>
+        <v>-34.609187</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>ATH-C</t>
+          <t>NRA-I</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9693,22 +9693,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>S01295589</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/24/2026</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CRAMER 4262</t>
+          <t>CABILDO AV. 1008</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>812440206</t>
+          <t>812440653</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -9750,14 +9750,14 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.476168</v>
+        <v>-58.446714</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.545546</v>
+        <v>-34.569183</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>COG-C</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -9779,22 +9779,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>S01406719</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/24/2026</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRAMER 4322 </t>
+          <t>3 DE FEBRERO 4481</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9809,12 +9809,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>812440204</t>
+          <t>812440639</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>base corroida inclnada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -9829,17 +9829,17 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L110" t="n">
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.476454</v>
+        <v>-58.467166</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.544962</v>
+        <v>-34.539469</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9865,22 +9865,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>S00867165</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/26/2026</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SANTO TOME 3588</t>
+          <t xml:space="preserve"> VALLEJOS 2250</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9895,12 +9895,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>812440197</t>
+          <t>812503628</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -9915,21 +9915,21 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L111" t="n">
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.4947</v>
+        <v>-58.493418</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.60925</v>
+        <v>-34.583307</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>DEV-D</t>
+          <t>PUE-K</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9951,22 +9951,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S00117686</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/26/2026</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2778</t>
+          <t xml:space="preserve">ESTADO PLURINACIONAL DE BOLIVIA 3526 </t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>812440183</t>
+          <t>812503597</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>inlinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10008,24 +10008,24 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.432102</v>
+        <v>-58.491306</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.574248</v>
+        <v>-34.592511</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10037,22 +10037,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S00506048</t>
+          <t>8397</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/26/2026</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TERRADA 1088</t>
+          <t>TERRADA 3739</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10067,17 +10067,17 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812503610</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Tensor</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -10087,17 +10087,17 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.472866</v>
+        <v>-58.494807</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.620121</v>
+        <v>-34.592416</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>NRA-M</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10123,22 +10123,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/26/2026</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CISNEROS, VIRREY 1610</t>
+          <t xml:space="preserve"> TERRADA 3695 </t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>812440520</t>
+          <t>812503605</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -10173,17 +10173,17 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L114" t="n">
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.469727</v>
+        <v>-58.494371</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.612013</v>
+        <v>-34.592899</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10209,22 +10209,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>8550</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/27/2026</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FRAGATA PRES. SARMIENTO 1390</t>
+          <t>SIMBRON 5855</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -10239,12 +10239,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>812440373</t>
+          <t>812503637</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -10259,21 +10259,21 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L115" t="n">
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.456778</v>
+        <v>-58.527129</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.609187</v>
+        <v>-34.620962</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -10283,7 +10283,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>NRA-I</t>
+          <t>DEV-G</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10295,22 +10295,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S00506118</t>
+          <t>S00208304</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>3/2/2026</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>TERRERO 588</t>
+          <t>CONDE 3080</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>812440289</t>
+          <t>812503654</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -10352,24 +10352,24 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.459689</v>
+        <v>-58.47322</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.620032</v>
+        <v>-34.558645</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>NRA-D</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10381,22 +10381,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S01295589</t>
+          <t>S00106358</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2/24/2026</t>
+          <t>3/4/2026</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CABILDO AV. 1008</t>
+          <t>TRONADOR 1194</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>812440653</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -10438,10 +10438,10 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.446714</v>
+        <v>-58.466138</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.569183</v>
+        <v>-34.579638</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>COG-C</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10467,22 +10467,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S01406719</t>
+          <t>S00169078</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2/24/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>3 DE FEBRERO 4481</t>
+          <t>LOPEZ, CARLOS ANTONIO 3911</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>812440639</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -10524,14 +10524,14 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.467166</v>
+        <v>-58.516319</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.539469</v>
+        <v>-34.593592</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10553,17 +10553,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S00867165</t>
+          <t>S00190060</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2/26/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VALLEJOS 2250</t>
+          <t xml:space="preserve">OBISPO SAN ALBERTO 3176 </t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>812503628</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -10610,10 +10610,10 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.493418</v>
+        <v>-58.509545</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.583307</v>
+        <v>-34.584532</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>PUE-K</t>
+          <t>PUE-M</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10639,22 +10639,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>8392</t>
+          <t>S00195815</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2/26/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESTADO PLURINACIONAL DE BOLIVIA 3526 </t>
+          <t>PEDRAZA, MANUELA 3345</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>812503597</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -10696,14 +10696,14 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.491306</v>
+        <v>-58.474542</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.592511</v>
+        <v>-34.556088</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>COG-N</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10725,17 +10725,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>8397</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2/26/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>TERRADA 3739</t>
+          <t>OROÑO, NICASIO 2540</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10755,12 +10755,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>812503610</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -10782,10 +10782,10 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.494807</v>
+        <v>-58.459566</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.592416</v>
+        <v>-34.597579</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
@@ -10799,34 +10799,34 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>NRA-N</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1NRA</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>8398</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2/26/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TERRADA 3695 </t>
+          <t>COSTA RICA 5733</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -10841,12 +10841,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>812503605</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -10868,24 +10868,24 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.494371</v>
+        <v>-58.436004</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.592899</v>
+        <v>-34.58156</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10897,22 +10897,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2/27/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SIMBRON 5855</t>
+          <t>LAVOISIER 3556</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>812503637</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -10947,21 +10947,21 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L123" t="n">
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.527129</v>
+        <v>-58.502869</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.620962</v>
+        <v>-34.567437</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>DEV-G</t>
+          <t>PUE-H</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10983,22 +10983,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S00208304</t>
+          <t>8508</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3/2/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CONDE 3080</t>
+          <t>NEWBERY, JORGE 3117</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11013,12 +11013,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>812503654</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -11040,24 +11040,24 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.47322</v>
+        <v>-58.446446</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.558645</v>
+        <v>-34.578293</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11069,22 +11069,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S00106358</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>3/4/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TRONADOR 1194</t>
+          <t>SOLDADO DE LA INDEPENDENCIA 851</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -11126,24 +11126,24 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.466138</v>
+        <v>-58.435443</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.579638</v>
+        <v>-34.56693</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11155,17 +11155,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S00169078</t>
+          <t>900009605910</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>LOPEZ, CARLOS ANTONIO 3911</t>
+          <t xml:space="preserve">BORDABEHERE ENZO 2801 </t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -11212,10 +11212,10 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.516319</v>
+        <v>-58.480297</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.593592</v>
+        <v>-34.600118</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>PUE-A</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11241,7 +11241,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S00190060</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11251,12 +11251,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBISPO SAN ALBERTO 3176 </t>
+          <t>NAZCA AV. 3312</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -11298,10 +11298,10 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.509545</v>
+        <v>-58.492236</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.584532</v>
+        <v>-34.598228</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>PUE-M</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11327,22 +11327,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S00195815</t>
+          <t>8519</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PEDRAZA, MANUELA 3345</t>
+          <t>OROÑO, NICASIO 2170</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11362,7 +11362,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>Columna Picada</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -11384,14 +11384,14 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.474542</v>
+        <v>-58.460865</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.556088</v>
+        <v>-34.601594</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -11401,34 +11401,34 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>COG-N</t>
+          <t>NRA-N</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1NRA</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>OROÑO, NICASIO 2540</t>
+          <t>MOLDES 3006</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>Columna Picada</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -11463,21 +11463,21 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L129" t="n">
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.459566</v>
+        <v>-58.466299</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.597579</v>
+        <v>-34.555783</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -11487,34 +11487,34 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>NRA-N</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>COSTA RICA 5733</t>
+          <t xml:space="preserve">ARGERICH 3561 </t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>Columna Picada</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -11556,24 +11556,24 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.436004</v>
+        <v>-58.495986</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.58156</v>
+        <v>-34.595286</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11585,22 +11585,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>LAVOISIER 3556</t>
+          <t>DE LOS INCAS AV. 4857</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -11642,10 +11642,10 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.502869</v>
+        <v>-58.478518</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.567437</v>
+        <v>-34.58436</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>PUE-H</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11671,22 +11671,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 3117</t>
+          <t>AVALOS 1654</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11728,24 +11728,24 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.446446</v>
+        <v>-58.480338</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.578293</v>
+        <v>-34.581544</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11757,22 +11757,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>SOLDADO DE LA INDEPENDENCIA 851</t>
+          <t xml:space="preserve">GAMARRA 1751 </t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -11814,24 +11814,24 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.435443</v>
+        <v>-58.479932</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.56693</v>
+        <v>-34.580069</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11843,22 +11843,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>900009605910</t>
+          <t>8439</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">BORDABEHERE ENZO 2801 </t>
+          <t xml:space="preserve">CADIZ 4091 </t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -11893,17 +11893,17 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L134" t="n">
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.480297</v>
+        <v>-58.478929</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.600118</v>
+        <v>-34.580774</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>PUE-A</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11929,22 +11929,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>8480</t>
+          <t>8441</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>NAZCA AV. 3312</t>
+          <t xml:space="preserve"> VICTORICA, BENJAMIN, GENERAL, AV. 2330</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -11986,10 +11986,10 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.492236</v>
+        <v>-58.478983</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.598228</v>
+        <v>-34.579669</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -12015,7 +12015,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>8519</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12025,7 +12025,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>OROÑO, NICASIO 2170</t>
+          <t>BERNA 2449</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Columna Picada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -12072,10 +12072,10 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.460865</v>
+        <v>-58.478248</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.601594</v>
+        <v>-34.581288</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -12089,19 +12089,19 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>NRA-N</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>8447</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12111,12 +12111,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>MOLDES 3006</t>
+          <t xml:space="preserve">AVALOS 1301 </t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Columna Picada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -12151,21 +12151,21 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.466299</v>
+        <v>-58.477244</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.555783</v>
+        <v>-34.584896</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>ATH-G</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12187,7 +12187,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12197,7 +12197,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARGERICH 3561 </t>
+          <t>GAMARRA 1504</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Columna Picada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -12244,10 +12244,10 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.495986</v>
+        <v>-58.476783</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.595286</v>
+        <v>-34.582937</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12273,7 +12273,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>8435</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>DE LOS INCAS AV. 4857</t>
+          <t>GANDARA 3308</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -12308,7 +12308,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -12330,10 +12330,10 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.478518</v>
+        <v>-58.485416</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.58436</v>
+        <v>-34.586085</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>8449</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12369,7 +12369,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>AVALOS 1654</t>
+          <t>GIRIBONE 3355</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -12394,7 +12394,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -12416,10 +12416,10 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.480338</v>
+        <v>-58.486528</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.581544</v>
+        <v>-34.585612</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12445,22 +12445,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>-771</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAMARRA 1751 </t>
+          <t>SAN BLAS 4112</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12478,11 +12478,7 @@
           <t>Pendiente ADM</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
+      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -12495,21 +12491,21 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L141" t="n">
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.479932</v>
+        <v>-58.494458</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.580069</v>
+        <v>-34.620078</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -12519,780 +12515,10 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>DEV-J</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>8439</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>3/9/2026</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CADIZ 4091 </t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>base corroida</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L142" t="n">
-        <v>1</v>
-      </c>
-      <c r="M142" t="n">
-        <v>-58.478929</v>
-      </c>
-      <c r="N142" t="n">
-        <v>-34.580774</v>
-      </c>
-      <c r="O142" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="P142" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>ATH-D</t>
-        </is>
-      </c>
-      <c r="R142" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>8441</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>3/9/2026</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> VICTORICA, BENJAMIN, GENERAL, AV. 2330</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L143" t="n">
-        <v>1</v>
-      </c>
-      <c r="M143" t="n">
-        <v>-58.478983</v>
-      </c>
-      <c r="N143" t="n">
-        <v>-34.579669</v>
-      </c>
-      <c r="O143" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="P143" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q143" t="inlineStr">
-        <is>
-          <t>ATH-D</t>
-        </is>
-      </c>
-      <c r="R143" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>8442</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>3/9/2026</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>BERNA 2425</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L144" t="n">
-        <v>1</v>
-      </c>
-      <c r="M144" t="n">
-        <v>-58.47814</v>
-      </c>
-      <c r="N144" t="n">
-        <v>-34.581156</v>
-      </c>
-      <c r="O144" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="P144" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q144" t="inlineStr">
-        <is>
-          <t>ATH-D</t>
-        </is>
-      </c>
-      <c r="R144" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>8443</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>3/9/2026</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>BERNA 2449</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L145" t="n">
-        <v>1</v>
-      </c>
-      <c r="M145" t="n">
-        <v>-58.478248</v>
-      </c>
-      <c r="N145" t="n">
-        <v>-34.581288</v>
-      </c>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="P145" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q145" t="inlineStr">
-        <is>
-          <t>ATH-D</t>
-        </is>
-      </c>
-      <c r="R145" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>8447</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>3/9/2026</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AVALOS 1301 </t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>base corroida</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L146" t="n">
-        <v>1</v>
-      </c>
-      <c r="M146" t="n">
-        <v>-58.477244</v>
-      </c>
-      <c r="N146" t="n">
-        <v>-34.584896</v>
-      </c>
-      <c r="O146" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="P146" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q146" t="inlineStr">
-        <is>
-          <t>ATH-G</t>
-        </is>
-      </c>
-      <c r="R146" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>8448</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>3/9/2026</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>GAMARRA 1504</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>inclinada corroida</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L147" t="n">
-        <v>1</v>
-      </c>
-      <c r="M147" t="n">
-        <v>-58.476783</v>
-      </c>
-      <c r="N147" t="n">
-        <v>-34.582937</v>
-      </c>
-      <c r="O147" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="P147" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q147" t="inlineStr">
-        <is>
-          <t>ATH-S</t>
-        </is>
-      </c>
-      <c r="R147" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>8450</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>3/9/2026</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>GANDARA 3308</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L148" t="n">
-        <v>1</v>
-      </c>
-      <c r="M148" t="n">
-        <v>-58.485416</v>
-      </c>
-      <c r="N148" t="n">
-        <v>-34.586085</v>
-      </c>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q148" t="inlineStr">
-        <is>
-          <t>ATH-S</t>
-        </is>
-      </c>
-      <c r="R148" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>8449</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>3/9/2026</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>GIRIBONE 3355</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L149" t="n">
-        <v>1</v>
-      </c>
-      <c r="M149" t="n">
-        <v>-58.486528</v>
-      </c>
-      <c r="N149" t="n">
-        <v>-34.585612</v>
-      </c>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="P149" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>ATH-S</t>
-        </is>
-      </c>
-      <c r="R149" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>-771</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>2/18/2026</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>SAN BLAS 4112</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>Poste</t>
-        </is>
-      </c>
-      <c r="L150" t="n">
-        <v>1</v>
-      </c>
-      <c r="M150" t="n">
-        <v>-58.494458</v>
-      </c>
-      <c r="N150" t="n">
-        <v>-34.620078</v>
-      </c>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="P150" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>DEV-J</t>
-        </is>
-      </c>
-      <c r="R150" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_NEW.xlsx
+++ b/mapa_interactivo_NEW.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R141"/>
+  <dimension ref="A1:R142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12524,6 +12524,88 @@
         </is>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>3/28/2026</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>GIRIBONE 3229</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>1</v>
+      </c>
+      <c r="M142" t="n">
+        <v>-58.485216</v>
+      </c>
+      <c r="N142" t="n">
+        <v>-34.584797</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>ATH-S</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapa_interactivo_NEW.xlsx
+++ b/mapa_interactivo_NEW.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R197"/>
+  <dimension ref="A1:R188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6867,17 +6867,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8181</t>
+          <t>S01318042</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1/22/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREIRE, RAMON, CAP. GRAL. 4748 </t>
+          <t>UGARTE, MANUEL 3815</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>811498074</t>
+          <t>811626754</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>inclinada base quebrada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6917,17 +6917,17 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L76" t="n">
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.482951</v>
+        <v>-58.476138</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.544273</v>
+        <v>-34.563825</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>COG-N</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6953,7 +6953,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S01318042</t>
+          <t>S01397288</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>UGARTE, MANUEL 3815</t>
+          <t xml:space="preserve">MOLDES 1918 </t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6983,41 +6983,29 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>811626754</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>base corroida</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
+          <t>inclinadaq</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.476138</v>
+        <v>-58.458035</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.563825</v>
+        <v>-34.565387</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7027,7 +7015,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>COG-N</t>
+          <t>COG-G</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7039,7 +7027,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S01397288</t>
+          <t>S01397364</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7049,7 +7037,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOLDES 1918 </t>
+          <t>AVILES, VIRREY 3008</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -7069,25 +7057,37 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811626732</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>inclinadaq</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+          <t>corroida</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
       <c r="L78" t="n">
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.458035</v>
+        <v>-58.457207</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.565387</v>
+        <v>-34.571602</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>COG-G</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7113,22 +7113,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S01397364</t>
+          <t>S01396837</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AVILES, VIRREY 3008</t>
+          <t>DEHEZA 3622</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7143,12 +7143,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>811626732</t>
+          <t>811626963</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado base quebrada</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7163,21 +7163,21 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L79" t="n">
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.457207</v>
+        <v>-58.485735</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.571602</v>
+        <v>-34.546249</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7199,7 +7199,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S01396837</t>
+          <t>S01406731</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>DEHEZA 3622</t>
+          <t xml:space="preserve"> CORREA 1807</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>811626963</t>
+          <t>811626953</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>inclinado base quebrada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7249,17 +7249,17 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L80" t="n">
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.485735</v>
+        <v>-58.466595</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.546249</v>
+        <v>-34.54099</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7285,17 +7285,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S01406731</t>
+          <t>S01406812</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CORREA 1807</t>
+          <t xml:space="preserve">VUELTA DE OBLIGADO 3201 </t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>811626953</t>
+          <t>811626783</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7342,10 +7342,10 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.466595</v>
+        <v>-58.464784</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.54099</v>
+        <v>-34.551419</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>BLO-R</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7371,17 +7371,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S01406812</t>
+          <t>S00019326</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">VUELTA DE OBLIGADO 3201 </t>
+          <t>OLLEROS 3050</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>811626783</t>
+          <t>811627002</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7428,24 +7428,24 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.464784</v>
+        <v>-58.447708</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.551419</v>
+        <v>-34.577055</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>BLO-R</t>
+          <t>ATH-P</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7457,7 +7457,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S00019326</t>
+          <t>S00021988</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>OLLEROS 3050</t>
+          <t>ALVAREZ THOMAS AV. 1115</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>811627002</t>
+          <t>811626996</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7514,24 +7514,24 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.447708</v>
+        <v>-58.457565</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.577055</v>
+        <v>-34.578379</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>ATH-P</t>
+          <t>ATH-O</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -7543,7 +7543,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S00021988</t>
+          <t>S01450787</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ALVAREZ THOMAS AV. 1115</t>
+          <t>HERNANDEZ, JOSE 2110</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>811626996</t>
+          <t>811626983</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7593,17 +7593,17 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L84" t="n">
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.457565</v>
+        <v>-58.450727</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.578379</v>
+        <v>-34.56425</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>ATH-O</t>
+          <t>BLO-M</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -7629,22 +7629,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S01450787</t>
+          <t>S00036520</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HERNANDEZ, JOSE 2110</t>
+          <t>SEGUROLA AV. 856</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7659,12 +7659,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>811626983</t>
+          <t>811627070</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroidaq</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7679,21 +7679,21 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L85" t="n">
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.450727</v>
+        <v>-58.490765</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.56425</v>
+        <v>-34.627337</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>BLO-M</t>
+          <t>DEV-I</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -7715,22 +7715,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S00036520</t>
+          <t>S01337226</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/6/2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SEGUROLA AV. 856</t>
+          <t>MOLDES 3055</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7745,12 +7745,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>811627070</t>
+          <t>811627125</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>corroidaq</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7772,14 +7772,14 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.490765</v>
+        <v>-58.466692</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.627337</v>
+        <v>-34.555283</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>DEV-I</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7801,7 +7801,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S01337226</t>
+          <t>S01375612</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MOLDES 3055</t>
+          <t>LACROZE, FEDERICO AV. 2834</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>811627125</t>
+          <t>811627118</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroidaq</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7858,24 +7858,24 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.466692</v>
+        <v>-58.447177</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.555283</v>
+        <v>-34.574158</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>ATH-P</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7887,22 +7887,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S01375612</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2/6/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>LACROZE, FEDERICO AV. 2834</t>
+          <t>ARENGREEN 1584</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>811627118</t>
+          <t>812440072</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>corroidaq</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7937,21 +7937,21 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L88" t="n">
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.447177</v>
+        <v>-58.453265</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.574158</v>
+        <v>-34.615073</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>ATH-P</t>
+          <t>NRA-I</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7973,7 +7973,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7983,12 +7983,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ARENGREEN 1584</t>
+          <t>ARENAL, CONCEPCION 3814</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>812440072</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8018,36 +8018,36 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L89" t="n">
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.453265</v>
+        <v>-58.447805</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.615073</v>
+        <v>-34.587018</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>NRA-I</t>
+          <t>ATH-L</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8059,7 +8059,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ARENAL, CONCEPCION 3814</t>
+          <t>WARNES AV. 2239</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8089,12 +8089,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440018</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -8116,14 +8116,14 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.447805</v>
+        <v>-58.467815</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.587018</v>
+        <v>-34.596225</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>ATH-L</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8145,7 +8145,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>WARNES AV. 2239</t>
+          <t>PAZ SOLDAN 4991</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>812440018</t>
+          <t>812439995</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base quebrada</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8195,17 +8195,17 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L91" t="n">
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.467815</v>
+        <v>-58.468466</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.596225</v>
+        <v>-34.594154</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8241,12 +8241,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PAZ SOLDAN 4991</t>
+          <t>BLANCO ENCALADA 823</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>812439995</t>
+          <t>812439941</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>base quebrada</t>
+          <t>inclinado base quebrada</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8288,14 +8288,14 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.468466</v>
+        <v>-58.442692</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.594154</v>
+        <v>-34.549454</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>BLO-B</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8317,22 +8317,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GUALEGUAYCHU 4754</t>
+          <t>DORREGO AV. 2699</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>812439956</t>
+          <t>812440089</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>inclinado, base quebrada</t>
+          <t>base corrodia</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8367,31 +8367,31 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L93" t="n">
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.518803</v>
+        <v>-58.432807</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.595866</v>
+        <v>-34.574343</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8403,22 +8403,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BLANCO ENCALADA 823</t>
+          <t>BEIRO, FRANCISCO AV. 2435</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>812439941</t>
+          <t>812440250</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>inclinado base quebrada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -8453,21 +8453,21 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L94" t="n">
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.442692</v>
+        <v>-58.488914</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.549454</v>
+        <v>-34.59164</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>BLO-B</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8489,22 +8489,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2699</t>
+          <t>CARACAS 3559</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>812440089</t>
+          <t>812440223</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>base corrodia</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -8546,24 +8546,24 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.432807</v>
+        <v>-58.487793</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.574343</v>
+        <v>-34.590403</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8575,7 +8575,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>8368</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BEIRO, FRANCISCO AV. 2435</t>
+          <t>CARACAS 3519</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>812440250</t>
+          <t>812503552</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -8632,10 +8632,10 @@
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.488914</v>
+        <v>-58.487627</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.59164</v>
+        <v>-34.590585</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8671,12 +8671,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CARACAS 3559</t>
+          <t>ANDONAEGUI 2383</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8691,12 +8691,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>812440223</t>
+          <t>812440211</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -8718,10 +8718,10 @@
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.487793</v>
+        <v>-58.489606</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.590403</v>
+        <v>-34.57655</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>ATH-C</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8747,7 +8747,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CARACAS 3519</t>
+          <t>CRAMER 4262</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>812503552</t>
+          <t>812440206</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -8804,14 +8804,14 @@
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.487627</v>
+        <v>-58.476168</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.590585</v>
+        <v>-34.545546</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8833,7 +8833,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ANDONAEGUI 2383</t>
+          <t xml:space="preserve">CRAMER 4322 </t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8863,12 +8863,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>812440211</t>
+          <t>812440204</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>base corroida inclnada</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -8890,14 +8890,14 @@
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.489606</v>
+        <v>-58.476454</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.57655</v>
+        <v>-34.544962</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -8907,7 +8907,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>ATH-C</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8919,7 +8919,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>8382</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8929,12 +8929,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CRAMER 4262</t>
+          <t>SANTO TOME 3588</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>812440206</t>
+          <t>812440197</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -8969,21 +8969,21 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L100" t="n">
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.476168</v>
+        <v>-58.4947</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.545546</v>
+        <v>-34.60925</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>DEV-D</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9005,7 +9005,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>S00117686</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9015,12 +9015,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRAMER 4322 </t>
+          <t>DORREGO AV. 2778</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -9035,12 +9035,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>812440204</t>
+          <t>812440183</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>base corroida inclnada</t>
+          <t>inlinada</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9062,24 +9062,24 @@
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.476454</v>
+        <v>-58.432102</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.544962</v>
+        <v>-34.574248</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9091,7 +9091,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>S00506048</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SANTO TOME 3588</t>
+          <t>TERRADA 1088</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9121,17 +9121,17 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>812440197</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Tensor</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -9141,21 +9141,21 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L102" t="n">
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.4947</v>
+        <v>-58.472866</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.60925</v>
+        <v>-34.620121</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>DEV-D</t>
+          <t>NRA-M</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9177,22 +9177,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S00117686</t>
+          <t>-748</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2778</t>
+          <t>GUTENBERG 340</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9207,12 +9207,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>812440183</t>
+          <t>812440623</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>inlinada</t>
+          <t>inclinado base podrida</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9227,31 +9227,31 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L103" t="n">
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.432102</v>
+        <v>-58.471395</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.574248</v>
+        <v>-34.592451</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>PUE-?</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9263,22 +9263,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S00506048</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>TERRADA 1088</t>
+          <t>CISNEROS, VIRREY 1610</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -9293,17 +9293,17 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440520</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Tensor</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -9320,10 +9320,10 @@
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.472866</v>
+        <v>-58.469727</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.620121</v>
+        <v>-34.612013</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>NRA-M</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9349,7 +9349,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>-748</t>
+          <t>8550</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>GUTENBERG 340</t>
+          <t>FRAGATA PRES. SARMIENTO 1390</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>812440623</t>
+          <t>812440373</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>inclinado base podrida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -9399,17 +9399,17 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L105" t="n">
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.471395</v>
+        <v>-58.456778</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.592451</v>
+        <v>-34.609187</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>PUE-?</t>
+          <t>NRA-I</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9435,22 +9435,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>S01295589</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/24/2026</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CISNEROS, VIRREY 1610</t>
+          <t>CABILDO AV. 1008</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>812440520</t>
+          <t>812440653</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -9485,21 +9485,21 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L106" t="n">
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.469727</v>
+        <v>-58.446714</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.612013</v>
+        <v>-34.569183</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>COG-C</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9521,22 +9521,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>8550</t>
+          <t>S01406719</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/24/2026</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FRAGATA PRES. SARMIENTO 1390</t>
+          <t>3 DE FEBRERO 4481</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>812440373</t>
+          <t>812440639</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -9571,21 +9571,21 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L107" t="n">
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.456778</v>
+        <v>-58.467166</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.609187</v>
+        <v>-34.539469</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -9595,7 +9595,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>NRA-I</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9607,22 +9607,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S01295589</t>
+          <t>S00867165</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2/24/2026</t>
+          <t>2/26/2026</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CABILDO AV. 1008</t>
+          <t xml:space="preserve"> VALLEJOS 2250</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>812440653</t>
+          <t>812503628</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -9664,14 +9664,14 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.446714</v>
+        <v>-58.493418</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.569183</v>
+        <v>-34.583307</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>COG-C</t>
+          <t>PUE-K</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9693,22 +9693,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S01406719</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2/24/2026</t>
+          <t>2/26/2026</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>3 DE FEBRERO 4481</t>
+          <t xml:space="preserve">ESTADO PLURINACIONAL DE BOLIVIA 3526 </t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>812440639</t>
+          <t>812503597</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -9743,21 +9743,21 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L109" t="n">
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.467166</v>
+        <v>-58.491306</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.539469</v>
+        <v>-34.592511</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -9779,7 +9779,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S00867165</t>
+          <t>8397</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VALLEJOS 2250</t>
+          <t>TERRADA 3739</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9809,12 +9809,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>812503628</t>
+          <t>812503610</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -9836,10 +9836,10 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.493418</v>
+        <v>-58.494807</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.583307</v>
+        <v>-34.592416</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>PUE-K</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9865,7 +9865,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>8392</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9875,7 +9875,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESTADO PLURINACIONAL DE BOLIVIA 3526 </t>
+          <t xml:space="preserve"> TERRADA 3695 </t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9895,12 +9895,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>812503597</t>
+          <t>812503605</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -9922,10 +9922,10 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.491306</v>
+        <v>-58.494371</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.592511</v>
+        <v>-34.592899</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -9951,22 +9951,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>8397</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2/26/2026</t>
+          <t>2/27/2026</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TERRADA 3739</t>
+          <t>SIMBRON 5855</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>812503610</t>
+          <t>812503637</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10001,21 +10001,21 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L112" t="n">
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.494807</v>
+        <v>-58.527129</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.592416</v>
+        <v>-34.620962</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>DEV-G</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10037,22 +10037,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>8398</t>
+          <t>-769</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2/26/2026</t>
+          <t>3/2/2026</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TERRADA 3695 </t>
+          <t>RIVERA, PEDRO I., DR. 2734</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>812503605</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -10094,14 +10094,14 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.494371</v>
+        <v>-58.464354</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.592899</v>
+        <v>-34.5587</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10123,22 +10123,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>S00106358</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2/27/2026</t>
+          <t>3/4/2026</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SIMBRON 5855</t>
+          <t>TRONADOR 1194</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>812503637</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -10173,21 +10173,21 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L114" t="n">
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.527129</v>
+        <v>-58.466138</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.620962</v>
+        <v>-34.579638</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>DEV-G</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10209,22 +10209,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>-769</t>
+          <t>S00169078</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>3/2/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>RIVERA, PEDRO I., DR. 2734</t>
+          <t>LOPEZ, CARLOS ANTONIO 3911</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -10254,26 +10254,26 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L115" t="n">
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.464354</v>
+        <v>-58.516319</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.5587</v>
+        <v>-34.593592</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -10283,7 +10283,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10295,22 +10295,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S00106358</t>
+          <t>S00190060</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>3/4/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>TRONADOR 1194</t>
+          <t xml:space="preserve">OBISPO SAN ALBERTO 3176 </t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10352,14 +10352,14 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.466138</v>
+        <v>-58.509545</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.579638</v>
+        <v>-34.584532</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>PUE-M</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10381,22 +10381,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S00169078</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>LOPEZ, CARLOS ANTONIO 3911</t>
+          <t>OROÑO, NICASIO 2540</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -10431,17 +10431,17 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L117" t="n">
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.516319</v>
+        <v>-58.459566</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.593592</v>
+        <v>-34.597579</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -10455,34 +10455,34 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>NRA-N</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1NRA</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S00190060</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBISPO SAN ALBERTO 3176 </t>
+          <t>COSTA RICA 5733</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -10512,7 +10512,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -10524,24 +10524,24 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.509545</v>
+        <v>-58.436004</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.584532</v>
+        <v>-34.58156</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>PUE-M</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10553,7 +10553,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>OROÑO, NICASIO 2540</t>
+          <t>LAVOISIER 3556</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -10610,10 +10610,10 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.459566</v>
+        <v>-58.502869</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.597579</v>
+        <v>-34.567437</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -10627,19 +10627,19 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>NRA-N</t>
+          <t>PUE-H</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8508</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10649,12 +10649,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>COSTA RICA 5733</t>
+          <t>NEWBERY, JORGE 3117</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -10696,10 +10696,10 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.436004</v>
+        <v>-58.446446</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.58156</v>
+        <v>-34.578293</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10725,7 +10725,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10735,12 +10735,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>LAVOISIER 3556</t>
+          <t>SOLDADO DE LA INDEPENDENCIA 851</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -10782,24 +10782,24 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.502869</v>
+        <v>-58.435443</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.567437</v>
+        <v>-34.56693</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>PUE-H</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10811,7 +10811,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>900009605910</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10821,12 +10821,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 3117</t>
+          <t xml:space="preserve">BORDABEHERE ENZO 2801 </t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -10846,7 +10846,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -10861,31 +10861,31 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L122" t="n">
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.446446</v>
+        <v>-58.480297</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.578293</v>
+        <v>-34.600118</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>PUE-A</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10897,22 +10897,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SOLDADO DE LA INDEPENDENCIA 851</t>
+          <t>NAZCA AV. 3312</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -10954,24 +10954,24 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.435443</v>
+        <v>-58.492236</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.56693</v>
+        <v>-34.598228</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10983,22 +10983,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>900009605910</t>
+          <t>8519</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">BORDABEHERE ENZO 2801 </t>
+          <t>OROÑO, NICASIO 2170</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>Columna Picada</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -11033,17 +11033,17 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L124" t="n">
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.480297</v>
+        <v>-58.460865</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.600118</v>
+        <v>-34.601594</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -11057,34 +11057,34 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>PUE-A</t>
+          <t>NRA-N</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1NRA</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>8480</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>NAZCA AV. 3312</t>
+          <t>MOLDES 3006</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>Columna Picada</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -11119,21 +11119,21 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L125" t="n">
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.492236</v>
+        <v>-58.466299</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.598228</v>
+        <v>-34.555783</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11155,7 +11155,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>8519</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11165,7 +11165,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>OROÑO, NICASIO 2170</t>
+          <t xml:space="preserve">ARGERICH 3561 </t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11212,10 +11212,10 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.460865</v>
+        <v>-58.495986</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.601594</v>
+        <v>-34.595286</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -11229,19 +11229,19 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>NRA-N</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>8439</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11251,12 +11251,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MOLDES 3006</t>
+          <t xml:space="preserve">CADIZ 4091 </t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Columna Picada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -11291,21 +11291,21 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L127" t="n">
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.466299</v>
+        <v>-58.478929</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.555783</v>
+        <v>-34.580774</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11327,7 +11327,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARGERICH 3561 </t>
+          <t>BERNA 2449</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -11362,7 +11362,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Columna Picada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -11384,10 +11384,10 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.495986</v>
+        <v>-58.478248</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.595286</v>
+        <v>-34.581288</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11413,7 +11413,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11423,7 +11423,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>AVALOS 1654</t>
+          <t>GAMARRA 1504</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -11470,10 +11470,10 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.480338</v>
+        <v>-58.476783</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.581544</v>
+        <v>-34.582937</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11499,7 +11499,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAMARRA 1751 </t>
+          <t>GANDARA 3308</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11556,10 +11556,10 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.479932</v>
+        <v>-58.485416</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.580069</v>
+        <v>-34.586085</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11585,7 +11585,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>8449</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">CADIZ 4091 </t>
+          <t>GIRIBONE 3355</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -11642,10 +11642,10 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.478929</v>
+        <v>-58.486528</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.580774</v>
+        <v>-34.585612</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11671,22 +11671,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>-771</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VICTORICA, BENJAMIN, GENERAL, AV. 2330</t>
+          <t>SAN BLAS 4112</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11704,11 +11704,7 @@
           <t>Pendiente ADM</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
+      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -11721,21 +11717,21 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L132" t="n">
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.478983</v>
+        <v>-58.494458</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.579669</v>
+        <v>-34.620078</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -11745,7 +11741,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>DEV-J</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11757,7 +11753,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>8443</t>
+          <t>-773</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11767,12 +11763,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>BERNA 2449</t>
+          <t>LA PLATA AV. 2244</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11792,12 +11788,12 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>desmonte</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -11814,24 +11810,24 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.478248</v>
+        <v>-58.423288</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.581288</v>
+        <v>-34.640581</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11843,17 +11839,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>8447</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/10/2026</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">AVALOS 1301 </t>
+          <t xml:space="preserve">LIVERPOOL 2903 </t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11878,7 +11874,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>Columna Picada</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -11900,10 +11896,10 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.477244</v>
+        <v>-58.482265</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.584896</v>
+        <v>-34.582718</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -11917,7 +11913,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>ATH-G</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11929,17 +11925,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>8448</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/10/2026</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>GAMARRA 1504</t>
+          <t>BAUNESS 1600</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11964,7 +11960,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>Columna Picada</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -11986,10 +11982,10 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.476783</v>
+        <v>-58.481148</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.582937</v>
+        <v>-34.583622</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -12015,17 +12011,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>8461</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/10/2026</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>GANDARA 3308</t>
+          <t>BARZANA 1676</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -12050,7 +12046,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Columna Picada</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -12063,19 +12059,15 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" t="n">
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.485416</v>
+        <v>-58.484405</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.586085</v>
+        <v>-34.583582</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -12101,22 +12093,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/10/2026</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>GIRIBONE 3355</t>
+          <t>LA PAMPA 5896</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12136,7 +12128,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Columna Picada</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -12158,10 +12150,10 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.486528</v>
+        <v>-58.487925</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.585612</v>
+        <v>-34.584375</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -12175,7 +12167,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>ATH-K</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12187,22 +12179,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>-771</t>
+          <t xml:space="preserve">8471 </t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>3/11/2026</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SAN BLAS 4112</t>
+          <t>BUCARELLI 1253</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12217,10 +12209,14 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr"/>
+          <t>812878745</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Cambiar columna</t>
+        </is>
+      </c>
       <c r="I138" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -12233,21 +12229,21 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L138" t="n">
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.494458</v>
+        <v>-58.47844</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.620078</v>
+        <v>-34.586982</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -12257,7 +12253,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>DEV-J</t>
+          <t>ATH-G</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12269,22 +12265,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>-773</t>
+          <t xml:space="preserve">8474 </t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/11/2026</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>LA PLATA AV. 2244</t>
+          <t>ESTOMBA 1327</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12299,51 +12295,51 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812878830</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>desmonte</t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L139" t="n">
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.423288</v>
+        <v>-58.464844</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.640581</v>
+        <v>-34.578243</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>ATH-G</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12355,17 +12351,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>8453</t>
+          <t xml:space="preserve">8475 </t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>3/10/2026</t>
+          <t>3/11/2026</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIVERPOOL 2903 </t>
+          <t>AV. DE LOS INCAS 3594</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -12385,17 +12381,17 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812878864</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Columna Picada</t>
+          <t xml:space="preserve">Columna Inclinada </t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -12412,14 +12408,14 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.482265</v>
+        <v>-58.463971</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.582718</v>
+        <v>-34.575577</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -12429,7 +12425,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12441,17 +12437,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t xml:space="preserve">8476 </t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>3/10/2026</t>
+          <t>3/11/2026</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>BAUNESS 1600</t>
+          <t>GIRIBONE 2219</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -12471,17 +12467,17 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812878866</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Columna Picada</t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -12498,14 +12494,14 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.481148</v>
+        <v>-58.472418</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.583622</v>
+        <v>-34.57958</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -12515,7 +12511,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>ATH-E</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12527,22 +12523,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t xml:space="preserve">8568 </t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>3/10/2026</t>
+          <t>3/11/2026</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>BARZANA 1676</t>
+          <t>HOLMBERG 1053</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12557,17 +12553,17 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812878877</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Columna Picada</t>
+          <t>Columna Cementar</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -12575,19 +12571,23 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
       <c r="L142" t="n">
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.484405</v>
+        <v>-58.468422</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.583582</v>
+        <v>-34.582173</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12609,22 +12609,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t xml:space="preserve">8569 </t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>3/10/2026</t>
+          <t>3/11/2026</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>LA PAMPA 5896</t>
+          <t>GARCIA DEL RIO 4577</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12639,17 +12639,17 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812878879</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Columna Picada</t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -12666,14 +12666,14 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.487925</v>
+        <v>-58.489649</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.584375</v>
+        <v>-34.556653</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>ATH-K</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12695,22 +12695,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">8471 </t>
+          <t xml:space="preserve">8574 </t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>3/11/2026</t>
+          <t>3/13/2026</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>BUCARELLI 1253</t>
+          <t xml:space="preserve">MANZANARES 4746 </t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -12725,17 +12725,17 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>812878745</t>
+          <t>812878883</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Cambiar columna</t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -12752,14 +12752,14 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.47844</v>
+        <v>-58.490797</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.586982</v>
+        <v>-34.558302</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -12769,7 +12769,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>ATH-G</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12781,22 +12781,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">8474 </t>
+          <t xml:space="preserve">8575 </t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>3/11/2026</t>
+          <t>3/13/2026</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ESTOMBA 1327</t>
+          <t>LUGONES 3806</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>812878830</t>
+          <t>812878895</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -12826,26 +12826,26 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L145" t="n">
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.464844</v>
+        <v>-58.490494</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.578243</v>
+        <v>-34.557966</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>ATH-G</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12867,22 +12867,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">8475 </t>
+          <t>8576</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>3/11/2026</t>
+          <t>3/13/2026</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>AV. DE LOS INCAS 3594</t>
+          <t>LUGONES 3866</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -12897,12 +12897,12 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>812878864</t>
+          <t>812878898</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Columna Inclinada </t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -12924,14 +12924,14 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.463971</v>
+        <v>-58.490728</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.575577</v>
+        <v>-34.55763</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12953,22 +12953,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">8476 </t>
+          <t>8577</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>3/11/2026</t>
+          <t>3/13/2026</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>GIRIBONE 2219</t>
+          <t xml:space="preserve">LUGONES 3992 </t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -12983,7 +12983,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>812878866</t>
+          <t>812878931</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -13010,14 +13010,14 @@
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.472418</v>
+        <v>-58.491397</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.57958</v>
+        <v>-34.556668</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -13027,7 +13027,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>ATH-E</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -13039,17 +13039,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">8568 </t>
+          <t>8578</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>3/11/2026</t>
+          <t>3/13/2026</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>HOLMBERG 1053</t>
+          <t xml:space="preserve">LUGONES 4030 </t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -13069,12 +13069,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>812878877</t>
+          <t>812878948</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Columna Cementar</t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -13096,14 +13096,14 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.468422</v>
+        <v>-58.491655</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.582173</v>
+        <v>-34.556298</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13125,17 +13125,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">8569 </t>
+          <t>8579</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>3/11/2026</t>
+          <t>3/13/2026</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>GARCIA DEL RIO 4577</t>
+          <t>LUGONES 4090</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -13155,7 +13155,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>812878879</t>
+          <t>812878958</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -13182,10 +13182,10 @@
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.489649</v>
+        <v>-58.49191</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.556653</v>
+        <v>-34.555928</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13211,7 +13211,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">8574 </t>
+          <t>8580</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANZANARES 4746 </t>
+          <t>PAROISSIEN 4711</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -13241,17 +13241,17 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>812878883</t>
+          <t>812878986</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Columna Inclinada</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -13268,10 +13268,10 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.490797</v>
+        <v>-58.491698</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.558302</v>
+        <v>-34.556615</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -13297,7 +13297,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">8575 </t>
+          <t>8581</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>LUGONES 3806</t>
+          <t>MILLER 4016</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -13327,7 +13327,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>812878895</t>
+          <t>812879363</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -13354,10 +13354,10 @@
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>-58.490494</v>
+        <v>-58.492605</v>
       </c>
       <c r="N151" t="n">
-        <v>-34.557966</v>
+        <v>-34.556761</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -13383,7 +13383,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>LUGONES 3866</t>
+          <t>ACHA MARIANO GRAL 3712</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -13413,22 +13413,22 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>812878898</t>
+          <t>812879378</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Columna Inclinada</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Sin chequear</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -13440,10 +13440,10 @@
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.490728</v>
+        <v>-58.489045</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.55763</v>
+        <v>-34.558226</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -13469,7 +13469,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>8577</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13479,7 +13479,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUGONES 3992 </t>
+          <t>ACHA MARIANO GRAL 3744</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -13499,17 +13499,17 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>812878931</t>
+          <t>812879404</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Columna Inclinada</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -13526,10 +13526,10 @@
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>-58.491397</v>
+        <v>-58.489142</v>
       </c>
       <c r="N153" t="n">
-        <v>-34.556668</v>
+        <v>-34.558086</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -13555,7 +13555,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>8578</t>
+          <t>8585</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUGONES 4030 </t>
+          <t>MANZANARES 4512</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -13585,17 +13585,17 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>812878948</t>
+          <t>812879418</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Columna Inclinada</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -13612,10 +13612,10 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>-58.491655</v>
+        <v>-58.488739</v>
       </c>
       <c r="N154" t="n">
-        <v>-34.556298</v>
+        <v>-34.557321</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -13641,7 +13641,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>8579</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>LUGONES 4090</t>
+          <t>MACHAIN 3709</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>812878958</t>
+          <t>812879441</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -13698,10 +13698,10 @@
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>-58.49191</v>
+        <v>-58.488038</v>
       </c>
       <c r="N155" t="n">
-        <v>-34.555928</v>
+        <v>-34.557763</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -13727,7 +13727,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>8580</t>
+          <t>8587</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>PAROISSIEN 4711</t>
+          <t>ACHA MARIANO GRAL 3802</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>812878986</t>
+          <t>812879447</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -13784,10 +13784,10 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>-58.491698</v>
+        <v>-58.489543</v>
       </c>
       <c r="N156" t="n">
-        <v>-34.556615</v>
+        <v>-34.557511</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -13813,7 +13813,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>8588</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13823,7 +13823,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>MILLER 4016</t>
+          <t>ACHA MARIANO GRAL 3874</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>812879363</t>
+          <t>812879462</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -13853,7 +13853,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -13870,10 +13870,10 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>-58.492605</v>
+        <v>-58.489778</v>
       </c>
       <c r="N157" t="n">
-        <v>-34.556761</v>
+        <v>-34.557174</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ACHA MARIANO GRAL 3712</t>
+          <t>ACHA MARIANO GRAL 3948</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>812879378</t>
+          <t>812879479</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Sin chequear</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -13956,10 +13956,10 @@
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>-58.489045</v>
+        <v>-58.490224</v>
       </c>
       <c r="N158" t="n">
-        <v>-34.558226</v>
+        <v>-34.556533</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -13985,22 +13985,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>8584</t>
+          <t xml:space="preserve">8618 </t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>3/13/2026</t>
+          <t>3/17/2026</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>ACHA MARIANO GRAL 3744</t>
+          <t>VALLEJOS 4319</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14015,12 +14015,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>812879404</t>
+          <t>812879612</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>Cambiar Poste de madera a PRFV</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -14033,23 +14033,19 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
+      <c r="K159" t="inlineStr"/>
       <c r="L159" t="n">
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>-58.489142</v>
+        <v>-58.51875</v>
       </c>
       <c r="N159" t="n">
-        <v>-34.558086</v>
+        <v>-34.598858</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -14059,7 +14055,7 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>PUE-P</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -14071,22 +14067,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t xml:space="preserve">8619 </t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>3/13/2026</t>
+          <t>3/17/2026</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>MANZANARES 4512</t>
+          <t>CONCORDIA 3575</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14101,17 +14097,17 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>812879418</t>
+          <t>812879757</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>Desmontar Poste y migrar a Columna</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -14128,14 +14124,14 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>-58.488739</v>
+        <v>-58.502664</v>
       </c>
       <c r="N160" t="n">
-        <v>-34.557321</v>
+        <v>-34.599377</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -14145,7 +14141,7 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -14157,22 +14153,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>8586</t>
+          <t xml:space="preserve">8623    </t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>3/13/2026</t>
+          <t>3/17/2026</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>MACHAIN 3709</t>
+          <t>INCLAN 2402</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14187,12 +14183,12 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>812879441</t>
+          <t>812879763</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Columna Inclinada</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -14214,24 +14210,24 @@
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>-58.488038</v>
+        <v>-58.398304</v>
       </c>
       <c r="N161" t="n">
-        <v>-34.557763</v>
+        <v>-34.629576</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -14243,22 +14239,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>R001</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>3/13/2026</t>
+          <t>3/18/2026</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>ACHA MARIANO GRAL 3802</t>
+          <t>EL PROFETA DE LA PAMPA 4523</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14273,12 +14269,12 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>812879447</t>
+          <t>812879773</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -14288,7 +14284,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -14300,14 +14296,14 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>-58.489543</v>
+        <v>-58.477211</v>
       </c>
       <c r="N162" t="n">
-        <v>-34.557511</v>
+        <v>-34.652708</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -14317,7 +14313,7 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>PAV-O</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -14329,22 +14325,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>8588</t>
+          <t>00239146</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>3/13/2026</t>
+          <t>3/19/2026</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>ACHA MARIANO GRAL 3874</t>
+          <t>POLA 1104</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14359,12 +14355,12 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>812879462</t>
+          <t>812879780</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Columna Inclinada</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -14379,21 +14375,21 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L163" t="n">
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>-58.489778</v>
+        <v>-58.50158</v>
       </c>
       <c r="N163" t="n">
-        <v>-34.557174</v>
+        <v>-34.648954</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -14403,7 +14399,7 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>PAV-J</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -14415,22 +14411,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>3/13/2026</t>
+          <t>3/19/2026</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>ACHA MARIANO GRAL 3948</t>
+          <t>BONIFACIO JOSE 2319</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14445,7 +14441,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>812879479</t>
+          <t>812879799</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -14472,24 +14468,24 @@
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>-58.490224</v>
+        <v>-58.459955</v>
       </c>
       <c r="N164" t="n">
-        <v>-34.556533</v>
+        <v>-34.631973</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -14501,22 +14497,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">8618 </t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>3/17/2026</t>
+          <t>3/19/2026</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>VALLEJOS 4319</t>
+          <t>RIVADAVIA AV 5764</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14531,12 +14527,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>812879612</t>
+          <t>812879872</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Cambiar Poste de madera a PRFV</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -14549,29 +14545,33 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
       <c r="L165" t="n">
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>-58.51875</v>
+        <v>-58.446644</v>
       </c>
       <c r="N165" t="n">
-        <v>-34.598858</v>
+        <v>-34.622863</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>PUE-P</t>
+          <t>PCH-I</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -14583,22 +14583,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">8619 </t>
+          <t>00185436</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>3/17/2026</t>
+          <t>3/19/2026</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>CONCORDIA 3575</t>
+          <t>BESARES 3453</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14613,17 +14613,17 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>812879757</t>
+          <t>812879885</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Desmontar Poste y migrar a Columna</t>
+          <t>Cambiar Poste por Columna</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -14640,14 +14640,14 @@
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>-58.502664</v>
+        <v>-58.48116</v>
       </c>
       <c r="N166" t="n">
-        <v>-34.599377</v>
+        <v>-34.549119</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
@@ -14657,7 +14657,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -14669,17 +14669,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">8623    </t>
+          <t>01168971</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>3/17/2026</t>
+          <t>3/19/2026</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>INCLAN 2402</t>
+          <t>NECOCHEA 369</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>812879763</t>
+          <t>812879892</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -14726,10 +14726,10 @@
         <v>1</v>
       </c>
       <c r="M167" t="n">
-        <v>-58.398304</v>
+        <v>-58.364132</v>
       </c>
       <c r="N167" t="n">
-        <v>-34.629576</v>
+        <v>-34.628423</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>CON-F</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -14755,22 +14755,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>R001</t>
+          <t xml:space="preserve">8642   </t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>3/18/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>EL PROFETA DE LA PAMPA 4523</t>
+          <t>CALCENA 347</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14785,22 +14785,22 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>812879773</t>
+          <t>812879950</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>DESMONTAR COLUMNA Y MIGRAR RED A COLUMNA ALEDAÑA</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -14812,24 +14812,24 @@
         <v>1</v>
       </c>
       <c r="M168" t="n">
-        <v>-58.477211</v>
+        <v>-58.457348</v>
       </c>
       <c r="N168" t="n">
-        <v>-34.652708</v>
+        <v>-34.622249</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>PAV-O</t>
+          <t>NRA-C</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
@@ -14841,22 +14841,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>00239146</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>3/19/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>POLA 1104</t>
+          <t>GARMENDIA AV. 4945</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14871,12 +14871,12 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>812879780</t>
+          <t>812879971</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -14891,21 +14891,21 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L169" t="n">
         <v>1</v>
       </c>
       <c r="M169" t="n">
-        <v>-58.50158</v>
+        <v>-58.465345</v>
       </c>
       <c r="N169" t="n">
-        <v>-34.648954</v>
+        <v>-34.595549</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>PAV-J</t>
+          <t>ATH-?</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -14927,22 +14927,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>00223191</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>3/19/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>BONIFACIO JOSE 2319</t>
+          <t>CATAMARCA 254</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -14957,12 +14957,12 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>812879799</t>
+          <t>812879982</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -14972,7 +14972,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -14984,14 +14984,14 @@
         <v>1</v>
       </c>
       <c r="M170" t="n">
-        <v>-58.459955</v>
+        <v>-58.406734</v>
       </c>
       <c r="N170" t="n">
-        <v>-34.631973</v>
+        <v>-34.613107</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -15013,22 +15013,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t xml:space="preserve">8654 </t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>3/19/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>RIVADAVIA AV 5764</t>
+          <t>CONCORDIA 3663</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -15043,17 +15043,17 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>812879872</t>
+          <t>812879993</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>DESMONTAR POSTE Y MIGRAR RED A COLUMNA EXT.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -15070,24 +15070,24 @@
         <v>1</v>
       </c>
       <c r="M171" t="n">
-        <v>-58.446644</v>
+        <v>-58.503291</v>
       </c>
       <c r="N171" t="n">
-        <v>-34.622863</v>
+        <v>-34.598681</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>PCH-I</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
@@ -15099,22 +15099,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>00185436</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>3/19/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>BESARES 3453</t>
+          <t>REPUBLICA BOLIVARIANA DE VENEZUELA 2071</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -15129,12 +15129,12 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>812879885</t>
+          <t>812880000</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Cambiar Poste por Columna</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -15156,24 +15156,24 @@
         <v>1</v>
       </c>
       <c r="M172" t="n">
-        <v>-58.48116</v>
+        <v>-58.395567</v>
       </c>
       <c r="N172" t="n">
-        <v>-34.549119</v>
+        <v>-34.615169</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -15185,22 +15185,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>01168971</t>
+          <t>8663</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>3/19/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>NECOCHEA 369</t>
+          <t>MONTENEGRO 1539</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -15215,22 +15215,22 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>812879892</t>
+          <t>812880004</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>APLOMAR COLUMNA</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -15242,24 +15242,24 @@
         <v>1</v>
       </c>
       <c r="M173" t="n">
-        <v>-58.364132</v>
+        <v>-58.468478</v>
       </c>
       <c r="N173" t="n">
-        <v>-34.628423</v>
+        <v>-34.587599</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>CON-F</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
@@ -15271,7 +15271,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">8642   </t>
+          <t>8664</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15281,12 +15281,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>CALCENA 347</t>
+          <t>JEREZ PEDRO DE 430</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -15301,17 +15301,17 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>812879950</t>
+          <t>812880006</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>DESMONTAR COLUMNA Y MIGRAR RED A COLUMNA ALEDAÑA</t>
+          <t>APLOMAR COLUMNA</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -15328,24 +15328,24 @@
         <v>1</v>
       </c>
       <c r="M174" t="n">
-        <v>-58.457348</v>
+        <v>-58.467418</v>
       </c>
       <c r="N174" t="n">
-        <v>-34.622249</v>
+        <v>-34.586278</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>NRA-C</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
@@ -15357,7 +15357,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15367,12 +15367,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>GARMENDIA AV. 4945</t>
+          <t>GARCIA DEL RIO 4457</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -15387,17 +15387,17 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>812879971</t>
+          <t>812880010</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>APLOMAR COLUMNA</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -15414,14 +15414,14 @@
         <v>1</v>
       </c>
       <c r="M175" t="n">
-        <v>-58.465345</v>
+        <v>-58.488608</v>
       </c>
       <c r="N175" t="n">
-        <v>-34.595549</v>
+        <v>-34.556155</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -15431,7 +15431,7 @@
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>ATH-?</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
@@ -15443,7 +15443,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>00223191</t>
+          <t>8667</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15453,12 +15453,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>CATAMARCA 254</t>
+          <t>MACHAIN 3817</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -15473,22 +15473,22 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>812879982</t>
+          <t>812880018</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>APLOMAR COLUMNA</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -15500,24 +15500,24 @@
         <v>1</v>
       </c>
       <c r="M176" t="n">
-        <v>-58.406734</v>
+        <v>-58.488586</v>
       </c>
       <c r="N176" t="n">
-        <v>-34.613107</v>
+        <v>-34.556965</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
@@ -15529,7 +15529,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">8654 </t>
+          <t>8669</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15539,12 +15539,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>CONCORDIA 3663</t>
+          <t>MACHAIN 3961</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -15559,17 +15559,17 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>812879993</t>
+          <t>812880026</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>DESMONTAR POSTE Y MIGRAR RED A COLUMNA EXT.</t>
+          <t>APLOMAR COLUMNA</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -15586,14 +15586,14 @@
         <v>1</v>
       </c>
       <c r="M177" t="n">
-        <v>-58.503291</v>
+        <v>-58.489299</v>
       </c>
       <c r="N177" t="n">
-        <v>-34.598681</v>
+        <v>-34.555926</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
@@ -15615,7 +15615,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>00201041</t>
+          <t>8671</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15625,12 +15625,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>HABANA 4448</t>
+          <t>TRONADOR 284</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -15645,17 +15645,17 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>812879994</t>
+          <t>812880206</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>DEMONTAR POSTE Y REEMPLAZAR POR COLUMNA</t>
+          <t>APLOMAR COLUMNA</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -15672,10 +15672,10 @@
         <v>1</v>
       </c>
       <c r="M178" t="n">
-        <v>-58.518808</v>
+        <v>-58.470504</v>
       </c>
       <c r="N178" t="n">
-        <v>-34.601236</v>
+        <v>-34.588131</v>
       </c>
       <c r="O178" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>PUE-P</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
@@ -15701,7 +15701,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>8658</t>
+          <t>8673</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15711,12 +15711,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>REPUBLICA BOLIVARIANA DE VENEZUELA 2071</t>
+          <t>CADIZ 3715</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -15731,17 +15731,17 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>812880000</t>
+          <t>812880209</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>APLOMAR COLUMNA</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -15758,24 +15758,24 @@
         <v>1</v>
       </c>
       <c r="M179" t="n">
-        <v>-58.395567</v>
+        <v>-58.474682</v>
       </c>
       <c r="N179" t="n">
-        <v>-34.615169</v>
+        <v>-34.581396</v>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
@@ -15787,7 +15787,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15797,7 +15797,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>MONTENEGRO 1539</t>
+          <t>LA HAYA 3722</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -15817,7 +15817,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>812880004</t>
+          <t>812880230</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -15844,14 +15844,14 @@
         <v>1</v>
       </c>
       <c r="M180" t="n">
-        <v>-58.468478</v>
+        <v>-58.475097</v>
       </c>
       <c r="N180" t="n">
-        <v>-34.587599</v>
+        <v>-34.581101</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -15861,7 +15861,7 @@
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
@@ -15873,7 +15873,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>8676</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15883,12 +15883,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>JEREZ PEDRO DE 430</t>
+          <t>HOLMBERG 979</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -15903,7 +15903,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>812880006</t>
+          <t>812880241</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -15930,10 +15930,10 @@
         <v>1</v>
       </c>
       <c r="M181" t="n">
-        <v>-58.467418</v>
+        <v>-58.468449</v>
       </c>
       <c r="N181" t="n">
-        <v>-34.586278</v>
+        <v>-34.582898</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15969,12 +15969,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>GARCIA DEL RIO 4457</t>
+          <t>GIRARDOT 1384</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -15989,17 +15989,17 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>812880010</t>
+          <t>812880404</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>APLOMAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -16016,14 +16016,14 @@
         <v>1</v>
       </c>
       <c r="M182" t="n">
-        <v>-58.488608</v>
+        <v>-58.466063</v>
       </c>
       <c r="N182" t="n">
-        <v>-34.556155</v>
+        <v>-34.587896</v>
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
@@ -16045,7 +16045,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -16055,12 +16055,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>MACHAIN 3817</t>
+          <t>CORRIENTES AV 4073</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -16075,17 +16075,17 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>812880018</t>
+          <t>812880406</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>APLOMAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -16102,24 +16102,24 @@
         <v>1</v>
       </c>
       <c r="M183" t="n">
-        <v>-58.488586</v>
+        <v>-58.422076</v>
       </c>
       <c r="N183" t="n">
-        <v>-34.556965</v>
+        <v>-34.60298</v>
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
@@ -16131,7 +16131,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>00223023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -16141,12 +16141,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>MACHAIN 3961</t>
+          <t>SAN JUAN AV. 2201</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -16161,17 +16161,17 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>812880026</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>APLOMAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -16188,24 +16188,24 @@
         <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>-58.489299</v>
+        <v>-58.396491</v>
       </c>
       <c r="N184" t="n">
-        <v>-34.555926</v>
+        <v>-34.622986</v>
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>CEN-B</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
@@ -16217,7 +16217,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>00275970</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -16227,12 +16227,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>TRONADOR 284</t>
+          <t xml:space="preserve"> JUJUY AV. 252</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -16247,17 +16247,17 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>812880206</t>
+          <t>812880578</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>APLOMAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -16274,24 +16274,24 @@
         <v>1</v>
       </c>
       <c r="M185" t="n">
-        <v>-58.470504</v>
+        <v>-58.405319</v>
       </c>
       <c r="N185" t="n">
-        <v>-34.588131</v>
+        <v>-34.612931</v>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
@@ -16303,7 +16303,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>00283507</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -16313,12 +16313,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>CADIZ 3715</t>
+          <t xml:space="preserve">HERRERA 475 </t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -16333,17 +16333,17 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>812880209</t>
+          <t>812880593</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>APLOMAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -16360,24 +16360,24 @@
         <v>1</v>
       </c>
       <c r="M186" t="n">
-        <v>-58.474682</v>
+        <v>-58.378709</v>
       </c>
       <c r="N186" t="n">
-        <v>-34.581396</v>
+        <v>-34.635064</v>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>CON-H</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
@@ -16389,7 +16389,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>8675</t>
+          <t>00289536</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16399,12 +16399,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>LA HAYA 3722</t>
+          <t>VALDENEGRO 3554</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -16419,17 +16419,17 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>812880230</t>
+          <t>812880608</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>APLOMAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -16446,14 +16446,14 @@
         <v>1</v>
       </c>
       <c r="M187" t="n">
-        <v>-58.475097</v>
+        <v>-58.490576</v>
       </c>
       <c r="N187" t="n">
-        <v>-34.581101</v>
+        <v>-34.561508</v>
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
@@ -16463,7 +16463,7 @@
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>PUE-F</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
@@ -16475,22 +16475,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>0000001</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>3/28/2026</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>HOLMBERG 979</t>
+          <t>GIRIBONE 3229</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -16505,17 +16505,17 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>812880241</t>
+          <t>812880759</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>APLOMAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -16532,14 +16532,14 @@
         <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>-58.468449</v>
+        <v>-58.485216</v>
       </c>
       <c r="N188" t="n">
-        <v>-34.582898</v>
+        <v>-34.584797</v>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -16549,780 +16549,10 @@
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>8681</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>3/21/2026</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>GIRARDOT 1384</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>812880404</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L189" t="n">
-        <v>1</v>
-      </c>
-      <c r="M189" t="n">
-        <v>-58.466063</v>
-      </c>
-      <c r="N189" t="n">
-        <v>-34.587896</v>
-      </c>
-      <c r="O189" t="inlineStr">
-        <is>
-          <t>Colegiales</t>
-        </is>
-      </c>
-      <c r="P189" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q189" t="inlineStr">
-        <is>
-          <t>ATH-F</t>
-        </is>
-      </c>
-      <c r="R189" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>8682</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>3/21/2026</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>CORRIENTES AV 4073</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>812880406</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L190" t="n">
-        <v>1</v>
-      </c>
-      <c r="M190" t="n">
-        <v>-58.422076</v>
-      </c>
-      <c r="N190" t="n">
-        <v>-34.60298</v>
-      </c>
-      <c r="O190" t="inlineStr">
-        <is>
-          <t>Almagro</t>
-        </is>
-      </c>
-      <c r="P190" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q190" t="inlineStr">
-        <is>
-          <t>CLI-K</t>
-        </is>
-      </c>
-      <c r="R190" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>00223023</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>3/21/2026</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>SAN JUAN AV. 2201</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L191" t="n">
-        <v>1</v>
-      </c>
-      <c r="M191" t="n">
-        <v>-58.396491</v>
-      </c>
-      <c r="N191" t="n">
-        <v>-34.622986</v>
-      </c>
-      <c r="O191" t="inlineStr">
-        <is>
-          <t>San Telmo</t>
-        </is>
-      </c>
-      <c r="P191" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q191" t="inlineStr">
-        <is>
-          <t>CEN-B</t>
-        </is>
-      </c>
-      <c r="R191" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>00275970</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>3/21/2026</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> JUJUY AV. 252</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>812880578</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L192" t="n">
-        <v>1</v>
-      </c>
-      <c r="M192" t="n">
-        <v>-58.405319</v>
-      </c>
-      <c r="N192" t="n">
-        <v>-34.612931</v>
-      </c>
-      <c r="O192" t="inlineStr">
-        <is>
-          <t>Almagro</t>
-        </is>
-      </c>
-      <c r="P192" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q192" t="inlineStr">
-        <is>
-          <t>CEN-H</t>
-        </is>
-      </c>
-      <c r="R192" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>00283507</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>3/21/2026</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HERRERA 475 </t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>812880593</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L193" t="n">
-        <v>1</v>
-      </c>
-      <c r="M193" t="n">
-        <v>-58.378709</v>
-      </c>
-      <c r="N193" t="n">
-        <v>-34.635064</v>
-      </c>
-      <c r="O193" t="inlineStr">
-        <is>
-          <t>San Telmo</t>
-        </is>
-      </c>
-      <c r="P193" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q193" t="inlineStr">
-        <is>
-          <t>CON-H</t>
-        </is>
-      </c>
-      <c r="R193" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>00289536</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>3/21/2026</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>VALDENEGRO 3554</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>812880608</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L194" t="n">
-        <v>1</v>
-      </c>
-      <c r="M194" t="n">
-        <v>-58.490576</v>
-      </c>
-      <c r="N194" t="n">
-        <v>-34.561508</v>
-      </c>
-      <c r="O194" t="inlineStr">
-        <is>
-          <t>Saavedra</t>
-        </is>
-      </c>
-      <c r="P194" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q194" t="inlineStr">
-        <is>
-          <t>PUE-F</t>
-        </is>
-      </c>
-      <c r="R194" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>R0050</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>3/25/2026</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>IBERA 3244</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>812880728</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L195" t="n">
-        <v>1</v>
-      </c>
-      <c r="M195" t="n">
-        <v>-58.472542</v>
-      </c>
-      <c r="N195" t="n">
-        <v>-34.55798</v>
-      </c>
-      <c r="O195" t="inlineStr">
-        <is>
-          <t>Saavedra</t>
-        </is>
-      </c>
-      <c r="P195" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q195" t="inlineStr">
-        <is>
-          <t>COG-L</t>
-        </is>
-      </c>
-      <c r="R195" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>3/28/2026</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>GIRIBONE 3229</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>812880759</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L196" t="n">
-        <v>1</v>
-      </c>
-      <c r="M196" t="n">
-        <v>-58.485216</v>
-      </c>
-      <c r="N196" t="n">
-        <v>-34.584797</v>
-      </c>
-      <c r="O196" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="P196" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q196" t="inlineStr">
-        <is>
-          <t>ATH-S</t>
-        </is>
-      </c>
-      <c r="R196" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>M880</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>4/1/2026</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>PEDRO VARELA 3713</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr"/>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DESMONTAR POSTE MADERA </t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>Desmonte</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L197" t="n">
-        <v>0</v>
-      </c>
-      <c r="M197" t="n">
-        <v>-58.50431</v>
-      </c>
-      <c r="N197" t="n">
-        <v>-34.602597</v>
-      </c>
-      <c r="O197" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="P197" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q197" t="inlineStr">
-        <is>
-          <t>DEV-C</t>
-        </is>
-      </c>
-      <c r="R197" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_NEW.xlsx
+++ b/mapa_interactivo_NEW.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R188"/>
+  <dimension ref="A1:R192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14972,7 +14972,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -16553,6 +16553,334 @@
         </is>
       </c>
       <c r="R188" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr"/>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>4/14/2026</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>AV INDEPENDENCIA 3810</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>813107750</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L189" t="n">
+        <v>1</v>
+      </c>
+      <c r="M189" t="n">
+        <v>-58.444908</v>
+      </c>
+      <c r="N189" t="n">
+        <v>-34.607205</v>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>ALM-O</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr"/>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>4/14/2026</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>AV INDEPENDENCIA 3810</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>813107750</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L190" t="n">
+        <v>1</v>
+      </c>
+      <c r="M190" t="n">
+        <v>-58.419576</v>
+      </c>
+      <c r="N190" t="n">
+        <v>-34.621289</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>ALM-A</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>4/14/2026</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>AV INDEPENDENCIA 3810</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>813107750</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L191" t="n">
+        <v>1</v>
+      </c>
+      <c r="M191" t="n">
+        <v>-58.430568</v>
+      </c>
+      <c r="N191" t="n">
+        <v>-34.599485</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>CLI-N</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>M00002</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>4/16/2026</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>MELIAN AV 3893</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L192" t="n">
+        <v>1</v>
+      </c>
+      <c r="M192" t="n">
+        <v>-58.481571</v>
+      </c>
+      <c r="N192" t="n">
+        <v>-34.552784</v>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>COG-O</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_NEW.xlsx
+++ b/mapa_interactivo_NEW.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R192"/>
+  <dimension ref="A1:R190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16217,7 +16217,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>00275970</t>
+          <t>00283507</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -16227,12 +16227,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JUJUY AV. 252</t>
+          <t xml:space="preserve">HERRERA 475 </t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>812880578</t>
+          <t>812880593</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -16274,14 +16274,14 @@
         <v>1</v>
       </c>
       <c r="M185" t="n">
-        <v>-58.405319</v>
+        <v>-58.378709</v>
       </c>
       <c r="N185" t="n">
-        <v>-34.612931</v>
+        <v>-34.635064</v>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>CON-H</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
@@ -16303,7 +16303,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>00283507</t>
+          <t>00289536</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -16313,12 +16313,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERRERA 475 </t>
+          <t>VALDENEGRO 3554</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -16333,7 +16333,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>812880593</t>
+          <t>812880608</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -16360,24 +16360,24 @@
         <v>1</v>
       </c>
       <c r="M186" t="n">
-        <v>-58.378709</v>
+        <v>-58.490576</v>
       </c>
       <c r="N186" t="n">
-        <v>-34.635064</v>
+        <v>-34.561508</v>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>CON-H</t>
+          <t>PUE-F</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
@@ -16389,22 +16389,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>00289536</t>
+          <t>0000001</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>3/28/2026</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>VALDENEGRO 3554</t>
+          <t>GIRIBONE 3229</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>812880608</t>
+          <t>812880759</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -16446,14 +16446,14 @@
         <v>1</v>
       </c>
       <c r="M187" t="n">
-        <v>-58.490576</v>
+        <v>-58.485216</v>
       </c>
       <c r="N187" t="n">
-        <v>-34.561508</v>
+        <v>-34.584797</v>
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
@@ -16463,7 +16463,7 @@
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>PUE-F</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
@@ -16473,24 +16473,20 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
+      <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>3/28/2026</t>
+          <t>4/14/2026</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>GIRIBONE 3229</t>
+          <t>AV INDEPENDENCIA 3810</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -16505,7 +16501,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>812880759</t>
+          <t>813107750</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -16532,24 +16528,24 @@
         <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>-58.485216</v>
+        <v>-58.444908</v>
       </c>
       <c r="N188" t="n">
-        <v>-34.584797</v>
+        <v>-34.607205</v>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
@@ -16614,14 +16610,14 @@
         <v>1</v>
       </c>
       <c r="M189" t="n">
-        <v>-58.444908</v>
+        <v>-58.419576</v>
       </c>
       <c r="N189" t="n">
-        <v>-34.607205</v>
+        <v>-34.621289</v>
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
@@ -16631,7 +16627,7 @@
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
@@ -16696,14 +16692,14 @@
         <v>1</v>
       </c>
       <c r="M190" t="n">
-        <v>-58.419576</v>
+        <v>-58.430568</v>
       </c>
       <c r="N190" t="n">
-        <v>-34.621289</v>
+        <v>-34.599485</v>
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
@@ -16713,174 +16709,10 @@
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr"/>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>4/14/2026</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>AV INDEPENDENCIA 3810</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>813107750</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L191" t="n">
-        <v>1</v>
-      </c>
-      <c r="M191" t="n">
-        <v>-58.430568</v>
-      </c>
-      <c r="N191" t="n">
-        <v>-34.599485</v>
-      </c>
-      <c r="O191" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P191" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q191" t="inlineStr">
-        <is>
-          <t>CLI-N</t>
-        </is>
-      </c>
-      <c r="R191" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>M00002</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>4/16/2026</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>MELIAN AV 3893</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L192" t="n">
-        <v>1</v>
-      </c>
-      <c r="M192" t="n">
-        <v>-58.481571</v>
-      </c>
-      <c r="N192" t="n">
-        <v>-34.552784</v>
-      </c>
-      <c r="O192" t="inlineStr">
-        <is>
-          <t>Saavedra</t>
-        </is>
-      </c>
-      <c r="P192" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q192" t="inlineStr">
-        <is>
-          <t>COG-O</t>
-        </is>
-      </c>
-      <c r="R192" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_NEW.xlsx
+++ b/mapa_interactivo_NEW.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R191"/>
+  <dimension ref="A1:R194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16804,6 +16804,252 @@
         </is>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" t="inlineStr"/>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>4/14/2026</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>AV INDEPENDENCIA 3810</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>813107750</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L192" t="n">
+        <v>1</v>
+      </c>
+      <c r="M192" t="n">
+        <v>-58.437499</v>
+      </c>
+      <c r="N192" t="n">
+        <v>-34.578324</v>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>ATH-B</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>4/14/2026</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>AV INDEPENDENCIA 3810</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>813107750</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L193" t="n">
+        <v>1</v>
+      </c>
+      <c r="M193" t="n">
+        <v>-58.435547</v>
+      </c>
+      <c r="N193" t="n">
+        <v>-34.576622</v>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>ATH-B</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>4/14/2026</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>AV INDEPENDENCIA 3810</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>813107750</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L194" t="n">
+        <v>1</v>
+      </c>
+      <c r="M194" t="n">
+        <v>-58.373629</v>
+      </c>
+      <c r="N194" t="n">
+        <v>-34.64417</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>CON-A</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>ARATO-25058.AF.1CON</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapa_interactivo_NEW.xlsx
+++ b/mapa_interactivo_NEW.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R195"/>
+  <dimension ref="A1:R194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9091,22 +9091,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S00506048</t>
+          <t>-748</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TERRADA 1088</t>
+          <t>GUTENBERG 340</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9121,17 +9121,17 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440623</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>inclinado base podrida</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Tensor</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -9141,17 +9141,17 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L102" t="n">
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.472866</v>
+        <v>-58.471395</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.620121</v>
+        <v>-34.592451</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>NRA-M</t>
+          <t>PUE-?</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9177,7 +9177,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>-748</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>GUTENBERG 340</t>
+          <t>CISNEROS, VIRREY 1610</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9207,12 +9207,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>812440623</t>
+          <t>812440520</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>inclinado base podrida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9227,17 +9227,17 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L103" t="n">
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.471395</v>
+        <v>-58.469727</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.592451</v>
+        <v>-34.612013</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>PUE-?</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9263,7 +9263,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8550</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CISNEROS, VIRREY 1610</t>
+          <t>FRAGATA PRES. SARMIENTO 1390</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>812440520</t>
+          <t>812440373</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -9313,17 +9313,17 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L104" t="n">
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.469727</v>
+        <v>-58.456778</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.612013</v>
+        <v>-34.609187</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>NRA-I</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9349,22 +9349,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>8550</t>
+          <t>S01295589</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/24/2026</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FRAGATA PRES. SARMIENTO 1390</t>
+          <t>CABILDO AV. 1008</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>812440373</t>
+          <t>812440653</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -9406,14 +9406,14 @@
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.456778</v>
+        <v>-58.446714</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.609187</v>
+        <v>-34.569183</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>NRA-I</t>
+          <t>COG-C</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9435,7 +9435,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S01295589</t>
+          <t>S01406719</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CABILDO AV. 1008</t>
+          <t>3 DE FEBRERO 4481</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>812440653</t>
+          <t>812440639</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -9485,21 +9485,21 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L106" t="n">
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.446714</v>
+        <v>-58.467166</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.569183</v>
+        <v>-34.539469</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>COG-C</t>
+          <t>BLO-S</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9521,22 +9521,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S01406719</t>
+          <t>S00867165</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2/24/2026</t>
+          <t>2/26/2026</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>3 DE FEBRERO 4481</t>
+          <t xml:space="preserve"> VALLEJOS 2250</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>812440639</t>
+          <t>812503628</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -9571,21 +9571,21 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L107" t="n">
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.467166</v>
+        <v>-58.493418</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.539469</v>
+        <v>-34.583307</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -9595,7 +9595,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>BLO-S</t>
+          <t>PUE-K</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9607,7 +9607,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S00867165</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VALLEJOS 2250</t>
+          <t xml:space="preserve">ESTADO PLURINACIONAL DE BOLIVIA 3526 </t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>812503628</t>
+          <t>812503597</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -9664,10 +9664,10 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.493418</v>
+        <v>-58.491306</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.583307</v>
+        <v>-34.592511</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>PUE-K</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9693,7 +9693,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>8392</t>
+          <t>8397</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESTADO PLURINACIONAL DE BOLIVIA 3526 </t>
+          <t>TERRADA 3739</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>812503597</t>
+          <t>812503610</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -9750,10 +9750,10 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.491306</v>
+        <v>-58.494807</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.592511</v>
+        <v>-34.592416</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>8397</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TERRADA 3739</t>
+          <t xml:space="preserve"> TERRADA 3695 </t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>812503610</t>
+          <t>812503605</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -9836,10 +9836,10 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.494807</v>
+        <v>-58.494371</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.592416</v>
+        <v>-34.592899</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -9865,22 +9865,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>8398</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2/26/2026</t>
+          <t>2/27/2026</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TERRADA 3695 </t>
+          <t>SIMBRON 5855</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9895,12 +9895,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>812503605</t>
+          <t>812503637</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -9915,21 +9915,21 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L111" t="n">
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.494371</v>
+        <v>-58.527129</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.592899</v>
+        <v>-34.620962</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>DEV-G</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9951,22 +9951,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>-769</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2/27/2026</t>
+          <t>3/2/2026</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SIMBRON 5855</t>
+          <t>RIVERA, PEDRO I., DR. 2734</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>812503637</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -9996,26 +9996,26 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L112" t="n">
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.527129</v>
+        <v>-58.464354</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.620962</v>
+        <v>-34.5587</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>DEV-G</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10037,22 +10037,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>-769</t>
+          <t>S00106358</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>3/2/2026</t>
+          <t>3/4/2026</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>RIVERA, PEDRO I., DR. 2734</t>
+          <t>TRONADOR 1194</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -10094,14 +10094,14 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.464354</v>
+        <v>-58.466138</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.5587</v>
+        <v>-34.579638</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10123,22 +10123,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S00106358</t>
+          <t>S00169078</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>3/4/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TRONADOR 1194</t>
+          <t>LOPEZ, CARLOS ANTONIO 3911</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -10173,21 +10173,21 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L114" t="n">
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.466138</v>
+        <v>-58.516319</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.579638</v>
+        <v>-34.593592</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10209,7 +10209,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S00169078</t>
+          <t>S00190060</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>LOPEZ, CARLOS ANTONIO 3911</t>
+          <t xml:space="preserve">OBISPO SAN ALBERTO 3176 </t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -10259,17 +10259,17 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L115" t="n">
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.516319</v>
+        <v>-58.509545</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.593592</v>
+        <v>-34.584532</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>PUE-M</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10295,22 +10295,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S00190060</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBISPO SAN ALBERTO 3176 </t>
+          <t>OROÑO, NICASIO 2540</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -10352,10 +10352,10 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.509545</v>
+        <v>-58.459566</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.584532</v>
+        <v>-34.597579</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -10369,19 +10369,19 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>PUE-M</t>
+          <t>NRA-N</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1NRA</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>OROÑO, NICASIO 2540</t>
+          <t>COSTA RICA 5733</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -10438,36 +10438,36 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.459566</v>
+        <v>-58.436004</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.597579</v>
+        <v>-34.58156</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>NRA-N</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>COSTA RICA 5733</t>
+          <t>LAVOISIER 3556</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -10512,7 +10512,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -10524,24 +10524,24 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.436004</v>
+        <v>-58.502869</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.58156</v>
+        <v>-34.567437</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>PUE-H</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10553,7 +10553,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>8508</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>LAVOISIER 3556</t>
+          <t>NEWBERY, JORGE 3117</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -10610,24 +10610,24 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.502869</v>
+        <v>-58.446446</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.567437</v>
+        <v>-34.578293</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>PUE-H</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10639,7 +10639,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10649,12 +10649,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 3117</t>
+          <t>SOLDADO DE LA INDEPENDENCIA 851</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -10696,10 +10696,10 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.446446</v>
+        <v>-58.435443</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.578293</v>
+        <v>-34.56693</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10725,7 +10725,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>900009605910</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10735,12 +10735,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SOLDADO DE LA INDEPENDENCIA 851</t>
+          <t xml:space="preserve">BORDABEHERE ENZO 2801 </t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -10775,31 +10775,31 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L121" t="n">
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.435443</v>
+        <v>-58.480297</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.56693</v>
+        <v>-34.600118</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>PUE-A</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10811,17 +10811,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>900009605910</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">BORDABEHERE ENZO 2801 </t>
+          <t>NAZCA AV. 3312</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10861,17 +10861,17 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L122" t="n">
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.480297</v>
+        <v>-58.492236</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.600118</v>
+        <v>-34.598228</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>PUE-A</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10897,22 +10897,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>8480</t>
+          <t>8519</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>NAZCA AV. 3312</t>
+          <t>OROÑO, NICASIO 2170</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>Columna Picada</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -10954,10 +10954,10 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.492236</v>
+        <v>-58.460865</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.598228</v>
+        <v>-34.601594</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
@@ -10971,19 +10971,19 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>NRA-N</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1NRA</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>8519</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10993,12 +10993,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>OROÑO, NICASIO 2170</t>
+          <t>MOLDES 3006</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11033,21 +11033,21 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L124" t="n">
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.460865</v>
+        <v>-58.466299</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.601594</v>
+        <v>-34.555783</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -11057,19 +11057,19 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>NRA-N</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11079,12 +11079,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>MOLDES 3006</t>
+          <t xml:space="preserve">ARGERICH 3561 </t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11119,21 +11119,21 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L125" t="n">
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.466299</v>
+        <v>-58.495986</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.555783</v>
+        <v>-34.595286</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>COG-L</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11155,7 +11155,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>8439</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11165,7 +11165,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARGERICH 3561 </t>
+          <t xml:space="preserve">CADIZ 4091 </t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Columna Picada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -11212,10 +11212,10 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.495986</v>
+        <v>-58.478929</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.595286</v>
+        <v>-34.580774</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11241,7 +11241,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">CADIZ 4091 </t>
+          <t>BERNA 2449</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -11298,10 +11298,10 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.478929</v>
+        <v>-58.478248</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.580774</v>
+        <v>-34.581288</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>8443</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BERNA 2449</t>
+          <t>GAMARRA 1504</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -11362,7 +11362,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -11384,10 +11384,10 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.478248</v>
+        <v>-58.476783</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.581288</v>
+        <v>-34.582937</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11413,7 +11413,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>8448</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11423,7 +11423,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>GAMARRA 1504</t>
+          <t>GANDARA 3308</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -11470,10 +11470,10 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.476783</v>
+        <v>-58.485416</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.582937</v>
+        <v>-34.586085</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>8449</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>GANDARA 3308</t>
+          <t>GIRIBONE 3355</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11556,10 +11556,10 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.485416</v>
+        <v>-58.486528</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.586085</v>
+        <v>-34.585612</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -11585,22 +11585,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>-771</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>GIRIBONE 3355</t>
+          <t>SAN BLAS 4112</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11618,11 +11618,7 @@
           <t>Pendiente ADM</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -11635,21 +11631,21 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L131" t="n">
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.486528</v>
+        <v>-58.494458</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.585612</v>
+        <v>-34.620078</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -11659,7 +11655,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>DEV-J</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11671,22 +11667,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>-771</t>
+          <t>-773</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SAN BLAS 4112</t>
+          <t>LA PLATA AV. 2244</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11704,10 +11700,14 @@
           <t>Pendiente ADM</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>desmonte</t>
+        </is>
+      </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -11717,31 +11717,31 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L132" t="n">
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.494458</v>
+        <v>-58.423288</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.620078</v>
+        <v>-34.640581</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>DEV-J</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11753,22 +11753,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>-773</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/10/2026</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>LA PLATA AV. 2244</t>
+          <t xml:space="preserve">LIVERPOOL 2903 </t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11788,12 +11788,12 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>desmonte</t>
+          <t>Columna Picada</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -11810,24 +11810,24 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.423288</v>
+        <v>-58.482265</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.640581</v>
+        <v>-34.582718</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11839,7 +11839,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>8453</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIVERPOOL 2903 </t>
+          <t>BAUNESS 1600</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11896,10 +11896,10 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.482265</v>
+        <v>-58.481148</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.582718</v>
+        <v>-34.583622</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11925,7 +11925,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>8461</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BAUNESS 1600</t>
+          <t>BARZANA 1676</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11973,19 +11973,15 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
+      <c r="K135" t="inlineStr"/>
       <c r="L135" t="n">
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.481148</v>
+        <v>-58.484405</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.583622</v>
+        <v>-34.583582</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -12011,7 +12007,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12021,12 +12017,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>BARZANA 1676</t>
+          <t>LA PAMPA 5896</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12059,15 +12055,19 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
       <c r="L136" t="n">
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.484405</v>
+        <v>-58.487925</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.583582</v>
+        <v>-34.584375</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>ATH-K</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12093,22 +12093,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t xml:space="preserve">8471 </t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>3/10/2026</t>
+          <t>3/11/2026</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>LA PAMPA 5896</t>
+          <t>BUCARELLI 1253</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812878745</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Columna Picada</t>
+          <t>Cambiar columna</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -12150,10 +12150,10 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.487925</v>
+        <v>-58.47844</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.584375</v>
+        <v>-34.586982</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>ATH-K</t>
+          <t>ATH-G</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12179,7 +12179,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">8471 </t>
+          <t xml:space="preserve">8474 </t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>BUCARELLI 1253</t>
+          <t>ESTOMBA 1327</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -12209,41 +12209,41 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>812878745</t>
+          <t>812878830</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Cambiar columna</t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L138" t="n">
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.47844</v>
+        <v>-58.464844</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.586982</v>
+        <v>-34.578243</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -12265,7 +12265,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">8474 </t>
+          <t xml:space="preserve">8475 </t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ESTOMBA 1327</t>
+          <t>AV. DE LOS INCAS 3594</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>812878830</t>
+          <t>812878864</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Columna Inclinada</t>
+          <t xml:space="preserve">Columna Inclinada </t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -12310,22 +12310,22 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L139" t="n">
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.464844</v>
+        <v>-58.463971</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.578243</v>
+        <v>-34.575577</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>ATH-G</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12351,7 +12351,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">8475 </t>
+          <t xml:space="preserve">8476 </t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>AV. DE LOS INCAS 3594</t>
+          <t>GIRIBONE 2219</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>812878864</t>
+          <t>812878866</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Columna Inclinada </t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -12408,10 +12408,10 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.463971</v>
+        <v>-58.472418</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.575577</v>
+        <v>-34.57958</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>ATH-E</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12437,7 +12437,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">8476 </t>
+          <t xml:space="preserve">8568 </t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12447,12 +12447,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>GIRIBONE 2219</t>
+          <t>HOLMBERG 1053</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>812878866</t>
+          <t>812878877</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Columna Inclinada</t>
+          <t>Columna Cementar</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -12494,10 +12494,10 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.472418</v>
+        <v>-58.468422</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.57958</v>
+        <v>-34.582173</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>ATH-E</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12523,7 +12523,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">8568 </t>
+          <t xml:space="preserve">8569 </t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12533,7 +12533,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>HOLMBERG 1053</t>
+          <t>GARCIA DEL RIO 4577</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -12553,12 +12553,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>812878877</t>
+          <t>812878879</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Columna Cementar</t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -12580,14 +12580,14 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.468422</v>
+        <v>-58.489649</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.582173</v>
+        <v>-34.556653</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12609,17 +12609,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">8569 </t>
+          <t xml:space="preserve">8574 </t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>3/11/2026</t>
+          <t>3/13/2026</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>GARCIA DEL RIO 4577</t>
+          <t xml:space="preserve">MANZANARES 4746 </t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>812878879</t>
+          <t>812878883</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -12666,10 +12666,10 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.489649</v>
+        <v>-58.490797</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.556653</v>
+        <v>-34.558302</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">8574 </t>
+          <t xml:space="preserve">8575 </t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12705,7 +12705,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANZANARES 4746 </t>
+          <t>LUGONES 3806</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -12725,7 +12725,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>812878883</t>
+          <t>812878895</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -12752,10 +12752,10 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.490797</v>
+        <v>-58.490494</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.558302</v>
+        <v>-34.557966</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">8575 </t>
+          <t>8576</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>LUGONES 3806</t>
+          <t>LUGONES 3866</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>812878895</t>
+          <t>812878898</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -12838,10 +12838,10 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.490494</v>
+        <v>-58.490728</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.557966</v>
+        <v>-34.55763</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12867,7 +12867,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>8577</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>LUGONES 3866</t>
+          <t xml:space="preserve">LUGONES 3992 </t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>812878898</t>
+          <t>812878931</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -12924,10 +12924,10 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.490728</v>
+        <v>-58.491397</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.55763</v>
+        <v>-34.556668</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>8577</t>
+          <t>8578</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUGONES 3992 </t>
+          <t xml:space="preserve">LUGONES 4030 </t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -12983,7 +12983,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>812878931</t>
+          <t>812878948</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -13010,10 +13010,10 @@
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.491397</v>
+        <v>-58.491655</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.556668</v>
+        <v>-34.556298</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>8578</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUGONES 4030 </t>
+          <t>LUGONES 4090</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>812878948</t>
+          <t>812878958</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -13096,10 +13096,10 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.491655</v>
+        <v>-58.49191</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.556298</v>
+        <v>-34.555928</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>8579</t>
+          <t>8580</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13135,7 +13135,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>LUGONES 4090</t>
+          <t>PAROISSIEN 4711</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -13155,17 +13155,17 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>812878958</t>
+          <t>812878986</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Columna Inclinada</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -13182,10 +13182,10 @@
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.49191</v>
+        <v>-58.491698</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.555928</v>
+        <v>-34.556615</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>8580</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>PAROISSIEN 4711</t>
+          <t>MILLER 4016</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -13241,17 +13241,17 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>812878986</t>
+          <t>812879363</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -13268,10 +13268,10 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.491698</v>
+        <v>-58.492605</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.556615</v>
+        <v>-34.556761</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>MILLER 4016</t>
+          <t>ACHA MARIANO GRAL 3712</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -13327,22 +13327,22 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>812879363</t>
+          <t>812879378</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Columna Inclinada</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Sin chequear</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -13354,10 +13354,10 @@
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>-58.492605</v>
+        <v>-58.489045</v>
       </c>
       <c r="N151" t="n">
-        <v>-34.556761</v>
+        <v>-34.558226</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -13383,7 +13383,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ACHA MARIANO GRAL 3712</t>
+          <t>ACHA MARIANO GRAL 3744</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -13413,7 +13413,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>812879378</t>
+          <t>812879404</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Sin chequear</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -13440,10 +13440,10 @@
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.489045</v>
+        <v>-58.489142</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.558226</v>
+        <v>-34.558086</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>8584</t>
+          <t>8585</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13479,7 +13479,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>ACHA MARIANO GRAL 3744</t>
+          <t>MANZANARES 4512</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>812879404</t>
+          <t>812879418</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -13526,10 +13526,10 @@
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>-58.489142</v>
+        <v>-58.488739</v>
       </c>
       <c r="N153" t="n">
-        <v>-34.558086</v>
+        <v>-34.557321</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>MANZANARES 4512</t>
+          <t>MACHAIN 3709</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -13585,12 +13585,12 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>812879418</t>
+          <t>812879441</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -13612,10 +13612,10 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>-58.488739</v>
+        <v>-58.488038</v>
       </c>
       <c r="N154" t="n">
-        <v>-34.557321</v>
+        <v>-34.557763</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>8586</t>
+          <t>8587</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>MACHAIN 3709</t>
+          <t>ACHA MARIANO GRAL 3802</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -13671,12 +13671,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>812879441</t>
+          <t>812879447</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Columna Inclinada</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -13698,10 +13698,10 @@
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>-58.488038</v>
+        <v>-58.489543</v>
       </c>
       <c r="N155" t="n">
-        <v>-34.557763</v>
+        <v>-34.557511</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>8588</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>ACHA MARIANO GRAL 3802</t>
+          <t>ACHA MARIANO GRAL 3874</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -13757,12 +13757,12 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>812879447</t>
+          <t>812879462</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>Columna Inclinada</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -13784,10 +13784,10 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>-58.489543</v>
+        <v>-58.489778</v>
       </c>
       <c r="N156" t="n">
-        <v>-34.557511</v>
+        <v>-34.557174</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -13813,7 +13813,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>8588</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13823,7 +13823,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>ACHA MARIANO GRAL 3874</t>
+          <t>ACHA MARIANO GRAL 3948</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -13843,12 +13843,12 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>812879462</t>
+          <t>812879479</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Columna Inclinada</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -13870,10 +13870,10 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>-58.489778</v>
+        <v>-58.490224</v>
       </c>
       <c r="N157" t="n">
-        <v>-34.557174</v>
+        <v>-34.556533</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -13899,22 +13899,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t xml:space="preserve">8618 </t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>3/13/2026</t>
+          <t>3/17/2026</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ACHA MARIANO GRAL 3948</t>
+          <t>VALLEJOS 4319</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -13929,12 +13929,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>812879479</t>
+          <t>812879612</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>Cambiar Poste de madera a PRFV</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -13947,23 +13947,19 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
+      <c r="K158" t="inlineStr"/>
       <c r="L158" t="n">
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>-58.490224</v>
+        <v>-58.51875</v>
       </c>
       <c r="N158" t="n">
-        <v>-34.556533</v>
+        <v>-34.598858</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -13973,7 +13969,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>PUE-P</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -13985,7 +13981,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">8618 </t>
+          <t xml:space="preserve">8619 </t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13995,7 +13991,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>VALLEJOS 4319</t>
+          <t>CONCORDIA 3575</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -14015,17 +14011,17 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>812879612</t>
+          <t>812879757</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Cambiar Poste de madera a PRFV</t>
+          <t>Desmontar Poste y migrar a Columna</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -14033,15 +14029,19 @@
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
       <c r="L159" t="n">
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>-58.51875</v>
+        <v>-58.502664</v>
       </c>
       <c r="N159" t="n">
-        <v>-34.598858</v>
+        <v>-34.599377</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>PUE-P</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -14067,7 +14067,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">8619 </t>
+          <t xml:space="preserve">8623    </t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14077,12 +14077,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>CONCORDIA 3575</t>
+          <t>INCLAN 2402</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14097,17 +14097,17 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>812879757</t>
+          <t>812879763</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Desmontar Poste y migrar a Columna</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -14124,24 +14124,24 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>-58.502664</v>
+        <v>-58.398304</v>
       </c>
       <c r="N160" t="n">
-        <v>-34.599377</v>
+        <v>-34.629576</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -14153,22 +14153,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">8623    </t>
+          <t>8882</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>3/17/2026</t>
+          <t>3/18/2026</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>INCLAN 2402</t>
+          <t>EL PROFETA DE LA PAMPA 4523</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14183,12 +14183,12 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>812879763</t>
+          <t>812879773</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -14210,24 +14210,24 @@
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>-58.398304</v>
+        <v>-58.477211</v>
       </c>
       <c r="N161" t="n">
-        <v>-34.629576</v>
+        <v>-34.652708</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>PAV-O</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -14239,17 +14239,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>8882</t>
+          <t>00239146</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>3/18/2026</t>
+          <t>3/19/2026</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>EL PROFETA DE LA PAMPA 4523</t>
+          <t>POLA 1104</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -14269,12 +14269,12 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>812879773</t>
+          <t>812879780</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -14284,22 +14284,22 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L162" t="n">
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>-58.477211</v>
+        <v>-58.50158</v>
       </c>
       <c r="N162" t="n">
-        <v>-34.652708</v>
+        <v>-34.648954</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>PAV-O</t>
+          <t>PAV-J</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -14325,7 +14325,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>00239146</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>POLA 1104</t>
+          <t>BONIFACIO JOSE 2319</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -14355,7 +14355,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>812879780</t>
+          <t>812879799</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -14375,31 +14375,31 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L163" t="n">
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>-58.50158</v>
+        <v>-58.459955</v>
       </c>
       <c r="N163" t="n">
-        <v>-34.648954</v>
+        <v>-34.631973</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>PAV-J</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -14411,7 +14411,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14421,12 +14421,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>BONIFACIO JOSE 2319</t>
+          <t>RIVADAVIA AV 5764</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>812879799</t>
+          <t>812879872</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -14468,10 +14468,10 @@
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>-58.459955</v>
+        <v>-58.446644</v>
       </c>
       <c r="N164" t="n">
-        <v>-34.631973</v>
+        <v>-34.622863</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>PCH-I</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -14497,7 +14497,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>00185436</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14507,12 +14507,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>RIVADAVIA AV 5764</t>
+          <t>BESARES 3453</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14527,12 +14527,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>812879872</t>
+          <t>812879885</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>Cambiar Poste por Columna</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -14554,24 +14554,24 @@
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>-58.446644</v>
+        <v>-58.48116</v>
       </c>
       <c r="N165" t="n">
-        <v>-34.622863</v>
+        <v>-34.549119</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>PCH-I</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -14583,7 +14583,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>00185436</t>
+          <t>01168971</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14593,12 +14593,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>BESARES 3453</t>
+          <t>NECOCHEA 369</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14613,12 +14613,12 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>812879885</t>
+          <t>812879892</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Cambiar Poste por Columna</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -14628,7 +14628,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -14640,24 +14640,24 @@
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>-58.48116</v>
+        <v>-58.364132</v>
       </c>
       <c r="N166" t="n">
-        <v>-34.549119</v>
+        <v>-34.628423</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>CON-F</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -14669,22 +14669,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>01168971</t>
+          <t xml:space="preserve">8642   </t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>3/19/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>NECOCHEA 369</t>
+          <t>CALCENA 347</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14699,22 +14699,22 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>812879892</t>
+          <t>812879950</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>DESMONTAR COLUMNA Y MIGRAR RED A COLUMNA ALEDAÑA</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -14726,14 +14726,14 @@
         <v>1</v>
       </c>
       <c r="M167" t="n">
-        <v>-58.364132</v>
+        <v>-58.457348</v>
       </c>
       <c r="N167" t="n">
-        <v>-34.628423</v>
+        <v>-34.622249</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>CON-F</t>
+          <t>NRA-C</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -14755,7 +14755,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">8642   </t>
+          <t>8644</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14765,12 +14765,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>CALCENA 347</t>
+          <t>GARMENDIA AV. 4945</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14785,17 +14785,17 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>812879950</t>
+          <t>812879971</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>DESMONTAR COLUMNA Y MIGRAR RED A COLUMNA ALEDAÑA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -14812,24 +14812,24 @@
         <v>1</v>
       </c>
       <c r="M168" t="n">
-        <v>-58.457348</v>
+        <v>-58.465345</v>
       </c>
       <c r="N168" t="n">
-        <v>-34.622249</v>
+        <v>-34.595549</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>NRA-C</t>
+          <t>ATH-?</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
@@ -14841,7 +14841,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>00223191</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14851,12 +14851,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>GARMENDIA AV. 4945</t>
+          <t>CATAMARCA 254</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>812879971</t>
+          <t>812879982</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -14886,7 +14886,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -14898,24 +14898,24 @@
         <v>1</v>
       </c>
       <c r="M169" t="n">
-        <v>-58.465345</v>
+        <v>-58.406734</v>
       </c>
       <c r="N169" t="n">
-        <v>-34.595549</v>
+        <v>-34.613107</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>ATH-?</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -14927,7 +14927,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>00223191</t>
+          <t xml:space="preserve">8654 </t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14937,12 +14937,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>CATAMARCA 254</t>
+          <t>CONCORDIA 3663</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -14957,22 +14957,22 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>812879982</t>
+          <t>812879993</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>DESMONTAR POSTE Y MIGRAR RED A COLUMNA EXT.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -14984,24 +14984,24 @@
         <v>1</v>
       </c>
       <c r="M170" t="n">
-        <v>-58.406734</v>
+        <v>-58.503291</v>
       </c>
       <c r="N170" t="n">
-        <v>-34.613107</v>
+        <v>-34.598681</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -15013,7 +15013,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">8654 </t>
+          <t>8658</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>CONCORDIA 3663</t>
+          <t>REPUBLICA BOLIVARIANA DE VENEZUELA 2071</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -15043,17 +15043,17 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>812879993</t>
+          <t>812880000</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>DESMONTAR POSTE Y MIGRAR RED A COLUMNA EXT.</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -15070,24 +15070,24 @@
         <v>1</v>
       </c>
       <c r="M171" t="n">
-        <v>-58.503291</v>
+        <v>-58.395567</v>
       </c>
       <c r="N171" t="n">
-        <v>-34.598681</v>
+        <v>-34.615169</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
@@ -15099,7 +15099,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>8658</t>
+          <t>8663</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -15109,12 +15109,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>REPUBLICA BOLIVARIANA DE VENEZUELA 2071</t>
+          <t>MONTENEGRO 1539</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -15129,17 +15129,17 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>812880000</t>
+          <t>812880004</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>APLOMAR COLUMNA</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -15156,24 +15156,24 @@
         <v>1</v>
       </c>
       <c r="M172" t="n">
-        <v>-58.395567</v>
+        <v>-58.468478</v>
       </c>
       <c r="N172" t="n">
-        <v>-34.615169</v>
+        <v>-34.587599</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -15185,7 +15185,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15195,7 +15195,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>MONTENEGRO 1539</t>
+          <t>JEREZ PEDRO DE 430</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -15215,7 +15215,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>812880004</t>
+          <t>812880006</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -15242,10 +15242,10 @@
         <v>1</v>
       </c>
       <c r="M173" t="n">
-        <v>-58.468478</v>
+        <v>-58.467418</v>
       </c>
       <c r="N173" t="n">
-        <v>-34.587599</v>
+        <v>-34.586278</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15281,12 +15281,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>JEREZ PEDRO DE 430</t>
+          <t>GARCIA DEL RIO 4457</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>812880006</t>
+          <t>812880010</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -15328,14 +15328,14 @@
         <v>1</v>
       </c>
       <c r="M174" t="n">
-        <v>-58.467418</v>
+        <v>-58.488608</v>
       </c>
       <c r="N174" t="n">
-        <v>-34.586278</v>
+        <v>-34.556155</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -15345,7 +15345,7 @@
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
@@ -15357,7 +15357,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>8667</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>GARCIA DEL RIO 4457</t>
+          <t>MACHAIN 3817</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -15387,7 +15387,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>812880010</t>
+          <t>812880018</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -15414,10 +15414,10 @@
         <v>1</v>
       </c>
       <c r="M175" t="n">
-        <v>-58.488608</v>
+        <v>-58.488586</v>
       </c>
       <c r="N175" t="n">
-        <v>-34.556155</v>
+        <v>-34.556965</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>MACHAIN 3817</t>
+          <t>MACHAIN 3961</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>812880018</t>
+          <t>812880026</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -15500,10 +15500,10 @@
         <v>1</v>
       </c>
       <c r="M176" t="n">
-        <v>-58.488586</v>
+        <v>-58.489299</v>
       </c>
       <c r="N176" t="n">
-        <v>-34.556965</v>
+        <v>-34.555926</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
@@ -15529,7 +15529,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>8671</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15539,7 +15539,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>MACHAIN 3961</t>
+          <t>TRONADOR 284</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>812880026</t>
+          <t>812880206</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -15586,14 +15586,14 @@
         <v>1</v>
       </c>
       <c r="M177" t="n">
-        <v>-58.489299</v>
+        <v>-58.470504</v>
       </c>
       <c r="N177" t="n">
-        <v>-34.555926</v>
+        <v>-34.588131</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
@@ -15615,7 +15615,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>8673</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15625,12 +15625,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>TRONADOR 284</t>
+          <t>CADIZ 3715</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>812880206</t>
+          <t>812880209</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -15672,10 +15672,10 @@
         <v>1</v>
       </c>
       <c r="M178" t="n">
-        <v>-58.470504</v>
+        <v>-58.474682</v>
       </c>
       <c r="N178" t="n">
-        <v>-34.588131</v>
+        <v>-34.581396</v>
       </c>
       <c r="O178" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
@@ -15701,7 +15701,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15711,7 +15711,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>CADIZ 3715</t>
+          <t>LA HAYA 3722</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -15731,7 +15731,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>812880209</t>
+          <t>812880230</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -15758,10 +15758,10 @@
         <v>1</v>
       </c>
       <c r="M179" t="n">
-        <v>-58.474682</v>
+        <v>-58.475097</v>
       </c>
       <c r="N179" t="n">
-        <v>-34.581396</v>
+        <v>-34.581101</v>
       </c>
       <c r="O179" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>8675</t>
+          <t>8676</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15797,12 +15797,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>LA HAYA 3722</t>
+          <t>HOLMBERG 979</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -15817,7 +15817,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>812880230</t>
+          <t>812880241</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -15844,14 +15844,14 @@
         <v>1</v>
       </c>
       <c r="M180" t="n">
-        <v>-58.475097</v>
+        <v>-58.468449</v>
       </c>
       <c r="N180" t="n">
-        <v>-34.581101</v>
+        <v>-34.582898</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -15861,7 +15861,7 @@
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
@@ -15873,7 +15873,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15883,12 +15883,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>HOLMBERG 979</t>
+          <t>GIRARDOT 1384</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -15903,17 +15903,17 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>812880241</t>
+          <t>812880404</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>APLOMAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -15930,10 +15930,10 @@
         <v>1</v>
       </c>
       <c r="M181" t="n">
-        <v>-58.468449</v>
+        <v>-58.466063</v>
       </c>
       <c r="N181" t="n">
-        <v>-34.582898</v>
+        <v>-34.587896</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15969,12 +15969,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>GIRARDOT 1384</t>
+          <t>CORRIENTES AV 4073</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -15989,7 +15989,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>812880404</t>
+          <t>812880406</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -16016,24 +16016,24 @@
         <v>1</v>
       </c>
       <c r="M182" t="n">
-        <v>-58.466063</v>
+        <v>-58.422076</v>
       </c>
       <c r="N182" t="n">
-        <v>-34.587896</v>
+        <v>-34.60298</v>
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
@@ -16045,7 +16045,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>00223023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -16055,12 +16055,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>CORRIENTES AV 4073</t>
+          <t>SAN JUAN AV. 2201</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -16075,7 +16075,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>812880406</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -16102,14 +16102,14 @@
         <v>1</v>
       </c>
       <c r="M183" t="n">
-        <v>-58.422076</v>
+        <v>-58.396491</v>
       </c>
       <c r="N183" t="n">
-        <v>-34.60298</v>
+        <v>-34.622986</v>
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>CEN-B</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
@@ -16131,7 +16131,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>00223023</t>
+          <t>00283507</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -16141,12 +16141,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 2201</t>
+          <t xml:space="preserve">HERRERA 475 </t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -16161,14 +16161,14 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
+          <t>812880593</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
           <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
       <c r="I184" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -16188,10 +16188,10 @@
         <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>-58.396491</v>
+        <v>-58.378709</v>
       </c>
       <c r="N184" t="n">
-        <v>-34.622986</v>
+        <v>-34.635064</v>
       </c>
       <c r="O184" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>CON-H</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
@@ -16217,7 +16217,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>00283507</t>
+          <t>00289536</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -16227,12 +16227,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERRERA 475 </t>
+          <t>VALDENEGRO 3554</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>812880593</t>
+          <t>812880608</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -16274,24 +16274,24 @@
         <v>1</v>
       </c>
       <c r="M185" t="n">
-        <v>-58.378709</v>
+        <v>-58.490576</v>
       </c>
       <c r="N185" t="n">
-        <v>-34.635064</v>
+        <v>-34.561508</v>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>CON-H</t>
+          <t>PUE-F</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
@@ -16303,22 +16303,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>00289536</t>
+          <t>0000001</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>3/28/2026</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>VALDENEGRO 3554</t>
+          <t>GIRIBONE 3229</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -16333,7 +16333,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>812880608</t>
+          <t>812880759</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -16360,14 +16360,14 @@
         <v>1</v>
       </c>
       <c r="M186" t="n">
-        <v>-58.490576</v>
+        <v>-58.485216</v>
       </c>
       <c r="N186" t="n">
-        <v>-34.561508</v>
+        <v>-34.584797</v>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -16377,7 +16377,7 @@
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>PUE-F</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
@@ -16387,24 +16387,20 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
+      <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>3/28/2026</t>
+          <t>4/14/2026</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>GIRIBONE 3229</t>
+          <t>AV INDEPENDENCIA 3810</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -16419,7 +16415,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>812880759</t>
+          <t>813107750</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -16446,24 +16442,24 @@
         <v>1</v>
       </c>
       <c r="M187" t="n">
-        <v>-58.485216</v>
+        <v>-58.444908</v>
       </c>
       <c r="N187" t="n">
-        <v>-34.584797</v>
+        <v>-34.607205</v>
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
@@ -16528,14 +16524,14 @@
         <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>-58.444908</v>
+        <v>-58.419576</v>
       </c>
       <c r="N188" t="n">
-        <v>-34.607205</v>
+        <v>-34.621289</v>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -16545,7 +16541,7 @@
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
@@ -16610,14 +16606,14 @@
         <v>1</v>
       </c>
       <c r="M189" t="n">
-        <v>-58.419576</v>
+        <v>-58.430568</v>
       </c>
       <c r="N189" t="n">
-        <v>-34.621289</v>
+        <v>-34.599485</v>
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
@@ -16627,7 +16623,7 @@
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
@@ -16692,10 +16688,10 @@
         <v>1</v>
       </c>
       <c r="M190" t="n">
-        <v>-58.430568</v>
+        <v>-58.437499</v>
       </c>
       <c r="N190" t="n">
-        <v>-34.599485</v>
+        <v>-34.578324</v>
       </c>
       <c r="O190" t="inlineStr">
         <is>
@@ -16709,7 +16705,7 @@
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
@@ -16774,10 +16770,10 @@
         <v>1</v>
       </c>
       <c r="M191" t="n">
-        <v>-58.437499</v>
+        <v>-58.435547</v>
       </c>
       <c r="N191" t="n">
-        <v>-34.578324</v>
+        <v>-34.576622</v>
       </c>
       <c r="O191" t="inlineStr">
         <is>
@@ -16856,14 +16852,14 @@
         <v>1</v>
       </c>
       <c r="M192" t="n">
-        <v>-58.435547</v>
+        <v>-58.373629</v>
       </c>
       <c r="N192" t="n">
-        <v>-34.576622</v>
+        <v>-34.64417</v>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
@@ -16873,30 +16869,34 @@
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>CON-A</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr"/>
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>GG10111</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>4/14/2026</t>
+          <t>4/21/2026</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>AV INDEPENDENCIA 3810</t>
+          <t>HUSARES 2211</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -16909,14 +16909,10 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>813107750</t>
-        </is>
-      </c>
+      <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>CAMBIAR POSTE POR COLUMNA</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -16938,36 +16934,36 @@
         <v>1</v>
       </c>
       <c r="M193" t="n">
-        <v>-58.373629</v>
+        <v>-58.443101</v>
       </c>
       <c r="N193" t="n">
-        <v>-34.64417</v>
+        <v>-34.552275</v>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>CON-A</t>
+          <t>BLO-B</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>GG10111</t>
+          <t>GG10112</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16977,7 +16973,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>HUSARES 2211</t>
+          <t>HUSARES 2255</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -17020,10 +17016,10 @@
         <v>1</v>
       </c>
       <c r="M194" t="n">
-        <v>-58.443101</v>
+        <v>-58.443375</v>
       </c>
       <c r="N194" t="n">
-        <v>-34.552275</v>
+        <v>-34.551956</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
@@ -17041,88 +17037,6 @@
         </is>
       </c>
       <c r="R194" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>GG10112</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>4/21/2026</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>HUSARES 2255</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr"/>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>CAMBIAR POSTE POR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L195" t="n">
-        <v>0</v>
-      </c>
-      <c r="M195" t="n">
-        <v>-58.443375</v>
-      </c>
-      <c r="N195" t="n">
-        <v>-34.551956</v>
-      </c>
-      <c r="O195" t="inlineStr">
-        <is>
-          <t>Saavedra</t>
-        </is>
-      </c>
-      <c r="P195" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q195" t="inlineStr">
-        <is>
-          <t>BLO-B</t>
-        </is>
-      </c>
-      <c r="R195" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_NEW.xlsx
+++ b/mapa_interactivo_NEW.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R444"/>
+  <dimension ref="A1:R445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36835,7 +36835,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t xml:space="preserve">10081 </t>
+          <t xml:space="preserve">10080 </t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -36845,7 +36845,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORRIENTES AV. 5697 </t>
+          <t>THAMES 549</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -36866,7 +36866,7 @@
       <c r="G430" t="inlineStr"/>
       <c r="H430" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -36888,10 +36888,10 @@
         <v>1</v>
       </c>
       <c r="M430" t="n">
-        <v>-58.443323</v>
+        <v>-58.442534</v>
       </c>
       <c r="N430" t="n">
-        <v>-34.595549</v>
+        <v>-34.59499</v>
       </c>
       <c r="O430" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t xml:space="preserve">10084 </t>
+          <t xml:space="preserve">10081 </t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -36927,12 +36927,12 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>UGARTE, MANUEL 3258</t>
+          <t xml:space="preserve">CORRIENTES AV. 5697 </t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -36953,7 +36953,7 @@
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
@@ -36970,24 +36970,24 @@
         <v>1</v>
       </c>
       <c r="M431" t="n">
-        <v>-58.470323</v>
+        <v>-58.443323</v>
       </c>
       <c r="N431" t="n">
-        <v>-34.560769</v>
+        <v>-34.595549</v>
       </c>
       <c r="O431" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P431" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q431" t="inlineStr">
         <is>
-          <t>COG-I</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R431" t="inlineStr">
@@ -36999,7 +36999,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t xml:space="preserve">10087 </t>
+          <t xml:space="preserve">10084 </t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -37009,12 +37009,12 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>CASTILLO 40</t>
+          <t>UGARTE, MANUEL 3258</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -37052,24 +37052,24 @@
         <v>1</v>
       </c>
       <c r="M432" t="n">
-        <v>-58.430621</v>
+        <v>-58.470323</v>
       </c>
       <c r="N432" t="n">
-        <v>-34.599429</v>
+        <v>-34.560769</v>
       </c>
       <c r="O432" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P432" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q432" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>COG-I</t>
         </is>
       </c>
       <c r="R432" t="inlineStr">
@@ -37081,7 +37081,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t xml:space="preserve">10102 </t>
+          <t xml:space="preserve">10087 </t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -37091,7 +37091,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>ELCANO AV. 3950</t>
+          <t>CASTILLO 40</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -37112,7 +37112,7 @@
       <c r="G433" t="inlineStr"/>
       <c r="H433" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -37134,24 +37134,24 @@
         <v>1</v>
       </c>
       <c r="M433" t="n">
-        <v>-58.460457</v>
+        <v>-58.430621</v>
       </c>
       <c r="N433" t="n">
-        <v>-34.582381</v>
+        <v>-34.599429</v>
       </c>
       <c r="O433" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P433" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q433" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R433" t="inlineStr">
@@ -37163,7 +37163,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t xml:space="preserve">10113 </t>
+          <t xml:space="preserve">10102 </t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -37173,12 +37173,12 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>CONCORDIA 4213</t>
+          <t>ELCANO AV. 3950</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -37199,7 +37199,7 @@
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
@@ -37216,14 +37216,14 @@
         <v>1</v>
       </c>
       <c r="M434" t="n">
-        <v>-58.506878</v>
+        <v>-58.460457</v>
       </c>
       <c r="N434" t="n">
-        <v>-34.59474</v>
+        <v>-34.582381</v>
       </c>
       <c r="O434" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P434" t="inlineStr">
@@ -37233,7 +37233,7 @@
       </c>
       <c r="Q434" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R434" t="inlineStr">
@@ -37245,7 +37245,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t xml:space="preserve">10116 </t>
+          <t xml:space="preserve">10113 </t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -37255,7 +37255,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>TRIUNVIRATO AV. 5858</t>
+          <t>CONCORDIA 4213</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -37276,12 +37276,12 @@
       <c r="G435" t="inlineStr"/>
       <c r="H435" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
@@ -37298,10 +37298,10 @@
         <v>1</v>
       </c>
       <c r="M435" t="n">
-        <v>-58.496239</v>
+        <v>-58.506878</v>
       </c>
       <c r="N435" t="n">
-        <v>-34.564136</v>
+        <v>-34.59474</v>
       </c>
       <c r="O435" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
       </c>
       <c r="Q435" t="inlineStr">
         <is>
-          <t>PUE-F</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R435" t="inlineStr">
@@ -37327,7 +37327,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t xml:space="preserve">10119 </t>
+          <t xml:space="preserve">10116 </t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -37337,7 +37337,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>TRIUNVIRATO AV. 5900</t>
+          <t>TRIUNVIRATO AV. 5858</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -37358,12 +37358,12 @@
       <c r="G436" t="inlineStr"/>
       <c r="H436" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
@@ -37373,17 +37373,17 @@
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L436" t="n">
         <v>1</v>
       </c>
       <c r="M436" t="n">
-        <v>-58.496593</v>
+        <v>-58.496239</v>
       </c>
       <c r="N436" t="n">
-        <v>-34.563646</v>
+        <v>-34.564136</v>
       </c>
       <c r="O436" t="inlineStr">
         <is>
@@ -37409,7 +37409,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t xml:space="preserve">10126 </t>
+          <t xml:space="preserve">10119 </t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -37419,7 +37419,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROOSEVELT FRANKLIN D. 4647 </t>
+          <t>TRIUNVIRATO AV. 5900</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -37440,12 +37440,12 @@
       <c r="G437" t="inlineStr"/>
       <c r="H437" t="inlineStr">
         <is>
-          <t>DESMONTAR POSTE</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
@@ -37455,21 +37455,21 @@
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L437" t="n">
         <v>1</v>
       </c>
       <c r="M437" t="n">
-        <v>-58.482122</v>
+        <v>-58.496593</v>
       </c>
       <c r="N437" t="n">
-        <v>-34.570386</v>
+        <v>-34.563646</v>
       </c>
       <c r="O437" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P437" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="Q437" t="inlineStr">
         <is>
-          <t>ATH-E</t>
+          <t>PUE-F</t>
         </is>
       </c>
       <c r="R437" t="inlineStr">
@@ -37491,7 +37491,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t xml:space="preserve">10133 </t>
+          <t xml:space="preserve">10126 </t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -37501,7 +37501,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t xml:space="preserve">BATALLA DEL PARI 593 </t>
+          <t xml:space="preserve">ROOSEVELT FRANKLIN D. 4647 </t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -37522,12 +37522,12 @@
       <c r="G438" t="inlineStr"/>
       <c r="H438" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>DESMONTAR POSTE</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
@@ -37544,14 +37544,14 @@
         <v>1</v>
       </c>
       <c r="M438" t="n">
-        <v>-58.453426</v>
+        <v>-58.482122</v>
       </c>
       <c r="N438" t="n">
-        <v>-34.600121</v>
+        <v>-34.570386</v>
       </c>
       <c r="O438" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P438" t="inlineStr">
@@ -37561,7 +37561,7 @@
       </c>
       <c r="Q438" t="inlineStr">
         <is>
-          <t>VCR-?</t>
+          <t>ATH-E</t>
         </is>
       </c>
       <c r="R438" t="inlineStr">
@@ -37573,7 +37573,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t xml:space="preserve">10136 </t>
+          <t xml:space="preserve">10133 </t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -37583,12 +37583,12 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>REPETTO, NICOLAS, DR. 2118</t>
+          <t xml:space="preserve">BATALLA DEL PARI 593 </t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -37626,10 +37626,10 @@
         <v>1</v>
       </c>
       <c r="M439" t="n">
-        <v>-58.456381</v>
+        <v>-58.453426</v>
       </c>
       <c r="N439" t="n">
-        <v>-34.60076</v>
+        <v>-34.600121</v>
       </c>
       <c r="O439" t="inlineStr">
         <is>
@@ -37643,7 +37643,7 @@
       </c>
       <c r="Q439" t="inlineStr">
         <is>
-          <t>NRA-G</t>
+          <t>VCR-?</t>
         </is>
       </c>
       <c r="R439" t="inlineStr">
@@ -37655,7 +37655,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t xml:space="preserve">10145 </t>
+          <t xml:space="preserve">10136 </t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -37665,12 +37665,12 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>DONADO 2554</t>
+          <t>REPETTO, NICOLAS, DR. 2118</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -37708,14 +37708,14 @@
         <v>1</v>
       </c>
       <c r="M440" t="n">
-        <v>-58.478634</v>
+        <v>-58.456381</v>
       </c>
       <c r="N440" t="n">
-        <v>-34.569063</v>
+        <v>-34.60076</v>
       </c>
       <c r="O440" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P440" t="inlineStr">
@@ -37725,7 +37725,7 @@
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>ATH-J</t>
+          <t>NRA-G</t>
         </is>
       </c>
       <c r="R440" t="inlineStr">
@@ -37737,7 +37737,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t xml:space="preserve">10147 </t>
+          <t xml:space="preserve">10145 </t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -37747,7 +37747,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>ROOSEVELT FRANKLIN D. 4336</t>
+          <t>DONADO 2554</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -37768,12 +37768,12 @@
       <c r="G441" t="inlineStr"/>
       <c r="H441" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
@@ -37783,17 +37783,17 @@
       </c>
       <c r="K441" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L441" t="n">
         <v>1</v>
       </c>
       <c r="M441" t="n">
-        <v>-58.479316</v>
+        <v>-58.478634</v>
       </c>
       <c r="N441" t="n">
-        <v>-34.568762</v>
+        <v>-34.569063</v>
       </c>
       <c r="O441" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t xml:space="preserve">10148 </t>
+          <t xml:space="preserve">10147 </t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -37829,7 +37829,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>ACHA, MARIANO, GRAL. 2595</t>
+          <t>ROOSEVELT FRANKLIN D. 4336</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -37850,12 +37850,12 @@
       <c r="G442" t="inlineStr"/>
       <c r="H442" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
@@ -37865,17 +37865,17 @@
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L442" t="n">
         <v>1</v>
       </c>
       <c r="M442" t="n">
-        <v>-58.479759</v>
+        <v>-58.479316</v>
       </c>
       <c r="N442" t="n">
-        <v>-34.569184</v>
+        <v>-34.568762</v>
       </c>
       <c r="O442" t="inlineStr">
         <is>
@@ -37901,7 +37901,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>10113B</t>
+          <t xml:space="preserve">10148 </t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -37911,7 +37911,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>CONCORDIA 4213</t>
+          <t>ACHA, MARIANO, GRAL. 2595</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -37932,12 +37932,12 @@
       <c r="G443" t="inlineStr"/>
       <c r="H443" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
@@ -37954,14 +37954,14 @@
         <v>1</v>
       </c>
       <c r="M443" t="n">
-        <v>-58.506878</v>
+        <v>-58.479759</v>
       </c>
       <c r="N443" t="n">
-        <v>-34.59474</v>
+        <v>-34.569184</v>
       </c>
       <c r="O443" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P443" t="inlineStr">
@@ -37971,7 +37971,7 @@
       </c>
       <c r="Q443" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>ATH-J</t>
         </is>
       </c>
       <c r="R443" t="inlineStr">
@@ -37983,7 +37983,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>10116B</t>
+          <t>10113B</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -37993,7 +37993,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>TRIUNVIRATO AV. 5858</t>
+          <t>CONCORDIA 4213</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -38036,27 +38036,109 @@
         <v>1</v>
       </c>
       <c r="M444" t="n">
+        <v>-58.506878</v>
+      </c>
+      <c r="N444" t="n">
+        <v>-34.59474</v>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>PUE-O</t>
+        </is>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>10116B</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>5/14/2026</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>TRIUNVIRATO AV. 5858</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr"/>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>COLUMNA INCLINADA</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L445" t="n">
+        <v>1</v>
+      </c>
+      <c r="M445" t="n">
         <v>-58.496239</v>
       </c>
-      <c r="N444" t="n">
+      <c r="N445" t="n">
         <v>-34.564136</v>
       </c>
-      <c r="O444" t="inlineStr">
+      <c r="O445" t="inlineStr">
         <is>
           <t>Paternal</t>
         </is>
       </c>
-      <c r="P444" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q444" t="inlineStr">
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
         <is>
           <t>PUE-F</t>
         </is>
       </c>
-      <c r="R444" t="inlineStr">
+      <c r="R445" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_NEW.xlsx
+++ b/mapa_interactivo_NEW.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R422"/>
+  <dimension ref="A1:R415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814107624</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -15633,7 +15633,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814105606</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -15719,7 +15719,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814107582</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -15805,7 +15805,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814107133</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814107222</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -16063,7 +16063,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814107525</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -16149,7 +16149,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814107531</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -16235,7 +16235,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814106880</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -16321,7 +16321,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814107066</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -16407,7 +16407,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814107096</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -16493,7 +16493,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814107119</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -16579,7 +16579,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814105882</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814105883</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -16751,7 +16751,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814105884</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -16837,7 +16837,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814105886</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -16923,7 +16923,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814105888</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>GAMARRA y TREVERIS</t>
+          <t>GAMARRA 1551</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -17009,7 +17009,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814106178</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -17032,10 +17032,10 @@
         <v>1</v>
       </c>
       <c r="M194" t="n">
-        <v>-58.477099</v>
+        <v>-58.477242</v>
       </c>
       <c r="N194" t="n">
-        <v>-34.582525</v>
+        <v>-34.582318</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814106206</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -17177,7 +17177,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814106207</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -17259,7 +17259,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814106255</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -26505,7 +26505,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -26515,7 +26515,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>GAVILAN 4873</t>
+          <t>GRIVEO 2249</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -26535,7 +26535,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>813632437</t>
+          <t>813632438</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -26555,17 +26555,17 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L305" t="n">
         <v>1</v>
       </c>
       <c r="M305" t="n">
-        <v>-58.495488</v>
+        <v>-58.496181</v>
       </c>
       <c r="N305" t="n">
-        <v>-34.579964</v>
+        <v>-34.579831</v>
       </c>
       <c r="O305" t="inlineStr">
         <is>
@@ -26591,22 +26591,22 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t xml:space="preserve">9129 </t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>GRIVEO 2249</t>
+          <t>ALVAREZ THOMAS AV. 1744</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -26619,11 +26619,7 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>813632438</t>
-        </is>
-      </c>
+      <c r="G306" t="inlineStr"/>
       <c r="H306" t="inlineStr">
         <is>
           <t>COLUMNA INCLINADA</t>
@@ -26648,14 +26644,14 @@
         <v>1</v>
       </c>
       <c r="M306" t="n">
-        <v>-58.496181</v>
+        <v>-58.466536</v>
       </c>
       <c r="N306" t="n">
-        <v>-34.579831</v>
+        <v>-34.579205</v>
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P306" t="inlineStr">
@@ -26665,7 +26661,7 @@
       </c>
       <c r="Q306" t="inlineStr">
         <is>
-          <t>PUE-M</t>
+          <t>ATH-G</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -26677,7 +26673,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t xml:space="preserve">9129 </t>
+          <t xml:space="preserve">9131 </t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -26687,7 +26683,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>ALVAREZ THOMAS AV. 1744</t>
+          <t>ELCANO AV. 3705</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -26730,10 +26726,10 @@
         <v>1</v>
       </c>
       <c r="M307" t="n">
-        <v>-58.466536</v>
+        <v>-58.460607</v>
       </c>
       <c r="N307" t="n">
-        <v>-34.579205</v>
+        <v>-34.579859</v>
       </c>
       <c r="O307" t="inlineStr">
         <is>
@@ -26747,7 +26743,7 @@
       </c>
       <c r="Q307" t="inlineStr">
         <is>
-          <t>ATH-G</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -26759,7 +26755,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t xml:space="preserve">9130 </t>
+          <t xml:space="preserve">9135 </t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -26769,12 +26765,12 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>ALVAREZ THOMAS AV. 1718</t>
+          <t>PESTALOZZI 3470</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -26812,14 +26808,14 @@
         <v>1</v>
       </c>
       <c r="M308" t="n">
-        <v>-58.466331</v>
+        <v>-58.500605</v>
       </c>
       <c r="N308" t="n">
-        <v>-34.579159</v>
+        <v>-34.567984</v>
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P308" t="inlineStr">
@@ -26829,7 +26825,7 @@
       </c>
       <c r="Q308" t="inlineStr">
         <is>
-          <t>ATH-G</t>
+          <t>PUE-H</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -26841,7 +26837,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t xml:space="preserve">9131 </t>
+          <t xml:space="preserve">9178 </t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -26851,12 +26847,12 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>ELCANO AV. 3705</t>
+          <t>VERA 311</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -26872,46 +26868,46 @@
       <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L309" t="n">
         <v>1</v>
       </c>
       <c r="M309" t="n">
-        <v>-58.460607</v>
+        <v>-58.436262</v>
       </c>
       <c r="N309" t="n">
-        <v>-34.579859</v>
+        <v>-34.600478</v>
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P309" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q309" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -26923,7 +26919,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t xml:space="preserve">9135 </t>
+          <t xml:space="preserve">9133 </t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -26933,12 +26929,12 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>PESTALOZZI 3470</t>
+          <t>ESTOMBA 1191</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -26951,15 +26947,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G310" t="inlineStr"/>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>814108669</t>
+        </is>
+      </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
@@ -26976,14 +26976,14 @@
         <v>1</v>
       </c>
       <c r="M310" t="n">
-        <v>-58.500605</v>
+        <v>-58.464637</v>
       </c>
       <c r="N310" t="n">
-        <v>-34.567984</v>
+        <v>-34.579742</v>
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P310" t="inlineStr">
@@ -26993,7 +26993,7 @@
       </c>
       <c r="Q310" t="inlineStr">
         <is>
-          <t>PUE-H</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -27005,7 +27005,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178 </t>
+          <t xml:space="preserve">9142 </t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -27015,7 +27015,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>VERA 311</t>
+          <t>ESTOMBA 1163</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -27033,7 +27033,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G311" t="inlineStr"/>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>814108680</t>
+        </is>
+      </c>
       <c r="H311" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -27046,36 +27050,36 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L311" t="n">
         <v>1</v>
       </c>
       <c r="M311" t="n">
-        <v>-58.436262</v>
+        <v>-58.464649</v>
       </c>
       <c r="N311" t="n">
-        <v>-34.600478</v>
+        <v>-34.580057</v>
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -27087,7 +27091,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t xml:space="preserve">9133 </t>
+          <t xml:space="preserve">9146 </t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -27097,7 +27101,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>ESTOMBA 1191</t>
+          <t>HEREDIA 1158</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -27115,7 +27119,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr"/>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>814108690</t>
+        </is>
+      </c>
       <c r="H312" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -27140,10 +27148,10 @@
         <v>1</v>
       </c>
       <c r="M312" t="n">
-        <v>-58.464637</v>
+        <v>-58.463317</v>
       </c>
       <c r="N312" t="n">
-        <v>-34.579742</v>
+        <v>-34.580092</v>
       </c>
       <c r="O312" t="inlineStr">
         <is>
@@ -27169,7 +27177,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t xml:space="preserve">9142 </t>
+          <t xml:space="preserve">9147 </t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -27179,7 +27187,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>ESTOMBA 1163</t>
+          <t>ELCANO AV. 3811</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -27197,7 +27205,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G313" t="inlineStr"/>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>814108711</t>
+        </is>
+      </c>
       <c r="H313" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -27222,10 +27234,10 @@
         <v>1</v>
       </c>
       <c r="M313" t="n">
-        <v>-58.464649</v>
+        <v>-58.460612</v>
       </c>
       <c r="N313" t="n">
-        <v>-34.580057</v>
+        <v>-34.580887</v>
       </c>
       <c r="O313" t="inlineStr">
         <is>
@@ -27251,7 +27263,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t xml:space="preserve">9146 </t>
+          <t xml:space="preserve">9149 </t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -27261,7 +27273,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>HEREDIA 1158</t>
+          <t>GIRIBONE 1301</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -27292,7 +27304,7 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
@@ -27304,10 +27316,10 @@
         <v>1</v>
       </c>
       <c r="M314" t="n">
-        <v>-58.463317</v>
+        <v>-58.460784</v>
       </c>
       <c r="N314" t="n">
-        <v>-34.580092</v>
+        <v>-34.579621</v>
       </c>
       <c r="O314" t="inlineStr">
         <is>
@@ -27333,7 +27345,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t xml:space="preserve">9147 </t>
+          <t xml:space="preserve">9150 </t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -27343,7 +27355,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>ELCANO AV. 3811</t>
+          <t>GIRIBONE 1365</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -27361,7 +27373,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G315" t="inlineStr"/>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>814108720</t>
+        </is>
+      </c>
       <c r="H315" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -27386,10 +27402,10 @@
         <v>1</v>
       </c>
       <c r="M315" t="n">
-        <v>-58.460612</v>
+        <v>-58.461208</v>
       </c>
       <c r="N315" t="n">
-        <v>-34.580887</v>
+        <v>-34.579609</v>
       </c>
       <c r="O315" t="inlineStr">
         <is>
@@ -27415,7 +27431,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t xml:space="preserve">9149 </t>
+          <t>9151</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -27425,7 +27441,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>GIRIBONE 1301</t>
+          <t>CHARLONE 1491</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -27443,7 +27459,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G316" t="inlineStr"/>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>814108759</t>
+        </is>
+      </c>
       <c r="H316" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -27456,7 +27476,7 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
@@ -27468,10 +27488,10 @@
         <v>1</v>
       </c>
       <c r="M316" t="n">
-        <v>-58.460784</v>
+        <v>-58.463072</v>
       </c>
       <c r="N316" t="n">
-        <v>-34.579621</v>
+        <v>-34.58065</v>
       </c>
       <c r="O316" t="inlineStr">
         <is>
@@ -27497,7 +27517,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t xml:space="preserve">9150 </t>
+          <t xml:space="preserve">9164 </t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -27507,12 +27527,12 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>GIRIBONE 1365</t>
+          <t>ESCOBAR 2395</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -27525,7 +27545,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G317" t="inlineStr"/>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>814108775</t>
+        </is>
+      </c>
       <c r="H317" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -27550,14 +27574,14 @@
         <v>1</v>
       </c>
       <c r="M317" t="n">
-        <v>-58.461208</v>
+        <v>-58.503555</v>
       </c>
       <c r="N317" t="n">
-        <v>-34.579609</v>
+        <v>-34.574803</v>
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P317" t="inlineStr">
@@ -27567,7 +27591,7 @@
       </c>
       <c r="Q317" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>PUE-I</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -27579,7 +27603,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t xml:space="preserve">9165 </t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -27589,12 +27613,12 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>CHARLONE 1491</t>
+          <t>ESCOBAR 2383</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -27607,7 +27631,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G318" t="inlineStr"/>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>814108830</t>
+        </is>
+      </c>
       <c r="H318" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -27632,14 +27660,14 @@
         <v>1</v>
       </c>
       <c r="M318" t="n">
-        <v>-58.463072</v>
+        <v>-58.503388</v>
       </c>
       <c r="N318" t="n">
-        <v>-34.58065</v>
+        <v>-34.5747</v>
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P318" t="inlineStr">
@@ -27649,7 +27677,7 @@
       </c>
       <c r="Q318" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>PUE-I</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -27661,7 +27689,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t xml:space="preserve">9164 </t>
+          <t xml:space="preserve">9166 </t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -27671,7 +27699,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>ESCOBAR 2395</t>
+          <t>DE LOS CONSTITUYENTES AV. 5739</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -27689,7 +27717,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G319" t="inlineStr"/>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>814108833</t>
+        </is>
+      </c>
       <c r="H319" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -27714,10 +27746,10 @@
         <v>1</v>
       </c>
       <c r="M319" t="n">
-        <v>-58.503555</v>
+        <v>-58.502319</v>
       </c>
       <c r="N319" t="n">
-        <v>-34.574803</v>
+        <v>-34.573945</v>
       </c>
       <c r="O319" t="inlineStr">
         <is>
@@ -27743,7 +27775,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t xml:space="preserve">9165 </t>
+          <t xml:space="preserve">9167 </t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -27753,7 +27785,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>ESCOBAR 2383</t>
+          <t>DE LOS CONSTITUYENTES AV. 5776</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -27771,7 +27803,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G320" t="inlineStr"/>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>814108840</t>
+        </is>
+      </c>
       <c r="H320" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -27796,10 +27832,10 @@
         <v>1</v>
       </c>
       <c r="M320" t="n">
-        <v>-58.503388</v>
+        <v>-58.502932</v>
       </c>
       <c r="N320" t="n">
-        <v>-34.5747</v>
+        <v>-34.573648</v>
       </c>
       <c r="O320" t="inlineStr">
         <is>
@@ -27825,7 +27861,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t xml:space="preserve">9166 </t>
+          <t xml:space="preserve">9168 </t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -27835,7 +27871,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>DE LOS CONSTITUYENTES AV. 5739</t>
+          <t>DE LOS CONSTITUYENTES AV. 5620</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -27853,7 +27889,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G321" t="inlineStr"/>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>814108846</t>
+        </is>
+      </c>
       <c r="H321" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -27878,10 +27918,10 @@
         <v>1</v>
       </c>
       <c r="M321" t="n">
-        <v>-58.502319</v>
+        <v>-58.501786</v>
       </c>
       <c r="N321" t="n">
-        <v>-34.573945</v>
+        <v>-34.574535</v>
       </c>
       <c r="O321" t="inlineStr">
         <is>
@@ -27907,7 +27947,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t xml:space="preserve">9167 </t>
+          <t>9169</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -27917,7 +27957,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>DE LOS CONSTITUYENTES AV. 5776</t>
+          <t>DE LOS CONSTITUYENTES AV. 5596</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -27935,7 +27975,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G322" t="inlineStr"/>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>814108850</t>
+        </is>
+      </c>
       <c r="H322" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -27960,10 +28004,10 @@
         <v>1</v>
       </c>
       <c r="M322" t="n">
-        <v>-58.502932</v>
+        <v>-58.501436</v>
       </c>
       <c r="N322" t="n">
-        <v>-34.573648</v>
+        <v>-34.574802</v>
       </c>
       <c r="O322" t="inlineStr">
         <is>
@@ -27989,7 +28033,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t xml:space="preserve">9168 </t>
+          <t xml:space="preserve">9170 </t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -27999,7 +28043,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>DE LOS CONSTITUYENTES AV. 5620</t>
+          <t>DE LOS CONSTITUYENTES AV. 5556</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -28017,7 +28061,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G323" t="inlineStr"/>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>814108863</t>
+        </is>
+      </c>
       <c r="H323" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -28042,10 +28090,10 @@
         <v>1</v>
       </c>
       <c r="M323" t="n">
-        <v>-58.501786</v>
+        <v>-58.501219</v>
       </c>
       <c r="N323" t="n">
-        <v>-34.574535</v>
+        <v>-34.57497</v>
       </c>
       <c r="O323" t="inlineStr">
         <is>
@@ -28071,7 +28119,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t xml:space="preserve">9171 </t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -28081,7 +28129,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>DE LOS CONSTITUYENTES AV. 5596</t>
+          <t>LARSEN 2347</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -28099,7 +28147,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G324" t="inlineStr"/>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>814108863</t>
+        </is>
+      </c>
       <c r="H324" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -28124,10 +28176,10 @@
         <v>1</v>
       </c>
       <c r="M324" t="n">
-        <v>-58.501436</v>
+        <v>-58.502229</v>
       </c>
       <c r="N324" t="n">
-        <v>-34.574802</v>
+        <v>-34.57511</v>
       </c>
       <c r="O324" t="inlineStr">
         <is>
@@ -28153,7 +28205,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t xml:space="preserve">9170 </t>
+          <t xml:space="preserve">9174 </t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -28163,7 +28215,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>DE LOS CONSTITUYENTES AV. 5556</t>
+          <t>ZAMUDIO 5459</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -28181,7 +28233,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G325" t="inlineStr"/>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>814109101</t>
+        </is>
+      </c>
       <c r="H325" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -28206,10 +28262,10 @@
         <v>1</v>
       </c>
       <c r="M325" t="n">
-        <v>-58.501219</v>
+        <v>-58.501935</v>
       </c>
       <c r="N325" t="n">
-        <v>-34.57497</v>
+        <v>-34.576744</v>
       </c>
       <c r="O325" t="inlineStr">
         <is>
@@ -28235,7 +28291,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t xml:space="preserve">9171 </t>
+          <t xml:space="preserve">9175 </t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -28245,7 +28301,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>LARSEN 2347</t>
+          <t>DE LOS CONSTITUYENTES AV. 5481</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -28263,7 +28319,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G326" t="inlineStr"/>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>814109111</t>
+        </is>
+      </c>
       <c r="H326" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -28288,10 +28348,10 @@
         <v>1</v>
       </c>
       <c r="M326" t="n">
-        <v>-58.502229</v>
+        <v>-58.500385</v>
       </c>
       <c r="N326" t="n">
-        <v>-34.57511</v>
+        <v>-34.575443</v>
       </c>
       <c r="O326" t="inlineStr">
         <is>
@@ -28317,7 +28377,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>9172</t>
+          <t xml:space="preserve">9176 </t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -28327,7 +28387,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAMUDIO 5541 </t>
+          <t>DE LOS CONSTITUYENTES AV. 5464</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -28345,7 +28405,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G327" t="inlineStr"/>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>814109118</t>
+        </is>
+      </c>
       <c r="H327" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -28370,10 +28434,10 @@
         <v>1</v>
       </c>
       <c r="M327" t="n">
-        <v>-58.502621</v>
+        <v>-58.500219</v>
       </c>
       <c r="N327" t="n">
-        <v>-34.575983</v>
+        <v>-34.575746</v>
       </c>
       <c r="O327" t="inlineStr">
         <is>
@@ -28399,7 +28463,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>9173</t>
+          <t xml:space="preserve">9177 </t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -28409,7 +28473,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>ZAMUDIO 5483</t>
+          <t>DE LOS CONSTITUYENTES AV. 5418</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -28427,7 +28491,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G328" t="inlineStr"/>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>814109131</t>
+        </is>
+      </c>
       <c r="H328" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -28452,10 +28520,10 @@
         <v>1</v>
       </c>
       <c r="M328" t="n">
-        <v>-58.502093</v>
+        <v>-58.499983</v>
       </c>
       <c r="N328" t="n">
-        <v>-34.576569</v>
+        <v>-34.575929</v>
       </c>
       <c r="O328" t="inlineStr">
         <is>
@@ -28481,7 +28549,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t xml:space="preserve">9174 </t>
+          <t xml:space="preserve">9183 </t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -28491,7 +28559,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>ZAMUDIO 5459</t>
+          <t>BAZURCO 2290</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -28509,7 +28577,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G329" t="inlineStr"/>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>814109143</t>
+        </is>
+      </c>
       <c r="H329" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -28534,10 +28606,10 @@
         <v>1</v>
       </c>
       <c r="M329" t="n">
-        <v>-58.501935</v>
+        <v>-58.500229</v>
       </c>
       <c r="N329" t="n">
-        <v>-34.576744</v>
+        <v>-34.576482</v>
       </c>
       <c r="O329" t="inlineStr">
         <is>
@@ -28563,7 +28635,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t xml:space="preserve">9175 </t>
+          <t xml:space="preserve">9192 </t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -28573,12 +28645,12 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>DE LOS CONSTITUYENTES AV. 5481</t>
+          <t>GANDARA 3184</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -28591,7 +28663,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G330" t="inlineStr"/>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>814109150</t>
+        </is>
+      </c>
       <c r="H330" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -28616,10 +28692,10 @@
         <v>1</v>
       </c>
       <c r="M330" t="n">
-        <v>-58.500385</v>
+        <v>-58.484009</v>
       </c>
       <c r="N330" t="n">
-        <v>-34.575443</v>
+        <v>-34.585212</v>
       </c>
       <c r="O330" t="inlineStr">
         <is>
@@ -28633,7 +28709,7 @@
       </c>
       <c r="Q330" t="inlineStr">
         <is>
-          <t>PUE-I</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
@@ -28645,7 +28721,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t xml:space="preserve">9176 </t>
+          <t>9191</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -28655,12 +28731,12 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>DE LOS CONSTITUYENTES AV. 5464</t>
+          <t>ALTOLAGUIRRE 1417</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -28673,7 +28749,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G331" t="inlineStr"/>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>814109153</t>
+        </is>
+      </c>
       <c r="H331" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -28698,10 +28778,10 @@
         <v>1</v>
       </c>
       <c r="M331" t="n">
-        <v>-58.500219</v>
+        <v>-58.482801</v>
       </c>
       <c r="N331" t="n">
-        <v>-34.575746</v>
+        <v>-34.587072</v>
       </c>
       <c r="O331" t="inlineStr">
         <is>
@@ -28715,7 +28795,7 @@
       </c>
       <c r="Q331" t="inlineStr">
         <is>
-          <t>PUE-I</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -28727,7 +28807,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t xml:space="preserve">9177 </t>
+          <t xml:space="preserve">9196 </t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -28737,12 +28817,12 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>DE LOS CONSTITUYENTES AV. 5418</t>
+          <t>PADILLA 1295</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -28755,7 +28835,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G332" t="inlineStr"/>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>814109185</t>
+        </is>
+      </c>
       <c r="H332" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -28780,10 +28864,10 @@
         <v>1</v>
       </c>
       <c r="M332" t="n">
-        <v>-58.499983</v>
+        <v>-58.447848</v>
       </c>
       <c r="N332" t="n">
-        <v>-34.575929</v>
+        <v>-34.595146</v>
       </c>
       <c r="O332" t="inlineStr">
         <is>
@@ -28797,7 +28881,7 @@
       </c>
       <c r="Q332" t="inlineStr">
         <is>
-          <t>PUE-I</t>
+          <t>VCR-?</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
@@ -28809,7 +28893,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t xml:space="preserve">9183 </t>
+          <t xml:space="preserve">9198 </t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -28819,12 +28903,12 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>BAZURCO 2290</t>
+          <t>JUSTO, JUAN B. AV. 2960</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -28837,7 +28921,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G333" t="inlineStr"/>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>814109216</t>
+        </is>
+      </c>
       <c r="H333" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -28862,10 +28950,10 @@
         <v>1</v>
       </c>
       <c r="M333" t="n">
-        <v>-58.500229</v>
+        <v>-58.44825</v>
       </c>
       <c r="N333" t="n">
-        <v>-34.576482</v>
+        <v>-34.597626</v>
       </c>
       <c r="O333" t="inlineStr">
         <is>
@@ -28879,7 +28967,7 @@
       </c>
       <c r="Q333" t="inlineStr">
         <is>
-          <t>PUE-I</t>
+          <t>VCR-?</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
@@ -28891,7 +28979,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t xml:space="preserve">9192 </t>
+          <t xml:space="preserve">7947 </t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -28901,12 +28989,12 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>GANDARA 3184</t>
+          <t>MILLER 3597</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -28944,14 +29032,14 @@
         <v>1</v>
       </c>
       <c r="M334" t="n">
-        <v>-58.484009</v>
+        <v>-58.489898</v>
       </c>
       <c r="N334" t="n">
-        <v>-34.585212</v>
+        <v>-34.560497</v>
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P334" t="inlineStr">
@@ -28961,7 +29049,7 @@
       </c>
       <c r="Q334" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>PUE-F</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -28973,7 +29061,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t xml:space="preserve">9925 </t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -28983,12 +29071,12 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>ALTOLAGUIRRE 1417</t>
+          <t>MENDOZA AV. 5482</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -29004,12 +29092,12 @@
       <c r="G335" t="inlineStr"/>
       <c r="H335" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
@@ -29026,10 +29114,10 @@
         <v>1</v>
       </c>
       <c r="M335" t="n">
-        <v>-58.482801</v>
+        <v>-58.487368</v>
       </c>
       <c r="N335" t="n">
-        <v>-34.587072</v>
+        <v>-34.579375</v>
       </c>
       <c r="O335" t="inlineStr">
         <is>
@@ -29043,7 +29131,7 @@
       </c>
       <c r="Q335" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>PUE-C</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
@@ -29055,7 +29143,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t xml:space="preserve">9196 </t>
+          <t xml:space="preserve">9926 </t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -29065,12 +29153,12 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>PADILLA 1295</t>
+          <t>DEL LIBERTADOR AV. 5864</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -29108,24 +29196,24 @@
         <v>1</v>
       </c>
       <c r="M336" t="n">
-        <v>-58.447848</v>
+        <v>-58.446592</v>
       </c>
       <c r="N336" t="n">
-        <v>-34.595146</v>
+        <v>-34.558163</v>
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P336" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q336" t="inlineStr">
         <is>
-          <t>VCR-?</t>
+          <t>BLO-A</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -29137,7 +29225,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t xml:space="preserve">9198 </t>
+          <t xml:space="preserve">9928 </t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -29147,12 +29235,12 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>JUSTO, JUAN B. AV. 2960</t>
+          <t>TRIUNVIRATO AV. 5209</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -29168,12 +29256,12 @@
       <c r="G337" t="inlineStr"/>
       <c r="H337" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
@@ -29190,10 +29278,10 @@
         <v>1</v>
       </c>
       <c r="M337" t="n">
-        <v>-58.44825</v>
+        <v>-58.490609</v>
       </c>
       <c r="N337" t="n">
-        <v>-34.597626</v>
+        <v>-34.570845</v>
       </c>
       <c r="O337" t="inlineStr">
         <is>
@@ -29207,7 +29295,7 @@
       </c>
       <c r="Q337" t="inlineStr">
         <is>
-          <t>VCR-?</t>
+          <t>PUE-D</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
@@ -29219,7 +29307,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t xml:space="preserve">7947 </t>
+          <t xml:space="preserve">9929 </t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -29229,7 +29317,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>MILLER 3597</t>
+          <t>NAHUEL HUAPI 5014</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -29250,12 +29338,12 @@
       <c r="G338" t="inlineStr"/>
       <c r="H338" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
@@ -29272,14 +29360,14 @@
         <v>1</v>
       </c>
       <c r="M338" t="n">
-        <v>-58.489898</v>
+        <v>-58.488105</v>
       </c>
       <c r="N338" t="n">
-        <v>-34.560497</v>
+        <v>-34.5709</v>
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P338" t="inlineStr">
@@ -29289,7 +29377,7 @@
       </c>
       <c r="Q338" t="inlineStr">
         <is>
-          <t>PUE-F</t>
+          <t>PUE-D</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
@@ -29301,7 +29389,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t xml:space="preserve">9925 </t>
+          <t xml:space="preserve">9930 </t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -29311,7 +29399,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>MENDOZA AV. 5482</t>
+          <t>NAHUEL HUAPI 4984</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -29354,14 +29442,14 @@
         <v>1</v>
       </c>
       <c r="M339" t="n">
-        <v>-58.487368</v>
+        <v>-58.487664</v>
       </c>
       <c r="N339" t="n">
-        <v>-34.579375</v>
+        <v>-34.57066</v>
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P339" t="inlineStr">
@@ -29371,7 +29459,7 @@
       </c>
       <c r="Q339" t="inlineStr">
         <is>
-          <t>PUE-C</t>
+          <t>PUE-D</t>
         </is>
       </c>
       <c r="R339" t="inlineStr">
@@ -29383,7 +29471,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t xml:space="preserve">9926 </t>
+          <t xml:space="preserve">9931 </t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -29393,12 +29481,12 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>DEL LIBERTADOR AV. 5864</t>
+          <t>DIAZ COLODRERO 2849</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -29414,12 +29502,12 @@
       <c r="G340" t="inlineStr"/>
       <c r="H340" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
@@ -29436,24 +29524,24 @@
         <v>1</v>
       </c>
       <c r="M340" t="n">
-        <v>-58.446592</v>
+        <v>-58.488191</v>
       </c>
       <c r="N340" t="n">
-        <v>-34.558163</v>
+        <v>-34.570326</v>
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P340" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q340" t="inlineStr">
         <is>
-          <t>BLO-A</t>
+          <t>PUE-D</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
@@ -29465,7 +29553,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t xml:space="preserve">9928 </t>
+          <t xml:space="preserve">9932 </t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -29475,7 +29563,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>TRIUNVIRATO AV. 5209</t>
+          <t xml:space="preserve">DIAZ COLODRERO 2879 </t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -29518,14 +29606,14 @@
         <v>1</v>
       </c>
       <c r="M341" t="n">
-        <v>-58.490609</v>
+        <v>-58.488288</v>
       </c>
       <c r="N341" t="n">
-        <v>-34.570845</v>
+        <v>-34.570206</v>
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P341" t="inlineStr">
@@ -29547,7 +29635,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t xml:space="preserve">9929 </t>
+          <t xml:space="preserve">9933 </t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -29557,7 +29645,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>NAHUEL HUAPI 5014</t>
+          <t>LE BRETON, TOMAS A. 4958</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -29600,10 +29688,10 @@
         <v>1</v>
       </c>
       <c r="M342" t="n">
-        <v>-58.488105</v>
+        <v>-58.487974</v>
       </c>
       <c r="N342" t="n">
-        <v>-34.5709</v>
+        <v>-34.569737</v>
       </c>
       <c r="O342" t="inlineStr">
         <is>
@@ -29629,7 +29717,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t xml:space="preserve">9930 </t>
+          <t xml:space="preserve">9935 </t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -29639,7 +29727,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>NAHUEL HUAPI 4984</t>
+          <t>PACHECO 3005</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -29682,14 +29770,14 @@
         <v>1</v>
       </c>
       <c r="M343" t="n">
-        <v>-58.487664</v>
+        <v>-58.487962</v>
       </c>
       <c r="N343" t="n">
-        <v>-34.57066</v>
+        <v>-34.568372</v>
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P343" t="inlineStr">
@@ -29699,7 +29787,7 @@
       </c>
       <c r="Q343" t="inlineStr">
         <is>
-          <t>PUE-D</t>
+          <t>PUE-F</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
@@ -29711,7 +29799,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t xml:space="preserve">9931 </t>
+          <t xml:space="preserve">9936 </t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -29721,7 +29809,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>DIAZ COLODRERO 2849</t>
+          <t>PACHECO 3018</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -29764,14 +29852,14 @@
         <v>1</v>
       </c>
       <c r="M344" t="n">
-        <v>-58.488191</v>
+        <v>-58.488135</v>
       </c>
       <c r="N344" t="n">
-        <v>-34.570326</v>
+        <v>-34.568286</v>
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P344" t="inlineStr">
@@ -29781,7 +29869,7 @@
       </c>
       <c r="Q344" t="inlineStr">
         <is>
-          <t>PUE-D</t>
+          <t>PUE-F</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
@@ -29793,7 +29881,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t xml:space="preserve">9932 </t>
+          <t xml:space="preserve">9937 </t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -29803,7 +29891,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIAZ COLODRERO 2879 </t>
+          <t>PACHECO 3081</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -29846,14 +29934,14 @@
         <v>1</v>
       </c>
       <c r="M345" t="n">
-        <v>-58.488288</v>
+        <v>-58.488419</v>
       </c>
       <c r="N345" t="n">
-        <v>-34.570206</v>
+        <v>-34.567783</v>
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P345" t="inlineStr">
@@ -29863,7 +29951,7 @@
       </c>
       <c r="Q345" t="inlineStr">
         <is>
-          <t>PUE-D</t>
+          <t>PUE-F</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
@@ -29875,7 +29963,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t xml:space="preserve">9933 </t>
+          <t xml:space="preserve">9947 </t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -29885,7 +29973,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>LE BRETON, TOMAS A. 4958</t>
+          <t xml:space="preserve">GALVAN 4083 </t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -29928,14 +30016,14 @@
         <v>1</v>
       </c>
       <c r="M346" t="n">
-        <v>-58.487974</v>
+        <v>-58.494734</v>
       </c>
       <c r="N346" t="n">
-        <v>-34.569737</v>
+        <v>-34.55713</v>
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P346" t="inlineStr">
@@ -29945,7 +30033,7 @@
       </c>
       <c r="Q346" t="inlineStr">
         <is>
-          <t>PUE-D</t>
+          <t>COG-A</t>
         </is>
       </c>
       <c r="R346" t="inlineStr">
@@ -29957,7 +30045,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t xml:space="preserve">9935 </t>
+          <t xml:space="preserve">9951 </t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -29967,7 +30055,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>PACHECO 3005</t>
+          <t>TRIUNVIRATO AV. 4112</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -30010,14 +30098,14 @@
         <v>1</v>
       </c>
       <c r="M347" t="n">
-        <v>-58.487962</v>
+        <v>-58.479286</v>
       </c>
       <c r="N347" t="n">
-        <v>-34.568372</v>
+        <v>-34.579045</v>
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P347" t="inlineStr">
@@ -30027,7 +30115,7 @@
       </c>
       <c r="Q347" t="inlineStr">
         <is>
-          <t>PUE-F</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R347" t="inlineStr">
@@ -30039,7 +30127,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t xml:space="preserve">9936 </t>
+          <t xml:space="preserve">9952 </t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -30049,7 +30137,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>PACHECO 3018</t>
+          <t>ECHEVERRIA 4957</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -30092,14 +30180,14 @@
         <v>1</v>
       </c>
       <c r="M348" t="n">
-        <v>-58.488135</v>
+        <v>-58.479691</v>
       </c>
       <c r="N348" t="n">
-        <v>-34.568286</v>
+        <v>-34.57797</v>
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P348" t="inlineStr">
@@ -30109,7 +30197,7 @@
       </c>
       <c r="Q348" t="inlineStr">
         <is>
-          <t>PUE-F</t>
+          <t>ATH-E</t>
         </is>
       </c>
       <c r="R348" t="inlineStr">
@@ -30121,7 +30209,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t xml:space="preserve">9937 </t>
+          <t xml:space="preserve">9953 </t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -30131,7 +30219,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>PACHECO 3081</t>
+          <t>ECHEVERRIA 4935</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -30162,7 +30250,7 @@
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
@@ -30174,14 +30262,14 @@
         <v>1</v>
       </c>
       <c r="M349" t="n">
-        <v>-58.488419</v>
+        <v>-58.479498</v>
       </c>
       <c r="N349" t="n">
-        <v>-34.567783</v>
+        <v>-34.577799</v>
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P349" t="inlineStr">
@@ -30191,7 +30279,7 @@
       </c>
       <c r="Q349" t="inlineStr">
         <is>
-          <t>PUE-F</t>
+          <t>ATH-E</t>
         </is>
       </c>
       <c r="R349" t="inlineStr">
@@ -30203,7 +30291,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t xml:space="preserve">9946 </t>
+          <t xml:space="preserve">9954 </t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -30213,7 +30301,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALVAN 4111 </t>
+          <t>ECHEVERRIA 4917</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -30256,14 +30344,14 @@
         <v>1</v>
       </c>
       <c r="M350" t="n">
-        <v>-58.494982</v>
+        <v>-58.479366</v>
       </c>
       <c r="N350" t="n">
-        <v>-34.556769</v>
+        <v>-34.577682</v>
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P350" t="inlineStr">
@@ -30273,7 +30361,7 @@
       </c>
       <c r="Q350" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>ATH-E</t>
         </is>
       </c>
       <c r="R350" t="inlineStr">
@@ -30285,7 +30373,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t xml:space="preserve">9947 </t>
+          <t xml:space="preserve">9955 </t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -30295,7 +30383,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALVAN 4083 </t>
+          <t>ANDONAEGUI 1812</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -30338,14 +30426,14 @@
         <v>1</v>
       </c>
       <c r="M351" t="n">
-        <v>-58.494734</v>
+        <v>-58.484377</v>
       </c>
       <c r="N351" t="n">
-        <v>-34.55713</v>
+        <v>-34.581873</v>
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P351" t="inlineStr">
@@ -30355,7 +30443,7 @@
       </c>
       <c r="Q351" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R351" t="inlineStr">
@@ -30367,7 +30455,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t xml:space="preserve">9949 </t>
+          <t xml:space="preserve">9956 </t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -30377,7 +30465,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>GALVAN 4063</t>
+          <t>ANDONAEGUI 1929</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -30420,14 +30508,14 @@
         <v>1</v>
       </c>
       <c r="M352" t="n">
-        <v>-58.494649</v>
+        <v>-58.485167</v>
       </c>
       <c r="N352" t="n">
-        <v>-34.557253</v>
+        <v>-34.580822</v>
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P352" t="inlineStr">
@@ -30437,7 +30525,7 @@
       </c>
       <c r="Q352" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R352" t="inlineStr">
@@ -30449,7 +30537,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t xml:space="preserve">9950 </t>
+          <t xml:space="preserve">9957 </t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -30459,7 +30547,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>MILLER 4090</t>
+          <t>JURAMENTO 5347</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -30502,14 +30590,14 @@
         <v>1</v>
       </c>
       <c r="M353" t="n">
-        <v>-58.49285</v>
+        <v>-58.485468</v>
       </c>
       <c r="N353" t="n">
-        <v>-34.556314</v>
+        <v>-34.579765</v>
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P353" t="inlineStr">
@@ -30519,7 +30607,7 @@
       </c>
       <c r="Q353" t="inlineStr">
         <is>
-          <t>COG-A</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R353" t="inlineStr">
@@ -30531,7 +30619,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t xml:space="preserve">9951 </t>
+          <t xml:space="preserve">9960 </t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -30541,7 +30629,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>TRIUNVIRATO AV. 4112</t>
+          <t>BUCARELLI 1995</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -30562,17 +30650,17 @@
       <c r="G354" t="inlineStr"/>
       <c r="H354" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
@@ -30584,10 +30672,10 @@
         <v>1</v>
       </c>
       <c r="M354" t="n">
-        <v>-58.479286</v>
+        <v>-58.484744</v>
       </c>
       <c r="N354" t="n">
-        <v>-34.579045</v>
+        <v>-34.579576</v>
       </c>
       <c r="O354" t="inlineStr">
         <is>
@@ -30613,7 +30701,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t xml:space="preserve">9952 </t>
+          <t xml:space="preserve">9961 </t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -30623,12 +30711,12 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>ECHEVERRIA 4957</t>
+          <t>JURAMENTO 5261</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -30666,10 +30754,10 @@
         <v>1</v>
       </c>
       <c r="M355" t="n">
-        <v>-58.479691</v>
+        <v>-58.484396</v>
       </c>
       <c r="N355" t="n">
-        <v>-34.57797</v>
+        <v>-34.579179</v>
       </c>
       <c r="O355" t="inlineStr">
         <is>
@@ -30683,7 +30771,7 @@
       </c>
       <c r="Q355" t="inlineStr">
         <is>
-          <t>ATH-E</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R355" t="inlineStr">
@@ -30695,7 +30783,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t xml:space="preserve">9953 </t>
+          <t xml:space="preserve">9963 </t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -30705,7 +30793,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>ECHEVERRIA 4935</t>
+          <t xml:space="preserve">BARZANA 1814 </t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -30736,7 +30824,7 @@
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
@@ -30748,10 +30836,10 @@
         <v>1</v>
       </c>
       <c r="M356" t="n">
-        <v>-58.479498</v>
+        <v>-58.485279</v>
       </c>
       <c r="N356" t="n">
-        <v>-34.577799</v>
+        <v>-34.582509</v>
       </c>
       <c r="O356" t="inlineStr">
         <is>
@@ -30765,7 +30853,7 @@
       </c>
       <c r="Q356" t="inlineStr">
         <is>
-          <t>ATH-E</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R356" t="inlineStr">
@@ -30777,7 +30865,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t xml:space="preserve">9954 </t>
+          <t xml:space="preserve">9964 </t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -30787,7 +30875,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>ECHEVERRIA 4917</t>
+          <t>BARZANA 1844</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -30830,10 +30918,10 @@
         <v>1</v>
       </c>
       <c r="M357" t="n">
-        <v>-58.479366</v>
+        <v>-58.485434</v>
       </c>
       <c r="N357" t="n">
-        <v>-34.577682</v>
+        <v>-34.582311</v>
       </c>
       <c r="O357" t="inlineStr">
         <is>
@@ -30847,7 +30935,7 @@
       </c>
       <c r="Q357" t="inlineStr">
         <is>
-          <t>ATH-E</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R357" t="inlineStr">
@@ -30859,7 +30947,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t xml:space="preserve">9955 </t>
+          <t xml:space="preserve">9965 </t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -30869,7 +30957,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>ANDONAEGUI 1812</t>
+          <t>ALTOLAGUIRRE 1813</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -30912,10 +31000,10 @@
         <v>1</v>
       </c>
       <c r="M358" t="n">
-        <v>-58.484377</v>
+        <v>-58.486073</v>
       </c>
       <c r="N358" t="n">
-        <v>-34.581873</v>
+        <v>-34.582965</v>
       </c>
       <c r="O358" t="inlineStr">
         <is>
@@ -30941,7 +31029,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t xml:space="preserve">9956 </t>
+          <t xml:space="preserve">9966 </t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -30951,7 +31039,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>ANDONAEGUI 1929</t>
+          <t>BURELA 1845</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -30972,12 +31060,12 @@
       <c r="G359" t="inlineStr"/>
       <c r="H359" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
@@ -30994,10 +31082,10 @@
         <v>1</v>
       </c>
       <c r="M359" t="n">
-        <v>-58.485167</v>
+        <v>-58.487319</v>
       </c>
       <c r="N359" t="n">
-        <v>-34.580822</v>
+        <v>-34.583364</v>
       </c>
       <c r="O359" t="inlineStr">
         <is>
@@ -31011,7 +31099,7 @@
       </c>
       <c r="Q359" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>PUE-K</t>
         </is>
       </c>
       <c r="R359" t="inlineStr">
@@ -31023,7 +31111,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t xml:space="preserve">9957 </t>
+          <t xml:space="preserve">9967 </t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -31033,7 +31121,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>JURAMENTO 5347</t>
+          <t>CERETTI 1850</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -31076,10 +31164,10 @@
         <v>1</v>
       </c>
       <c r="M360" t="n">
-        <v>-58.485468</v>
+        <v>-58.488493</v>
       </c>
       <c r="N360" t="n">
-        <v>-34.579765</v>
+        <v>-34.583983</v>
       </c>
       <c r="O360" t="inlineStr">
         <is>
@@ -31093,7 +31181,7 @@
       </c>
       <c r="Q360" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>PUE-K</t>
         </is>
       </c>
       <c r="R360" t="inlineStr">
@@ -31105,7 +31193,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t xml:space="preserve">9960 </t>
+          <t xml:space="preserve">9969 </t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -31115,12 +31203,12 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>BUCARELLI 1995</t>
+          <t>MONTAÑESES 1910</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -31146,7 +31234,7 @@
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
@@ -31158,14 +31246,14 @@
         <v>1</v>
       </c>
       <c r="M361" t="n">
-        <v>-58.484744</v>
+        <v>-58.447489</v>
       </c>
       <c r="N361" t="n">
-        <v>-34.579576</v>
+        <v>-34.559091</v>
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P361" t="inlineStr">
@@ -31175,7 +31263,7 @@
       </c>
       <c r="Q361" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>BLO-A</t>
         </is>
       </c>
       <c r="R361" t="inlineStr">
@@ -31187,7 +31275,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t xml:space="preserve">9961 </t>
+          <t xml:space="preserve">9970 </t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -31197,12 +31285,12 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>JURAMENTO 5261</t>
+          <t>ECHEVERRIA 5051</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -31240,10 +31328,10 @@
         <v>1</v>
       </c>
       <c r="M362" t="n">
-        <v>-58.484396</v>
+        <v>-58.481099</v>
       </c>
       <c r="N362" t="n">
-        <v>-34.579179</v>
+        <v>-34.578912</v>
       </c>
       <c r="O362" t="inlineStr">
         <is>
@@ -31269,7 +31357,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t xml:space="preserve">9963 </t>
+          <t xml:space="preserve">9971 </t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -31279,7 +31367,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARZANA 1814 </t>
+          <t>ECHEVERRIA 5021</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -31322,10 +31410,10 @@
         <v>1</v>
       </c>
       <c r="M363" t="n">
-        <v>-58.485279</v>
+        <v>-58.480634</v>
       </c>
       <c r="N363" t="n">
-        <v>-34.582509</v>
+        <v>-34.578647</v>
       </c>
       <c r="O363" t="inlineStr">
         <is>
@@ -31339,7 +31427,7 @@
       </c>
       <c r="Q363" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R363" t="inlineStr">
@@ -31351,7 +31439,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t xml:space="preserve">9964 </t>
+          <t xml:space="preserve">9974 </t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -31361,7 +31449,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>BARZANA 1844</t>
+          <t>NAVARRO 2319</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -31404,10 +31492,10 @@
         <v>1</v>
       </c>
       <c r="M364" t="n">
-        <v>-58.485434</v>
+        <v>-58.488431</v>
       </c>
       <c r="N364" t="n">
-        <v>-34.582311</v>
+        <v>-34.59018</v>
       </c>
       <c r="O364" t="inlineStr">
         <is>
@@ -31421,7 +31509,7 @@
       </c>
       <c r="Q364" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R364" t="inlineStr">
@@ -31433,7 +31521,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t xml:space="preserve">9965 </t>
+          <t xml:space="preserve">9975 </t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -31443,7 +31531,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>ALTOLAGUIRRE 1813</t>
+          <t xml:space="preserve">PLAZA 3692 </t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -31486,14 +31574,14 @@
         <v>1</v>
       </c>
       <c r="M365" t="n">
-        <v>-58.486073</v>
+        <v>-58.485304</v>
       </c>
       <c r="N365" t="n">
-        <v>-34.582965</v>
+        <v>-34.556915</v>
       </c>
       <c r="O365" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P365" t="inlineStr">
@@ -31503,7 +31591,7 @@
       </c>
       <c r="Q365" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R365" t="inlineStr">
@@ -31515,7 +31603,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t xml:space="preserve">9966 </t>
+          <t xml:space="preserve">9976 </t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -31525,7 +31613,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>BURELA 1845</t>
+          <t>JARAMILLO 4240</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -31546,12 +31634,12 @@
       <c r="G366" t="inlineStr"/>
       <c r="H366" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
@@ -31568,14 +31656,14 @@
         <v>1</v>
       </c>
       <c r="M366" t="n">
-        <v>-58.487319</v>
+        <v>-58.485606</v>
       </c>
       <c r="N366" t="n">
-        <v>-34.583364</v>
+        <v>-34.556876</v>
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P366" t="inlineStr">
@@ -31585,7 +31673,7 @@
       </c>
       <c r="Q366" t="inlineStr">
         <is>
-          <t>PUE-K</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R366" t="inlineStr">
@@ -31597,7 +31685,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t xml:space="preserve">9967 </t>
+          <t xml:space="preserve">9977 </t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -31607,7 +31695,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>CERETTI 1850</t>
+          <t>JARAMILLO 4290</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -31650,14 +31738,14 @@
         <v>1</v>
       </c>
       <c r="M367" t="n">
-        <v>-58.488493</v>
+        <v>-58.485814</v>
       </c>
       <c r="N367" t="n">
-        <v>-34.583983</v>
+        <v>-34.556975</v>
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P367" t="inlineStr">
@@ -31667,7 +31755,7 @@
       </c>
       <c r="Q367" t="inlineStr">
         <is>
-          <t>PUE-K</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R367" t="inlineStr">
@@ -31679,7 +31767,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t xml:space="preserve">9969 </t>
+          <t xml:space="preserve">9978 </t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -31689,12 +31777,12 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>MONTAÑESES 1910</t>
+          <t>JARAMILLO 4316</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -31710,12 +31798,12 @@
       <c r="G368" t="inlineStr"/>
       <c r="H368" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
@@ -31732,10 +31820,10 @@
         <v>1</v>
       </c>
       <c r="M368" t="n">
-        <v>-58.447489</v>
+        <v>-58.486296</v>
       </c>
       <c r="N368" t="n">
-        <v>-34.559091</v>
+        <v>-34.557209</v>
       </c>
       <c r="O368" t="inlineStr">
         <is>
@@ -31749,7 +31837,7 @@
       </c>
       <c r="Q368" t="inlineStr">
         <is>
-          <t>BLO-A</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R368" t="inlineStr">
@@ -31761,7 +31849,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t xml:space="preserve">9970 </t>
+          <t xml:space="preserve">9979 </t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -31771,7 +31859,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>ECHEVERRIA 5051</t>
+          <t>JARAMILLO 4418</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -31814,14 +31902,14 @@
         <v>1</v>
       </c>
       <c r="M369" t="n">
-        <v>-58.481099</v>
+        <v>-58.48725</v>
       </c>
       <c r="N369" t="n">
-        <v>-34.578912</v>
+        <v>-34.557662</v>
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P369" t="inlineStr">
@@ -31831,7 +31919,7 @@
       </c>
       <c r="Q369" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R369" t="inlineStr">
@@ -31843,7 +31931,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t xml:space="preserve">9971 </t>
+          <t xml:space="preserve">9980 </t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -31853,7 +31941,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>ECHEVERRIA 5021</t>
+          <t>JARAMILLO 4480</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -31896,14 +31984,14 @@
         <v>1</v>
       </c>
       <c r="M370" t="n">
-        <v>-58.480634</v>
+        <v>-58.487657</v>
       </c>
       <c r="N370" t="n">
-        <v>-34.578647</v>
+        <v>-34.557857</v>
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P370" t="inlineStr">
@@ -31913,7 +32001,7 @@
       </c>
       <c r="Q370" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R370" t="inlineStr">
@@ -31925,7 +32013,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t xml:space="preserve">9974 </t>
+          <t xml:space="preserve">9981 </t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -31935,7 +32023,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>NAVARRO 2319</t>
+          <t>MACHAIN 3685</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -31978,14 +32066,14 @@
         <v>1</v>
       </c>
       <c r="M371" t="n">
-        <v>-58.488431</v>
+        <v>-58.487792</v>
       </c>
       <c r="N371" t="n">
-        <v>-34.59018</v>
+        <v>-34.558117</v>
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P371" t="inlineStr">
@@ -31995,7 +32083,7 @@
       </c>
       <c r="Q371" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R371" t="inlineStr">
@@ -32007,7 +32095,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t xml:space="preserve">9975 </t>
+          <t xml:space="preserve">9982 </t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -32017,7 +32105,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLAZA 3692 </t>
+          <t>JARAMILLO 4596</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -32060,10 +32148,10 @@
         <v>1</v>
       </c>
       <c r="M372" t="n">
-        <v>-58.485304</v>
+        <v>-58.488713</v>
       </c>
       <c r="N372" t="n">
-        <v>-34.556915</v>
+        <v>-34.558359</v>
       </c>
       <c r="O372" t="inlineStr">
         <is>
@@ -32089,7 +32177,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t xml:space="preserve">9976 </t>
+          <t xml:space="preserve">9983 </t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -32099,7 +32187,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>JARAMILLO 4240</t>
+          <t>CHAJARI 4494</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -32142,10 +32230,10 @@
         <v>1</v>
       </c>
       <c r="M373" t="n">
-        <v>-58.485606</v>
+        <v>-58.487376</v>
       </c>
       <c r="N373" t="n">
-        <v>-34.556876</v>
+        <v>-34.558432</v>
       </c>
       <c r="O373" t="inlineStr">
         <is>
@@ -32171,7 +32259,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t xml:space="preserve">9977 </t>
+          <t xml:space="preserve">9985 </t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -32181,7 +32269,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>JARAMILLO 4290</t>
+          <t>VILELA 3247</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -32202,12 +32290,12 @@
       <c r="G374" t="inlineStr"/>
       <c r="H374" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
@@ -32224,10 +32312,10 @@
         <v>1</v>
       </c>
       <c r="M374" t="n">
-        <v>-58.485814</v>
+        <v>-58.478755</v>
       </c>
       <c r="N374" t="n">
-        <v>-34.556975</v>
+        <v>-34.548872</v>
       </c>
       <c r="O374" t="inlineStr">
         <is>
@@ -32241,7 +32329,7 @@
       </c>
       <c r="Q374" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>COG-P</t>
         </is>
       </c>
       <c r="R374" t="inlineStr">
@@ -32253,7 +32341,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t xml:space="preserve">9978 </t>
+          <t xml:space="preserve">9986 </t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -32263,7 +32351,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>JARAMILLO 4316</t>
+          <t xml:space="preserve">MANZANARES 3891 </t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -32284,12 +32372,12 @@
       <c r="G375" t="inlineStr"/>
       <c r="H375" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
@@ -32306,10 +32394,10 @@
         <v>1</v>
       </c>
       <c r="M375" t="n">
-        <v>-58.486296</v>
+        <v>-58.482841</v>
       </c>
       <c r="N375" t="n">
-        <v>-34.557209</v>
+        <v>-34.554298</v>
       </c>
       <c r="O375" t="inlineStr">
         <is>
@@ -32335,7 +32423,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t xml:space="preserve">9979 </t>
+          <t xml:space="preserve">9987 </t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -32345,7 +32433,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>JARAMILLO 4418</t>
+          <t>NUÑEZ 3313</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -32366,12 +32454,12 @@
       <c r="G376" t="inlineStr"/>
       <c r="H376" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
@@ -32388,10 +32476,10 @@
         <v>1</v>
       </c>
       <c r="M376" t="n">
-        <v>-58.48725</v>
+        <v>-58.475457</v>
       </c>
       <c r="N376" t="n">
-        <v>-34.557662</v>
+        <v>-34.554525</v>
       </c>
       <c r="O376" t="inlineStr">
         <is>
@@ -32405,7 +32493,7 @@
       </c>
       <c r="Q376" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>COG-N</t>
         </is>
       </c>
       <c r="R376" t="inlineStr">
@@ -32417,7 +32505,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t xml:space="preserve">9980 </t>
+          <t xml:space="preserve">9992 </t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -32427,7 +32515,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>JARAMILLO 4480</t>
+          <t>MENDOZA 5705</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -32470,14 +32558,14 @@
         <v>1</v>
       </c>
       <c r="M377" t="n">
-        <v>-58.487657</v>
+        <v>-58.489753</v>
       </c>
       <c r="N377" t="n">
-        <v>-34.557857</v>
+        <v>-34.58055</v>
       </c>
       <c r="O377" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P377" t="inlineStr">
@@ -32487,7 +32575,7 @@
       </c>
       <c r="Q377" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>PUE-C</t>
         </is>
       </c>
       <c r="R377" t="inlineStr">
@@ -32499,7 +32587,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t xml:space="preserve">9981 </t>
+          <t xml:space="preserve">9993 </t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -32509,7 +32597,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>MACHAIN 3685</t>
+          <t>MONROE 5212</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -32552,14 +32640,14 @@
         <v>1</v>
       </c>
       <c r="M378" t="n">
-        <v>-58.487792</v>
+        <v>-58.487529</v>
       </c>
       <c r="N378" t="n">
-        <v>-34.558117</v>
+        <v>-34.575028</v>
       </c>
       <c r="O378" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P378" t="inlineStr">
@@ -32569,7 +32657,7 @@
       </c>
       <c r="Q378" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>ATH-C</t>
         </is>
       </c>
       <c r="R378" t="inlineStr">
@@ -32581,7 +32669,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t xml:space="preserve">9982 </t>
+          <t xml:space="preserve">9994 </t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -32591,7 +32679,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>JARAMILLO 4596</t>
+          <t>MONROE 5399</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -32627,21 +32715,21 @@
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L379" t="n">
         <v>1</v>
       </c>
       <c r="M379" t="n">
-        <v>-58.488713</v>
+        <v>-58.489782</v>
       </c>
       <c r="N379" t="n">
-        <v>-34.558359</v>
+        <v>-34.576217</v>
       </c>
       <c r="O379" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P379" t="inlineStr">
@@ -32651,7 +32739,7 @@
       </c>
       <c r="Q379" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>ATH-C</t>
         </is>
       </c>
       <c r="R379" t="inlineStr">
@@ -32663,7 +32751,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t xml:space="preserve">9983 </t>
+          <t xml:space="preserve">9995 </t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -32673,7 +32761,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>CHAJARI 4494</t>
+          <t>BURELA 2409</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -32709,21 +32797,21 @@
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L380" t="n">
         <v>1</v>
       </c>
       <c r="M380" t="n">
-        <v>-58.487376</v>
+        <v>-58.492031</v>
       </c>
       <c r="N380" t="n">
-        <v>-34.558432</v>
+        <v>-34.577453</v>
       </c>
       <c r="O380" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P380" t="inlineStr">
@@ -32733,7 +32821,7 @@
       </c>
       <c r="Q380" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>PUE-C</t>
         </is>
       </c>
       <c r="R380" t="inlineStr">
@@ -32745,7 +32833,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t xml:space="preserve">9985 </t>
+          <t xml:space="preserve">9996 </t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -32755,7 +32843,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>VILELA 3247</t>
+          <t>ZAMUDIO 4784</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -32776,12 +32864,12 @@
       <c r="G381" t="inlineStr"/>
       <c r="H381" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
@@ -32798,14 +32886,14 @@
         <v>1</v>
       </c>
       <c r="M381" t="n">
-        <v>-58.478755</v>
+        <v>-58.497199</v>
       </c>
       <c r="N381" t="n">
-        <v>-34.548872</v>
+        <v>-34.582097</v>
       </c>
       <c r="O381" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P381" t="inlineStr">
@@ -32815,7 +32903,7 @@
       </c>
       <c r="Q381" t="inlineStr">
         <is>
-          <t>COG-P</t>
+          <t>PUE-M</t>
         </is>
       </c>
       <c r="R381" t="inlineStr">
@@ -32827,22 +32915,22 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t xml:space="preserve">9986 </t>
+          <t xml:space="preserve">8804 </t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANZANARES 3891 </t>
+          <t>LOPEZ MERINO, FRANCISCO 3988</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -32855,7 +32943,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G382" t="inlineStr"/>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>814108011</t>
+        </is>
+      </c>
       <c r="H382" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -32880,14 +32972,14 @@
         <v>1</v>
       </c>
       <c r="M382" t="n">
-        <v>-58.482841</v>
+        <v>-58.493486</v>
       </c>
       <c r="N382" t="n">
-        <v>-34.554298</v>
+        <v>-34.589105</v>
       </c>
       <c r="O382" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P382" t="inlineStr">
@@ -32897,7 +32989,7 @@
       </c>
       <c r="Q382" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R382" t="inlineStr">
@@ -32909,17 +33001,17 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t xml:space="preserve">9987 </t>
+          <t xml:space="preserve">8949 </t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>NUÑEZ 3313</t>
+          <t>DE LOS CONSTITUYENTES AV. 5398</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -32937,7 +33029,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G383" t="inlineStr"/>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>814108037</t>
+        </is>
+      </c>
       <c r="H383" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -32962,14 +33058,14 @@
         <v>1</v>
       </c>
       <c r="M383" t="n">
-        <v>-58.475457</v>
+        <v>-58.499639</v>
       </c>
       <c r="N383" t="n">
-        <v>-34.554525</v>
+        <v>-34.576202</v>
       </c>
       <c r="O383" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P383" t="inlineStr">
@@ -32979,7 +33075,7 @@
       </c>
       <c r="Q383" t="inlineStr">
         <is>
-          <t>COG-N</t>
+          <t>PUE-I</t>
         </is>
       </c>
       <c r="R383" t="inlineStr">
@@ -32991,17 +33087,17 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t xml:space="preserve">9992 </t>
+          <t xml:space="preserve">8962 </t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>MENDOZA 5705</t>
+          <t>CONGRESO AV. 5856</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -33019,15 +33115,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G384" t="inlineStr"/>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>814108043</t>
+        </is>
+      </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
@@ -33044,10 +33144,10 @@
         <v>1</v>
       </c>
       <c r="M384" t="n">
-        <v>-58.489753</v>
+        <v>-58.499051</v>
       </c>
       <c r="N384" t="n">
-        <v>-34.58055</v>
+        <v>-34.57451</v>
       </c>
       <c r="O384" t="inlineStr">
         <is>
@@ -33061,7 +33161,7 @@
       </c>
       <c r="Q384" t="inlineStr">
         <is>
-          <t>PUE-C</t>
+          <t>PUE-I</t>
         </is>
       </c>
       <c r="R384" t="inlineStr">
@@ -33073,17 +33173,17 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t xml:space="preserve">9993 </t>
+          <t xml:space="preserve">8982 </t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>MONROE 5212</t>
+          <t>LOPEZ, CARLOS ANTONIO 2197</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -33101,15 +33201,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G385" t="inlineStr"/>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>814108057</t>
+        </is>
+      </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
@@ -33126,10 +33230,10 @@
         <v>1</v>
       </c>
       <c r="M385" t="n">
-        <v>-58.487529</v>
+        <v>-58.494928</v>
       </c>
       <c r="N385" t="n">
-        <v>-34.575028</v>
+        <v>-34.580378</v>
       </c>
       <c r="O385" t="inlineStr">
         <is>
@@ -33143,7 +33247,7 @@
       </c>
       <c r="Q385" t="inlineStr">
         <is>
-          <t>ATH-C</t>
+          <t>PUE-M</t>
         </is>
       </c>
       <c r="R385" t="inlineStr">
@@ -33155,17 +33259,17 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t xml:space="preserve">9994 </t>
+          <t xml:space="preserve">10022 </t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>MONROE 5399</t>
+          <t>IBERA 6188</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -33201,17 +33305,17 @@
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L386" t="n">
         <v>1</v>
       </c>
       <c r="M386" t="n">
-        <v>-58.489782</v>
+        <v>-58.502669</v>
       </c>
       <c r="N386" t="n">
-        <v>-34.576217</v>
+        <v>-34.573449</v>
       </c>
       <c r="O386" t="inlineStr">
         <is>
@@ -33225,7 +33329,7 @@
       </c>
       <c r="Q386" t="inlineStr">
         <is>
-          <t>ATH-C</t>
+          <t>PUE-I</t>
         </is>
       </c>
       <c r="R386" t="inlineStr">
@@ -33237,17 +33341,17 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995 </t>
+          <t xml:space="preserve">10024 </t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>BURELA 2409</t>
+          <t>IBERA 6146</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -33283,17 +33387,17 @@
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L387" t="n">
         <v>1</v>
       </c>
       <c r="M387" t="n">
-        <v>-58.492031</v>
+        <v>-58.502338</v>
       </c>
       <c r="N387" t="n">
-        <v>-34.577453</v>
+        <v>-34.573275</v>
       </c>
       <c r="O387" t="inlineStr">
         <is>
@@ -33307,7 +33411,7 @@
       </c>
       <c r="Q387" t="inlineStr">
         <is>
-          <t>PUE-C</t>
+          <t>PUE-I</t>
         </is>
       </c>
       <c r="R387" t="inlineStr">
@@ -33319,22 +33423,22 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t xml:space="preserve">9996 </t>
+          <t xml:space="preserve">10025 </t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>ZAMUDIO 4784</t>
+          <t>JUSTO, JUAN B. AV. 3073</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -33372,10 +33476,10 @@
         <v>1</v>
       </c>
       <c r="M388" t="n">
-        <v>-58.497199</v>
+        <v>-58.449604</v>
       </c>
       <c r="N388" t="n">
-        <v>-34.582097</v>
+        <v>-34.598286</v>
       </c>
       <c r="O388" t="inlineStr">
         <is>
@@ -33389,7 +33493,7 @@
       </c>
       <c r="Q388" t="inlineStr">
         <is>
-          <t>PUE-M</t>
+          <t>VCR-?</t>
         </is>
       </c>
       <c r="R388" t="inlineStr">
@@ -33401,7 +33505,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t xml:space="preserve">8804 </t>
+          <t xml:space="preserve">10026 </t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -33411,12 +33515,12 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>LOPEZ MERINO, FRANCISCO 3988</t>
+          <t>HUMBOLDT 47</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -33432,12 +33536,12 @@
       <c r="G389" t="inlineStr"/>
       <c r="H389" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
@@ -33454,10 +33558,10 @@
         <v>1</v>
       </c>
       <c r="M389" t="n">
-        <v>-58.493486</v>
+        <v>-58.451981</v>
       </c>
       <c r="N389" t="n">
-        <v>-34.589105</v>
+        <v>-34.597952</v>
       </c>
       <c r="O389" t="inlineStr">
         <is>
@@ -33471,7 +33575,7 @@
       </c>
       <c r="Q389" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>VCR-?</t>
         </is>
       </c>
       <c r="R389" t="inlineStr">
@@ -33483,17 +33587,17 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t xml:space="preserve">8949 </t>
+          <t xml:space="preserve">10027 </t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>5/7/2026</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>DE LOS CONSTITUYENTES AV. 5398</t>
+          <t>HUMBOLDT 37</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -33514,12 +33618,12 @@
       <c r="G390" t="inlineStr"/>
       <c r="H390" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
@@ -33536,10 +33640,10 @@
         <v>1</v>
       </c>
       <c r="M390" t="n">
-        <v>-58.499639</v>
+        <v>-58.452157</v>
       </c>
       <c r="N390" t="n">
-        <v>-34.576202</v>
+        <v>-34.598081</v>
       </c>
       <c r="O390" t="inlineStr">
         <is>
@@ -33553,7 +33657,7 @@
       </c>
       <c r="Q390" t="inlineStr">
         <is>
-          <t>PUE-I</t>
+          <t>VCR-?</t>
         </is>
       </c>
       <c r="R390" t="inlineStr">
@@ -33565,7 +33669,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t xml:space="preserve">8962 </t>
+          <t xml:space="preserve">10028 </t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -33575,12 +33679,12 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>CONGRESO AV. 5856</t>
+          <t>HUMBOLDT 23</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -33596,17 +33700,17 @@
       <c r="G391" t="inlineStr"/>
       <c r="H391" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
@@ -33618,10 +33722,10 @@
         <v>1</v>
       </c>
       <c r="M391" t="n">
-        <v>-58.499051</v>
+        <v>-58.452473</v>
       </c>
       <c r="N391" t="n">
-        <v>-34.57451</v>
+        <v>-34.598316</v>
       </c>
       <c r="O391" t="inlineStr">
         <is>
@@ -33635,7 +33739,7 @@
       </c>
       <c r="Q391" t="inlineStr">
         <is>
-          <t>PUE-I</t>
+          <t>VCR-?</t>
         </is>
       </c>
       <c r="R391" t="inlineStr">
@@ -33647,7 +33751,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t xml:space="preserve">8982 </t>
+          <t xml:space="preserve">10030 </t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -33657,12 +33761,12 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>LOPEZ, CARLOS ANTONIO 2197</t>
+          <t>SUSINI, ANTONIO, CNEL. 2190</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -33678,12 +33782,12 @@
       <c r="G392" t="inlineStr"/>
       <c r="H392" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
@@ -33700,10 +33804,10 @@
         <v>1</v>
       </c>
       <c r="M392" t="n">
-        <v>-58.494928</v>
+        <v>-58.452997</v>
       </c>
       <c r="N392" t="n">
-        <v>-34.580378</v>
+        <v>-34.597674</v>
       </c>
       <c r="O392" t="inlineStr">
         <is>
@@ -33717,7 +33821,7 @@
       </c>
       <c r="Q392" t="inlineStr">
         <is>
-          <t>PUE-M</t>
+          <t>VCR-?</t>
         </is>
       </c>
       <c r="R392" t="inlineStr">
@@ -33729,7 +33833,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t xml:space="preserve">10022 </t>
+          <t xml:space="preserve">9053 </t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -33739,12 +33843,12 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>IBERA 6188</t>
+          <t>FRAGA 1848</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -33757,15 +33861,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G393" t="inlineStr"/>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>814108072</t>
+        </is>
+      </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
@@ -33782,14 +33890,14 @@
         <v>1</v>
       </c>
       <c r="M393" t="n">
-        <v>-58.502669</v>
+        <v>-58.468977</v>
       </c>
       <c r="N393" t="n">
-        <v>-34.573449</v>
+        <v>-34.582742</v>
       </c>
       <c r="O393" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P393" t="inlineStr">
@@ -33799,7 +33907,7 @@
       </c>
       <c r="Q393" t="inlineStr">
         <is>
-          <t>PUE-I</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R393" t="inlineStr">
@@ -33811,7 +33919,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t xml:space="preserve">10024 </t>
+          <t xml:space="preserve">10036 </t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -33821,7 +33929,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>IBERA 6146</t>
+          <t xml:space="preserve">COCHRANE 2314 </t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -33864,10 +33972,10 @@
         <v>1</v>
       </c>
       <c r="M394" t="n">
-        <v>-58.502338</v>
+        <v>-58.501425</v>
       </c>
       <c r="N394" t="n">
-        <v>-34.573275</v>
+        <v>-34.575827</v>
       </c>
       <c r="O394" t="inlineStr">
         <is>
@@ -33893,7 +34001,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t xml:space="preserve">10025 </t>
+          <t>S00527817</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -33903,7 +34011,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>JUSTO, JUAN B. AV. 3073</t>
+          <t>TINOGASTA 2561</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -33924,12 +34032,12 @@
       <c r="G395" t="inlineStr"/>
       <c r="H395" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>DESMONTAR POSTE</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
@@ -33946,10 +34054,10 @@
         <v>1</v>
       </c>
       <c r="M395" t="n">
-        <v>-58.449604</v>
+        <v>-58.487709</v>
       </c>
       <c r="N395" t="n">
-        <v>-34.598286</v>
+        <v>-34.595778</v>
       </c>
       <c r="O395" t="inlineStr">
         <is>
@@ -33963,7 +34071,7 @@
       </c>
       <c r="Q395" t="inlineStr">
         <is>
-          <t>VCR-?</t>
+          <t>PUE-A</t>
         </is>
       </c>
       <c r="R395" t="inlineStr">
@@ -33975,7 +34083,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t xml:space="preserve">10026 </t>
+          <t xml:space="preserve">10049 </t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -33985,12 +34093,12 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>HUMBOLDT 47</t>
+          <t>HEREDIA 1295</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -34028,14 +34136,14 @@
         <v>1</v>
       </c>
       <c r="M396" t="n">
-        <v>-58.451981</v>
+        <v>-58.463173</v>
       </c>
       <c r="N396" t="n">
-        <v>-34.597952</v>
+        <v>-34.57859</v>
       </c>
       <c r="O396" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P396" t="inlineStr">
@@ -34045,7 +34153,7 @@
       </c>
       <c r="Q396" t="inlineStr">
         <is>
-          <t>VCR-?</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R396" t="inlineStr">
@@ -34057,17 +34165,17 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t xml:space="preserve">10027 </t>
+          <t xml:space="preserve">10053 </t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>5/7/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>HUMBOLDT 37</t>
+          <t>ARGERICH 4784</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -34085,15 +34193,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G397" t="inlineStr"/>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>814108235</t>
+        </is>
+      </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
@@ -34110,10 +34222,10 @@
         <v>1</v>
       </c>
       <c r="M397" t="n">
-        <v>-58.452157</v>
+        <v>-58.504104</v>
       </c>
       <c r="N397" t="n">
-        <v>-34.598081</v>
+        <v>-34.586449</v>
       </c>
       <c r="O397" t="inlineStr">
         <is>
@@ -34127,7 +34239,7 @@
       </c>
       <c r="Q397" t="inlineStr">
         <is>
-          <t>VCR-?</t>
+          <t>PUE-N</t>
         </is>
       </c>
       <c r="R397" t="inlineStr">
@@ -34139,22 +34251,22 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t xml:space="preserve">10028 </t>
+          <t xml:space="preserve">10057 </t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>5/7/2026</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>HUMBOLDT 23</t>
+          <t>TERRADA 4593</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -34170,17 +34282,17 @@
       <c r="G398" t="inlineStr"/>
       <c r="H398" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
@@ -34192,10 +34304,10 @@
         <v>1</v>
       </c>
       <c r="M398" t="n">
-        <v>-58.452473</v>
+        <v>-58.500145</v>
       </c>
       <c r="N398" t="n">
-        <v>-34.598316</v>
+        <v>-34.586507</v>
       </c>
       <c r="O398" t="inlineStr">
         <is>
@@ -34209,7 +34321,7 @@
       </c>
       <c r="Q398" t="inlineStr">
         <is>
-          <t>VCR-?</t>
+          <t>PUE-K</t>
         </is>
       </c>
       <c r="R398" t="inlineStr">
@@ -34221,7 +34333,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t xml:space="preserve">10030 </t>
+          <t xml:space="preserve">10060 </t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -34231,12 +34343,12 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>SUSINI, ANTONIO, CNEL. 2190</t>
+          <t xml:space="preserve">AREVALO 2951 </t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -34249,15 +34361,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G399" t="inlineStr"/>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>814108282</t>
+        </is>
+      </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>DESMONTAR POSTE Y VER POSIBILIDAD DE COLOCAR COLUMNA</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
@@ -34274,24 +34390,24 @@
         <v>1</v>
       </c>
       <c r="M399" t="n">
-        <v>-58.452997</v>
+        <v>-58.430757</v>
       </c>
       <c r="N399" t="n">
-        <v>-34.597674</v>
+        <v>-34.571657</v>
       </c>
       <c r="O399" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P399" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q399" t="inlineStr">
         <is>
-          <t>VCR-?</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R399" t="inlineStr">
@@ -34303,7 +34419,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t xml:space="preserve">9053 </t>
+          <t xml:space="preserve">10069 </t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -34313,7 +34429,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>FRAGA 1848</t>
+          <t xml:space="preserve">CORDOBA AV. 5387 </t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -34334,12 +34450,12 @@
       <c r="G400" t="inlineStr"/>
       <c r="H400" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
@@ -34356,24 +34472,24 @@
         <v>1</v>
       </c>
       <c r="M400" t="n">
-        <v>-58.468977</v>
+        <v>-58.437815</v>
       </c>
       <c r="N400" t="n">
-        <v>-34.582742</v>
+        <v>-34.589036</v>
       </c>
       <c r="O400" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P400" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q400" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>VCR-I</t>
         </is>
       </c>
       <c r="R400" t="inlineStr">
@@ -34385,7 +34501,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t xml:space="preserve">10036 </t>
+          <t xml:space="preserve">10070 </t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -34395,7 +34511,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t xml:space="preserve">COCHRANE 2314 </t>
+          <t>NUÑEZ 4634</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -34413,15 +34529,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G401" t="inlineStr"/>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>814108373</t>
+        </is>
+      </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
@@ -34438,14 +34558,14 @@
         <v>1</v>
       </c>
       <c r="M401" t="n">
-        <v>-58.501425</v>
+        <v>-58.487462</v>
       </c>
       <c r="N401" t="n">
-        <v>-34.575827</v>
+        <v>-34.561007</v>
       </c>
       <c r="O401" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P401" t="inlineStr">
@@ -34455,7 +34575,7 @@
       </c>
       <c r="Q401" t="inlineStr">
         <is>
-          <t>PUE-I</t>
+          <t>PUE-F</t>
         </is>
       </c>
       <c r="R401" t="inlineStr">
@@ -34467,7 +34587,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>S00527817</t>
+          <t xml:space="preserve">10079 </t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -34477,7 +34597,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>TINOGASTA 2561</t>
+          <t>VILLARROEL 1035</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -34498,12 +34618,12 @@
       <c r="G402" t="inlineStr"/>
       <c r="H402" t="inlineStr">
         <is>
-          <t>DESMONTAR POSTE</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
@@ -34520,24 +34640,24 @@
         <v>1</v>
       </c>
       <c r="M402" t="n">
-        <v>-58.487709</v>
+        <v>-58.442939</v>
       </c>
       <c r="N402" t="n">
-        <v>-34.595778</v>
+        <v>-34.594741</v>
       </c>
       <c r="O402" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P402" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q402" t="inlineStr">
         <is>
-          <t>PUE-A</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R402" t="inlineStr">
@@ -34549,7 +34669,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t xml:space="preserve">10049 </t>
+          <t xml:space="preserve">10080 </t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -34559,7 +34679,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>HEREDIA 1295</t>
+          <t>THAMES 549</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -34602,24 +34722,24 @@
         <v>1</v>
       </c>
       <c r="M403" t="n">
-        <v>-58.463173</v>
+        <v>-58.442534</v>
       </c>
       <c r="N403" t="n">
-        <v>-34.57859</v>
+        <v>-34.59499</v>
       </c>
       <c r="O403" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P403" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q403" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R403" t="inlineStr">
@@ -34631,7 +34751,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t xml:space="preserve">10053 </t>
+          <t xml:space="preserve">10081 </t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -34641,12 +34761,12 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>ARGERICH 4784</t>
+          <t xml:space="preserve">CORRIENTES AV. 5697 </t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -34667,7 +34787,7 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
@@ -34684,24 +34804,24 @@
         <v>1</v>
       </c>
       <c r="M404" t="n">
-        <v>-58.504104</v>
+        <v>-58.443323</v>
       </c>
       <c r="N404" t="n">
-        <v>-34.586449</v>
+        <v>-34.595549</v>
       </c>
       <c r="O404" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P404" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q404" t="inlineStr">
         <is>
-          <t>PUE-N</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R404" t="inlineStr">
@@ -34713,17 +34833,17 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t xml:space="preserve">10057 </t>
+          <t xml:space="preserve">10084 </t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>5/7/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>TERRADA 4593</t>
+          <t>UGARTE, MANUEL 3258</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -34741,7 +34861,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G405" t="inlineStr"/>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>814108396</t>
+        </is>
+      </c>
       <c r="H405" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -34766,14 +34890,14 @@
         <v>1</v>
       </c>
       <c r="M405" t="n">
-        <v>-58.500145</v>
+        <v>-58.470323</v>
       </c>
       <c r="N405" t="n">
-        <v>-34.586507</v>
+        <v>-34.560769</v>
       </c>
       <c r="O405" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P405" t="inlineStr">
@@ -34783,7 +34907,7 @@
       </c>
       <c r="Q405" t="inlineStr">
         <is>
-          <t>PUE-K</t>
+          <t>COG-I</t>
         </is>
       </c>
       <c r="R405" t="inlineStr">
@@ -34795,7 +34919,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t xml:space="preserve">10060 </t>
+          <t xml:space="preserve">10087 </t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -34805,12 +34929,12 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t xml:space="preserve">AREVALO 2951 </t>
+          <t>CASTILLO 40</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -34823,10 +34947,14 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G406" t="inlineStr"/>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>814108420</t>
+        </is>
+      </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>DESMONTAR POSTE Y VER POSIBILIDAD DE COLOCAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -34848,10 +34976,10 @@
         <v>1</v>
       </c>
       <c r="M406" t="n">
-        <v>-58.430757</v>
+        <v>-58.430621</v>
       </c>
       <c r="N406" t="n">
-        <v>-34.571657</v>
+        <v>-34.599429</v>
       </c>
       <c r="O406" t="inlineStr">
         <is>
@@ -34865,7 +34993,7 @@
       </c>
       <c r="Q406" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R406" t="inlineStr">
@@ -34877,7 +35005,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t xml:space="preserve">10069 </t>
+          <t xml:space="preserve">10102 </t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -34887,7 +35015,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORDOBA AV. 5387 </t>
+          <t>ELCANO AV. 3950</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -34905,7 +35033,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G407" t="inlineStr"/>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>814108464</t>
+        </is>
+      </c>
       <c r="H407" t="inlineStr">
         <is>
           <t>COLUMNA INCLINADA</t>
@@ -34913,7 +35045,7 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
@@ -34930,24 +35062,24 @@
         <v>1</v>
       </c>
       <c r="M407" t="n">
-        <v>-58.437815</v>
+        <v>-58.460457</v>
       </c>
       <c r="N407" t="n">
-        <v>-34.589036</v>
+        <v>-34.582381</v>
       </c>
       <c r="O407" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P407" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q407" t="inlineStr">
         <is>
-          <t>VCR-I</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R407" t="inlineStr">
@@ -34959,7 +35091,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t xml:space="preserve">10070 </t>
+          <t xml:space="preserve">10113 </t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -34969,7 +35101,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>NUÑEZ 4634</t>
+          <t>CONCORDIA 4213</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -34990,12 +35122,12 @@
       <c r="G408" t="inlineStr"/>
       <c r="H408" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
@@ -35012,14 +35144,14 @@
         <v>1</v>
       </c>
       <c r="M408" t="n">
-        <v>-58.487462</v>
+        <v>-58.506878</v>
       </c>
       <c r="N408" t="n">
-        <v>-34.561007</v>
+        <v>-34.59474</v>
       </c>
       <c r="O408" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P408" t="inlineStr">
@@ -35029,7 +35161,7 @@
       </c>
       <c r="Q408" t="inlineStr">
         <is>
-          <t>PUE-F</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R408" t="inlineStr">
@@ -35041,7 +35173,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t xml:space="preserve">10079 </t>
+          <t xml:space="preserve">10119 </t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -35051,12 +35183,12 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>VILLARROEL 1035</t>
+          <t>TRIUNVIRATO AV. 5900</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -35087,31 +35219,31 @@
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L409" t="n">
         <v>1</v>
       </c>
       <c r="M409" t="n">
-        <v>-58.442939</v>
+        <v>-58.496593</v>
       </c>
       <c r="N409" t="n">
-        <v>-34.594741</v>
+        <v>-34.563646</v>
       </c>
       <c r="O409" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P409" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q409" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>PUE-F</t>
         </is>
       </c>
       <c r="R409" t="inlineStr">
@@ -35123,7 +35255,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t xml:space="preserve">10080 </t>
+          <t xml:space="preserve">10126 </t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -35133,12 +35265,12 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>THAMES 549</t>
+          <t xml:space="preserve">ROOSEVELT FRANKLIN D. 4647 </t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -35154,12 +35286,12 @@
       <c r="G410" t="inlineStr"/>
       <c r="H410" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>DESMONTAR POSTE</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
@@ -35176,24 +35308,24 @@
         <v>1</v>
       </c>
       <c r="M410" t="n">
-        <v>-58.442534</v>
+        <v>-58.482122</v>
       </c>
       <c r="N410" t="n">
-        <v>-34.59499</v>
+        <v>-34.570386</v>
       </c>
       <c r="O410" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P410" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q410" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>ATH-E</t>
         </is>
       </c>
       <c r="R410" t="inlineStr">
@@ -35205,7 +35337,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t xml:space="preserve">10081 </t>
+          <t xml:space="preserve">10133 </t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -35215,12 +35347,12 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORRIENTES AV. 5697 </t>
+          <t xml:space="preserve">BATALLA DEL PARI 593 </t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -35233,7 +35365,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G411" t="inlineStr"/>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>814108490</t>
+        </is>
+      </c>
       <c r="H411" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -35241,7 +35377,7 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
@@ -35258,24 +35394,24 @@
         <v>1</v>
       </c>
       <c r="M411" t="n">
-        <v>-58.443323</v>
+        <v>-58.453426</v>
       </c>
       <c r="N411" t="n">
-        <v>-34.595549</v>
+        <v>-34.600121</v>
       </c>
       <c r="O411" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P411" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q411" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>VCR-?</t>
         </is>
       </c>
       <c r="R411" t="inlineStr">
@@ -35287,7 +35423,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t xml:space="preserve">10084 </t>
+          <t xml:space="preserve">10136 </t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -35297,12 +35433,12 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>UGARTE, MANUEL 3258</t>
+          <t>REPETTO, NICOLAS, DR. 2118</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -35315,7 +35451,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G412" t="inlineStr"/>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>814108495</t>
+        </is>
+      </c>
       <c r="H412" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -35340,14 +35480,14 @@
         <v>1</v>
       </c>
       <c r="M412" t="n">
-        <v>-58.470323</v>
+        <v>-58.456381</v>
       </c>
       <c r="N412" t="n">
-        <v>-34.560769</v>
+        <v>-34.60076</v>
       </c>
       <c r="O412" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P412" t="inlineStr">
@@ -35357,7 +35497,7 @@
       </c>
       <c r="Q412" t="inlineStr">
         <is>
-          <t>COG-I</t>
+          <t>NRA-G</t>
         </is>
       </c>
       <c r="R412" t="inlineStr">
@@ -35369,7 +35509,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t xml:space="preserve">10087 </t>
+          <t xml:space="preserve">10145 </t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -35379,12 +35519,12 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>CASTILLO 40</t>
+          <t>DONADO 2554</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -35397,7 +35537,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G413" t="inlineStr"/>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>814108500</t>
+        </is>
+      </c>
       <c r="H413" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -35422,24 +35566,24 @@
         <v>1</v>
       </c>
       <c r="M413" t="n">
-        <v>-58.430621</v>
+        <v>-58.478634</v>
       </c>
       <c r="N413" t="n">
-        <v>-34.599429</v>
+        <v>-34.569063</v>
       </c>
       <c r="O413" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>ATH-J</t>
         </is>
       </c>
       <c r="R413" t="inlineStr">
@@ -35451,7 +35595,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t xml:space="preserve">10102 </t>
+          <t xml:space="preserve">10147 </t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -35461,12 +35605,12 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>ELCANO AV. 3950</t>
+          <t>ROOSEVELT FRANKLIN D. 4336</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -35487,7 +35631,7 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
@@ -35497,17 +35641,17 @@
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L414" t="n">
         <v>1</v>
       </c>
       <c r="M414" t="n">
-        <v>-58.460457</v>
+        <v>-58.479316</v>
       </c>
       <c r="N414" t="n">
-        <v>-34.582381</v>
+        <v>-34.568762</v>
       </c>
       <c r="O414" t="inlineStr">
         <is>
@@ -35521,7 +35665,7 @@
       </c>
       <c r="Q414" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>ATH-J</t>
         </is>
       </c>
       <c r="R414" t="inlineStr">
@@ -35533,7 +35677,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t xml:space="preserve">10113 </t>
+          <t xml:space="preserve">10148 </t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -35543,7 +35687,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>CONCORDIA 4213</t>
+          <t>ACHA, MARIANO, GRAL. 2595</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -35561,15 +35705,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G415" t="inlineStr"/>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>814108503</t>
+        </is>
+      </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
@@ -35586,14 +35734,14 @@
         <v>1</v>
       </c>
       <c r="M415" t="n">
-        <v>-58.506878</v>
+        <v>-58.479759</v>
       </c>
       <c r="N415" t="n">
-        <v>-34.59474</v>
+        <v>-34.569184</v>
       </c>
       <c r="O415" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P415" t="inlineStr">
@@ -35603,584 +35751,10 @@
       </c>
       <c r="Q415" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>ATH-J</t>
         </is>
       </c>
       <c r="R415" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10119 </t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>TRIUNVIRATO AV. 5900</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F416" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G416" t="inlineStr"/>
-      <c r="H416" t="inlineStr">
-        <is>
-          <t>COLUMNA INCLINADA</t>
-        </is>
-      </c>
-      <c r="I416" t="inlineStr">
-        <is>
-          <t>Aplomo</t>
-        </is>
-      </c>
-      <c r="J416" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K416" t="inlineStr">
-        <is>
-          <t>Terminal</t>
-        </is>
-      </c>
-      <c r="L416" t="n">
-        <v>1</v>
-      </c>
-      <c r="M416" t="n">
-        <v>-58.496593</v>
-      </c>
-      <c r="N416" t="n">
-        <v>-34.563646</v>
-      </c>
-      <c r="O416" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="P416" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q416" t="inlineStr">
-        <is>
-          <t>PUE-F</t>
-        </is>
-      </c>
-      <c r="R416" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10126 </t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ROOSEVELT FRANKLIN D. 4647 </t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F417" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G417" t="inlineStr"/>
-      <c r="H417" t="inlineStr">
-        <is>
-          <t>DESMONTAR POSTE</t>
-        </is>
-      </c>
-      <c r="I417" t="inlineStr">
-        <is>
-          <t>Desmonte</t>
-        </is>
-      </c>
-      <c r="J417" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K417" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L417" t="n">
-        <v>1</v>
-      </c>
-      <c r="M417" t="n">
-        <v>-58.482122</v>
-      </c>
-      <c r="N417" t="n">
-        <v>-34.570386</v>
-      </c>
-      <c r="O417" t="inlineStr">
-        <is>
-          <t>Colegiales</t>
-        </is>
-      </c>
-      <c r="P417" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q417" t="inlineStr">
-        <is>
-          <t>ATH-E</t>
-        </is>
-      </c>
-      <c r="R417" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10133 </t>
-        </is>
-      </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BATALLA DEL PARI 593 </t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F418" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G418" t="inlineStr"/>
-      <c r="H418" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I418" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J418" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K418" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L418" t="n">
-        <v>1</v>
-      </c>
-      <c r="M418" t="n">
-        <v>-58.453426</v>
-      </c>
-      <c r="N418" t="n">
-        <v>-34.600121</v>
-      </c>
-      <c r="O418" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="P418" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q418" t="inlineStr">
-        <is>
-          <t>VCR-?</t>
-        </is>
-      </c>
-      <c r="R418" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10136 </t>
-        </is>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>REPETTO, NICOLAS, DR. 2118</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E419" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G419" t="inlineStr"/>
-      <c r="H419" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I419" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J419" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K419" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L419" t="n">
-        <v>1</v>
-      </c>
-      <c r="M419" t="n">
-        <v>-58.456381</v>
-      </c>
-      <c r="N419" t="n">
-        <v>-34.60076</v>
-      </c>
-      <c r="O419" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="P419" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q419" t="inlineStr">
-        <is>
-          <t>NRA-G</t>
-        </is>
-      </c>
-      <c r="R419" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10145 </t>
-        </is>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>DONADO 2554</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F420" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G420" t="inlineStr"/>
-      <c r="H420" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I420" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J420" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K420" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L420" t="n">
-        <v>1</v>
-      </c>
-      <c r="M420" t="n">
-        <v>-58.478634</v>
-      </c>
-      <c r="N420" t="n">
-        <v>-34.569063</v>
-      </c>
-      <c r="O420" t="inlineStr">
-        <is>
-          <t>Colegiales</t>
-        </is>
-      </c>
-      <c r="P420" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q420" t="inlineStr">
-        <is>
-          <t>ATH-J</t>
-        </is>
-      </c>
-      <c r="R420" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10147 </t>
-        </is>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>ROOSEVELT FRANKLIN D. 4336</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E421" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F421" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G421" t="inlineStr"/>
-      <c r="H421" t="inlineStr">
-        <is>
-          <t>COLUMNA INCLINADA</t>
-        </is>
-      </c>
-      <c r="I421" t="inlineStr">
-        <is>
-          <t>Aplomo</t>
-        </is>
-      </c>
-      <c r="J421" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K421" t="inlineStr">
-        <is>
-          <t>Terminal</t>
-        </is>
-      </c>
-      <c r="L421" t="n">
-        <v>1</v>
-      </c>
-      <c r="M421" t="n">
-        <v>-58.479316</v>
-      </c>
-      <c r="N421" t="n">
-        <v>-34.568762</v>
-      </c>
-      <c r="O421" t="inlineStr">
-        <is>
-          <t>Colegiales</t>
-        </is>
-      </c>
-      <c r="P421" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q421" t="inlineStr">
-        <is>
-          <t>ATH-J</t>
-        </is>
-      </c>
-      <c r="R421" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10148 </t>
-        </is>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>ACHA, MARIANO, GRAL. 2595</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E422" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F422" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G422" t="inlineStr"/>
-      <c r="H422" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I422" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J422" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K422" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L422" t="n">
-        <v>1</v>
-      </c>
-      <c r="M422" t="n">
-        <v>-58.479759</v>
-      </c>
-      <c r="N422" t="n">
-        <v>-34.569184</v>
-      </c>
-      <c r="O422" t="inlineStr">
-        <is>
-          <t>Colegiales</t>
-        </is>
-      </c>
-      <c r="P422" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q422" t="inlineStr">
-        <is>
-          <t>ATH-J</t>
-        </is>
-      </c>
-      <c r="R422" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_NEW.xlsx
+++ b/mapa_interactivo_NEW.xlsx
@@ -29007,7 +29007,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G334" t="inlineStr"/>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>814109727</t>
+        </is>
+      </c>
       <c r="H334" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -29171,7 +29175,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G336" t="inlineStr"/>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>814109768</t>
+        </is>
+      </c>
       <c r="H336" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -31057,7 +31065,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G359" t="inlineStr"/>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>814109792</t>
+        </is>
+      </c>
       <c r="H359" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -31221,7 +31233,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G361" t="inlineStr"/>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>814109807</t>
+        </is>
+      </c>
       <c r="H361" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -32287,7 +32303,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G374" t="inlineStr"/>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>814109811</t>
+        </is>
+      </c>
       <c r="H374" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -32369,7 +32389,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G375" t="inlineStr"/>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>814109827</t>
+        </is>
+      </c>
       <c r="H375" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -32451,7 +32475,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G376" t="inlineStr"/>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>814109832</t>
+        </is>
+      </c>
       <c r="H376" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -34279,7 +34307,11 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="G398" t="inlineStr"/>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>814109844</t>
+        </is>
+      </c>
       <c r="H398" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>

--- a/mapa_interactivo_NEW.xlsx
+++ b/mapa_interactivo_NEW.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R373"/>
+  <dimension ref="A1:R371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27537,7 +27537,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t xml:space="preserve">9957 </t>
+          <t xml:space="preserve">9960 </t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -27547,7 +27547,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>JURAMENTO 5347</t>
+          <t>BUCARELLI 1995</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -27560,11 +27560,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>814111217</t>
-        </is>
-      </c>
+      <c r="F317" t="inlineStr"/>
       <c r="G317" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -27572,7 +27568,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -27582,7 +27578,7 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -27594,10 +27590,10 @@
         <v>1</v>
       </c>
       <c r="M317" t="n">
-        <v>-58.485468</v>
+        <v>-58.484744</v>
       </c>
       <c r="N317" t="n">
-        <v>-34.579765</v>
+        <v>-34.579576</v>
       </c>
       <c r="O317" t="inlineStr">
         <is>
@@ -27623,7 +27619,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t xml:space="preserve">9960 </t>
+          <t xml:space="preserve">9963 </t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -27633,7 +27629,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>BUCARELLI 1995</t>
+          <t xml:space="preserve">BARZANA 1814 </t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -27646,7 +27642,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F318" t="inlineStr"/>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>814111225</t>
+        </is>
+      </c>
       <c r="G318" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -27654,7 +27654,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
@@ -27676,10 +27676,10 @@
         <v>1</v>
       </c>
       <c r="M318" t="n">
-        <v>-58.484744</v>
+        <v>-58.485279</v>
       </c>
       <c r="N318" t="n">
-        <v>-34.579576</v>
+        <v>-34.582509</v>
       </c>
       <c r="O318" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
       </c>
       <c r="Q318" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -27705,7 +27705,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t xml:space="preserve">9961 </t>
+          <t xml:space="preserve">9964 </t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -27715,12 +27715,12 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>JURAMENTO 5261</t>
+          <t>BARZANA 1844</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -27730,7 +27730,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>814111218</t>
+          <t>814111227</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -27762,10 +27762,10 @@
         <v>1</v>
       </c>
       <c r="M319" t="n">
-        <v>-58.484396</v>
+        <v>-58.485434</v>
       </c>
       <c r="N319" t="n">
-        <v>-34.579179</v>
+        <v>-34.582311</v>
       </c>
       <c r="O319" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
       </c>
       <c r="Q319" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -27791,7 +27791,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t xml:space="preserve">9963 </t>
+          <t xml:space="preserve">9965 </t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -27801,7 +27801,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARZANA 1814 </t>
+          <t>ALTOLAGUIRRE 1813</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -27816,7 +27816,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>814111225</t>
+          <t>814111230</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -27848,10 +27848,10 @@
         <v>1</v>
       </c>
       <c r="M320" t="n">
-        <v>-58.485279</v>
+        <v>-58.486073</v>
       </c>
       <c r="N320" t="n">
-        <v>-34.582509</v>
+        <v>-34.582965</v>
       </c>
       <c r="O320" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t xml:space="preserve">9964 </t>
+          <t xml:space="preserve">9966 </t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -27887,7 +27887,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>BARZANA 1844</t>
+          <t>BURELA 1845</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -27902,7 +27902,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>814111227</t>
+          <t>814109792</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -27912,7 +27912,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -27934,10 +27934,10 @@
         <v>1</v>
       </c>
       <c r="M321" t="n">
-        <v>-58.485434</v>
+        <v>-58.487319</v>
       </c>
       <c r="N321" t="n">
-        <v>-34.582311</v>
+        <v>-34.583364</v>
       </c>
       <c r="O321" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
       </c>
       <c r="Q321" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>PUE-K</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
@@ -27963,7 +27963,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t xml:space="preserve">9965 </t>
+          <t xml:space="preserve">9967 </t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -27973,7 +27973,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>ALTOLAGUIRRE 1813</t>
+          <t>CERETTI 1850</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -27988,7 +27988,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>814111230</t>
+          <t>814111327</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -28020,10 +28020,10 @@
         <v>1</v>
       </c>
       <c r="M322" t="n">
-        <v>-58.486073</v>
+        <v>-58.488493</v>
       </c>
       <c r="N322" t="n">
-        <v>-34.582965</v>
+        <v>-34.583983</v>
       </c>
       <c r="O322" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
       </c>
       <c r="Q322" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>PUE-K</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
@@ -28049,7 +28049,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t xml:space="preserve">9966 </t>
+          <t xml:space="preserve">9969 </t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -28059,12 +28059,12 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>BURELA 1845</t>
+          <t>MONTAÑESES 1910</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -28074,7 +28074,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>814109792</t>
+          <t>814109807</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -28106,14 +28106,14 @@
         <v>1</v>
       </c>
       <c r="M323" t="n">
-        <v>-58.487319</v>
+        <v>-58.447489</v>
       </c>
       <c r="N323" t="n">
-        <v>-34.583364</v>
+        <v>-34.559091</v>
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P323" t="inlineStr">
@@ -28123,7 +28123,7 @@
       </c>
       <c r="Q323" t="inlineStr">
         <is>
-          <t>PUE-K</t>
+          <t>BLO-A</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -28135,7 +28135,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t xml:space="preserve">9967 </t>
+          <t xml:space="preserve">9970 </t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -28145,7 +28145,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>CERETTI 1850</t>
+          <t>ECHEVERRIA 5051</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -28160,7 +28160,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>814111327</t>
+          <t>814111395</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -28192,10 +28192,10 @@
         <v>1</v>
       </c>
       <c r="M324" t="n">
-        <v>-58.488493</v>
+        <v>-58.481099</v>
       </c>
       <c r="N324" t="n">
-        <v>-34.583983</v>
+        <v>-34.578912</v>
       </c>
       <c r="O324" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
       </c>
       <c r="Q324" t="inlineStr">
         <is>
-          <t>PUE-K</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -28221,7 +28221,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t xml:space="preserve">9969 </t>
+          <t xml:space="preserve">9971 </t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -28231,12 +28231,12 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>MONTAÑESES 1910</t>
+          <t>ECHEVERRIA 5021</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -28246,7 +28246,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>814109807</t>
+          <t>814111401</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -28256,7 +28256,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -28278,14 +28278,14 @@
         <v>1</v>
       </c>
       <c r="M325" t="n">
-        <v>-58.447489</v>
+        <v>-58.480634</v>
       </c>
       <c r="N325" t="n">
-        <v>-34.559091</v>
+        <v>-34.578647</v>
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P325" t="inlineStr">
@@ -28295,7 +28295,7 @@
       </c>
       <c r="Q325" t="inlineStr">
         <is>
-          <t>BLO-A</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
@@ -28307,7 +28307,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t xml:space="preserve">9970 </t>
+          <t xml:space="preserve">9993 </t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -28317,7 +28317,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>ECHEVERRIA 5051</t>
+          <t>MONROE 5212</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -28332,7 +28332,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>814111395</t>
+          <t>814111591</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -28364,10 +28364,10 @@
         <v>1</v>
       </c>
       <c r="M326" t="n">
-        <v>-58.481099</v>
+        <v>-58.487529</v>
       </c>
       <c r="N326" t="n">
-        <v>-34.578912</v>
+        <v>-34.575028</v>
       </c>
       <c r="O326" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
       </c>
       <c r="Q326" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>ATH-C</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -28393,7 +28393,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t xml:space="preserve">9971 </t>
+          <t xml:space="preserve">9996 </t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -28403,7 +28403,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>ECHEVERRIA 5021</t>
+          <t>ZAMUDIO 4784</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -28418,7 +28418,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>814111401</t>
+          <t>814111621</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -28450,10 +28450,10 @@
         <v>1</v>
       </c>
       <c r="M327" t="n">
-        <v>-58.480634</v>
+        <v>-58.497199</v>
       </c>
       <c r="N327" t="n">
-        <v>-34.578647</v>
+        <v>-34.582097</v>
       </c>
       <c r="O327" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
       </c>
       <c r="Q327" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>PUE-M</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -28479,22 +28479,22 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t xml:space="preserve">9993 </t>
+          <t xml:space="preserve">8804 </t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>MONROE 5212</t>
+          <t>LOPEZ MERINO, FRANCISCO 3988</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>814111591</t>
+          <t>814108011</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -28514,7 +28514,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -28536,10 +28536,10 @@
         <v>1</v>
       </c>
       <c r="M328" t="n">
-        <v>-58.487529</v>
+        <v>-58.493486</v>
       </c>
       <c r="N328" t="n">
-        <v>-34.575028</v>
+        <v>-34.589105</v>
       </c>
       <c r="O328" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
       </c>
       <c r="Q328" t="inlineStr">
         <is>
-          <t>ATH-C</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -28565,17 +28565,17 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t xml:space="preserve">9996 </t>
+          <t xml:space="preserve">8962 </t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>ZAMUDIO 4784</t>
+          <t>CONGRESO AV. 5856</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -28590,7 +28590,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>814111621</t>
+          <t>814108043</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -28600,7 +28600,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -28622,10 +28622,10 @@
         <v>1</v>
       </c>
       <c r="M329" t="n">
-        <v>-58.497199</v>
+        <v>-58.499051</v>
       </c>
       <c r="N329" t="n">
-        <v>-34.582097</v>
+        <v>-34.57451</v>
       </c>
       <c r="O329" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
       </c>
       <c r="Q329" t="inlineStr">
         <is>
-          <t>PUE-M</t>
+          <t>PUE-I</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -28651,7 +28651,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t xml:space="preserve">8804 </t>
+          <t xml:space="preserve">8982 </t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -28661,12 +28661,12 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>LOPEZ MERINO, FRANCISCO 3988</t>
+          <t>LOPEZ, CARLOS ANTONIO 2197</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -28676,7 +28676,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>814108011</t>
+          <t>814108057</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -28708,10 +28708,10 @@
         <v>1</v>
       </c>
       <c r="M330" t="n">
-        <v>-58.493486</v>
+        <v>-58.494928</v>
       </c>
       <c r="N330" t="n">
-        <v>-34.589105</v>
+        <v>-34.580378</v>
       </c>
       <c r="O330" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
       </c>
       <c r="Q330" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>PUE-M</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
@@ -28737,7 +28737,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t xml:space="preserve">8962 </t>
+          <t xml:space="preserve">10024 </t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -28747,7 +28747,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>CONGRESO AV. 5856</t>
+          <t>IBERA 6146</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -28762,7 +28762,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>814108043</t>
+          <t>814111657</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -28772,7 +28772,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -28794,10 +28794,10 @@
         <v>1</v>
       </c>
       <c r="M331" t="n">
-        <v>-58.499051</v>
+        <v>-58.502338</v>
       </c>
       <c r="N331" t="n">
-        <v>-34.57451</v>
+        <v>-34.573275</v>
       </c>
       <c r="O331" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t xml:space="preserve">8982 </t>
+          <t xml:space="preserve">10025 </t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -28833,12 +28833,12 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>LOPEZ, CARLOS ANTONIO 2197</t>
+          <t>JUSTO, JUAN B. AV. 3073</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -28848,7 +28848,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>814108057</t>
+          <t>814111671</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -28858,7 +28858,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -28880,10 +28880,10 @@
         <v>1</v>
       </c>
       <c r="M332" t="n">
-        <v>-58.494928</v>
+        <v>-58.449604</v>
       </c>
       <c r="N332" t="n">
-        <v>-34.580378</v>
+        <v>-34.598286</v>
       </c>
       <c r="O332" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
       </c>
       <c r="Q332" t="inlineStr">
         <is>
-          <t>PUE-M</t>
+          <t>VCR-?</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
@@ -28909,7 +28909,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t xml:space="preserve">10024 </t>
+          <t xml:space="preserve">10026 </t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -28919,7 +28919,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>IBERA 6146</t>
+          <t>HUMBOLDT 47</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -28934,7 +28934,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>814111657</t>
+          <t>814111684</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -28966,10 +28966,10 @@
         <v>1</v>
       </c>
       <c r="M333" t="n">
-        <v>-58.502338</v>
+        <v>-58.451981</v>
       </c>
       <c r="N333" t="n">
-        <v>-34.573275</v>
+        <v>-34.597952</v>
       </c>
       <c r="O333" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
       </c>
       <c r="Q333" t="inlineStr">
         <is>
-          <t>PUE-I</t>
+          <t>VCR-?</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
@@ -28995,22 +28995,22 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t xml:space="preserve">10025 </t>
+          <t xml:space="preserve">10027 </t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>5/7/2026</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>JUSTO, JUAN B. AV. 3073</t>
+          <t>HUMBOLDT 37</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -29020,7 +29020,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>814111671</t>
+          <t>814111686</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -29052,10 +29052,10 @@
         <v>1</v>
       </c>
       <c r="M334" t="n">
-        <v>-58.449604</v>
+        <v>-58.452157</v>
       </c>
       <c r="N334" t="n">
-        <v>-34.598286</v>
+        <v>-34.598081</v>
       </c>
       <c r="O334" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t xml:space="preserve">10026 </t>
+          <t xml:space="preserve">10028 </t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -29091,12 +29091,12 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>HUMBOLDT 47</t>
+          <t>HUMBOLDT 23</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -29104,11 +29104,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>814111684</t>
-        </is>
-      </c>
+      <c r="F335" t="inlineStr"/>
       <c r="G335" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -29121,12 +29117,12 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
@@ -29138,10 +29134,10 @@
         <v>1</v>
       </c>
       <c r="M335" t="n">
-        <v>-58.451981</v>
+        <v>-58.452473</v>
       </c>
       <c r="N335" t="n">
-        <v>-34.597952</v>
+        <v>-34.598316</v>
       </c>
       <c r="O335" t="inlineStr">
         <is>
@@ -29167,22 +29163,22 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t xml:space="preserve">10027 </t>
+          <t xml:space="preserve">10030 </t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>5/7/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>HUMBOLDT 37</t>
+          <t>SUSINI, ANTONIO, CNEL. 2190</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -29192,7 +29188,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>814111686</t>
+          <t>814111692</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
@@ -29224,10 +29220,10 @@
         <v>1</v>
       </c>
       <c r="M336" t="n">
-        <v>-58.452157</v>
+        <v>-58.452997</v>
       </c>
       <c r="N336" t="n">
-        <v>-34.598081</v>
+        <v>-34.597674</v>
       </c>
       <c r="O336" t="inlineStr">
         <is>
@@ -29253,7 +29249,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t xml:space="preserve">10028 </t>
+          <t xml:space="preserve">9053 </t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -29263,7 +29259,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>HUMBOLDT 23</t>
+          <t>FRAGA 1848</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -29276,7 +29272,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F337" t="inlineStr"/>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>814108072</t>
+        </is>
+      </c>
       <c r="G337" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -29284,17 +29284,17 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
@@ -29306,14 +29306,14 @@
         <v>1</v>
       </c>
       <c r="M337" t="n">
-        <v>-58.452473</v>
+        <v>-58.468977</v>
       </c>
       <c r="N337" t="n">
-        <v>-34.598316</v>
+        <v>-34.582742</v>
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P337" t="inlineStr">
@@ -29323,7 +29323,7 @@
       </c>
       <c r="Q337" t="inlineStr">
         <is>
-          <t>VCR-?</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
@@ -29335,7 +29335,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t xml:space="preserve">10030 </t>
+          <t>S00527817</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -29345,7 +29345,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>SUSINI, ANTONIO, CNEL. 2190</t>
+          <t>TINOGASTA 2561</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -29358,11 +29358,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>814111692</t>
-        </is>
-      </c>
+      <c r="F338" t="inlineStr"/>
       <c r="G338" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -29370,12 +29366,12 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>DESMONTAR POSTE</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
@@ -29392,10 +29388,10 @@
         <v>1</v>
       </c>
       <c r="M338" t="n">
-        <v>-58.452997</v>
+        <v>-58.487709</v>
       </c>
       <c r="N338" t="n">
-        <v>-34.597674</v>
+        <v>-34.595778</v>
       </c>
       <c r="O338" t="inlineStr">
         <is>
@@ -29409,7 +29405,7 @@
       </c>
       <c r="Q338" t="inlineStr">
         <is>
-          <t>VCR-?</t>
+          <t>PUE-A</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
@@ -29421,7 +29417,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t xml:space="preserve">9053 </t>
+          <t xml:space="preserve">10049 </t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -29431,7 +29427,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>FRAGA 1848</t>
+          <t>HEREDIA 1295</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -29446,7 +29442,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>814108072</t>
+          <t>814111714</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -29456,7 +29452,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -29478,10 +29474,10 @@
         <v>1</v>
       </c>
       <c r="M339" t="n">
-        <v>-58.468977</v>
+        <v>-58.463173</v>
       </c>
       <c r="N339" t="n">
-        <v>-34.582742</v>
+        <v>-34.57859</v>
       </c>
       <c r="O339" t="inlineStr">
         <is>
@@ -29495,7 +29491,7 @@
       </c>
       <c r="Q339" t="inlineStr">
         <is>
-          <t>ATH-F</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R339" t="inlineStr">
@@ -29507,22 +29503,22 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>S00527817</t>
+          <t xml:space="preserve">10057 </t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>5/7/2026</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>TINOGASTA 2561</t>
+          <t>TERRADA 4593</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -29530,7 +29526,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F340" t="inlineStr"/>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>814109844</t>
+        </is>
+      </c>
       <c r="G340" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -29538,12 +29538,12 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>DESMONTAR POSTE</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
@@ -29560,10 +29560,10 @@
         <v>1</v>
       </c>
       <c r="M340" t="n">
-        <v>-58.487709</v>
+        <v>-58.500145</v>
       </c>
       <c r="N340" t="n">
-        <v>-34.595778</v>
+        <v>-34.586507</v>
       </c>
       <c r="O340" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
       </c>
       <c r="Q340" t="inlineStr">
         <is>
-          <t>PUE-A</t>
+          <t>PUE-K</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
@@ -29589,7 +29589,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t xml:space="preserve">10049 </t>
+          <t xml:space="preserve">10060 </t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -29599,12 +29599,12 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>HEREDIA 1295</t>
+          <t xml:space="preserve">AREVALO 2951 </t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -29614,7 +29614,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>814111714</t>
+          <t>814108282</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>DESMONTAR POSTE Y VER POSIBILIDAD DE COLOCAR COLUMNA</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -29646,24 +29646,24 @@
         <v>1</v>
       </c>
       <c r="M341" t="n">
-        <v>-58.463173</v>
+        <v>-58.430757</v>
       </c>
       <c r="N341" t="n">
-        <v>-34.57859</v>
+        <v>-34.571657</v>
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P341" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q341" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
@@ -29675,22 +29675,22 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t xml:space="preserve">10057 </t>
+          <t xml:space="preserve">10069 </t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>5/7/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>TERRADA 4593</t>
+          <t xml:space="preserve">CORDOBA AV. 5387 </t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -29700,7 +29700,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>814109844</t>
+          <t>814111735</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -29710,7 +29710,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -29732,24 +29732,24 @@
         <v>1</v>
       </c>
       <c r="M342" t="n">
-        <v>-58.500145</v>
+        <v>-58.437815</v>
       </c>
       <c r="N342" t="n">
-        <v>-34.586507</v>
+        <v>-34.589036</v>
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P342" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q342" t="inlineStr">
         <is>
-          <t>PUE-K</t>
+          <t>VCR-I</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
@@ -29761,7 +29761,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t xml:space="preserve">10060 </t>
+          <t xml:space="preserve">10070 </t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -29771,7 +29771,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t xml:space="preserve">AREVALO 2951 </t>
+          <t>NUÑEZ 4634</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -29786,7 +29786,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>814108282</t>
+          <t>814108373</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -29796,7 +29796,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>DESMONTAR POSTE Y VER POSIBILIDAD DE COLOCAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -29818,24 +29818,24 @@
         <v>1</v>
       </c>
       <c r="M343" t="n">
-        <v>-58.430757</v>
+        <v>-58.487462</v>
       </c>
       <c r="N343" t="n">
-        <v>-34.571657</v>
+        <v>-34.561007</v>
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P343" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q343" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>PUE-F</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
@@ -29847,7 +29847,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t xml:space="preserve">10069 </t>
+          <t xml:space="preserve">10079 </t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -29857,7 +29857,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORDOBA AV. 5387 </t>
+          <t>VILLARROEL 1035</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -29872,7 +29872,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>814111735</t>
+          <t>814111768</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -29904,10 +29904,10 @@
         <v>1</v>
       </c>
       <c r="M344" t="n">
-        <v>-58.437815</v>
+        <v>-58.442939</v>
       </c>
       <c r="N344" t="n">
-        <v>-34.589036</v>
+        <v>-34.594741</v>
       </c>
       <c r="O344" t="inlineStr">
         <is>
@@ -29921,7 +29921,7 @@
       </c>
       <c r="Q344" t="inlineStr">
         <is>
-          <t>VCR-I</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
@@ -29933,7 +29933,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t xml:space="preserve">10070 </t>
+          <t xml:space="preserve">10080 </t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>NUÑEZ 4634</t>
+          <t>THAMES 549</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -29958,7 +29958,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>814108373</t>
+          <t>814111773</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -29968,7 +29968,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -29990,24 +29990,24 @@
         <v>1</v>
       </c>
       <c r="M345" t="n">
-        <v>-58.487462</v>
+        <v>-58.442534</v>
       </c>
       <c r="N345" t="n">
-        <v>-34.561007</v>
+        <v>-34.59499</v>
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P345" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q345" t="inlineStr">
         <is>
-          <t>PUE-F</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
@@ -30019,7 +30019,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t xml:space="preserve">10079 </t>
+          <t xml:space="preserve">10081 </t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -30029,7 +30029,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>VILLARROEL 1035</t>
+          <t xml:space="preserve">CORRIENTES AV. 5697 </t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>814111768</t>
+          <t>814111776</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -30054,7 +30054,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -30076,10 +30076,10 @@
         <v>1</v>
       </c>
       <c r="M346" t="n">
-        <v>-58.442939</v>
+        <v>-58.443323</v>
       </c>
       <c r="N346" t="n">
-        <v>-34.594741</v>
+        <v>-34.595549</v>
       </c>
       <c r="O346" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t xml:space="preserve">10080 </t>
+          <t xml:space="preserve">10084 </t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -30115,12 +30115,12 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>THAMES 549</t>
+          <t>UGARTE, MANUEL 3258</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -30130,7 +30130,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>814111773</t>
+          <t>814108396</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -30140,7 +30140,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -30162,24 +30162,24 @@
         <v>1</v>
       </c>
       <c r="M347" t="n">
-        <v>-58.442534</v>
+        <v>-58.470323</v>
       </c>
       <c r="N347" t="n">
-        <v>-34.59499</v>
+        <v>-34.560769</v>
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P347" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q347" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>COG-I</t>
         </is>
       </c>
       <c r="R347" t="inlineStr">
@@ -30191,7 +30191,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t xml:space="preserve">10081 </t>
+          <t xml:space="preserve">10087 </t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -30201,7 +30201,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORRIENTES AV. 5697 </t>
+          <t>CASTILLO 40</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -30216,7 +30216,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>814111776</t>
+          <t>814108420</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -30248,10 +30248,10 @@
         <v>1</v>
       </c>
       <c r="M348" t="n">
-        <v>-58.443323</v>
+        <v>-58.430621</v>
       </c>
       <c r="N348" t="n">
-        <v>-34.595549</v>
+        <v>-34.599429</v>
       </c>
       <c r="O348" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
       </c>
       <c r="Q348" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R348" t="inlineStr">
@@ -30277,7 +30277,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t xml:space="preserve">10084 </t>
+          <t xml:space="preserve">10102 </t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -30287,12 +30287,12 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>UGARTE, MANUEL 3258</t>
+          <t>ELCANO AV. 3950</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -30302,7 +30302,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>814108396</t>
+          <t>814108464</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -30312,7 +30312,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -30334,10 +30334,10 @@
         <v>1</v>
       </c>
       <c r="M349" t="n">
-        <v>-58.470323</v>
+        <v>-58.460457</v>
       </c>
       <c r="N349" t="n">
-        <v>-34.560769</v>
+        <v>-34.582381</v>
       </c>
       <c r="O349" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
       </c>
       <c r="Q349" t="inlineStr">
         <is>
-          <t>COG-I</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R349" t="inlineStr">
@@ -30363,7 +30363,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t xml:space="preserve">10087 </t>
+          <t xml:space="preserve">10113 </t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -30373,12 +30373,12 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>CASTILLO 40</t>
+          <t>CONCORDIA 4213</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -30388,7 +30388,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>814108420</t>
+          <t>814111798</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
@@ -30398,7 +30398,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -30420,24 +30420,24 @@
         <v>1</v>
       </c>
       <c r="M350" t="n">
-        <v>-58.430621</v>
+        <v>-58.506878</v>
       </c>
       <c r="N350" t="n">
-        <v>-34.599429</v>
+        <v>-34.59474</v>
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P350" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q350" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R350" t="inlineStr">
@@ -30449,7 +30449,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t xml:space="preserve">10102 </t>
+          <t xml:space="preserve">10119 </t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -30459,12 +30459,12 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>ELCANO AV. 3950</t>
+          <t>TRIUNVIRATO AV. 5900</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -30474,7 +30474,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>814108464</t>
+          <t>814111801</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
@@ -30499,21 +30499,21 @@
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L351" t="n">
         <v>1</v>
       </c>
       <c r="M351" t="n">
-        <v>-58.460457</v>
+        <v>-58.496593</v>
       </c>
       <c r="N351" t="n">
-        <v>-34.582381</v>
+        <v>-34.563646</v>
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P351" t="inlineStr">
@@ -30523,7 +30523,7 @@
       </c>
       <c r="Q351" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>PUE-F</t>
         </is>
       </c>
       <c r="R351" t="inlineStr">
@@ -30535,7 +30535,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t xml:space="preserve">10113 </t>
+          <t xml:space="preserve">10126 </t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -30545,7 +30545,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>CONCORDIA 4213</t>
+          <t xml:space="preserve">ROOSEVELT FRANKLIN D. 4647 </t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -30558,11 +30558,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>814111798</t>
-        </is>
-      </c>
+      <c r="F352" t="inlineStr"/>
       <c r="G352" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -30570,12 +30566,12 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>DESMONTAR POSTE</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
@@ -30592,14 +30588,14 @@
         <v>1</v>
       </c>
       <c r="M352" t="n">
-        <v>-58.506878</v>
+        <v>-58.482122</v>
       </c>
       <c r="N352" t="n">
-        <v>-34.59474</v>
+        <v>-34.570386</v>
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P352" t="inlineStr">
@@ -30609,7 +30605,7 @@
       </c>
       <c r="Q352" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>ATH-E</t>
         </is>
       </c>
       <c r="R352" t="inlineStr">
@@ -30621,7 +30617,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t xml:space="preserve">10119 </t>
+          <t xml:space="preserve">10133 </t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -30631,7 +30627,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>TRIUNVIRATO AV. 5900</t>
+          <t xml:space="preserve">BATALLA DEL PARI 593 </t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -30646,7 +30642,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>814111801</t>
+          <t>814108490</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
@@ -30656,7 +30652,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -30671,17 +30667,17 @@
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L353" t="n">
         <v>1</v>
       </c>
       <c r="M353" t="n">
-        <v>-58.496593</v>
+        <v>-58.453426</v>
       </c>
       <c r="N353" t="n">
-        <v>-34.563646</v>
+        <v>-34.600121</v>
       </c>
       <c r="O353" t="inlineStr">
         <is>
@@ -30695,7 +30691,7 @@
       </c>
       <c r="Q353" t="inlineStr">
         <is>
-          <t>PUE-F</t>
+          <t>VCR-?</t>
         </is>
       </c>
       <c r="R353" t="inlineStr">
@@ -30707,7 +30703,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t xml:space="preserve">10126 </t>
+          <t xml:space="preserve">10136 </t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -30717,12 +30713,12 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROOSEVELT FRANKLIN D. 4647 </t>
+          <t>REPETTO, NICOLAS, DR. 2118</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -30730,7 +30726,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F354" t="inlineStr"/>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>814108495</t>
+        </is>
+      </c>
       <c r="G354" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -30738,12 +30738,12 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>DESMONTAR POSTE</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
@@ -30760,14 +30760,14 @@
         <v>1</v>
       </c>
       <c r="M354" t="n">
-        <v>-58.482122</v>
+        <v>-58.456381</v>
       </c>
       <c r="N354" t="n">
-        <v>-34.570386</v>
+        <v>-34.60076</v>
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P354" t="inlineStr">
@@ -30777,7 +30777,7 @@
       </c>
       <c r="Q354" t="inlineStr">
         <is>
-          <t>ATH-E</t>
+          <t>NRA-G</t>
         </is>
       </c>
       <c r="R354" t="inlineStr">
@@ -30789,7 +30789,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t xml:space="preserve">10133 </t>
+          <t xml:space="preserve">10145 </t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -30799,7 +30799,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t xml:space="preserve">BATALLA DEL PARI 593 </t>
+          <t>DONADO 2554</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>814108490</t>
+          <t>814108500</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
@@ -30846,14 +30846,14 @@
         <v>1</v>
       </c>
       <c r="M355" t="n">
-        <v>-58.453426</v>
+        <v>-58.478634</v>
       </c>
       <c r="N355" t="n">
-        <v>-34.600121</v>
+        <v>-34.569063</v>
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P355" t="inlineStr">
@@ -30863,7 +30863,7 @@
       </c>
       <c r="Q355" t="inlineStr">
         <is>
-          <t>VCR-?</t>
+          <t>ATH-J</t>
         </is>
       </c>
       <c r="R355" t="inlineStr">
@@ -30875,7 +30875,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t xml:space="preserve">10136 </t>
+          <t xml:space="preserve">10147 </t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -30885,12 +30885,12 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>REPETTO, NICOLAS, DR. 2118</t>
+          <t>ROOSEVELT FRANKLIN D. 4336</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -30900,7 +30900,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>814108495</t>
+          <t>814111809</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
@@ -30910,7 +30910,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -30925,21 +30925,21 @@
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L356" t="n">
         <v>1</v>
       </c>
       <c r="M356" t="n">
-        <v>-58.456381</v>
+        <v>-58.479316</v>
       </c>
       <c r="N356" t="n">
-        <v>-34.60076</v>
+        <v>-34.568762</v>
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P356" t="inlineStr">
@@ -30949,7 +30949,7 @@
       </c>
       <c r="Q356" t="inlineStr">
         <is>
-          <t>NRA-G</t>
+          <t>ATH-J</t>
         </is>
       </c>
       <c r="R356" t="inlineStr">
@@ -30961,7 +30961,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t xml:space="preserve">10145 </t>
+          <t xml:space="preserve">10148 </t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -30971,7 +30971,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>DONADO 2554</t>
+          <t>ACHA, MARIANO, GRAL. 2595</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -30986,7 +30986,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>814108500</t>
+          <t>814108503</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
@@ -31018,10 +31018,10 @@
         <v>1</v>
       </c>
       <c r="M357" t="n">
-        <v>-58.478634</v>
+        <v>-58.479759</v>
       </c>
       <c r="N357" t="n">
-        <v>-34.569063</v>
+        <v>-34.569184</v>
       </c>
       <c r="O357" t="inlineStr">
         <is>
@@ -31047,22 +31047,22 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t xml:space="preserve">10147 </t>
+          <t>-785</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>6/2/2026</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>ROOSEVELT FRANKLIN D. 4336</t>
+          <t>FOREST AV. 1167</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -31072,7 +31072,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>814111809</t>
+          <t>814125584</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
@@ -31082,7 +31082,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>columna doblada</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -31097,17 +31097,17 @@
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L358" t="n">
         <v>1</v>
       </c>
       <c r="M358" t="n">
-        <v>-58.479316</v>
+        <v>-58.459624</v>
       </c>
       <c r="N358" t="n">
-        <v>-34.568762</v>
+        <v>-34.578831</v>
       </c>
       <c r="O358" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
       </c>
       <c r="Q358" t="inlineStr">
         <is>
-          <t>ATH-J</t>
+          <t>ATH-O</t>
         </is>
       </c>
       <c r="R358" t="inlineStr">
@@ -31133,22 +31133,22 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t xml:space="preserve">10148 </t>
+          <t>-788</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>6/2/2026</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>ACHA, MARIANO, GRAL. 2595</t>
+          <t>AZURDUY JUANA 2004</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -31158,7 +31158,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>814108503</t>
+          <t>814125587</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
@@ -31168,7 +31168,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -31190,14 +31190,14 @@
         <v>1</v>
       </c>
       <c r="M359" t="n">
-        <v>-58.479759</v>
+        <v>-58.463454</v>
       </c>
       <c r="N359" t="n">
-        <v>-34.569184</v>
+        <v>-34.548783</v>
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P359" t="inlineStr">
@@ -31207,7 +31207,7 @@
       </c>
       <c r="Q359" t="inlineStr">
         <is>
-          <t>ATH-J</t>
+          <t>BLO-R</t>
         </is>
       </c>
       <c r="R359" t="inlineStr">
@@ -31219,7 +31219,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>-785</t>
+          <t>-789</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -31229,7 +31229,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>FOREST AV. 1167</t>
+          <t>BALLIVIAN 2749</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -31244,7 +31244,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>814125584</t>
+          <t>814125594</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
@@ -31254,7 +31254,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>columna doblada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -31276,14 +31276,14 @@
         <v>1</v>
       </c>
       <c r="M360" t="n">
-        <v>-58.459624</v>
+        <v>-58.481306</v>
       </c>
       <c r="N360" t="n">
-        <v>-34.578831</v>
+        <v>-34.581055</v>
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P360" t="inlineStr">
@@ -31293,7 +31293,7 @@
       </c>
       <c r="Q360" t="inlineStr">
         <is>
-          <t>ATH-O</t>
+          <t>ATH-D</t>
         </is>
       </c>
       <c r="R360" t="inlineStr">
@@ -31305,7 +31305,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>-788</t>
+          <t>-790</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -31315,12 +31315,12 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>AZURDUY JUANA 2004</t>
+          <t>BAUNESS 2834</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -31330,7 +31330,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>814125587</t>
+          <t>814125602</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
@@ -31362,14 +31362,14 @@
         <v>1</v>
       </c>
       <c r="M361" t="n">
-        <v>-58.463454</v>
+        <v>-58.490491</v>
       </c>
       <c r="N361" t="n">
-        <v>-34.548783</v>
+        <v>-34.571674</v>
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P361" t="inlineStr">
@@ -31379,7 +31379,7 @@
       </c>
       <c r="Q361" t="inlineStr">
         <is>
-          <t>BLO-R</t>
+          <t>PUE-D</t>
         </is>
       </c>
       <c r="R361" t="inlineStr">
@@ -31391,7 +31391,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>-789</t>
+          <t>-791</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -31401,12 +31401,12 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>BALLIVIAN 2749</t>
+          <t>BLANCO ENCALADA 5264</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -31416,7 +31416,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>814125594</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
@@ -31426,7 +31426,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t xml:space="preserve">correr </t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -31436,7 +31436,7 @@
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
@@ -31448,10 +31448,10 @@
         <v>1</v>
       </c>
       <c r="M362" t="n">
-        <v>-58.481306</v>
+        <v>-58.48847</v>
       </c>
       <c r="N362" t="n">
-        <v>-34.581055</v>
+        <v>-34.576825</v>
       </c>
       <c r="O362" t="inlineStr">
         <is>
@@ -31465,7 +31465,7 @@
       </c>
       <c r="Q362" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>ATH-C</t>
         </is>
       </c>
       <c r="R362" t="inlineStr">
@@ -31477,7 +31477,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>-790</t>
+          <t>-800</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -31487,7 +31487,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>BAUNESS 2834</t>
+          <t>ESTOMBA 1849</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -31502,7 +31502,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>814125602</t>
+          <t>814125637</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
@@ -31512,7 +31512,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -31534,14 +31534,14 @@
         <v>1</v>
       </c>
       <c r="M363" t="n">
-        <v>-58.490491</v>
+        <v>-58.469466</v>
       </c>
       <c r="N363" t="n">
-        <v>-34.571674</v>
+        <v>-34.572973</v>
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P363" t="inlineStr">
@@ -31551,7 +31551,7 @@
       </c>
       <c r="Q363" t="inlineStr">
         <is>
-          <t>PUE-D</t>
+          <t>ATH-A</t>
         </is>
       </c>
       <c r="R363" t="inlineStr">
@@ -31563,7 +31563,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>-791</t>
+          <t>-803</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>BLANCO ENCALADA 5264</t>
+          <t>LA PAMPA 3810</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -31588,7 +31588,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814125652</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
@@ -31598,7 +31598,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t xml:space="preserve">correr </t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -31608,7 +31608,7 @@
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
@@ -31620,14 +31620,14 @@
         <v>1</v>
       </c>
       <c r="M364" t="n">
-        <v>-58.48847</v>
+        <v>-58.468358</v>
       </c>
       <c r="N364" t="n">
-        <v>-34.576825</v>
+        <v>-34.573132</v>
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P364" t="inlineStr">
@@ -31637,7 +31637,7 @@
       </c>
       <c r="Q364" t="inlineStr">
         <is>
-          <t>ATH-C</t>
+          <t>ATH-A</t>
         </is>
       </c>
       <c r="R364" t="inlineStr">
@@ -31649,7 +31649,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>-800</t>
+          <t>-808</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -31659,7 +31659,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>ESTOMBA 1849</t>
+          <t>MELIAN AV. 2716</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -31674,7 +31674,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>814125637</t>
+          <t>814125660</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
@@ -31706,10 +31706,10 @@
         <v>1</v>
       </c>
       <c r="M365" t="n">
-        <v>-58.469466</v>
+        <v>-58.473328</v>
       </c>
       <c r="N365" t="n">
-        <v>-34.572973</v>
+        <v>-34.563428</v>
       </c>
       <c r="O365" t="inlineStr">
         <is>
@@ -31723,7 +31723,7 @@
       </c>
       <c r="Q365" t="inlineStr">
         <is>
-          <t>ATH-A</t>
+          <t>COG-I</t>
         </is>
       </c>
       <c r="R365" t="inlineStr">
@@ -31735,7 +31735,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>-803</t>
+          <t>-809</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -31745,12 +31745,12 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>LA PAMPA 3810</t>
+          <t>MENDOZA 2122</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -31760,7 +31760,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>814125652</t>
+          <t>814125661</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
@@ -31792,14 +31792,14 @@
         <v>1</v>
       </c>
       <c r="M366" t="n">
-        <v>-58.468358</v>
+        <v>-58.454849</v>
       </c>
       <c r="N366" t="n">
-        <v>-34.573132</v>
+        <v>-34.559562</v>
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P366" t="inlineStr">
@@ -31809,7 +31809,7 @@
       </c>
       <c r="Q366" t="inlineStr">
         <is>
-          <t>ATH-A</t>
+          <t>BLO-O</t>
         </is>
       </c>
       <c r="R366" t="inlineStr">
@@ -31821,7 +31821,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>-808</t>
+          <t>-813</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -31831,12 +31831,12 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>MELIAN AV. 2716</t>
+          <t>MURILLO 854</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -31846,7 +31846,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>814125660</t>
+          <t>814125670</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -31856,7 +31856,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>bae corroida</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -31878,14 +31878,14 @@
         <v>1</v>
       </c>
       <c r="M367" t="n">
-        <v>-58.473328</v>
+        <v>-58.445269</v>
       </c>
       <c r="N367" t="n">
-        <v>-34.563428</v>
+        <v>-34.599357</v>
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P367" t="inlineStr">
@@ -31895,7 +31895,7 @@
       </c>
       <c r="Q367" t="inlineStr">
         <is>
-          <t>COG-I</t>
+          <t>VCR-?</t>
         </is>
       </c>
       <c r="R367" t="inlineStr">
@@ -31907,7 +31907,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>-809</t>
+          <t>-814</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -31917,12 +31917,12 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>MENDOZA 2122</t>
+          <t>OLAZABAL AV. 4545</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -31932,7 +31932,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>814125661</t>
+          <t>814125673</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
@@ -31942,7 +31942,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -31964,14 +31964,14 @@
         <v>1</v>
       </c>
       <c r="M368" t="n">
-        <v>-58.454849</v>
+        <v>-58.480067</v>
       </c>
       <c r="N368" t="n">
-        <v>-34.559562</v>
+        <v>-34.573072</v>
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P368" t="inlineStr">
@@ -31981,7 +31981,7 @@
       </c>
       <c r="Q368" t="inlineStr">
         <is>
-          <t>BLO-O</t>
+          <t>ATH-E</t>
         </is>
       </c>
       <c r="R368" t="inlineStr">
@@ -31993,7 +31993,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>-813</t>
+          <t>-815</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -32003,12 +32003,12 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>MURILLO 854</t>
+          <t>PESTALOZZI 3482</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -32018,7 +32018,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>814125670</t>
+          <t>814125676</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
@@ -32028,7 +32028,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>bae corroida</t>
+          <t>base podrida</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -32043,17 +32043,17 @@
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L369" t="n">
         <v>1</v>
       </c>
       <c r="M369" t="n">
-        <v>-58.445269</v>
+        <v>-58.50075</v>
       </c>
       <c r="N369" t="n">
-        <v>-34.599357</v>
+        <v>-34.567798</v>
       </c>
       <c r="O369" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
       </c>
       <c r="Q369" t="inlineStr">
         <is>
-          <t>VCR-?</t>
+          <t>PUE-H</t>
         </is>
       </c>
       <c r="R369" t="inlineStr">
@@ -32079,7 +32079,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>-814</t>
+          <t>-816</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -32089,7 +32089,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>OLAZABAL AV. 4545</t>
+          <t>PINTO 4609</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -32104,7 +32104,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>814125673</t>
+          <t>814125678</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
@@ -32136,14 +32136,14 @@
         <v>1</v>
       </c>
       <c r="M370" t="n">
-        <v>-58.480067</v>
+        <v>-58.481182</v>
       </c>
       <c r="N370" t="n">
-        <v>-34.573072</v>
+        <v>-34.544737</v>
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P370" t="inlineStr">
@@ -32153,7 +32153,7 @@
       </c>
       <c r="Q370" t="inlineStr">
         <is>
-          <t>ATH-E</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R370" t="inlineStr">
@@ -32165,22 +32165,22 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>-815</t>
+          <t>994PN</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>6/2/2026</t>
+          <t>6/5/2026</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>PESTALOZZI 3482</t>
+          <t>MARIANO ACHA 994</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -32190,7 +32190,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>814125676</t>
+          <t>814254408</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -32200,7 +32200,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>base podrida</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -32215,21 +32215,21 @@
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L371" t="n">
         <v>1</v>
       </c>
       <c r="M371" t="n">
-        <v>-58.50075</v>
+        <v>-58.472091</v>
       </c>
       <c r="N371" t="n">
-        <v>-34.567798</v>
+        <v>-34.583875</v>
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P371" t="inlineStr">
@@ -32239,182 +32239,10 @@
       </c>
       <c r="Q371" t="inlineStr">
         <is>
-          <t>PUE-H</t>
+          <t>ATH-F</t>
         </is>
       </c>
       <c r="R371" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>-816</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>6/2/2026</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>PINTO 4609</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F372" t="inlineStr">
-        <is>
-          <t>814125678</t>
-        </is>
-      </c>
-      <c r="G372" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="H372" t="inlineStr">
-        <is>
-          <t>base corroida</t>
-        </is>
-      </c>
-      <c r="I372" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J372" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K372" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L372" t="n">
-        <v>1</v>
-      </c>
-      <c r="M372" t="n">
-        <v>-58.481182</v>
-      </c>
-      <c r="N372" t="n">
-        <v>-34.544737</v>
-      </c>
-      <c r="O372" t="inlineStr">
-        <is>
-          <t>Saavedra</t>
-        </is>
-      </c>
-      <c r="P372" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q372" t="inlineStr">
-        <is>
-          <t>COG-Q</t>
-        </is>
-      </c>
-      <c r="R372" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>994PN</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>6/5/2026</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>MARIANO ACHA 994</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E373" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>814254408</t>
-        </is>
-      </c>
-      <c r="G373" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="H373" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I373" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J373" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K373" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L373" t="n">
-        <v>1</v>
-      </c>
-      <c r="M373" t="n">
-        <v>-58.472091</v>
-      </c>
-      <c r="N373" t="n">
-        <v>-34.583875</v>
-      </c>
-      <c r="O373" t="inlineStr">
-        <is>
-          <t>Colegiales</t>
-        </is>
-      </c>
-      <c r="P373" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q373" t="inlineStr">
-        <is>
-          <t>ATH-F</t>
-        </is>
-      </c>
-      <c r="R373" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_NEW.xlsx
+++ b/mapa_interactivo_NEW.xlsx
@@ -11603,7 +11603,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>NAON, ROMULO 3525</t>
+          <t>NAON ROMULO 3525</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">

--- a/mapa_interactivo_NEW.xlsx
+++ b/mapa_interactivo_NEW.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R177"/>
+  <dimension ref="A1:R176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13391,7 +13391,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">9970 </t>
+          <t xml:space="preserve">9971 </t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13401,7 +13401,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ECHEVERRIA 5051</t>
+          <t>ECHEVERRIA 5021</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>814111395</t>
+          <t>814111401</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -13448,10 +13448,10 @@
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.481099</v>
+        <v>-58.480634</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.578912</v>
+        <v>-34.578647</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">9971 </t>
+          <t xml:space="preserve">9993 </t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>ECHEVERRIA 5021</t>
+          <t>MONROE 5212</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -13502,7 +13502,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>814111401</t>
+          <t>814111591</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -13534,10 +13534,10 @@
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>-58.480634</v>
+        <v>-58.487529</v>
       </c>
       <c r="N153" t="n">
-        <v>-34.578647</v>
+        <v>-34.575028</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>ATH-D</t>
+          <t>ATH-C</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -13563,7 +13563,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">9993 </t>
+          <t xml:space="preserve">9996 </t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>MONROE 5212</t>
+          <t>ZAMUDIO 4784</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>814111591</t>
+          <t>814111621</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -13620,10 +13620,10 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>-58.487529</v>
+        <v>-58.497199</v>
       </c>
       <c r="N154" t="n">
-        <v>-34.575028</v>
+        <v>-34.582097</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>ATH-C</t>
+          <t>PUE-M</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -13649,17 +13649,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">9996 </t>
+          <t xml:space="preserve">8962 </t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>ZAMUDIO 4784</t>
+          <t>CONGRESO AV. 5856</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -13674,7 +13674,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>814111621</t>
+          <t>814108043</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -13684,7 +13684,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -13706,10 +13706,10 @@
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>-58.497199</v>
+        <v>-58.499051</v>
       </c>
       <c r="N155" t="n">
-        <v>-34.582097</v>
+        <v>-34.57451</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>PUE-M</t>
+          <t>PUE-I</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -13735,7 +13735,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">8962 </t>
+          <t xml:space="preserve">8982 </t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>CONGRESO AV. 5856</t>
+          <t>LOPEZ, CARLOS ANTONIO 2197</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>814108043</t>
+          <t>814108057</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -13792,10 +13792,10 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>-58.499051</v>
+        <v>-58.494928</v>
       </c>
       <c r="N156" t="n">
-        <v>-34.57451</v>
+        <v>-34.580378</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>PUE-I</t>
+          <t>PUE-M</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -13821,7 +13821,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">8982 </t>
+          <t xml:space="preserve">10024 </t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13831,7 +13831,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>LOPEZ, CARLOS ANTONIO 2197</t>
+          <t>IBERA 6146</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -13846,7 +13846,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>814108057</t>
+          <t>814111657</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -13856,7 +13856,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -13878,10 +13878,10 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>-58.494928</v>
+        <v>-58.502338</v>
       </c>
       <c r="N157" t="n">
-        <v>-34.580378</v>
+        <v>-34.573275</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>PUE-M</t>
+          <t>PUE-I</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -13907,7 +13907,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">10024 </t>
+          <t xml:space="preserve">10026 </t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13917,7 +13917,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>IBERA 6146</t>
+          <t>HUMBOLDT 47</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -13932,7 +13932,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>814111657</t>
+          <t>814111684</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -13964,10 +13964,10 @@
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>-58.502338</v>
+        <v>-58.451981</v>
       </c>
       <c r="N158" t="n">
-        <v>-34.573275</v>
+        <v>-34.597952</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -13981,7 +13981,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>PUE-I</t>
+          <t>VCR-?</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -13993,17 +13993,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">10026 </t>
+          <t xml:space="preserve">10027 </t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>5/7/2026</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>HUMBOLDT 47</t>
+          <t>HUMBOLDT 37</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>814111684</t>
+          <t>814111686</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -14050,10 +14050,10 @@
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>-58.451981</v>
+        <v>-58.452157</v>
       </c>
       <c r="N159" t="n">
-        <v>-34.597952</v>
+        <v>-34.598081</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
@@ -14079,17 +14079,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">10027 </t>
+          <t xml:space="preserve">10060 </t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>5/7/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>HUMBOLDT 37</t>
+          <t xml:space="preserve">AREVALO 2951 </t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -14104,7 +14104,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>814111686</t>
+          <t>814108282</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -14114,7 +14114,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>DESMONTAR POSTE Y VER POSIBILIDAD DE COLOCAR COLUMNA</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -14136,24 +14136,24 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>-58.452157</v>
+        <v>-58.430757</v>
       </c>
       <c r="N160" t="n">
-        <v>-34.598081</v>
+        <v>-34.571657</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>VCR-?</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -14165,7 +14165,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">10060 </t>
+          <t xml:space="preserve">10070 </t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14175,7 +14175,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">AREVALO 2951 </t>
+          <t>NUÑEZ 4634</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>814108282</t>
+          <t>814108373</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>DESMONTAR POSTE Y VER POSIBILIDAD DE COLOCAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -14222,24 +14222,24 @@
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>-58.430757</v>
+        <v>-58.487462</v>
       </c>
       <c r="N161" t="n">
-        <v>-34.571657</v>
+        <v>-34.561007</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>PUE-F</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -14251,7 +14251,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">10070 </t>
+          <t xml:space="preserve">10084 </t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14261,7 +14261,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>NUÑEZ 4634</t>
+          <t>UGARTE, MANUEL 3258</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>814108373</t>
+          <t>814108396</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -14308,14 +14308,14 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>-58.487462</v>
+        <v>-58.470323</v>
       </c>
       <c r="N162" t="n">
-        <v>-34.561007</v>
+        <v>-34.560769</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -14325,7 +14325,7 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>PUE-F</t>
+          <t>COG-I</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -14337,7 +14337,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">10084 </t>
+          <t xml:space="preserve">10113 </t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14347,7 +14347,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>UGARTE, MANUEL 3258</t>
+          <t>CONCORDIA 4213</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -14362,7 +14362,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>814108396</t>
+          <t>814111798</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -14372,7 +14372,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -14394,14 +14394,14 @@
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>-58.470323</v>
+        <v>-58.506878</v>
       </c>
       <c r="N163" t="n">
-        <v>-34.560769</v>
+        <v>-34.59474</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -14411,7 +14411,7 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>COG-I</t>
+          <t>PUE-O</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -14423,7 +14423,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">10113 </t>
+          <t xml:space="preserve">10126 </t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14433,7 +14433,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>CONCORDIA 4213</t>
+          <t xml:space="preserve">ROOSEVELT FRANKLIN D. 4647 </t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -14446,11 +14446,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>814111798</t>
-        </is>
-      </c>
+      <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -14458,12 +14454,12 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>DESMONTAR POSTE</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -14480,14 +14476,14 @@
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>-58.506878</v>
+        <v>-58.482122</v>
       </c>
       <c r="N164" t="n">
-        <v>-34.59474</v>
+        <v>-34.570386</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -14497,7 +14493,7 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>PUE-O</t>
+          <t>ATH-E</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -14509,7 +14505,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">10126 </t>
+          <t xml:space="preserve">10133 </t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14519,7 +14515,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROOSEVELT FRANKLIN D. 4647 </t>
+          <t xml:space="preserve">BATALLA DEL PARI 593 </t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -14532,7 +14528,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>814108490</t>
+        </is>
+      </c>
       <c r="G165" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -14540,12 +14540,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>DESMONTAR POSTE</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -14562,14 +14562,14 @@
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>-58.482122</v>
+        <v>-58.453426</v>
       </c>
       <c r="N165" t="n">
-        <v>-34.570386</v>
+        <v>-34.600121</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>ATH-E</t>
+          <t>VCR-?</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -14591,7 +14591,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">10133 </t>
+          <t xml:space="preserve">10145 </t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">BATALLA DEL PARI 593 </t>
+          <t>DONADO 2554</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>814108490</t>
+          <t>814108500</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -14648,14 +14648,14 @@
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>-58.453426</v>
+        <v>-58.478634</v>
       </c>
       <c r="N166" t="n">
-        <v>-34.600121</v>
+        <v>-34.569063</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>VCR-?</t>
+          <t>ATH-J</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -14677,7 +14677,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">10145 </t>
+          <t xml:space="preserve">10147 </t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14687,7 +14687,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>DONADO 2554</t>
+          <t>ROOSEVELT FRANKLIN D. 4336</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -14702,7 +14702,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>814108500</t>
+          <t>814111809</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -14712,7 +14712,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -14727,17 +14727,17 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L167" t="n">
         <v>1</v>
       </c>
       <c r="M167" t="n">
-        <v>-58.478634</v>
+        <v>-58.479316</v>
       </c>
       <c r="N167" t="n">
-        <v>-34.569063</v>
+        <v>-34.568762</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">10147 </t>
+          <t xml:space="preserve">10148 </t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>ROOSEVELT FRANKLIN D. 4336</t>
+          <t>ACHA, MARIANO, GRAL. 2595</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -14788,7 +14788,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>814111809</t>
+          <t>814108503</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -14798,7 +14798,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -14813,17 +14813,17 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L168" t="n">
         <v>1</v>
       </c>
       <c r="M168" t="n">
-        <v>-58.479316</v>
+        <v>-58.479759</v>
       </c>
       <c r="N168" t="n">
-        <v>-34.568762</v>
+        <v>-34.569184</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
@@ -14849,22 +14849,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">10148 </t>
+          <t>-788</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>6/2/2026</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>ACHA, MARIANO, GRAL. 2595</t>
+          <t>AZURDUY JUANA 2004</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>814108503</t>
+          <t>814125587</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -14906,14 +14906,14 @@
         <v>1</v>
       </c>
       <c r="M169" t="n">
-        <v>-58.479759</v>
+        <v>-58.463454</v>
       </c>
       <c r="N169" t="n">
-        <v>-34.569184</v>
+        <v>-34.548783</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>ATH-J</t>
+          <t>BLO-R</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -14935,7 +14935,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>-788</t>
+          <t>-790</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14945,12 +14945,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>AZURDUY JUANA 2004</t>
+          <t>BAUNESS 2834</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -14960,7 +14960,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>814125587</t>
+          <t>814125602</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -14992,14 +14992,14 @@
         <v>1</v>
       </c>
       <c r="M170" t="n">
-        <v>-58.463454</v>
+        <v>-58.490491</v>
       </c>
       <c r="N170" t="n">
-        <v>-34.548783</v>
+        <v>-34.571674</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -15009,7 +15009,7 @@
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>BLO-R</t>
+          <t>PUE-D</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -15021,7 +15021,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>-790</t>
+          <t>-791</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>BAUNESS 2834</t>
+          <t>BLANCO ENCALADA 5264</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -15046,7 +15046,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>814125602</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t xml:space="preserve">correr </t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -15066,7 +15066,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -15078,10 +15078,10 @@
         <v>1</v>
       </c>
       <c r="M171" t="n">
-        <v>-58.490491</v>
+        <v>-58.48847</v>
       </c>
       <c r="N171" t="n">
-        <v>-34.571674</v>
+        <v>-34.576825</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>PUE-D</t>
+          <t>ATH-C</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
@@ -15107,7 +15107,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>-791</t>
+          <t>-800</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -15117,7 +15117,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>BLANCO ENCALADA 5264</t>
+          <t>ESTOMBA 1849</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814125637</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -15142,7 +15142,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">correr </t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -15164,14 +15164,14 @@
         <v>1</v>
       </c>
       <c r="M172" t="n">
-        <v>-58.48847</v>
+        <v>-58.469466</v>
       </c>
       <c r="N172" t="n">
-        <v>-34.576825</v>
+        <v>-34.572973</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>ATH-C</t>
+          <t>ATH-A</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -15193,7 +15193,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>-800</t>
+          <t>-808</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>ESTOMBA 1849</t>
+          <t>MELIAN AV. 2716</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -15218,7 +15218,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>814125637</t>
+          <t>814125660</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -15250,10 +15250,10 @@
         <v>1</v>
       </c>
       <c r="M173" t="n">
-        <v>-58.469466</v>
+        <v>-58.473328</v>
       </c>
       <c r="N173" t="n">
-        <v>-34.572973</v>
+        <v>-34.563428</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>ATH-A</t>
+          <t>COG-I</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
@@ -15279,7 +15279,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>-808</t>
+          <t>-809</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15289,12 +15289,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>MELIAN AV. 2716</t>
+          <t>MENDOZA 2122</t>
         